--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L612"/>
+  <dimension ref="A1:L616"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="3" min="1" max="1"/>
@@ -36855,6 +36855,226 @@
       </c>
       <c r="L612" s="3" t="inlineStr"/>
     </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>ר' משה מנדלסון (רמבמ"ן)</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>1729–1786</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>דסאו; ברלין, גרמניה</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>הגות, פרשנות מקרא ופילוסופיה</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>נאורות, הביאור, ירושלים, הפרדת דת ומדינה, פולמוס</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>הוגה דעות שניצב על קו התפר בין עולם ההלכה לערכי הנאורות במאה ה־18. חיבר את מפעל "הביאור" למקרא כדי לגשר על הפער הלשוני והתרבותי של יהודי זמנו, ובספרו "ירושלים" הציע הפרדת דת ומדינה והגדיר את היהדות כדת של מצוות מעשיות ולא של כפייה מחשבתית.</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>יהדות כדת המבוססת על מצוות מעשיות ולא על כפיית אמונה — פתיחת צוהר למודרנה שעוררה גם חשש מטמיעה.</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>היעב"ץ, בעל "ההפלאה"</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>לאה אמנו</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>תקופת האבות</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>ארם נהריים; ארץ כנען</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>האבות</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>תפילה, הודיה ומחשבה</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>ארבע האמהות, הודיה, עלמא דאתכסיא, מערת המכפלה</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>הרביעית מבין ארבע האמהות, המייצגת את עולם המחשבה והתפילה אל מול רחל המזוהה עם המעשה וההתגלות. בכוח תפילתה שינתה את גזירתה, וייסדה את מושג ההודיה — ההכרה בהשגחה פרטית החורגת מחוקי הטבע.</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>ההודיה ככוח מכונן: היכולת לזהות חסד ומתנת חינם דווקא בתוך קושי ודחייה.</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>יעקב אבינו, רחל אמנו</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>סוליקא חג'ואל</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>המאה ה־19</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>טנג'יר; פאס, מרוקו</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>מודרני</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>קידוש השם ומורשת</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>קידוש השם, מרוקו, צניעות, פיוטים, קבר בפאס</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>נערה יהודייה ממרוקו שהוצאה להורג במאה ה־19 לאחר שסירבה להתאסלם, והפכה לסמל של קידוש השם. עמדה איתנה על זהותה היהודית עד מותה, וזכרה נשמר עד היום בפיוטים ובתפילות על קברה בבית העלמין בפאס.</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>עמידה על הזהות היהודית עד מסירות נפש, והצניעות ככלי של קדושה אל מול פני המוות.</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>רב נחמן בר פפא</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr"/>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>בבל</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>אמוראים</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>הלכה ותלמוד</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>דיני שומרים, אחריות אומנים, הדראן, מעשה בראשית</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>אמורא בבלי שתרם לעיצוב דיני שומרים ואחריותם הנזיקית של בעלי מקצוע. השקפתו הרוחנית גורסת שהטבע מושעה וממתין לתפילת הצדיק, ושמו קבוע בטקס ה"הדראן" כסגולה לזיכרון הלימוד.</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>הטבע ממתין לתפילת הצדיק — זיקה בין כוח התפילה למעשה בראשית.</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>רב פפא</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L616"/>
+  <dimension ref="A1:L623"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="3" min="1" max="1"/>
@@ -36636,7 +36636,7 @@
       </c>
       <c r="C609" s="3" t="inlineStr">
         <is>
-          <t>רבי יוסף דב הלוי סולובייצ׳יק (הגרי״ד)</t>
+          <t>הרב יוסף דוב הלוי סולובייצ׳יק (הגרי״ד)</t>
         </is>
       </c>
       <c r="D609" s="3" t="inlineStr">
@@ -36646,40 +36646,44 @@
       </c>
       <c r="E609" s="3" t="inlineStr">
         <is>
-          <t>בריסק וליטא; ברלין; בוסטון וניו יורק</t>
+          <t>מזרח אירופה; ברלין; בוסטון; ניו יורק</t>
         </is>
       </c>
       <c r="F609" s="3" t="inlineStr">
         <is>
-          <t>מודרני</t>
+          <t>המאה ה־20</t>
         </is>
       </c>
       <c r="G609" s="3" t="inlineStr">
         <is>
-          <t>תלמוד בשיטת בריסק, פילוסופיה והנהגת האורתודוקסיה המודרנית</t>
+          <t>הלכה, פילוסופיה ואורתודוקסיה מודרנית</t>
         </is>
       </c>
       <c r="H609" s="3" t="inlineStr">
         <is>
-          <t>שיטת בריסק, הגרי״ד, ישיבה יוניברסיטי, אורתודוקסיה מודרנית, בוסטון, גברא וחפצא</t>
+          <t>בריסק, איש ההלכה, איש האמונה הבודד, קול דודי דופק, גורל וייעוד, תורה ומדע, מודרנה, ישיבה יוניברסיטי, עימות, ציונות</t>
         </is>
       </c>
       <c r="I609" s="3" t="inlineStr">
         <is>
-          <t>נכדו של רבי חיים סולובייצ׳יק וממשיך שיטת בריסק האנליטית, הנקרא על שם זקנו רבי יוסף דב הלוי בעל "בית הלוי" (1820–1892). למד בברלין, ובשנת 1932 היגר לארצות הברית; שם הנהיג את הקהילה בבוסטון ועמד בראש ההוראה בישיבה יוניברסיטי במשך למעלה מארבעה עשורים, כארכיטקט הרוחני של האורתודוקסיה המודרנית.</t>
+          <t>ממשיך שיטת בריסק, פילוסוף וראש ישיבה שהפך לדמות מרכזית באורתודוקסיה המודרנית בארצות הברית. שילב למדנות הלכתית אנליטית עם פילוסופיה מודרנית ועסק במתח שבין יצירה אנושית, מדע וחברה לבין ברית, תפילה ואמונה.</t>
         </is>
       </c>
       <c r="J609" s="3" t="inlineStr">
         <is>
-          <t>חיבור בין הדיוק המושגי של שיטת בריסק לבין הפילוסופיה המערבית: התורה כמערכת לוגית אוטונומית שדרך קטגוריותיה נקראת המציאות המודרנית.</t>
+          <t>אין הכרח לפתור את כל המתח שבין מסורת למודרנה. האדם המאמין יכול לחיות במלוא העוצמה בתוך שני העולמות - לפעול, ליצור ולשלוט במציאות, ובו בזמן לעמוד בענווה, ברית ואחריות לפני האלוהים.</t>
         </is>
       </c>
       <c r="K609" s="3" t="inlineStr">
         <is>
-          <t>רבי חיים סולובייצ׳יק; בית הלוי; רבי חיים מוולוז׳ין</t>
-        </is>
-      </c>
-      <c r="L609" s="3" t="inlineStr"/>
+          <t>רבי חיים סולובייצ׳יק, הרב משה סולובייצ׳יק, ישיבה יוניברסיטי, הרב אהרן ליכטנשטיין</t>
+        </is>
+      </c>
+      <c r="L609" s="3" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/4dG8KDTRRjIuVy0J4lXLLo?si=YJVuewruRNSUkDvbpmuIxQ&amp;utm_source=copy-link</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="3" t="inlineStr">
@@ -36856,222 +36860,670 @@
       <c r="L612" s="3" t="inlineStr"/>
     </row>
     <row r="613">
-      <c r="A613" t="inlineStr">
+      <c r="A613" s="3" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="B613" t="inlineStr">
+      <c r="B613" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C613" t="inlineStr">
+      <c r="C613" s="3" t="inlineStr">
         <is>
           <t>ר' משה מנדלסון (רמבמ"ן)</t>
         </is>
       </c>
-      <c r="D613" t="inlineStr">
+      <c r="D613" s="3" t="inlineStr">
         <is>
           <t>1729–1786</t>
         </is>
       </c>
-      <c r="E613" t="inlineStr">
+      <c r="E613" s="3" t="inlineStr">
         <is>
           <t>דסאו; ברלין, גרמניה</t>
         </is>
       </c>
-      <c r="F613" t="inlineStr">
+      <c r="F613" s="3" t="inlineStr">
         <is>
           <t>מודרני</t>
         </is>
       </c>
-      <c r="G613" t="inlineStr">
+      <c r="G613" s="3" t="inlineStr">
         <is>
           <t>הגות, פרשנות מקרא ופילוסופיה</t>
         </is>
       </c>
-      <c r="H613" t="inlineStr">
+      <c r="H613" s="3" t="inlineStr">
         <is>
           <t>נאורות, הביאור, ירושלים, הפרדת דת ומדינה, פולמוס</t>
         </is>
       </c>
-      <c r="I613" t="inlineStr">
+      <c r="I613" s="3" t="inlineStr">
         <is>
           <t>הוגה דעות שניצב על קו התפר בין עולם ההלכה לערכי הנאורות במאה ה־18. חיבר את מפעל "הביאור" למקרא כדי לגשר על הפער הלשוני והתרבותי של יהודי זמנו, ובספרו "ירושלים" הציע הפרדת דת ומדינה והגדיר את היהדות כדת של מצוות מעשיות ולא של כפייה מחשבתית.</t>
         </is>
       </c>
-      <c r="J613" t="inlineStr">
+      <c r="J613" s="3" t="inlineStr">
         <is>
           <t>יהדות כדת המבוססת על מצוות מעשיות ולא על כפיית אמונה — פתיחת צוהר למודרנה שעוררה גם חשש מטמיעה.</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr">
+      <c r="K613" s="3" t="inlineStr">
         <is>
           <t>היעב"ץ, בעל "ההפלאה"</t>
         </is>
       </c>
     </row>
     <row r="614">
-      <c r="A614" t="inlineStr">
+      <c r="A614" s="3" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="B614" t="inlineStr">
+      <c r="B614" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C614" t="inlineStr">
+      <c r="C614" s="3" t="inlineStr">
         <is>
           <t>לאה אמנו</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr">
+      <c r="D614" s="3" t="inlineStr">
         <is>
           <t>תקופת האבות</t>
         </is>
       </c>
-      <c r="E614" t="inlineStr">
-        <is>
-          <t>ארם נהריים; ארץ כנען</t>
-        </is>
-      </c>
-      <c r="F614" t="inlineStr">
-        <is>
-          <t>האבות</t>
-        </is>
-      </c>
-      <c r="G614" t="inlineStr">
-        <is>
-          <t>תפילה, הודיה ומחשבה</t>
-        </is>
-      </c>
-      <c r="H614" t="inlineStr">
-        <is>
-          <t>ארבע האמהות, הודיה, עלמא דאתכסיא, מערת המכפלה</t>
-        </is>
-      </c>
-      <c r="I614" t="inlineStr">
-        <is>
-          <t>הרביעית מבין ארבע האמהות, המייצגת את עולם המחשבה והתפילה אל מול רחל המזוהה עם המעשה וההתגלות. בכוח תפילתה שינתה את גזירתה, וייסדה את מושג ההודיה — ההכרה בהשגחה פרטית החורגת מחוקי הטבע.</t>
-        </is>
-      </c>
-      <c r="J614" t="inlineStr">
-        <is>
-          <t>ההודיה ככוח מכונן: היכולת לזהות חסד ומתנת חינם דווקא בתוך קושי ודחייה.</t>
-        </is>
-      </c>
-      <c r="K614" t="inlineStr">
-        <is>
-          <t>יעקב אבינו, רחל אמנו</t>
+      <c r="E614" s="3" t="inlineStr">
+        <is>
+          <t>פדן ארם (חרן); ארץ כנען; חברון</t>
+        </is>
+      </c>
+      <c r="F614" s="3" t="inlineStr">
+        <is>
+          <t>תקופת המקרא</t>
+        </is>
+      </c>
+      <c r="G614" s="3" t="inlineStr">
+        <is>
+          <t>אמהות ישראל, תפילה והודיה</t>
+        </is>
+      </c>
+      <c r="H614" s="3" t="inlineStr">
+        <is>
+          <t>יעקב אבינו, רחל אמנו, עשו, שבטי ישראל, יהודה, לוי, תפילה, הודיה, עלמא דאתכסיא, מערת המכפלה</t>
+        </is>
+      </c>
+      <c r="I614" s="3" t="inlineStr">
+        <is>
+          <t>אשת יעקב ואם שישה משבטי ישראל ודינה. חז״ל קשרו את ״עיניה הרכות״ לבכי ולתפילה על גורלה, ואת לידת יהודה למעבר מן הכמיהה לאהבה אל ההודיה; בתורת הסוד היא מזוהה עם העולם המכוסה והפנימיות.</t>
+        </is>
+      </c>
+      <c r="J614" s="3" t="inlineStr">
+        <is>
+          <t>תפילה יכולה לשנות את מסלול החיים, והודיה צומחת מן ההכרה שהאדם קיבל מעבר למובן מאליו; לאה מגלמת את הכוח הנסתר שממנו צומחים לוי ויהודה - כהונה ומלכות.</t>
+        </is>
+      </c>
+      <c r="K614" s="3" t="inlineStr">
+        <is>
+          <t>יעקב אבינו, רחל אמנו, עשו, יהודה, לוי, דוד המלך</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/5w5U7Y1zeZaiSWtmmA9Ev8?si=FdCNf0rVSuubfS6jQMWEdA&amp;utm_source=copy-link</t>
         </is>
       </c>
     </row>
     <row r="615">
-      <c r="A615" t="inlineStr">
+      <c r="A615" s="3" t="inlineStr">
         <is>
           <t>614</t>
         </is>
       </c>
-      <c r="B615" t="inlineStr">
+      <c r="B615" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C615" t="inlineStr">
+      <c r="C615" s="3" t="inlineStr">
         <is>
           <t>סוליקא חג'ואל</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr">
+      <c r="D615" s="3" t="inlineStr">
         <is>
           <t>המאה ה־19</t>
         </is>
       </c>
-      <c r="E615" t="inlineStr">
+      <c r="E615" s="3" t="inlineStr">
         <is>
           <t>טנג'יר; פאס, מרוקו</t>
         </is>
       </c>
-      <c r="F615" t="inlineStr">
+      <c r="F615" s="3" t="inlineStr">
         <is>
           <t>מודרני</t>
         </is>
       </c>
-      <c r="G615" t="inlineStr">
+      <c r="G615" s="3" t="inlineStr">
         <is>
           <t>קידוש השם ומורשת</t>
         </is>
       </c>
-      <c r="H615" t="inlineStr">
+      <c r="H615" s="3" t="inlineStr">
         <is>
           <t>קידוש השם, מרוקו, צניעות, פיוטים, קבר בפאס</t>
         </is>
       </c>
-      <c r="I615" t="inlineStr">
+      <c r="I615" s="3" t="inlineStr">
         <is>
           <t>נערה יהודייה ממרוקו שהוצאה להורג במאה ה־19 לאחר שסירבה להתאסלם, והפכה לסמל של קידוש השם. עמדה איתנה על זהותה היהודית עד מותה, וזכרה נשמר עד היום בפיוטים ובתפילות על קברה בבית העלמין בפאס.</t>
         </is>
       </c>
-      <c r="J615" t="inlineStr">
+      <c r="J615" s="3" t="inlineStr">
         <is>
           <t>עמידה על הזהות היהודית עד מסירות נפש, והצניעות ככלי של קדושה אל מול פני המוות.</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" s="3" t="inlineStr"/>
     </row>
     <row r="616">
-      <c r="A616" t="inlineStr">
+      <c r="A616" s="3" t="inlineStr">
         <is>
           <t>615</t>
         </is>
       </c>
-      <c r="B616" t="inlineStr">
+      <c r="B616" s="3" t="inlineStr">
         <is>
           <t>דמות</t>
         </is>
       </c>
-      <c r="C616" t="inlineStr">
+      <c r="C616" s="3" t="inlineStr">
         <is>
           <t>רב נחמן בר פפא</t>
         </is>
       </c>
-      <c r="D616" t="inlineStr"/>
-      <c r="E616" t="inlineStr">
+      <c r="D616" s="3" t="inlineStr">
+        <is>
+          <t>תקופת האמוראים (הזיהוי הכרונולוגי המדויק שנוי במחלוקת)</t>
+        </is>
+      </c>
+      <c r="E616" s="3" t="inlineStr">
         <is>
           <t>בבל</t>
         </is>
       </c>
-      <c r="F616" t="inlineStr">
+      <c r="F616" s="3" t="inlineStr">
         <is>
           <t>אמוראים</t>
         </is>
       </c>
-      <c r="G616" t="inlineStr">
-        <is>
-          <t>הלכה ותלמוד</t>
-        </is>
-      </c>
-      <c r="H616" t="inlineStr">
-        <is>
-          <t>דיני שומרים, אחריות אומנים, הדראן, מעשה בראשית</t>
-        </is>
-      </c>
-      <c r="I616" t="inlineStr">
-        <is>
-          <t>אמורא בבלי שתרם לעיצוב דיני שומרים ואחריותם הנזיקית של בעלי מקצוע. השקפתו הרוחנית גורסת שהטבע מושעה וממתין לתפילת הצדיק, ושמו קבוע בטקס ה"הדראן" כסגולה לזיכרון הלימוד.</t>
-        </is>
-      </c>
-      <c r="J616" t="inlineStr">
-        <is>
-          <t>הטבע ממתין לתפילת הצדיק — זיקה בין כוח התפילה למעשה בראשית.</t>
-        </is>
-      </c>
-      <c r="K616" t="inlineStr">
-        <is>
-          <t>רב פפא</t>
+      <c r="G616" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, תפילה ואגדה</t>
+        </is>
+      </c>
+      <c r="H616" s="3" t="inlineStr">
+        <is>
+          <t>בבא מציעא, שומר שכר, אומן, חולין, גשם, תפילת צדיקים, רב פפא, עשרת בני רב פפא, הדרן, סיום מסכת</t>
+        </is>
+      </c>
+      <c r="I616" s="3" t="inlineStr">
+        <is>
+          <t>אמורא בבלי שנזכר בסוגיות הלכתיות ובאגדה על תפילה שהביאה גשם וצמיחת זרעים. מסורת הסיום מונה אותו בין עשרת בני רב פפא, אף שהזיהוי והיוחסין המדויקים מעוררים קושי כרונולוגי.</t>
+        </is>
+      </c>
+      <c r="J616" s="3" t="inlineStr">
+        <is>
+          <t>המציאות דורשת השתתפות אנושית בשני מישורים: דיוק בזכויות ובחובות שבין אדם לחברו, ותפילה ההופכת את האדם משקיף מן הצד לשותף פעיל בתוך העולם.</t>
+        </is>
+      </c>
+      <c r="K616" s="3" t="inlineStr">
+        <is>
+          <t>רב פפא, רב אסי, אדם הראשון, עשרת בני רב פפא</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/3jacnS80DsxAGMO6Si3S41?si=LRSOFUOmQPeIMYbit4Zg2w&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="3" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="B617" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C617" s="3" t="inlineStr">
+        <is>
+          <t>גדליהו בן אחיקם</t>
+        </is>
+      </c>
+      <c r="D617" s="3" t="inlineStr">
+        <is>
+          <t>המאה ה־6 לפנה״ס; לאחר חורבן בית ראשון</t>
+        </is>
+      </c>
+      <c r="E617" s="3" t="inlineStr">
+        <is>
+          <t>מצפה; יהודה</t>
+        </is>
+      </c>
+      <c r="F617" s="3" t="inlineStr">
+        <is>
+          <t>תקופת המקרא - חורבן בית ראשון</t>
+        </is>
+      </c>
+      <c r="G617" s="3" t="inlineStr">
+        <is>
+          <t>הנהגה לאומית, שיקום ואחריות</t>
+        </is>
+      </c>
+      <c r="H617" s="3" t="inlineStr">
+        <is>
+          <t>חורבן בית ראשון, מצפה, שארית יהודה, ירמיהו, ישמעאל בן נתניה, יוחנן בן קרח, צום גדליה, שיקום לאומי, לשון הרע</t>
+        </is>
+      </c>
+      <c r="I617" s="3" t="inlineStr">
+        <is>
+          <t>מנהיג שארית יהודה שמונה בידי הבבלים לאחר חורבן ירושלים וניסה לחדש חיים חקלאיים וציבוריים בארץ. רציחתו בידי ישמעאל בן נתניה מוטטה את ניסיון השיקום והובילה לבריחת רבים למצרים.</t>
+        </is>
+      </c>
+      <c r="J617" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות אחראית מחייבת להבחין בין קבלת שמועה כאמת לבין נקיטת זהירות מול סכנה ממשית; סיפורו מלמד עד כמה קנאות פנימית יכולה לכבות אפשרות של שיקום לאומי.</t>
+        </is>
+      </c>
+      <c r="K617" s="3" t="inlineStr">
+        <is>
+          <t>אחיקם בן שפן, שפן הסופר, ירמיהו הנביא, ישמעאל בן נתניה, יוחנן בן קרח, נבוכדנצר</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0mqkIuCxWVRVmUhugvgUWl?si=YXuXnIBiRYOPlo1-zoqLbw&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="3" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="B618" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C618" s="3" t="inlineStr">
+        <is>
+          <t>הרב ישראל יצחק בזאנסון זצ״ל</t>
+        </is>
+      </c>
+      <c r="D618" s="3" t="inlineStr">
+        <is>
+          <t>1944–2026</t>
+        </is>
+      </c>
+      <c r="E618" s="3" t="inlineStr">
+        <is>
+          <t>ניס; פריז; תל אביב</t>
+        </is>
+      </c>
+      <c r="F618" s="3" t="inlineStr">
+        <is>
+          <t>העת החדשה</t>
+        </is>
+      </c>
+      <c r="G618" s="3" t="inlineStr">
+        <is>
+          <t>חסידות ברסלב, נפש ואמנות</t>
+        </is>
+      </c>
+      <c r="H618" s="3" t="inlineStr">
+        <is>
+          <t>ברסלב, רבי נחמן, שיר חדש, אומץ, נשמה נשימה, פאר הליקוטים, ציור, ניגון, התבודדות, תל אביב</t>
+        </is>
+      </c>
+      <c r="I618" s="3" t="inlineStr">
+        <is>
+          <t>רב, חסיד ברסלב, סופר, צייר ומלחין שחיבר בין עולם האמנות המודרנית לבין עבודת ה׳ ותורת רבי נחמן. הקים בתל אביב את קהילת ״שיר חדש״ ופיתח שפה של התמודדות נפשית, נשימה, יצירה והתבודדות.</t>
+        </is>
+      </c>
+      <c r="J618" s="3" t="inlineStr">
+        <is>
+          <t>מסורת עמוקה יכולה לדבר אל האדם המודרני גם דרך צבע, צליל ונשימה; יצירה ורגישות נפשית אינן חלופה לעבודת ה׳ אלא יכולות להפוך לכלים של תפילה, צמיחה וחיבור.</t>
+        </is>
+      </c>
+      <c r="K618" s="3" t="inlineStr">
+        <is>
+          <t>רבי נחמן מברסלב, רבי לוי יצחק בנדר, רבי ישראל דב אודסר, ברברה רובין</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/5qT5Z7oVMNOWfC9CTUkR30?si=rnD76gn3TE2Nv8eV8ygNyA&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="3" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="B619" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C619" s="3" t="inlineStr">
+        <is>
+          <t>הרב אליעזר יהודה וולדנברג (הציץ אליעזר)</t>
+        </is>
+      </c>
+      <c r="D619" s="3" t="inlineStr">
+        <is>
+          <t>1915–2006</t>
+        </is>
+      </c>
+      <c r="E619" s="3" t="inlineStr">
+        <is>
+          <t>ירושלים; ישראל</t>
+        </is>
+      </c>
+      <c r="F619" s="3" t="inlineStr">
+        <is>
+          <t>המאה ה־20–21</t>
+        </is>
+      </c>
+      <c r="G619" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, רפואה וביו־אתיקה</t>
+        </is>
+      </c>
+      <c r="H619" s="3" t="inlineStr">
+        <is>
+          <t>ציץ אליעזר, רפואה והלכה, ביו־אתיקה, הפלות, הפריה חוץ־גופית, פונדקאות, השתלות, קביעת מוות, חולה הנוטה למות, עישון, הלכות מדינה</t>
+        </is>
+      </c>
+      <c r="I619" s="3" t="inlineStr">
+        <is>
+          <t>מגדולי הפוסקים בדור האחרון ומחלוצי הפסיקה הרפואית המודרנית. בשו״ת ״ציץ אליעזר״ בן 22 הכרכים בירר שאלות רפואיות וטכנולוגיות מתוך לימוד המציאות המדעית, וב״הלכות מדינה״ עסק בריבונות, צבא ומערכות ציבוריות במדינה יהודית.</t>
+        </is>
+      </c>
+      <c r="J619" s="3" t="inlineStr">
+        <is>
+          <t>ההלכה אינה נסוגה מפני מציאות חדשה: כדי לפסוק נכון יש להבין תחילה את העובדות המדעיות והחברתיות, ואז להחיל עליהן את עקרונות התורה מתוך אחריות לחיים, לאדם ולציבור.</t>
+        </is>
+      </c>
+      <c r="K619" s="3" t="inlineStr">
+        <is>
+          <t>הרב בן ציון מאיר חי עוזיאל, הרב יצחק אייזיק הלוי הרצוג, בית הדין הרבני הגדול, רופאי המרכז הרפואי שערי צדק</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/10vxjISIbCayZsVsHOxPXS?si=ybUiuUKNQ8eBppEJsXEqHQ&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="3" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="B620" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C620" s="3" t="inlineStr">
+        <is>
+          <t>רבי אחאי בר פפא</t>
+        </is>
+      </c>
+      <c r="D620" s="3" t="inlineStr">
+        <is>
+          <t>המאה ה־3 לספירה בקירוב</t>
+        </is>
+      </c>
+      <c r="E620" s="3" t="inlineStr">
+        <is>
+          <t>בבל; ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F620" s="3" t="inlineStr">
+        <is>
+          <t>אמוראים</t>
+        </is>
+      </c>
+      <c r="G620" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, משפט ומסורת הסיום</t>
+        </is>
+      </c>
+      <c r="H620" s="3" t="inlineStr">
+        <is>
+          <t>רבי אחא בר פפא, רב אחא אריכא, רב הונא, רבי זירא, רבי אבהו, שבת, רפואה, סדרי דין, תקיעות שופר, עשרת בני רב פפא, הדרן</t>
+        </is>
+      </c>
+      <c r="I620" s="3" t="inlineStr">
+        <is>
+          <t>אמורא מן הדור השלישי שפעל בבבל ובארץ ישראל ונזכר בסוגיות הלכתיות הדורשות הבחנות דקות בין מצבים מעשיים. שמו נכלל במסורת ״עשרת בני רב פפא״, אף שהכרונולוגיה מלמדת שחי דורות לפני רב פפא המפורסם.</t>
+        </is>
+      </c>
+      <c r="J620" s="3" t="inlineStr">
+        <is>
+          <t>ההלכה פועלת בתוך מציאות אנושית מורכבת: דיוק בהגדרות, רגישות לפסיכולוגיה של בעלי הדין והבנת תנאי הזמן הם חלק מן הדין עצמו. דמותו גם ממחישה כיצד מסורת הזיכרון יכולה לאגד חכמים מתקופות שונות.</t>
+        </is>
+      </c>
+      <c r="K620" s="3" t="inlineStr">
+        <is>
+          <t>רב הונא, רבי זירא, רבי אבהו, רבי אמי, רבי אבא, רב פפא, רב האי גאון</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/5UnOSf9p89BTOE0JvSRkNB?si=Au9EzjlKQ5We2PTMTlpXmg&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="3" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="B621" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C621" s="3" t="inlineStr">
+        <is>
+          <t>הרב חנן פורת</t>
+        </is>
+      </c>
+      <c r="D621" s="3" t="inlineStr">
+        <is>
+          <t>1943–2011</t>
+        </is>
+      </c>
+      <c r="E621" s="3" t="inlineStr">
+        <is>
+          <t>כפר עציון; ירושלים; יהודה ושומרון</t>
+        </is>
+      </c>
+      <c r="F621" s="3" t="inlineStr">
+        <is>
+          <t>המאה ה־20–21</t>
+        </is>
+      </c>
+      <c r="G621" s="3" t="inlineStr">
+        <is>
+          <t>תורה, חינוך, התיישבות והנהגה ציבורית</t>
+        </is>
+      </c>
+      <c r="H621" s="3" t="inlineStr">
+        <is>
+          <t>כפר עציון, גוש עציון, סוד ההרכבה, עוד יוסף חי, ישיבת הר עציון, תנ״ך שבעל פה, התיישבות, חוק לא תעמוד על דם רעך, חסד</t>
+        </is>
+      </c>
+      <c r="I621" s="3" t="inlineStr">
+        <is>
+          <t>תלמיד חכם, מחנך, איש התיישבות וחבר כנסת שהיה מן הדמויות הבולטות בציונות הדתית שלאחר מלחמת ששת הימים. פעל לחידוש כפר עציון, להקמת מוסדות תורה ולחיבור בין לימוד התנ״ך, הארץ, החברה והעשייה הציבורית.</t>
+        </is>
+      </c>
+      <c r="J621" s="3" t="inlineStr">
+        <is>
+          <t>״סוד ההרכבה״ מבקש לחבר בין יוסף ליהודה - בין בניין הארץ, הצבא והחברה לבין תורה, קדושה ורוח. התורה נבחנת ביכולתה להפוך לחיי מעשה של חסד, אחריות לאומית וחיבור בין חלקי העם.</t>
+        </is>
+      </c>
+      <c r="K621" s="3" t="inlineStr">
+        <is>
+          <t>הרב יהודה עמיטל, הרב אהרן ליכטנשטיין, ישיבת הר עציון, גוש אמונים, תנועת ההתיישבות</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/32ZOjZ7ks26vRGCcPdt0pU?si=mS8hI1HuRHSnqwu574B36g&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="3" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="B622" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C622" s="3" t="inlineStr">
+        <is>
+          <t>רבי מנחם רקנאטי</t>
+        </is>
+      </c>
+      <c r="D622" s="3" t="inlineStr">
+        <is>
+          <t>שלהי המאה ה־13–ראשית המאה ה־14</t>
+        </is>
+      </c>
+      <c r="E622" s="3" t="inlineStr">
+        <is>
+          <t>איטליה</t>
+        </is>
+      </c>
+      <c r="F622" s="3" t="inlineStr">
+        <is>
+          <t>ימי הביניים</t>
+        </is>
+      </c>
+      <c r="G622" s="3" t="inlineStr">
+        <is>
+          <t>קבלה, פרשנות והלכה</t>
+        </is>
+      </c>
+      <c r="H622" s="3" t="inlineStr">
+        <is>
+          <t>הזוהר, קבלת ספרד, חסידי אשכנז, פירוש התורה, פסקי רקנאטי, ספירות, תפילה, אותיות, קבלה איטלקית, רנסנס</t>
+        </is>
+      </c>
+      <c r="I622" s="3" t="inlineStr">
+        <is>
+          <t>מגדולי מקובלי איטליה, שחיבר בין קבלת ספרד, מסורות חסידי אשכנז ועולם ההלכה האיטלקי. בכתביו שילב מאות מובאות מן הזוהר עוד לפני הדפסתו, ביאר את לשונו ותרם להפיכתו למקור סמכות מרכזי בעולם הקבלה.</t>
+        </is>
+      </c>
+      <c r="J622" s="3" t="inlineStr">
+        <is>
+          <t>הלכה וקבלה הן שתי קומות של אותה פעולה: ההלכה מגדירה את המעשה בעולם הנגלה, והקבלה מבארת את משמעותו בעולם הנסתר. תפילה, אותיות ומצוות נעשות לחלק ממערכת רוחנית של תיקון והשפעה.</t>
+        </is>
+      </c>
+      <c r="K622" s="3" t="inlineStr">
+        <is>
+          <t>ספר הזוהר, מקובלי גירונה וקסטיליה, חסידי אשכנז, רבי משה קורדובירו, פיקו דלה מירנדולה, יוהנס רויכלין</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/3ClGfKlKMCkIYPMAsM3Mjo?si=Azpcdkf6Sqiva0roERWiEA&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="3" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="B623" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C623" s="3" t="inlineStr">
+        <is>
+          <t>הרב יהודה לייב הלוי אשלג (בעל הסולם)</t>
+        </is>
+      </c>
+      <c r="D623" s="3" t="inlineStr">
+        <is>
+          <t>1884–1954</t>
+        </is>
+      </c>
+      <c r="E623" s="3" t="inlineStr">
+        <is>
+          <t>פולין; ירושלים</t>
+        </is>
+      </c>
+      <c r="F623" s="3" t="inlineStr">
+        <is>
+          <t>המאה ה־20</t>
+        </is>
+      </c>
+      <c r="G623" s="3" t="inlineStr">
+        <is>
+          <t>קבלה והגות חברתית</t>
+        </is>
+      </c>
+      <c r="H623" s="3" t="inlineStr">
+        <is>
+          <t>בעל הסולם, פירוש הסולם, תלמוד עשר הספירות, הזוהר, האר״י, השוואת הצורה, רצון לקבל, רצון להשפיע, ערבות, הדור האחרון, האומה, בן־גוריון</t>
+        </is>
+      </c>
+      <c r="I623" s="3" t="inlineStr">
+        <is>
+          <t>מגדולי מפרשי הקבלה בעת החדשה. ב״תלמוד עשר הספירות״ סידר את כתבי האר״י לשיטה לימודית, וב״פירוש הסולם״ הנגיש את הזוהר. לצד זאת פיתח הגות חברתית שבמרכזה מעבר מן הרצון לקבל לעצמו אל אחריות, ערבות והשפעה.</t>
+        </is>
+      </c>
+      <c r="J623" s="3" t="inlineStr">
+        <is>
+          <t>תיקון רוחני איננו נשאר בעולמות העליונים: שינוי הכוונה של היחיד אמור להקרין גם על מבנה החברה. אהבת הזולת, ערבות ואחריות הדדית הן בעיניו תרגום חברתי של רעיון ההשפעה הקבלי.</t>
+        </is>
+      </c>
+      <c r="K623" s="3" t="inlineStr">
+        <is>
+          <t>האר״י, הרמ״ק, הרב ברוך שלום אשלג (הרב״ש), דוד בן־גוריון, זלמן שזר</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/56ZfHwIuCVuWheqmgyawIj?si=3rkjd6YWTz6W7h1tqAVDJg&amp;utm_source=copy-link</t>
         </is>
       </c>
     </row>

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L623"/>
+  <dimension ref="A1:L630"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="3" min="1" max="1"/>
@@ -36972,7 +36972,7 @@
           <t>יעקב אבינו, רחל אמנו, עשו, יהודה, לוי, דוד המלך</t>
         </is>
       </c>
-      <c r="L614" t="inlineStr">
+      <c r="L614" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/5w5U7Y1zeZaiSWtmmA9Ev8?si=FdCNf0rVSuubfS6jQMWEdA&amp;utm_source=copy-link</t>
         </is>
@@ -37087,7 +37087,7 @@
           <t>רב פפא, רב אסי, אדם הראשון, עשרת בני רב פפא</t>
         </is>
       </c>
-      <c r="L616" t="inlineStr">
+      <c r="L616" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/3jacnS80DsxAGMO6Si3S41?si=LRSOFUOmQPeIMYbit4Zg2w&amp;utm_source=copy-link</t>
         </is>
@@ -37149,7 +37149,7 @@
           <t>אחיקם בן שפן, שפן הסופר, ירמיהו הנביא, ישמעאל בן נתניה, יוחנן בן קרח, נבוכדנצר</t>
         </is>
       </c>
-      <c r="L617" t="inlineStr">
+      <c r="L617" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/0mqkIuCxWVRVmUhugvgUWl?si=YXuXnIBiRYOPlo1-zoqLbw&amp;utm_source=copy-link</t>
         </is>
@@ -37211,7 +37211,7 @@
           <t>רבי נחמן מברסלב, רבי לוי יצחק בנדר, רבי ישראל דב אודסר, ברברה רובין</t>
         </is>
       </c>
-      <c r="L618" t="inlineStr">
+      <c r="L618" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/5qT5Z7oVMNOWfC9CTUkR30?si=rnD76gn3TE2Nv8eV8ygNyA&amp;utm_source=copy-link</t>
         </is>
@@ -37273,7 +37273,7 @@
           <t>הרב בן ציון מאיר חי עוזיאל, הרב יצחק אייזיק הלוי הרצוג, בית הדין הרבני הגדול, רופאי המרכז הרפואי שערי צדק</t>
         </is>
       </c>
-      <c r="L619" t="inlineStr">
+      <c r="L619" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/10vxjISIbCayZsVsHOxPXS?si=ybUiuUKNQ8eBppEJsXEqHQ&amp;utm_source=copy-link</t>
         </is>
@@ -37335,7 +37335,7 @@
           <t>רב הונא, רבי זירא, רבי אבהו, רבי אמי, רבי אבא, רב פפא, רב האי גאון</t>
         </is>
       </c>
-      <c r="L620" t="inlineStr">
+      <c r="L620" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/5UnOSf9p89BTOE0JvSRkNB?si=Au9EzjlKQ5We2PTMTlpXmg&amp;utm_source=copy-link</t>
         </is>
@@ -37397,7 +37397,7 @@
           <t>הרב יהודה עמיטל, הרב אהרן ליכטנשטיין, ישיבת הר עציון, גוש אמונים, תנועת ההתיישבות</t>
         </is>
       </c>
-      <c r="L621" t="inlineStr">
+      <c r="L621" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/32ZOjZ7ks26vRGCcPdt0pU?si=mS8hI1HuRHSnqwu574B36g&amp;utm_source=copy-link</t>
         </is>
@@ -37459,7 +37459,7 @@
           <t>ספר הזוהר, מקובלי גירונה וקסטיליה, חסידי אשכנז, רבי משה קורדובירו, פיקו דלה מירנדולה, יוהנס רויכלין</t>
         </is>
       </c>
-      <c r="L622" t="inlineStr">
+      <c r="L622" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/3ClGfKlKMCkIYPMAsM3Mjo?si=Azpcdkf6Sqiva0roERWiEA&amp;utm_source=copy-link</t>
         </is>
@@ -37521,9 +37521,419 @@
           <t>האר״י, הרמ״ק, הרב ברוך שלום אשלג (הרב״ש), דוד בן־גוריון, זלמן שזר</t>
         </is>
       </c>
-      <c r="L623" t="inlineStr">
+      <c r="L623" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/56ZfHwIuCVuWheqmgyawIj?si=3rkjd6YWTz6W7h1tqAVDJg&amp;utm_source=copy-link</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" s="3" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="B624" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C624" s="3" t="inlineStr">
+        <is>
+          <t>רבי אבהו</t>
+        </is>
+      </c>
+      <c r="D624" s="3" t="inlineStr">
+        <is>
+          <t>כ־279–320 לספירה</t>
+        </is>
+      </c>
+      <c r="E624" s="3" t="inlineStr">
+        <is>
+          <t>קיסריה; טבריה</t>
+        </is>
+      </c>
+      <c r="F624" s="3" t="inlineStr">
+        <is>
+          <t>אמוראים</t>
+        </is>
+      </c>
+      <c r="G624" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, אגדה, מנהיגות ופולמוס</t>
+        </is>
+      </c>
+      <c r="H624" s="3" t="inlineStr">
+        <is>
+          <t>קיסריה, רבי יוחנן, רבי אמי ורבי אסי, תקיעת שופר, תשר״ת תש״ת תר״ת, השומרונים, הפולמוס עם הנצרות, יוונית, ענווה, בעלי תשובה, בי קיסר</t>
+        </is>
+      </c>
+      <c r="I624" s="3" t="inlineStr">
+        <is>
+          <t>אמורא מדור שלישי בארץ ישראל, ראש בית המדרש בקיסריה ותלמידו של רבי יוחנן. עמד בקשר עם השלטון הרומי והשתדל לטובת היהודים, שימש דיין יחיד בעיר, ויצא בדרשותיו נגד הנצרות הקדומה. תיקן את סדר תקיעות השופר בראש השנה ונודע בענוותנותו.</t>
+        </is>
+      </c>
+      <c r="J624" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות תורנית יכולה לשלב סמכות הלכתית, שיחה עם השלטון והגנה על גבולות האמונה מבלי לאבד ענווה: ״מקום שבעלי תשובה עומדים — צדיקים גמורים אינם עומדים״, ו״אין העולם מתקיים אלא בשביל מי שמשים עצמו כמי שאינו״.</t>
+        </is>
+      </c>
+      <c r="K624" s="3" t="inlineStr"/>
+      <c r="L624" s="3" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="3" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="B625" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C625" s="3" t="inlineStr">
+        <is>
+          <t>אימא שלום</t>
+        </is>
+      </c>
+      <c r="D625" s="3" t="inlineStr">
+        <is>
+          <t>המאה ה־1–2 לספירה</t>
+        </is>
+      </c>
+      <c r="E625" s="3" t="inlineStr">
+        <is>
+          <t>יבנה; ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F625" s="3" t="inlineStr">
+        <is>
+          <t>תנאים</t>
+        </is>
+      </c>
+      <c r="G625" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, אגדה ומעמד נשים</t>
+        </is>
+      </c>
+      <c r="H625" s="3" t="inlineStr">
+        <is>
+          <t>תנורו של עכנאי, רבי אליעזר בן הורקנוס, רבן גמליאל דיבנה, בית הנשיא, אונאת דברים, שערי אונאה, מעשה הפילוסוף, נפילת אפיים, נשים בתלמוד</t>
+        </is>
+      </c>
+      <c r="I625" s="3" t="inlineStr">
+        <is>
+          <t>אחת הנשים המעטות בספרות התנאית שנזכרות בשמן: בתו של רבן שמעון בן גמליאל הזקן, אחותו של רבן גמליאל דיבנה ואשתו של רבי אליעזר בן הורקנוס. בעת נידוי בעלה פעלה כדי למנוע אסון מבית הנשיא, ובמעשה הפילוסוף חשפה שחיתות בדין.</t>
+        </is>
+      </c>
+      <c r="J625" s="3" t="inlineStr">
+        <is>
+          <t>גם כשהמערכת ההלכתית צודקת בצרכיה הציבוריים, לפגיעה באדם היחיד יש מחיר: ״שערי אונאה לא ננעלו״. אימא שלום מחברת מסורת שושלתית (״כך מקובלני מבית אבי אבא״), רגישות מוסרית ותחכום משפטי.</t>
+        </is>
+      </c>
+      <c r="K625" s="3" t="n"/>
+      <c r="L625" s="3" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0JARNwvbyB634RZzniPZhJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="3" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="B626" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C626" s="3" t="inlineStr">
+        <is>
+          <t>רבי רפאל בירדוגו (המלאך רפאל)</t>
+        </is>
+      </c>
+      <c r="D626" s="3" t="inlineStr">
+        <is>
+          <t>1747–1821</t>
+        </is>
+      </c>
+      <c r="E626" s="3" t="inlineStr">
+        <is>
+          <t>מקנס, מרוקו</t>
+        </is>
+      </c>
+      <c r="F626" s="3" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G626" s="3" t="inlineStr">
+        <is>
+          <t>הלכה, פרשנות ומנהיגות קהילתית</t>
+        </is>
+      </c>
+      <c r="H626" s="3" t="inlineStr">
+        <is>
+          <t>המלאך רפאל, מקנס, משפטים ישרים, תורות אמת, מי מנוחות, משמחי לב, רוקח מרקחת, לשון לימודים, יהדות מרוקו, תקנות הקהילה</t>
+        </is>
+      </c>
+      <c r="I626" s="3" t="inlineStr">
+        <is>
+          <t>אב בית הדין והמנהיג הרוחני של יהדות מקנס שבמרוקו, פוסק, מקובל ומפרש, שכונה ״המלאך רפאל״. תיקן תקנות לטובת העניים ובדיני ירושה, חיבר שו״ת, הגהות על השולחן ערוך, פירוש לתורה וחידושי ש״ס, ופירש את אגדות התלמוד בגישה רציונלית.</t>
+        </is>
+      </c>
+      <c r="J626" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות כוללת: עצמאות פסקנית מול המקורות, עדיפות לפשט, גישה רציונלית לאגדה והנגשת התורה לציבור בלשונו, לצד קדושה, פרישות ורגישות לשכבות החלשות.</t>
+        </is>
+      </c>
+      <c r="K626" s="3" t="inlineStr">
+        <is>
+          <t>רבי יוסף קארו</t>
+        </is>
+      </c>
+      <c r="L626" s="3" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/1b1k2Mg2koS5Li6L1is5nM</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="3" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="B627" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C627" s="3" t="inlineStr">
+        <is>
+          <t>רבי נתן שפירא הירושלמי (הרב הנשי״א)</t>
+        </is>
+      </c>
+      <c r="D627" s="3" t="inlineStr">
+        <is>
+          <t>המאה ה־17</t>
+        </is>
+      </c>
+      <c r="E627" s="3" t="inlineStr">
+        <is>
+          <t>קראקא; ירושלים; איטליה</t>
+        </is>
+      </c>
+      <c r="F627" s="3" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G627" s="3" t="inlineStr">
+        <is>
+          <t>קבלה, הלכה ושליחות</t>
+        </is>
+      </c>
+      <c r="H627" s="3" t="inlineStr">
+        <is>
+          <t>טוב הארץ, מצת שמורים, יין המשומר, מאורות נתן, הגהות הרנ״ש, כתבי האר״י, שד״ר, תיקון חצות, סתם יינם, הרמ״ז</t>
+        </is>
+      </c>
+      <c r="I627" s="3" t="inlineStr">
+        <is>
+          <t>מקובל, דיין ומנהיג הקהילה האשכנזית בירושלים, יליד קראקא. יצא כשליח לאיטליה, הולנד וגרמניה, ושם נפטר בסביבות שנת 1667. ערך והגיה את כתבי האר״י (״הגהות הרנ״ש״) וחיבר את ״טוב הארץ״, ״מצת שמורים״ ו״יין המשומר״.</t>
+        </is>
+      </c>
+      <c r="J627" s="3" t="inlineStr">
+        <is>
+          <t>הקבלה אינה נשארת בספרי הסוד: היא מעצבת מנהג והלכה, מתיקון חצות ועד האיסור על סתם יינם. גם עריכת כתבי האר״י והגהתם הן חלק מכך, כדי שתורת האר״י תעבור בדיוק ובסדר.</t>
+        </is>
+      </c>
+      <c r="K627" s="3" t="inlineStr">
+        <is>
+          <t>האר״י הקדוש, רבי חיים ויטאל</t>
+        </is>
+      </c>
+      <c r="L627" s="3" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/3hzrkzf5aotISpShNVrIiW</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="3" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="B628" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C628" s="3" t="inlineStr">
+        <is>
+          <t>רבי אברהם בן שלמה הלוי בוקראט</t>
+        </is>
+      </c>
+      <c r="D628" s="3" t="inlineStr">
+        <is>
+          <t>שלהי המאה ה־15 – ראשית המאה ה־16</t>
+        </is>
+      </c>
+      <c r="E628" s="3" t="inlineStr">
+        <is>
+          <t>מאלגה; תוניס</t>
+        </is>
+      </c>
+      <c r="F628" s="3" t="inlineStr">
+        <is>
+          <t>ראשית העת החדשה</t>
+        </is>
+      </c>
+      <c r="G628" s="3" t="inlineStr">
+        <is>
+          <t>פרשנות, פיוט, תרגום והלכה</t>
+        </is>
+      </c>
+      <c r="H628" s="3" t="inlineStr">
+        <is>
+          <t>ספר הזיכרון, רש״י, סופר־פירוש, גירוש ספרד, תוניס, תשובות הרי״ף, פיוט, דיוקא, הרמב״ן, שד״ל</t>
+        </is>
+      </c>
+      <c r="I628" s="3" t="inlineStr">
+        <is>
+          <t>מחכמי ספרד בדור הגירוש שהתיישב בתוניס. חיבר את ״ספר הזיכרון״ (1507), סופר־פירוש על פירוש רש״י לתורה, תירגם את תשובות הרי״ף מערבית־יהודית ללשון הקודש וכתב פיוטים. הספר נדפס לראשונה רק ב־1845, בידי שד״ל.</t>
+        </is>
+      </c>
+      <c r="J628" s="3" t="inlineStr">
+        <is>
+          <t>פירוש רש״י נשען על דיוק בלשון הפסוק ועל מדרשי חז״ל, ובוקראט עונה להשגות הרמב״ן ואחרים כדי להגן עליו. ההגנה הזאת משמרת אחרי הגירוש את הפרשנות המקראית ומחברת בין מסורת אשכנז וצרפת למסורת האנדלוסית.</t>
+        </is>
+      </c>
+      <c r="K628" s="3" t="inlineStr">
+        <is>
+          <t>רש״י (רבי שלמה יצחקי), רבי יצחק אלפסי (הרי״ף)</t>
+        </is>
+      </c>
+      <c r="L628" s="3" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="3" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="B629" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C629" s="3" t="inlineStr">
+        <is>
+          <t>רבי מאיר אבן אלדבי</t>
+        </is>
+      </c>
+      <c r="D629" s="3" t="inlineStr">
+        <is>
+          <t>כ־1310–1360</t>
+        </is>
+      </c>
+      <c r="E629" s="3" t="inlineStr">
+        <is>
+          <t>טולידו; ירושלים</t>
+        </is>
+      </c>
+      <c r="F629" s="3" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G629" s="3" t="inlineStr">
+        <is>
+          <t>הגות, קבלה ומדעים</t>
+        </is>
+      </c>
+      <c r="H629" s="3" t="inlineStr">
+        <is>
+          <t>שבילי אמונה, נכד הרא״ש, עשרה נתיבים, קבלה ופילוסופיה, אנטומיה ורפואה, שער השמים, הרמב״ן, הזוהר, השל״ה, צוואת הריב״ש</t>
+        </is>
+      </c>
+      <c r="I629" s="3" t="inlineStr">
+        <is>
+          <t>נכדו של הרא״ש, יליד טולידו, שעלה לארץ ישראל והשתקע בירושלים. ספרו האנציקלופדי ״שבילי אמונה״ (עשרה נתיבים) מאחד תורה, קבלה, פילוסופיה, אסטרונומיה, אנטומיה ורפואה, והשפיע על השל״ה ועל ספרות החסידות.</t>
+        </is>
+      </c>
+      <c r="J629" s="3" t="inlineStr">
+        <is>
+          <t>הידע המדעי והפילוסופי משרת את האמונה ואינו מתחרה בה: החקירה הרציונלית מבארת את העולם הנברא, ובסוגיות המטאפיזיות, כמהות האלוהות, טעמי המצוות והגמול, הקבלה היא מקור האמת.</t>
+        </is>
+      </c>
+      <c r="K629" s="3" t="inlineStr">
+        <is>
+          <t>הרמב"ם, הרמב"ן, הבעל שם טוב</t>
+        </is>
+      </c>
+      <c r="L629" s="3" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="3" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="B630" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C630" s="3" t="inlineStr">
+        <is>
+          <t>מרים הנביאה</t>
+        </is>
+      </c>
+      <c r="D630" s="3" t="inlineStr">
+        <is>
+          <t>תקופת יציאת מצרים והמדבר</t>
+        </is>
+      </c>
+      <c r="E630" s="3" t="inlineStr">
+        <is>
+          <t>מצרים; המדבר; קדש</t>
+        </is>
+      </c>
+      <c r="F630" s="3" t="inlineStr">
+        <is>
+          <t>יציאת מצרים</t>
+        </is>
+      </c>
+      <c r="G630" s="3" t="inlineStr">
+        <is>
+          <t>נבואה, מנהיגות ושירה</t>
+        </is>
+      </c>
+      <c r="H630" s="3" t="inlineStr">
+        <is>
+          <t>בארה של מרים, שירת הים, התוף והמחול, שלשת הפרנסים, צרעת מרים, לשון הרע, זכירת מעשה מרים, פועה, משה ואהרן, אור חוזר</t>
+        </is>
+      </c>
+      <c r="I630" s="3" t="inlineStr">
+        <is>
+          <t>הנביאה, אחותם של משה ואהרן, שפעלה כבר בשעבוד מצרים: התייצבה מול ייאושו של אביה, השגיחה על משה התינוק והובילה את הנשים בשירת הים. במדבר נמנתה עם שלשת הפרנסים ונקשר בה הבאר; הלשון הרע שלה ועונשה הפכו ליסוד במצוות זכירת מעשה מרים.</t>
+        </is>
+      </c>
+      <c r="J630" s="3" t="inlineStr">
+        <is>
+          <t>אמונה היא פעולה שמכינה את הכלים לפני בוא הנס: מרים והנשים הוציאו תופים ממצרים והובילו שירה מלמטה למעלה (״אור חוזר״). מנהיגותה סיפקה לעם את התשתית הקיומית, והעדרה במותה חשף עד כמה נשענו עליה המנהיגים האחרים.</t>
+        </is>
+      </c>
+      <c r="K630" s="3" t="n"/>
+      <c r="L630" s="3" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/7kOM2DavDUXYPcc4dWRv9A</t>
         </is>
       </c>
     </row>

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -2401,8 +2401,16 @@
           <t>תורה שבעל פה, פולמוס קראי, פילוסופיה אריסטוטלית, מסירת דורות</t>
         </is>
       </c>
-      <c r="I34" s="6" t="n"/>
-      <c r="J34" s="6" t="n"/>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>רבי אברהם אבן דאוד הלוי (1110–1180) זיהה איום כפול על היהדות הרבנית: הקראות מבפנים והפילוסופיה האריסטוטלית מבחוץ. ב'ספר הקבלה' ביצר את רציפות התורה שבעל פה, וב'האמונה הרמה' ביסס לראשונה את האמונה על יסודות אריסטוטליים, וסלל את הדרך לרמב״ם.</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>תורה וחכמה משלימות זו את זו: ההיסטוריה מבצרת את סמכות המסורת, והתבונה מבססת את האמונה עד המקום שבו היא נעצרת.</t>
+        </is>
+      </c>
       <c r="K34" s="6" t="n"/>
       <c r="L34" s="6" t="inlineStr">
         <is>
@@ -2869,8 +2877,16 @@
           <t>ספר יצירה, ספירות ואותיות, תורת הכוונות, גבולות כתיבת סוד</t>
         </is>
       </c>
-      <c r="I42" s="6" t="n"/>
-      <c r="J42" s="6" t="n"/>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>המכונה 'אבי הקבלה', בנו של הראב״ד מפושקייר, פעל בפרובאנס בסוף המאה ה־12 ובראשית ה־13. עיוור מלידה, פיתח הגות מופשטת על ה'אין סוף' והספירות, והעביר את תורת הסוד ממסורת שבעל פה לשיטה סדורה, שהשפיעה דרך תלמידיו מגירונה על גדולי הדור כרמב״ן.</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>הקבלה כרובד הפנימי של התורה והתפילה: הגות על האין סוף והספירות, שצמחה בלב הממסד התורני ולא בשוליו.</t>
+        </is>
+      </c>
       <c r="K42" s="6" t="n"/>
       <c r="L42" s="6" t="inlineStr">
         <is>
@@ -4255,8 +4271,16 @@
           <t>זהות יהודית בסוף ספרד, פילוסופיה וקבלה, דרשות ציבור</t>
         </is>
       </c>
-      <c r="I65" s="6" t="n"/>
-      <c r="J65" s="6" t="n"/>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>מגדולי הוגי יהדות ספרד במאה ה־15 (1420–1494), רב, דרשן וראש ישיבה. בספרו 'עקדת יצחק' פיתח שיטת דרשה בת שלושה שלבים, שנתנה מענה לנצרות ולפילוסופיה האריסטוטלית הקיצונית וחיזקה את אמונת המשכילים ערב הגירוש.</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>הדרשה כמבצר אמוני: שילוב שכל, פרשנות מקרא וקבלה לבניית חוסן רוחני בעידן של משבר.</t>
+        </is>
+      </c>
       <c r="K65" s="6" t="n"/>
       <c r="L65" s="6" t="inlineStr">
         <is>
@@ -5719,8 +5743,16 @@
           <t>מאבק בשבתאות, לשון חריפה, חכמות כלליות, אוטוביוגרפיה</t>
         </is>
       </c>
-      <c r="I89" s="6" t="n"/>
-      <c r="J89" s="6" t="n"/>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>מגדולי חכמי אשכנז במאה ה־18, בנו ותלמידו של ה'חכם צבי'. התרחק ממשרות רבניות רשמיות כדי לשמור על עצמאותו, שילב חידוש הלכתי אמיץ עם ביקורת טקסט ופתיחות למדע, ונאבק בשבתאות, ובכלל זה בפולמוס הקמיעות נגד רבי יהונתן אייבשיץ.</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>עצמאות רוחנית כתנאי לאמת: פסיקה אמיצה, דיוק פילולוגי ועמידה בלתי מתפשרת מול השבתאות.</t>
+        </is>
+      </c>
       <c r="K89" s="6" t="n"/>
       <c r="L89" s="6" t="inlineStr">
         <is>
@@ -10541,8 +10573,16 @@
           <t>הלכה ומודרנה, רפואה ומדע, הלכה לציבור, אהבת ישראל</t>
         </is>
       </c>
-      <c r="I168" s="6" t="n"/>
-      <c r="J168" s="6" t="n"/>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>מגדולי הפוסקים והוגי הדעות במדינת ישראל, ומשנת תשל״ג ועד פטירתו רבה הראשי של תל אביב–יפו. שילב נאמנות למסורת הפסיקה הספרדית עם ציונות הרואה בריבונות היהודית שלב בגאולה, וראה בהלכה מערכת חיה, כפי שעולה מספרו 'עשה לך רב' ומפסקו על איסור העישון.</t>
+        </is>
+      </c>
+      <c r="J168" s="6" t="inlineStr">
+        <is>
+          <t>הלכה חיה ומכוונת, הנענית לאתגרי המודרנה, הרפואה והטכנולוגיה מתוך ראיית המדינה כשלב בתהליך הגאולה.</t>
+        </is>
+      </c>
       <c r="K168" s="6" t="n"/>
       <c r="L168" s="6" t="inlineStr">
         <is>
@@ -11013,8 +11053,16 @@
           <t>רוח לחימה, רבנות בשטח, ממלכתיות, שירות צבאי</t>
         </is>
       </c>
-      <c r="I176" s="6" t="n"/>
-      <c r="J176" s="6" t="n"/>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>לוחם ומפקד פלוגה בסיירת שקד שפנה לעולם התורה אחרי מלחמת יום הכיפורים. היה שותף להקמת ישיבת אלון מורה, ממקימי היישוב איתמר ומייסד הישיבה בו, ועד 2010 הרב הצבאי הראשי החמישי של צה״ל.</t>
+        </is>
+      </c>
+      <c r="J176" s="6" t="inlineStr">
+        <is>
+          <t>שילוב של הנהגה צבאית, תורנית והתיישבותית: רוח הלחימה צומחת מציונות המחוברת לשורשי התורה והארץ.</t>
+        </is>
+      </c>
       <c r="K176" s="6" t="n"/>
       <c r="L176" s="6" t="inlineStr">
         <is>

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -481,8 +481,16 @@
           <t>ספרות בית שני, מוסר ודרך ארץ, גבולות קאנון, השפעה חז"לית</t>
         </is>
       </c>
-      <c r="I2" s="6" t="n"/>
-      <c r="J2" s="6" t="n"/>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>שמעון בן ישוע בן סירא, מגדולי חכמי ירושלים בימי הבית השני, חיבר את ספרו בסביבות שנת 180 לפני הספירה, כשהתרבות ההלניסטית חדרה לשכבות העליונות ביהודה. הספר לא נכלל בקאנון, אך חז״ל ציטטו את דבריו המעולים ושילבו אותם במדרש ובתפילה, והנוסח העברי שאבד נמצא מחדש בגניזת קהיר ובמצדה.</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>החכמה העליונה, שחיפשה לה משכן בין העמים, שכנה בירושלים והיא תורת משה; האדם בוחר בין טוב לרע, ושכרו בא בעולם הזה ובשם הטוב שהוא מותיר.</t>
+        </is>
+      </c>
       <c r="K2" s="6" t="n"/>
       <c r="L2" s="6" t="inlineStr">
         <is>
@@ -5321,8 +5329,16 @@
           <t>שבתאות, משיחיות שקר, סמכות רבנית, קהילות אירופה</t>
         </is>
       </c>
-      <c r="I82" s="6" t="n"/>
-      <c r="J82" s="6" t="n"/>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>רבי יעקב ששפורטש (1610–1698), יליד אוראן שבאלג׳יריה ומצאצאי הרמב״ן, כיהן בצעירותו כאב בית הדין בתלמסאן, ונדד בין צפון אפריקה, אמסטרדם, לונדון, המבורג וליוורנו עד שמונה לרב הראשי של עדת הספרדים באמסטרדם. בשנות שבתי צבי עמד כמעט לבדו נגד ההתלהבות המשיחית, ואת אגרות המאבק כינס ב'ציצת נובל צבי'.</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>סמכות תורנית אינה נובעת מחזיונות או מכריזמה אלא מכפיפות להלכה ולמסורת הפסיקה; קבלה אמיתית מקיימת את המצוות, וקבלה שפורצת אותן היא אש זרה.</t>
+        </is>
+      </c>
       <c r="K82" s="6" t="n"/>
       <c r="L82" s="6" t="inlineStr">
         <is>
@@ -11297,8 +11313,16 @@
           <t>כוונות הרש"ש, תפילה, ענווה והסתרה, אהבת ישראל</t>
         </is>
       </c>
-      <c r="I180" s="6" t="n"/>
-      <c r="J180" s="6" t="n"/>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>חכם ציון חביב ברכה (נפטר בי״ד בתשרי תשס״ה), יתום מחלב שעלה לארץ בנערותו, היה מקובל נסתר בירושלים, תלמיד רבי יהודה פתיה ורבי מרדכי שרעבי. הוא התפרנס כירקן בשוק מחנה יהודה וכדוור, ובשנת תש״ל ייסד בנחלאות את ישיבת לש״ם, שבה ישב דווקא עם המתחילים והמתקרבים.</t>
+        </is>
+      </c>
+      <c r="J180" s="6" t="inlineStr">
+        <is>
+          <t>לש״ם – להקמת שכינתא מעפרא: במרכז עומדים תיקון השכינה והכלל, ולא רק צורכו של היחיד, והם נעשים באהבה לכל יהודי, בענווה ובפשטות, ובקבלת ייסורים כפרה על הדור.</t>
+        </is>
+      </c>
       <c r="K180" s="6" t="n"/>
       <c r="L180" s="6" t="inlineStr">
         <is>

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -3940,7 +3940,11 @@
           <t>קנפנטון ייסד שיטה לוגית ללימוד הגמרא שהצילה את עולם התורה ערב הגירוש.</t>
         </is>
       </c>
-      <c r="J59" s="6" t="n"/>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>דרך הלימוד היא הגנת התורה: שיטה לוגית ומסודרת לעיון בגמרא, בחמישה שלבים ובכללים נגד כשלי היגיון, מראה שהחשיבה המדעית והמסורת התלמודית אינן סותרות זו את זו.</t>
+        </is>
+      </c>
       <c r="K59" s="6" t="n"/>
       <c r="L59" s="6" t="inlineStr">
         <is>
@@ -6194,7 +6198,11 @@
           <t>הרש"ש סידר את תורת האר"י למערכת מדויקת והפך למנהיג הקבלה בירושלים.</t>
         </is>
       </c>
-      <c r="J96" s="6" t="n"/>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>התפילה היא פעולה של תיקון: הכוונות שסידר על פי תורת האר״י הופכות כל מילה בתפילה לייחוד עולמות, ומאחדות קהילות סביב עבודה רוחנית משותפת.</t>
+        </is>
+      </c>
       <c r="K96" s="6" t="n"/>
       <c r="L96" s="6" t="inlineStr">
         <is>
@@ -34185,7 +34193,11 @@
           <t>פילוסוף ציני מגדרה שחז"ל ראו בו את 'גדול פילוסופי אומות העולם'. בן שיחם של חכמים ובעל פולמוס חריף נגד האמונה בגורל.</t>
         </is>
       </c>
-      <c r="J555" s="3" t="inlineStr"/>
+      <c r="J555" s="3" t="inlineStr">
+        <is>
+          <t>האדם אחראי למעשיו ואינו כבול לגורל: אוינומאוס תקף את האמונה בגורל ואת האורקלים בשם הבחירה החופשית, ובספרות חז״ל, אם הזיהוי נכון, הוא חכם נוכרי שמכבד את התורה ואת לומדיה.</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="3" t="inlineStr">
@@ -34229,7 +34241,11 @@
           <t>אבי האומה. יצא מאור כשדים בקריאת 'לך לך', הפיץ את האמונה בא-ל אחד וכרת את ברית בין הבתרים.</t>
         </is>
       </c>
-      <c r="J556" s="3" t="inlineStr"/>
+      <c r="J556" s="3" t="inlineStr">
+        <is>
+          <t>אמונה בא-ל אחד שנעשית דרך חיים: יציאה אל הלא נודע על פי דבר ה', חסד פתוח לכל אדם, וברית נצחית בין ה' לזרעו.</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="3" t="inlineStr">
@@ -34277,7 +34293,11 @@
           <t>החכמה הנודעת שבדור התנאים, אשת רבי מאיר ובת רבי חנינא בן תרדיון. הלכותיה ולמדנותה מובאות בש"ס — 'תלת מאה שמעתתא ביומא'.</t>
         </is>
       </c>
-      <c r="J557" s="3" t="inlineStr"/>
+      <c r="J557" s="3" t="inlineStr">
+        <is>
+          <t>למדנות ותבונה מוסרית שאינן תלויות במעמד: ברוריה פסקה בדיני טומאה וטהרה, לימדה להתפלל שיתמו החטאים ולא החוטאים, ועמדה בגבורה מול אסונותיה.</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="3" t="inlineStr">
@@ -34321,7 +34341,11 @@
           <t>מייסד מלכות בית דוד ומחבר ספר תהילים. כבש את ירושלים והעלה אליה את ארון הברית — 'נעים זמירות ישראל'.</t>
         </is>
       </c>
-      <c r="J558" s="3" t="inlineStr"/>
+      <c r="J558" s="3" t="inlineStr">
+        <is>
+          <t>המלכות בישראל נשענת על ענווה ותשובה לפני ה': דוד איחד את העם סביב ירושלים, ובתהילים הפך את מאבקיו, נפילותיו ותקוותו לתפילה של כל הדורות.</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="3" t="inlineStr">
@@ -34461,7 +34485,11 @@
           <t>הראשון לציון ומחבר שו"ת 'זרע אברהם'. ממנהיגי ירושלים במאבק בשבתאות ובביצור מעמדה התורני של העיר.</t>
         </is>
       </c>
-      <c r="J561" s="3" t="inlineStr"/>
+      <c r="J561" s="3" t="inlineStr">
+        <is>
+          <t>שמירת חומות המסורת בעת משבר: מלחמה בלתי מתפשרת בשבתאות, לצד פסיקה שאינה נרתעת מהחמרה או מחידוש כשהשעה דורשת, כמו במניעת עיגון נשים.</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="3" t="inlineStr">
@@ -34549,7 +34577,11 @@
           <t>מייסד ישיבת לייקווד ואדריכל עולם התורה באמריקה שלאחר השואה. העמיד את לימוד התורה לשמה כערך עליון ללא פשרות.</t>
         </is>
       </c>
-      <c r="J563" s="3" t="inlineStr"/>
+      <c r="J563" s="3" t="inlineStr">
+        <is>
+          <t>לימוד תורה לשמה, בשלמות ובלי פשרות, הוא שיבטיח את המשכיות העם אחרי החורבן: ישיבה של לומדים בלב אמריקה, ולא התאמה של התורה לתרבות הסובבת.</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="3" t="inlineStr">
@@ -34593,7 +34625,11 @@
           <t>האדמו"ר השישי של חב"ד. עמד בעוז מול השלטון הסובייטי, שוחרר ממאסר מוות, והעביר את מרכז חב"ד לאמריקה.</t>
         </is>
       </c>
-      <c r="J564" s="3" t="inlineStr"/>
+      <c r="J564" s="3" t="inlineStr">
+        <is>
+          <t>מסירות נפש ככוח המניע של ההנהגה: להחזיק תורה במחתרת מול הדיכוי הסובייטי, ולהכריז ש'אמריקה אינה שונה' — היהדות יכולה לשגשג בכל מקום.</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="3" t="inlineStr">
@@ -34637,7 +34673,11 @@
           <t>רבה הראשי של בריטניה והוגה יהודי בעל השפעה עולמית. הציג את קול התורה בשפת הפילוסופיה והמוסר האוניברסלי.</t>
         </is>
       </c>
-      <c r="J565" s="3" t="inlineStr"/>
+      <c r="J565" s="3" t="inlineStr">
+        <is>
+          <t>'כבוד השוני': שמירת הייחוד הדתי היא מפתח לשלום ולא מכשול בפניו, והאמונה היא קריאה לאחריות מוסרית, לברית ולתיקון העולם.</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="3" t="inlineStr">
@@ -34681,7 +34721,11 @@
           <t>מקובל וראש ישיבת המקובלים, מחכמי ארם צובא שקבעו משכנם בירושלים. קרא לגאולה מתוך תורת הסוד ומעשה.</t>
         </is>
       </c>
-      <c r="J566" s="3" t="inlineStr"/>
+      <c r="J566" s="3" t="inlineStr">
+        <is>
+          <t>הציונות אינה סתירה לדת אלא שלב בתהליך קבלי של גאולה: העלייה לארץ היא מצווה גדולה שאין לדחותה, ולימוד הסוד הוא דרך חיים שמקדשת כל תנועה וכל מילה בתפילה.</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="3" t="inlineStr">
@@ -34725,7 +34769,11 @@
           <t>משגיח ישיבת 'שעלבים' ומחבר פורה. כינס וביאר את כתבי הראי"ה קוק, הגר"א והרמח"ל — גשר בין עולם המוסר לתורת ארץ ישראל.</t>
         </is>
       </c>
-      <c r="J567" s="3" t="inlineStr"/>
+      <c r="J567" s="3" t="inlineStr">
+        <is>
+          <t>לסדר את אוצרות המחשבה היהודית כך שיהיו נגישים לכל לומד: תורת הרב קוק, המוסר והאגדה כמשנה סדורה, מתוך חיבור בין בקיאות ליטאית, עומק קבלי ותחייה לאומית.</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="3" t="inlineStr">
@@ -34769,7 +34817,11 @@
           <t>'הרבי המרקד' — מחולל מהפכת הנגינה היהודית בדור התשובה. ניגוניו ופתיחת לבו קירבו רבבות ליהדות.</t>
         </is>
       </c>
-      <c r="J568" s="3" t="inlineStr"/>
+      <c r="J568" s="3" t="inlineStr">
+        <is>
+          <t>הניגון והסיפור הם דרך אל התורה ואל הלב היהודי: אהבה ללא תנאי ושמחה כדרך לקרב רחוקים, בלי לוותר על ההלכה.</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="3" t="inlineStr">
@@ -34817,7 +34869,11 @@
           <t>גיבורת הספר החיצוני הקרוי על שמה, שמסרה נפשה להצלת עמה. דמותה נקשרה במסורת לנס חנוכה.</t>
         </is>
       </c>
-      <c r="J569" s="3" t="inlineStr"/>
+      <c r="J569" s="3" t="inlineStr">
+        <is>
+          <t>חובה לפעול בתוך הטבע וההיסטוריה מתוך ביטחון גמור בה', בלי לתחום את הישועה בזמן ובמקום ובלי לחכות לנס בחוסר מעש.</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="3" t="inlineStr">
@@ -34861,7 +34917,11 @@
           <t>השתדלן הגדול של יהדות אשכנז מול הקיסר קרל החמישי. 'ספר המקנה' שלו — עדות אישית להנהגה בדור של גזרות ורפורמציה.</t>
         </is>
       </c>
-      <c r="J570" s="3" t="inlineStr"/>
+      <c r="J570" s="3" t="inlineStr">
+        <is>
+          <t>ההגנה על הקהילות היא חובה דתית: שתדלנות מול הקיסר והשלטונות הנשענת על למדנות רבנית, משמעת מוסרית ובקיאות משפטית.</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="3" t="inlineStr">
@@ -34905,7 +34965,11 @@
           <t>בחיר האבות ואבי שנים־עשר השבטים. 'איש תם יושב אוהלים' שירד למצרים והניח את יסוד בית ישראל.</t>
         </is>
       </c>
-      <c r="J571" s="3" t="inlineStr"/>
+      <c r="J571" s="3" t="inlineStr">
+        <is>
+          <t>'תתן אמת ליעקב': אמת ותמימות שנבחנות בגלות ובמאבק, ומהן נבנה בית ישראל, שנים־עשר שבטים שהם עם אחד.</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="3" t="inlineStr">
@@ -34949,7 +35013,11 @@
           <t>השני שבאבות. נעקד על גבי המזבח בהר המוריה, וחפר מחדש את בארות אביו — ממשיך הדרך בארץ.</t>
         </is>
       </c>
-      <c r="J572" s="3" t="inlineStr"/>
+      <c r="J572" s="3" t="inlineStr">
+        <is>
+          <t>גבורה של מסירות והתמדה: נכונות להיעקד, תפילה בשדה, והמשך דרכו של האב בארץ — בחפירה מחדש של בארותיו.</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="3" t="inlineStr">
@@ -34993,7 +35061,11 @@
           <t>מגדולי נביאי הכתב. נבואות החורבן והנחמה שלו — 'נחמו נחמו עמי' — מלוות את ישראל בכל הדורות.</t>
         </is>
       </c>
-      <c r="J573" s="3" t="inlineStr"/>
+      <c r="J573" s="3" t="inlineStr">
+        <is>
+          <t>החורבן אינו סוף פסוק: מאותו נביא באו התוכחה על עוולות החברה והבטחת הנחמה והגאולה, לישראל ולכל העמים.</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="3" t="inlineStr">
@@ -35037,7 +35109,11 @@
           <t>גדול חכמי צפת בדורו ויוזם חידוש הסמיכה (1538) כצעד לקירוב הגאולה — מהלך שהצית את הפולמוס הגדול עם חכמי ירושלים.</t>
         </is>
       </c>
-      <c r="J574" s="3" t="inlineStr"/>
+      <c r="J574" s="3" t="inlineStr">
+        <is>
+          <t>ההלכה היא כלי חי שנועד לשרת את הגאולה: חידוש הסמיכה והסנהדרין בצפת, כדי להשיב לעם סמכות הלכתית ריבונית ולשקם את כבודו אחרי הגירוש.</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="3" t="inlineStr">
@@ -35129,7 +35205,11 @@
           <t>מחדש התורה בישראל בראשית ימי הבית השני. העלה את הגולה מבבל, כונן את קריאת התורה ברבים — 'ראוי היה עזרא שתינתן תורה על ידו'.</t>
         </is>
       </c>
-      <c r="J576" s="3" t="inlineStr"/>
+      <c r="J576" s="3" t="inlineStr">
+        <is>
+          <t>קיום האומה אינו תלוי רק בטריטוריה ובשלטון אלא בספר ובלימוד: עזרא הפך את התורה מקודקס סגור ליסוד חי של חיי היומיום, כך שבכל מקום שבו יהיה יהודי יהיו לו ספר, שפה וקהילה.</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="3" t="inlineStr">
@@ -35173,7 +35253,11 @@
           <t>עמוד התווך של הדור השני לאמוראי בבל וראש ישיבת סורא ארבעים שנה. הלכה כמותו בממונות ברוב מחלוקותיו.</t>
         </is>
       </c>
-      <c r="J577" s="3" t="inlineStr"/>
+      <c r="J577" s="3" t="inlineStr">
+        <is>
+          <t>תורה, הנהגה וצדק חברתי כמכלול אחד: למדנות מופלגת לצד תקיפות בדין, ענווה ציבורית ושימוש בעושר למעשי חסד ולרווחת הציבור.</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="3" t="inlineStr">
@@ -35217,7 +35301,11 @@
           <t>מאבות הקהילה הרבנית הקדומה ברינוס. ממניחי היסוד לתרבות התורה של אשכנז הקדומה, דורות לפני רבנו גרשום.</t>
         </is>
       </c>
-      <c r="J578" s="3" t="inlineStr"/>
+      <c r="J578" s="3" t="inlineStr">
+        <is>
+          <t>יסוד שושלת התורה של אשכנז: בית המדרש והמשפחה שהקים בריינוס יצרו את הסביבה שממנה יצאו רבותיו של רש״י, והניחו את התשתית לפרשנות התלמוד, לפיוט ולתורת הסוד של אשכנז הקדומה.</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="3" t="inlineStr">
@@ -35261,7 +35349,11 @@
           <t>מגדולי תנאי יבנה, כהן שזכה לשרת במקדש. בר פלוגתא ואוהבו של רבי עקיבא; 'היום קצר והמלאכה מרובה'.</t>
         </is>
       </c>
-      <c r="J579" s="3" t="inlineStr"/>
+      <c r="J579" s="3" t="inlineStr">
+        <is>
+          <t>גשר בין המקדש שחרב לבית המדרש שנבנה: שמירת הכהונה ומתנותיה גם אחרי החורבן ושימושן לצדקה, פסיקה שמקלה על הציבור, ולימוד תורה שחייב להביא לידי מעשה.</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="3" t="inlineStr">
@@ -35305,7 +35397,11 @@
           <t>מגדולי משוררי ספרד והוגה 'הכוזרי'. שירת געגועיו לציון — 'לבי במזרח ואנוכי בסוף מערב' — מלווה את האומה; בסוף ימיו יצא לארץ ישראל.</t>
         </is>
       </c>
-      <c r="J580" s="3" t="inlineStr"/>
+      <c r="J580" s="3" t="inlineStr">
+        <is>
+          <t>האמונה אינה מסקנה לוגית קרה אלא חוויה נבואית וחיים שלמים, הקשורים בקשר מהותי לעם ישראל, לארץ ישראל וללשון העברית.</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="3" t="inlineStr">
@@ -35397,7 +35493,11 @@
           <t>ממקובלי קאסטיליה הראשונים, מאבות 'קבלת האחים הכהנים'. חיבוריו על האותיות והמרכבה קדמו לזוהר והשפיעו עליו.</t>
         </is>
       </c>
-      <c r="J582" s="3" t="inlineStr"/>
+      <c r="J582" s="3" t="inlineStr">
+        <is>
+          <t>דרך אל הסוד בחזיון אישי ובצירופי אותיות; ומכאן גם תורת 'האצילות השמאלית', מיפוי כוחות הרע, שהשפיעה עמוקות על ספר הזוהר.</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="3" t="inlineStr">
@@ -35441,7 +35541,11 @@
           <t>גדול פוסקי הדור שבין הגאונים לראשונים. 'הלכות הרי"ף' זיקקו את התלמוד לפסק הלכה ושימשו עמוד יסוד לשולחן ערוך.</t>
         </is>
       </c>
-      <c r="J583" s="3" t="inlineStr"/>
+      <c r="J583" s="3" t="inlineStr">
+        <is>
+          <t>ההלכה דורשת ברירה, זיקוק והכרעה: הרי״ף תמצת את התלמוד הבבלי לפסק מעשי, קבע את הבבלי כמקור העליון ואת הכלל 'הלכתא כבתראי', וכך הנגיש את ההלכה לכל מורה הוראה.</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="3" t="inlineStr">
@@ -35529,7 +35633,11 @@
           <t>אב עולם ובעל שלוש-עשרה המידות שהתורה נדרשת בהן. בר פלוגתא הגדול של רבי עקיבא בדרכי המדרש — 'דיברה תורה כלשון בני אדם'.</t>
         </is>
       </c>
-      <c r="J585" s="3" t="inlineStr"/>
+      <c r="J585" s="3" t="inlineStr">
+        <is>
+          <t>'דברה תורה כלשון בני אדם': פרשנות שיטתית והגיונית בשלוש־עשרה המידות, שמונעת החמרה מיותרת, לצד שילוב תורה עם דרך ארץ וחמלה על עניי ישראל.</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="3" t="inlineStr">
@@ -35573,7 +35681,11 @@
           <t>רבה של ירושלים והמתנגד הגדול לחידוש הסמיכה. 'קונטרס הסמיכה' שלו הכריע את הפולמוס ההלכתי הנודע מול חכמי צפת.</t>
         </is>
       </c>
-      <c r="J586" s="3" t="inlineStr"/>
+      <c r="J586" s="3" t="inlineStr">
+        <is>
+          <t>סמכות הלכתית ריבונית אינה יכולה לקום בידי מרכז אחד: חידוש הסמיכה מחייב הסכמה של כל חכמי ארץ ישראל, כדי לשמור על אחדות העם ועל הלוח העברי.</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="3" t="inlineStr">
@@ -35617,7 +35729,11 @@
           <t>מגדולי הפוסקים שאחרי גירוש ספרד. ניצל מספינה טובעת, כיהן בדיינות במצרים ועלה בסוף ימיו לירושלים.</t>
         </is>
       </c>
-      <c r="J587" s="3" t="inlineStr"/>
+      <c r="J587" s="3" t="inlineStr">
+        <is>
+          <t>איזון בעת משבר: נאמנות מוחלטת לפסיקות הראשונים לצד הגנה על הרציונליזם של הרמב״ם, כדי להעניק ליהדות ספרד הנודדת מסגרת יציבה של הלכה ומחשבה.</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="3" t="inlineStr">
@@ -35661,7 +35777,11 @@
           <t>נכד הבעל שם טוב ובעל 'דגל מחנה אפרים' — מן המקורות הראשונים והנאמנים לתורת הסבא הגדול.</t>
         </is>
       </c>
-      <c r="J588" s="3" t="inlineStr"/>
+      <c r="J588" s="3" t="inlineStr">
+        <is>
+          <t>לחבר בין הגילוי המיסטי לבין תיקון הנפש בחיי היומיום: תורת הבעל שם טוב, כוונות האר״י והבנה עמוקה של נפש האדם, כעבודת ה' פנימית.</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="3" t="inlineStr">
@@ -35705,7 +35825,11 @@
           <t>מבעלי התוספות ומחבר 'ספר מצוות גדול' — הקודקס ההלכתי הגדול של יהדות צרפת. סבב בקהילות ספרד ואשכנז כמוכיח ומעורר.</t>
         </is>
       </c>
-      <c r="J589" s="3" t="inlineStr"/>
+      <c r="J589" s="3" t="inlineStr">
+        <is>
+          <t>לשמר את התורה שבעל פה אחרי שריפת התלמוד: קודקס מסודר של תרי״ג המצוות, המשלב תלמוד, פסיקה, אגדה ומוסר, וקריאה לציבור לקיים את המצוות במעשה ובמוסר.</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="3" t="inlineStr">
@@ -35749,7 +35873,11 @@
           <t>תלמידו הגדול וסופרו של רבי נחמן מברסלב. העלה על הכתב את תורותיו, ייסד את מסורת ההתבודדות והתפילה — 'ליקוטי תפילות'.</t>
         </is>
       </c>
-      <c r="J590" s="3" t="inlineStr"/>
+      <c r="J590" s="3" t="inlineStr">
+        <is>
+          <t>כדי שאש הנבואה של הרב תחמם גם את הדורות הבאים יש לצקת אותה לכלים של לשון, הלכה וקהילה; התפילה והתקווה הן התשובה לייאוש.</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="3" t="inlineStr">
@@ -35793,7 +35921,11 @@
           <t>ראב"ד מקנס ומחבר 'קיצור שולחן ערוך' לבני ספרד. פיוטו 'אשתחווה אפיים ארצה' מושר בכל תפוצות המזרח.</t>
         </is>
       </c>
-      <c r="J591" s="3" t="inlineStr"/>
+      <c r="J591" s="3" t="inlineStr">
+        <is>
+          <t>מנהיגות רוחנית אמיתית אינה מסתגרת בבית המדרש: לצד פסיקה ושירה, דאגה לעני, ליתום ולכבודם של המוחלשים, ושמירה על המורשת התורנית של יהדות מרוקו גם בישראל.</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="3" t="inlineStr">
@@ -35837,7 +35969,11 @@
           <t>נשיא ישראל אחרי החורבן. ביצר את סמכות הנשיאות ואת אחדות ההלכה בדור השיקום של יבנה.</t>
         </is>
       </c>
-      <c r="J592" s="3" t="inlineStr"/>
+      <c r="J592" s="3" t="inlineStr">
+        <is>
+          <t>אחדות האומה אחרי החורבן מחייבת סמכות מרכזית והלכה אחידה: תפילה קבועה, לוח שנה אחד וסדר הפסח כ'מקדש מעט' בבתים, לצד ענווה ודאגה לחלשים.</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="3" t="inlineStr">
@@ -35933,7 +36069,11 @@
           <t>השנייה שבאמהות. ראתה ברוח קודשה את ייעודם של בניה והכריעה את המשך דרך הברית — 'ורב יעבוד צעיר'.</t>
         </is>
       </c>
-      <c r="J594" s="3" t="inlineStr"/>
+      <c r="J594" s="3" t="inlineStr">
+        <is>
+          <t>ראיית עתיד נבואית ואחריות לעתיד האומה: רבקה הכריעה שהברכה תעבור ליעקב, ולימדה שהמהות הפנימית של היהודי חשובה יותר מבגדו החיצוני.</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="3" t="inlineStr">
@@ -36025,7 +36165,11 @@
           <t>החכם מכל אדם ובונה בית המקדש הראשון. חיבר את משלי, קהלת ושיר השירים.</t>
         </is>
       </c>
-      <c r="J596" s="3" t="inlineStr"/>
+      <c r="J596" s="3" t="inlineStr">
+        <is>
+          <t>חכמה היא מתנה מאת ה' שמחייבת את המלך: שלמה ביקש לב שומע לשפוט את העם, בנה את הבית לשם ה', וכתב את חכמתו לכל הדורות.</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="3" t="inlineStr">
@@ -36069,7 +36213,11 @@
           <t>אחרון השופטים וגדול הנביאים אחרי משה. הקים את המלוכה בישראל ומשח את שאול ואת דוד.</t>
         </is>
       </c>
-      <c r="J597" s="3" t="inlineStr"/>
+      <c r="J597" s="3" t="inlineStr">
+        <is>
+          <t>הנהגה כשליחות ולא כשלטון: שמואל סבב בערי ישראל לשפוט את העם, התפלל בעדם, והעביר את ההנהגה למלוכה בלי לוותר על סמכות הנבואה.</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="3" t="inlineStr">
@@ -36113,7 +36261,11 @@
           <t>וזיר גרנדה, מצביא, משורר ופוסק — סמל תור הזהב בספרד. 'מבוא התלמוד' שלו נלמד עד היום.</t>
         </is>
       </c>
-      <c r="J598" s="3" t="inlineStr"/>
+      <c r="J598" s="3" t="inlineStr">
+        <is>
+          <t>'תורה וגדולה במקום אחד': מדינאות, מצביאות, שירה, דקדוק ופסיקה משתלבים באישיות אחת, והכוח המדיני משמש לחיזוק התורה ולומדיה.</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="3" t="inlineStr">

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L630"/>
+  <dimension ref="A1:L680"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="3" min="1" max="1"/>
@@ -38161,6 +38161,2886 @@
         </is>
       </c>
     </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>רבי משה אלשיך (האלשיך הקדוש)</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>כ־1507–1600</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>צפת; אדריאנופול</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>דרשנות ופרשנות המקרא, הלכה ושו״ת</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>תורת משה, האלשיך הקדוש, רבי יוסף קארו, רבי חיים ויטאל, מראות הצובאות, שושנת העמקים, שו״ת מהר״ם אלשיך, שד״ר, דרשות שבת</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>דרשן, פרשן ופוסק בצפת, הנודע בכינוי ״האלשיך הקדוש״. נולד באדריאנופול ולמד בישיבת רבי יוסף קארו ובישיבת רבי יוסף טאיטצאק בסלוניקי, עלה לצפת ועמד בראש שתי ישיבות, ורבי חיים ויטאל היה תלמידו. חיבר את ״תורת משה״ על התורה, פירושים לנביאים, למגילות ולחלק מהכתובים, וקובץ שו״ת.</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>פירושיו צמחו מדרשות שנשא מדי שבת: בראש כל יחידה הוא מעלה שאלות וקשיים בלשון הכתוב, ובסופה משיב על כולם בזה אחר זה. בכל פסוק ובכל מילה הוא מבקש לקח מוסרי וחיזוק באמונה, ודבריו נלמדים עד היום.</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>רבי יוסף קארו, רבי יוסף טאיטצאק, רבי חיים ויטאל</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/7xXl4sOy18MABmQdtXzrQu</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>רבי שמואל די אוזידא (בעל מדרש שמואל)</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>1545–1604</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>צפת; קושטא</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>דרשנות, פרשנות משנה ומקרא, קבלה</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>מדרש שמואל, פרקי אבות, האר״י, רבי חיים ויטאל, לחם דמעה, אגרת שמואל, ישיבת צפת, שיטה מקובצת, שליחות לקושטא</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>ראש ישיבה, מקובל ודרשן, יליד צפת ומתלמידיו הראשונים של האר״י, שאחרי פטירתו המשיך ללמוד קבלה אצל רבי חיים ויטאל. ייסד בצפת ישיבה גדולה שעסקו בה בנגלה ובנסתר, ויצא לשליחות בקושטא. נודע בחיבורו ״מדרש שמואל״ על פרקי אבות, שנדפס לראשונה בוונציה בשנת 1579, וכתב גם פירושים למגילות איכה ורות.</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>״מדרש שמואל״ הוא ליקוט פרשני: מעין ״שיטה מקובצת״ לפירושים אחרים על אבות, בתוספת דרשותיו שלו, ולכן שימר גם פירושים שאינם בידינו כיום. אף שהיה מתלמידי האר״י, עסק בספריו בעיקר בדרש ולא בקבלה, והשתמש בתובנות קבליות כתשתית סמויה לדברי מוסר שנועדו לכלל הציבור.</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>האר״י הקדוש, רבי חיים ויטאל</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/6Umixwtvl1Jh3iq0E1sCHW</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>רבי משה מטראני (המבי״ט)</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>כ־1500–1580</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>צפת; סלוניקי</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, הגות ומוסר</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>קרית ספר, בית אלהים, שו״ת המבי״ט, רבי יעקב בירב, רבי יוסף קארו, פרק שירה, משנה תורה, בית הדין בצפת</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>ראש ישיבה, דיין ופוסק, מחכמי צפת במאה ה־16. נולד בסלוניקי, למד באדריאנופול אצל דודו רבי אהרן מטראני, עלה לצפת והיה תלמידו המובהק של רבי יעקב בירב, ויותר מחמישים שנה ישב בבית הדין בעיר. חיבר את ״קרית ספר״ על ״משנה תורה״ לרמב״ם, את ״בית אלהים״ ושני כרכי תשובות שנדפסו אחרי מותו.</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>ב״קרית ספר״ הוא בירר בכל דין ב״משנה תורה״ אם הוא מן התורה, ממידות שהתורה נדרשת בהן, מהלכה למשה מסיני או מדברי חכמים ותקנותיהם. ב״בית אלהים״ הוא ביאר את יסודות הדת בשערי התפילה, התשובה והעיקרים, ולספר צורף גם הפירוש הראשון שנדפס על פרק שירה.</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>מהר״י בירב (רבי יעקב בירב), רבי יוסף מטראני (המהרי״ט)</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0V7vkwok6itxSw9niOhmW0</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>רבי חזקיה בן מנוח (החזקוני)</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>כ־1250–1310</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>צרפת</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>פרשנות המקרא</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>החזקוני, פירוש לתורה, פשט, רש״י, רבי יוסף בכור שור, רשב״ם, אבן עזרא, מנחת יהודה</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>רב ופרשן מקרא צרפתי מהמאה ה־13, שנודע על שם ספרו ״החזקוני״ על חמשה חומשי תורה. פרטי חייו המדויקים אינם ידועים, ומקובל להעריך שנולד בצרפת בסביבות 1250 ונפטר בסביבות 1310. פירושו נדפס לראשונה בוונציה בשנת ה׳רפ״ד, בתוך חמישה חומשי תורה עם רש״י, ובהקדמתו הוא מבקש מקוראיו שיזכרו אותו ויחזקוהו.</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>פירושו הוא ליקוט מכוון: אחרי ששוטט במדינות רבות בחיפוש אחר פירושים ישרים לתורה, הוא הוציא את המיטב מעשרים חיבורים, ובהם רש״י, רשב״ם ואבן עזרא, ובדרך כלל אינו מציין את שמות מקורותיו. הוא נוטה לדרך הפשט הריאלית של רבי יוסף בכור שור, ומביא ממנו גם קטעי הגות בטעמי המצוות.</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>רבי יוסף בכור שור, רש״י (רבי שלמה יצחקי), הרשב״ם, אברהם אבן עזרא</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/6VBVggnMCgZu86mq2JMniv</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>הרב יוסף בא-גד</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>נולד ב־1932</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>פתח תקווה; ירושלים</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>העת החדשה</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>לימוד התלמוד, חינוך תורני</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>ש״ס בש״ס, שיטת הסוגיות, ישיבת נחלים, נחל יצחק, אוגדן הסוגיות, נחלי לימוד, תלמוד בבלי וירושלמי, תורה ומדע</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>ראש ישיבה ומחבר ספרי לימוד, יליד מוצא תחתית (1932). למד בישיבות כפר הרוא״ה, היישוב החדש וחברון, ובשנת 1955 ייסד את הישיבה התיכונית ״נחל יצחק״ בנחלים, שבראשה עמד עד 2004 ושבה הוא משמש מאז נשיא הישיבה. פיתח את שיטת הלימוד ״ש״ס בש״ס״, המכונה גם ״שיטת הסוגיות״, וחיבר את ״אוגדן הסוגיות״ ו״נחלי לימוד״, שזכו בפרס הרב טולידאנו; בשנים 1992–1996 היה גם חבר הכנסת.</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>שיטתו מלמדת תלמוד לפי סוגיות ולא לפי סדר הדפים: כל סוגיה נבחנת בבבלי ומיד אחריה מובאת מקבילתה מהירושלמי, תוך הצלבת מקורות ושילוב תורה ומדע. בחינוך הוא דגל בלמידה עצמאית, ביום לימודים ארוך, באישיות תורנית כמחנך הכיתה ובשילוב הרגש והשכל, והמליץ להעתיק מרכיבים אלה אל בתי הספר הדתיים.</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>הרב אברהם יצחק הכהן קוק</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>רבי עובדיה ספורנו</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>כ־1470–1549</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>בולוניה; רומא</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>פרשנות המקרא, הגות ורפואה</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>ספורנו, ביאור לתורה, כוונות התורה, אור עמים, פשט, בולוניה, רופא, פרקי אבות</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>פרשן מקרא, רב ורופא איטלקי, יליד צ׳זנה, מראשי קהילת רומא וקהילת בולוניה, שבה יסד בית דפוס עברי ושימש רופא. חיבורו החשוב והנפוץ ביותר הוא ביאורו לתורה, והוא חיבר גם פירושים לתהילים, לשיר השירים, לקהלת, לאיוב ולפרקי אבות, ואת הספר הפילוסופי ״אור עמים״.</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>פירושו מבוסס על הפשט, בלשון קצרה ובהירה, והוא נכתב לעם ולא כדי להרשים משכילים. בהקדמה לפירושו לתורה הוא קובע שמטרת התורה להדריך את האדם באשר הוא אדם; הוא חוזר ומדגיש שהבחירה בישראל היא אחריות וחובה ולא זכות, וקושר את הידיעות המדעיות לתיקון המידות.</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>רש״י (רבי שלמה יצחקי), אברהם אבן עזרא, הרשב״ם, הרמב״ן (רבי משה בן נחמן)</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>רבנו ירוחם בן משולם</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>כ־1290–1350</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>טולדו; פרובנס</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>הלכה ופסיקה</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>מישרים, תולדות אדם וחוה, הרא״ש, רבי אברהם בן אסמעאל, בית יוסף, שולחן ערוך, גירוש צרפת, דיני ממונות</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>רב ופוסק מגדולי הראשונים, שנולד בפרובנס ועבר לטולדו אחרי גירוש יהודי צרפת; פרטים בחייו שנויים במחלוקת. למד אצל הרא״ש ואחר כך אצל רבי אברהם בן אסמעאל, תלמיד הרשב״א והרא״ש, שהיה רבו המובהק. חיבר את ״מישרים״ על דיני ממונות ואת ״תולדות אדם וחוה״ על דינים הנוהגים בגלות, ושני החיבורים נודעים יחד בשם ״רבנו ירוחם״.</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>את ההלכה הנוהגת בגלות הוא ארגן ב״תולדות אדם וחוה״ לפי מהלך חייו של האדם: ב״אדם״ הדינים מלידתו ועד נישואיו, לצד ברכות, תפילות ומנהגים, וב״חוה״ מנישואיו ועד פטירתו. פסקיו מוזכרים פעמים רבות ב״בית יוסף״ והשפיעו על פסיקתו של רבי יוסף קארו בשולחן ערוך, ומתוך כך על הלכות רבות הנהוגות גם בימינו.</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>רבנו אשר בן יחיאל (הרא״ש), רבי יוסף קארו</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>רבי ברוך בן יצחק (בעל התרומה)</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>כ־1140–1211</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>פריז; ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>הלכה ופסיקה, תוספות</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>ספר התרומה, ר״י הזקן, בעלי התוספות, הלכות ארץ ישראל, עליית בעלי התוספות, בית המדרש הצרפתי, בית יוסף, תוספות על זבחים</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>תלמיד חכם ופוסק מבעלי התוספות ותלמידו המובהק של ר״י הזקן, שחי ופעל בצרפת, ובין היתר בפריז. נודע בכינוי בעל התרומה על שם ספרו ״ספר התרומה״, קובץ פסקי הלכה בלשון קצרה שנכתב בראשית המאה ה־13. לקראת פטירתו עלה לארץ ישראל, בתקופת עליית בעלי התוספות, ושם נפטר ונקבר.</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>ספרו הולך אחר בית המדרש הצרפתי: הוא פוסק הלכה בלשון קצרה במגוון נושאים, אינו עוסק במנהגי הקהילות ומסתיים במפתחות המסכמים את הפרקים. הוא כולל גם פרק מיוחד על ״הלכות ארץ ישראל״, ופוסקים רבים בססו עליו את פסיקתם; הבית יוסף מביא את דבריו רבות.</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>ר״י הזקן מדמפייר, יעקב בן אשר, רבי יוסף קארו, רבי אלעזר מגרמייזא (בעל הרוקח)</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>רבי יהושע פלק כ״ץ (הסמ״ע)</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>כ־1555–1614</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>קרקוב; לבוב</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>הלכה, פרשנות הטור, פרשנות השולחן ערוך</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>מאירת עינים, הסמ״ע, דרישה ופרישה, בית ישראל, ארבעה טורים, שולחן ערוך, המהרש״ל, הרמ״א, ישיבת לבוב, ועד ארבע הארצות</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>מגדולי האחרונים בפולין, יליד קראקא ותלמידם של המהרש״ל והרמ״א. עמד בראש ישיבה בלבוב, שם נפטר בשנת 1614, והעמיד תלמידים רבים. חיבר את ״דרישה ופרישה״ על הטור ואת ״מאירת עינים״ (הסמ״ע) על חושן משפט שבשולחן ערוך, ושניהם נדפסו אחר כך ברוב מהדורות הטור והשולחן ערוך.</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>הסמ״ע התנגד להישענות על ספרי הפסק תוך זניחת העיון במקורות המקוריים, ולכן חיבר פירושים לטור ולשולחן ערוך. ב״פרישה״ הוא מתחקה אחר הכרעות הטור עד מקורותיהן בתלמוד ובראשונים, וב״דרישה״ הוא דן בהרחבה בשיטות השונות.</t>
+        </is>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>המהרש״ל (רבי שלמה לוריא), הרמ״א (רבי משה איסרליש)</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>רבי שמואל די מדינה (המהרשד״ם)</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>כ־1505–1589</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>סלוניקי</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, ראשות ישיבה</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>שו״ת מהרשד״ם, בן שמואל, רבי יוסף טאיטצאק, המהרלב״ח, לחם משנה, סלוניקי, האימפריה העות׳מאנית, תקנות קהל, אנוסים, פסיקה</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>מן הפוסקים המרכזיים באימפריה העות׳מאנית במאה ה־16, יליד סלוניקי, דיין וראש ישיבה בעירו. תלמידם של רבי יוסף טאיטצאק ורבי לוי בן חביב, ורבו של רבי אברהם די בוטון, בעל ״לחם משנה״. שאלות הלכתיות נשלחו אליו מקהילות רבות, וכאלף מתשובותיו נדפסו ב״שו״ת מהרשד״ם״, ודרשותיו בספר ״בן שמואל״.</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>תשובותיו קושרות את ההלכה לחיי הקהילה: לצד איסור והיתר, קידושין וגירושין הן עוסקות בתקנות קהל, במנהגי קהילות, בחלוקת נטל המיסים, בענייני מסחר ובמעמד האנוסים וצאצאיהם. שו״ת מהרשד״ם נמנה עם ספרי הפסיקה שחכמי המזרח הסתמכו עליהם, והוא משמש גם מקור היסטורי חשוב לחיי היהודים בסלוניקי.</t>
+        </is>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>רבי יוסף טאיטצאק, רבי לוי בן חביב (המהרלב״ח), רבי אברהם די בוטון, רבי מנחם די לונזאנו</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>רבי יוסף בן לב (מהריב״ל)</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>כ־1503–1580</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>סלוניקי; קושטא</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, ראשות ישיבה</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>שו״ת מהריב״ל, מונסטיר, סלוניקי, קושטא, דונה גרציה, רבי יוסף קארו, רבי יוסף טאיטצאק, אנוסים, לימוד לפי סוגיות, ישיבת קושטא</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>מחכמי מונסטיר שבאימפריה העות׳מאנית במאה ה־16, דיין ופוסק וראש ישיבה בסלוניקי ובקושטא, שנודע באישיותו התקיפה ובפסיקת הלכה בלתי מתפשרת. בקושטא מינתה אותו דונה גרציה מנדס לראש הישיבה שהקימה. תשובותיו, ״שו״ת מהריב״ל״, נדפסו עוד בחייו, ובהן גם חידושיו לכמה מסכתות בתלמוד הבבלי.</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>דרך לימודו מיזגה את הדרך הספרדית, המצטיינת בבקיאות ועוסקת בעיקר בבירור ההלכה, עם הדרך האשכנזית, המצטיינת בחריפות ועוסקת רבות גם בפלפול. בישיבתו הנהיג, כבישיבות האשכנזיות, לימוד לפי נושאים וסוגיות ולא לפי סדר התלמוד.</t>
+        </is>
+      </c>
+      <c r="K641" t="inlineStr"/>
+      <c r="L641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>רבי יוסף מטראני (המהרי״ט)</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>1568–1639</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>צפת; קושטא</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, ראשות ישיבה, פרשנות לתורה</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>שו״ת המהרי״ט, צפנת פענח, חידושי מהרי״ט, החכם באשי, המבי״ט, רבי חיים בנבנשתי, דינא דחיי, צפת, קושטא, הסמ״ג</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>מגדולי הפוסקים, בנו של רבי משה מטראני (המבי״ט), יליד צפת ומרבניה. עבר לקושטא, ייסד בה בית דין לענייני איסור והיתר ונתמנה לחכם באשי של טורקיה, ולישיבתו נהרו תלמידים מכל טורקיה ואף מעבר לה. נודע בשו״ת המהרי״ט ובחידושיו, וכן בפירושו ״צפנת פענח״ על התורה והמועדים.</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>הוא היה פוסק ומרביץ תורה גם יחד: קיבל אלפי שאלות והשיב עליהן, חיבר פירושים על הר״ן, הרי״ף והרמב״ם, והעמיד תלמידים. אחד מהם, בעל ״כנסת הגדולה״, זכה לברכתו שיחבר חיבור על הסמ״ג.</t>
+        </is>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>רבי משה מטראני (המבי״ט), רבי חיים בנבנשתי (בעל כנסת הגדולה)</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>רבי אברהם די בוטון (בעל לחם משנה)</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>המאה ה־16</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>סלוניקי</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, פרשנות הרמב״ם</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>לחם משנה, לחם רב, משנה תורה, הרמב״ם, המהרשד״ם, המגיד משנה, כסף משנה, סלוניקי, ראשות ישיבה, מגפה</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>רב, פוסק וראש ישיבה, מצאצאי מגורשי ספרד ומחכמי סלוניקי במאה ה־16, תלמידו של המהרשד״ם. פירש את משנה תורה של הרמב״ם בספרו ״לחם משנה״, שזכה לתפוצה רחבה והודפס במהדורה הסטנדרטית של הספר, וחיבר גם ספר שו״ת בשם ״לחם רב״. בשעת מחלתו נוסף לו השם חייא, ולפעמים היה חותם בשם זה.</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>בפירושו הוא מעמיק בדברי הרמב״ם ומשווה אותם לראשונים אחרים ולמפרשי הרמב״ם שקדמו לו, המגיד משנה והכסף משנה. החיד״א כתב שהחל לכתוב את חיבורו לפני שהתוודע לפירוש ״כסף משנה״, ולאחר שהתוודע אליו ציין אותו גם בו.</t>
+        </is>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>רבי שמואל די מדינה (המהרשד״ם)</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>רבי שמואל בן אורי שרגא פייבוש (בעל בית שמואל)</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>כ־1650–1706</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>פולין; גרמניה</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>הלכה, פרשנות השולחן ערוך, ראשות ישיבה</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>בית שמואל, אבן העזר, שולחן ערוך, חלקת מחוקק, אפי רברבי, פיורדא, שידלוב, ישיבת קרקוב, דירנפורט, מהדורא בתרא</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>רבן של שידלוב ופיורדא, יליד פולין באמצע המאה ה־17, שלמד בישיבת קרקוב. נודע בזכות ״בית שמואל״, מ״נושאי הכלים״ לחלק אבן העזר בשולחן ערוך. את המהדורה הראשונה הדפיס בדירנפורט, ואחרי שעבר עליה בפיורדא עם תלמידיו הוציא מהדורה שנייה מתוקנת, שמודפסת מאז ברוב מהדורות השולחן ערוך.</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>״בית שמואל״ נכתב כדי ״לגאול״ את חלק אבן העזר, שתלמידי החכמים זנחו, ולהפוך אותו מ״אבן מאסו הבונים״ ל״ראש פינה״ ולמרכז העיסוק הלימודי. המהדורה השנייה, שהמחבר הוסיף וגרע ושינה בה בעצמו יחד עם תלמידיו, היא העיקרית: שם הגדולים קובע ש״מהדורא קמא אין להשגיח בו״.</t>
+        </is>
+      </c>
+      <c r="K644" t="inlineStr"/>
+      <c r="L644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>רבי יהושע בועז (בעל שלטי הגיבורים)</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>המאה ה־16</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>איטליה</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>הלכה, פרשנות הרי״ף, עריכת הש״ס</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>שלטי הגיבורים, מסורת הש״ס, עין משפט נר מצווה, תורה אור, הרי״ף, ריא״ז, הרמ״א, הגהות אלפסי, ש״ס ונציה, איטליה</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>מגדולי הפוסקים האחרונים, נולד באיטליה לרבי שמעון לבית ברוך, ממשפחה ממגורשי ספרד. חיבר את ״מסורת הש״ס״, הפניות למקבילות בתלמוד שנדפסו כמעט בכל מהדורותיו, את ״עין משפט נר מצווה״, הפניות להלכה שבדברי הרמב״ם והסמ״ג, ואת ״שלטי הגיבורים״ על הרי״ף, שהרמ״א הרבה להביא ממנו פסקים.</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>ספריו קושרים את הלימוד בגמרא להלכה: ״עין משפט״ מפנה ממקום הדין בגמרא לדברי הרמב״ם והסמ״ג, ולאחר מכן גם לשולחן ערוך ולארבעה טורים, והוא כלי עזר חשוב ללומדי הגמרא ״אליבא דהלכתא״. ״שלטי הגיבורים״ מתמצת את פסקי ההלכה הנובעים מדברי הרי״ף ומהתייחסות הראשונים אליהם, ובו גם מעט מחידושיו.</t>
+        </is>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>הרמ״א (רבי משה איסרליש)</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>רבי שלמה סיריליו</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>1485–1554</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>צפת; ירושלים; סלוניקי</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>פרשנות התלמוד הירושלמי, הלכה, ראשות ישיבה</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>תלמוד ירושלמי, פירוש לירושלמי, סדר זרעים, מסכת שקלים, מסכת עדויות, מגורשי ספרד, צפת, ירושלים, סלוניקי, המצוות התלויות בארץ</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>ממגורשי ספרד ומחכמי צפת וירושלים במחצית הראשונה של המאה ה־16, מראשוני פרשני התלמוד הירושלמי. למד בקושטא ובסלוניקי, עלה לצפת ב־1532 ולימים עבר לירושלים והקים בה ישיבה. פירש את כל סדר זרעים ואת מסכת שקלים, ופירושו לסדר זרעים הוא הפירוש הרציף הראשון הידוע לירושלמי, וכן ערך מעין גמרא על מסכת עדויות.</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>ברוב הסוגיות לא עמד לפניו פירוש קדום, ופירושו לירושלמי מקורי ברובו, והוא לא נרתע מלחלוק על הראשונים ולעיתים אף על הרמב״ם. הוא שילב בפירושו פסקי הלכה הנובעים מן הסוגיות, ופסקים אלה הם מאבני היסוד בפסיקת ההלכה בימינו בנושא המצוות התלויות בארץ.</t>
+        </is>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>רבי לוי בן חביב (המהרלב״ח), רבי יעקב אבן חביב (עין יעקב), רבי שלמה עדני (בעל מלאכת שלמה)</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>רבי חיים בנבנשתי (בעל כנסת הגדולה)</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>1603–1673</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>איזמיר; קושטא</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, ראשות ישיבה, פרשנות הטור</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>ספר כנסת הגדולה, שיירי כנסת הגדולה, דינא דחיי, בעי חיי, פסח מעובין, חמרא וחיי, המהרי״ט, הסמ״ג, בית יוסף, איזמיר</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>רב ופוסק באיזמיר, יליד קושטא ותלמידו של רבי יוסף מטראני (המהרי״ט), שבירך אותו לחבר חיבור על הסמ״ג. בגיל 21 חיבר את ספרו הראשון, ״דינא דחיי״ על הסמ״ג. כיהן ברבנות בטירה הסמוכה לאיזמיר ואחר כך באיזמיר, כדיין וכראש ישיבה, ונודע בעיקר בספרו ״כנסת הגדולה״ על הטור והבית יוסף.</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>״כנסת הגדולה״ על הטור והבית יוסף הפך לאחד מספרי היסוד בפסיקה, ועל שמו נקרא מחברו. החיד״א כתב שאיש מורה הוראה בקי אינו מרים יד בשום הוראה בלי שיעיין בו תחילה.</t>
+        </is>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>רבי יוסף מטראני (המהרי״ט)</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>רבי אליהו די וידאש (בעל ראשית חכמה)</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>המאה ה־16</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>צפת; חברון</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>קבלה ומוסר, הגות</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>ראשית חכמה, תוצאות חיים, הרמ״ק, האר״י, רבי שלמה אלקבץ, רבי יצחק דמן עכו, ראשות רבני חברון, תיקון המידות, הזוהר, קבלה ומוסר</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>מקובל והוגה דעות, יליד צפת ותלמידו של הרמ״ק, שלמד גם מפי האר״י. עבר לחברון והתמנה לראש רבניה, ושם נקבר. בשנת 1575 סיים את כתיבת ספרו ״ראשית חכמה״, העוסק בהיבטים השונים של חיי האדם על פי המשמעות הקבלית, והספר זכה למהדורות רבות, למהדורה מקוצרת ולתרגום ליידיש.</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>״ראשית חכמה״ הוא ספר קבלי על מידות האדם הראויות, המבוסס ברובו על הזוהר. לדברי שם הגדולים, מי שיקבע בו שיעור יומי ודאי יתנוצצו בו קדושה וטהרה.</t>
+        </is>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>הרמ״ק (רבי משה קורדובירו), האר״י הקדוש, רבי יצחק דמן עכו</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>רבי אליה שפירא (בעל אליה רבה)</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>כ־1660–1712</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>פראג</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>הלכה, פסיקה ודרשנות</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>אליה רבה, אליה זוטא, הלבושים, רבי מרדכי יפה, מגן אברהם, משנה ברורה, פסיקה אשכנזית, פראג, שולחן ערוך</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>דיין, ראש ישיבה ודרשן בפראג, יליד העיר בסביבות שנת 1660, שנפטר ב־1712 בחיי אביו. למד אצל סבו, רבי אהרן שמעון מפראג, ובפולין למד מפי בעל ״מגן אברהם״. חיבר את ״אליה זוטא״ ואת ״אליה רבה״, פירושים לחלק אורח חיים בספרי ״הלבוש״ של רבי מרדכי יפה; שני הפירושים נחשבים לספרי יסוד בפסיקה האשכנזית.</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>פסיקה דרך פירוש: ״אליה רבה״ נכתב על סדר ״הלבוש״ של רבי מרדכי יפה ונעשה אחד מספרי היסוד בפסיקה האשכנזית. המשנה ברורה מביא אותו תדיר כמקור הפסיקה ההלכתית שלו.</t>
+        </is>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>רבי אברהם אבלי גומבינר (המגן אברהם), רבי מרדכי יפה, רבי יעקב ריישר</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>רבי דוד אלטשולר (בעל מצודת דוד)</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>1687–1769</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>יאברוב; גליציה</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>פרשנות המקרא</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>מצודת דוד, מצודת ציון, פירוש לנביאים ולכתובים, פשט, מקראות גדולות, רד״ק, יאברוב, זאלקווא</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>פרשן מקרא ממשפחת אלטשולר, יליד יאברוב שבגליציה, שנזכר בה כדיין או כרב. כדי להנגיש את התנ״ך גם למלמדי תינוקות וילדים כתב את ״מצודת דוד״, ביאור פשוט וברור על התנ״ך (חוץ ממגילות רות, איכה ואסתר) שליקט מפירושי הראשונים, והדפיס ב־1753 בזאלקווא את הפירוש לאיוב, למשלי ולתהילים. בנו, רבי יחיאל הלל, השלים את הפירוש והדפיסו.</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>הנגשת המקרא לכל לומד: ״מצודת דוד״ מלקט בעברית פשוטה וצחה את פירושי הראשונים, כך שתלמידי החכמים חוסכים זמן יקר של עיון בהם והיהודים הפשוטים מבינים את המקרא על פי פשוטו. הפירוש זכה לאהדה רבה מפני שהוא ברור ומובן לכל, והוא נדפס כמעט בכל מהדורות ״מקראות גדולות״.</t>
+        </is>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>רבי דוד קמחי (הרד״ק), רבי יחיאל הלל אלטשולר</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>רבי יחיאל הלל אלטשולר (בעל מצודת ציון)</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>המאה ה־18</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>יאברוב; עמדין; גליציה</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>פרשנות המקרא והלכה</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>מצודת ציון, מצודת דוד, בנין הבית, בית המקדש השלישי, נבואת יחזקאל, מקראות גדולות, ליוורנו, יאברוב, עמדין</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>פרשן מקרא ופוסק, בנו של רבי דוד אלטשולר, יליד יאברוב שבגליציה, שכיהן כרב בעמדין וביאברוב. השלים וערך את ״המצודות״ של אביו על התנ״ך, חילק אותן ל״מצודת דוד״ ול״מצודת ציון״, ונדד לברלין, להולנד ולאיטליה כדי להדפיסן, עד שהודפסו בליוורנו. כתב גם את ״בנין הבית״ על צורת בית המקדש השלישי.</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>עריכה שהופכת כתבי אב לפירוש מקיף: ״מצודת דוד״ מבארת את ענייני הפסוקים ופשטם, ו״מצודת ציון״ מפרשת מילים וביטויים בתנ״ך, והוא שכלל והוסיף הוספות משלו. הפירוש המוגמר זכה לאהדה רבה מפני שהוא ברור ומובן לכל, ובמהרה נעשה אבן יסוד של פרשנות התנ״ך.</t>
+        </is>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>רבי דוד אלטשולר</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>רבי שלמה עדני (בעל מלאכת שלמה)</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>כ־1567–1630</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>חברון; ירושלים; צנעא</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>פרשנות משנה</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>מלאכת שלמה, פירוש המשנה, נוסח המשנה, רבי חיים ויטאל, רבי בצלאל אשכנזי, בנין שלמה לחכמת בצלאל, דברי אמת, יהדות תימן</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>מגדולי מפרשי המשנה, יליד צנעא שבתימן, שעלה עם משפחתו לארץ ישראל והתיישב בצפת ואחר כך בירושלים, ובירושלים למד לפני רבי חיים ויטאל ורבי בצלאל אשכנזי. עבר לחברון וכתב בה במשך שלושים שנה את ״מלאכת שלמה״, פירוש על ששת סדרי משנה. חיבר גם את ״בנין שלמה לחכמת בצלאל״ ואת ״דברי אמת״, הגהות למקרא.</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>פירוש למשנה שמברר את נוסח המשנה וניקודה, ומתוך בקיאות בשני התלמודים, במפרשים ובפוסקים הוא דן בדבריהם עד לפסיקת ההלכה. בפירושו ניכרת חיבתו לרמב״ם, שאותו הוא מכנה ״גדול הפוסקים״.</t>
+        </is>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>רבי בצלאל אשכנזי, רבי חיים ויטאל</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>רבי יעקב יהושע פלק (בעל פני יהושע)</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>1680–1756</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>לבוב; ברלין; מץ; פרנקפורט; גרמניה; גליציה</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>פרשנות התלמוד</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>פני יהושע, מגיני שלמה, תוספות, רש״י, עיון ופלפול, לבוב, ברלין, מץ, פרנקפורט, מחלוקת עמדין־אייבשיץ</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>נולד בקרקוב ב־1680, כיהן כרבן של לבוב, ברלין, מץ ופרנקפורט על המיין, ונפטר ב־1756 באופנבך. כתב את סדרת ספרי ״פני יהושע״ על התלמוד הבבלי, שבהם הוא מבאר את סוגיות הש״ס על פי התוספות ורש״י בדרך העיון, החקירה, הסברה והפלפול. לפי הקדמתו התחיל לכתוב את הספר בנדר, אחרי שניצל מפיצוץ מחסן חומר נפץ.</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>הגנה על רש״י דרך עיון: ״פני יהושע״ ממשיך את דרכו של ״מגיני שלמה״ ומיישב את קושיות בעלי התוספות על פירוש רש״י, ויורד לפרטי הפרטים של כל סוגיה. אף ששיטת הלימוד שהתקבלה בדורות האחרונים רחוקה מדרכו, הספר זוכה לפופולריות רבה בישיבות.</t>
+        </is>
+      </c>
+      <c r="K653" t="inlineStr"/>
+      <c r="L653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>רבי יהונתן אייבשיץ</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>כ־1690–1764</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>פראג; מץ; אלטונה; המבורג</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>הלכה, קבלה ודרשנות</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>כרתי ופלתי, אורים ותומים, יערות דבש, מחלוקת עמדין־אייבשיץ, קמעות, שבתאות, לוחות עדות, פלפול, פראג, מץ</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>ראש ישיבה ודרשן בפראג, ולימים רבה של מץ ורבן של קהילות אלטונה, המבורג ואנדסבק, ומגדולי פוסקי ההלכה ביהדות אשכנז בזמנו. חיבר את ״כרתי ופלתי״ על יורה דעה, את ״אורים ותומים״ על חושן משפט ואת ספר הדרשות ״יערות דבש״. עיסוקו בקבלה ובקמעות עורר נגדו פולמוס, שפתח רבי יעקב עמדין שמצא רמזים שבתאיים בכתביו; רוב רבני דורו תמכו בו והפולמוס דעך.</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>פלפול מחוכם שמלווה גם את ההלכה וגם את המוסר: חיבור של רעיונות שונים זה מזה מאפשר לו לפתור קושיות ולהתמודד עם סתירות. כפוסק הוא מחמיר, ודבקותו בשולחן ערוך גדולה, והוא מציע להתעלם מדעות שאינן מוזכרות בו.</t>
+        </is>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>רבי אליה שפירא (בעל אליה רבה), רבי יעקב ריישר</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>רבי מנחם די לונזאנו</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>כ־1550–1626</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>ירושלים; קושטא; איטליה</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>נוסח המקרא, מילונאות, קבלה ושירה</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>שתי ידות, אור תורה, מעריך, עבודת המקדש, דרך חיים, נוסח המקרא, מסורה, מדרש אגור, הרמד״ל</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>רב, מקובל, משורר, חוקר המסורה ומהדיר ספרי מדרש, ומן העולים הקדמונים לארץ ישראל. נולד, לפי אגרת המלצה, בפיסארו שבאיטליה, עלה לירושלים אחרי 1575 ונפטר בה לפני 1626. חיבר את ״שתי ידות״ (ונציה, 1618), ספר הכולל עשרה חיבורים: חמישה משלו, ובהם ״אור תורה״ לבירור נוסח המקרא לפי המסורה ו״מעריך״, תשלום לספר הערוך, וחמישה חיבורים קדומים של חז״ל שהדיר.</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>הכרעה בנוסח המקרא לפי כתבי היד והמסורה: ״אור תורה״ נשען על יותר מעשרה כתבי יד של המקרא ועל ספרי מגיהי המקרא שקדמוהו, ויחד עם דברי הרמ״ה (רבי מאיר הלוי אבולעפיה) ובעל ״מנחת שי״ נעשה לקובע נוסח המקרא המקובל. בנדודיו נחשף לכתבי יד עתיקים של מדרשי חז״ל והשתדל להוציאם לאור.</t>
+        </is>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>רבי נתן מרומי, רבי שמואל די מדינה (המהרשד״ם)</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>רבי יעקב חגיז (בעל הלכות קטנות)</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>1620–1674</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>ירושלים; ליוורנו; קושטא; פאס</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, פרשנות משנה וראשות ישיבה</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>הלכות קטנות, עץ חיים, ישיבת בית יעקב, פתיל תכלת, תחילת חכמה, שבתי צבי, שבתאות, ליוורנו, פאס</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>נולד בפאס שבמרוקו ב־1620, עבר בצעירותו לאיטליה והדפיס שם חיבורים, ובשנת 1658 עלה לירושלים והקים בה את בית המדרש ״בית יעקב״. חיבר את שו״ת ״הלכות קטנות״, את ״עץ חיים״ על המשנה ואת ״פתיל תכלת״ על אזהרות אבן גבירול. בראש רבני ירושלים נקט קו תקיף נגד שבתי צבי, ורבני העיר בראשותו פרסמו נגדו חרם; הוא נפטר בקושטא ב־1674.</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>הכשרת דיינים ורבנים דרך התנסות: בישיבת ״בית יעקב״ קבע סדרי לימוד חדשים, ובהם מקום לתלמידים צעירים ולתלמידי חכמים; התלמידים למדו בחמישה ״שולחנות״, ואחר כך התמחו בפסיקה ובדיינות לצד עשרה חכמים, עד מינוי לדיינים בקהילות שבחוץ לארץ. גם את תשובותיו ב״הלכות קטנות״ כתב, לפי החיד״א, בדרך קצרה כדי לחדד את התלמידים.</t>
+        </is>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>רבי משה חגיז, רבי משה גלאנטי (המג״ן)</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>רבי אברהם הלוי (בעל גינת ורדים)</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>כ־1650–1712</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>קהיר; רוזטה; מצרים</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>גינת ורדים, גן המלך, דרכי נועם, רבני מצרים, רוזטה, קהיר, באר היטב</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>מרבני מצרים במאה ה־17, נולד בה בסביבות 1650 ונפטר ב־1712. שימש בדיינות ואחר כך נבחר לראש רבני מצרים בקהיר, ומילא את מקום אביו, רבי מרדכי הלוי בעל ״דרכי נועם״, כראש הישיבה ואב בית הדין ברוזטה. חיבר את שו״ת ״גינת ורדים״, בסדר ארבעה טורים, שנתפרסמו אחרי מותו והשפיעו רבות בכל המזרח וגם על חכמים אשכנזים.</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>שו״ת מסודר לפי ארבעה טורים, הכולל גם תשובות של חכמי התקופה ומכתבים עם חברו ובר פלוגתא רבי יעקב פראג׳י. השפעת הספר הייתה רבה בכל המזרח וגם על חכמים אשכנזים, ובעל ״באר היטב״ מביאו פעמים רבות.</t>
+        </is>
+      </c>
+      <c r="K657" t="inlineStr"/>
+      <c r="L657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>רבי יאיר חיים בכרך (בעל חוות יאיר)</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>1638–1702</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>וורמייזא; מגנצא; קובלנץ; פרנקפורט</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>חוות יאיר, מקור חיים, חוט השני, המהר״ל, וורמייזא, מגן אברהם, הט״ז, אחרי רבים להטות, פסיקה אשכנזית</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>נולד בלייפניק שבמוראביה ב־1638, כיהן כרב בקובלנץ ובמגנצא ובסוף ימיו בוורמייזא, ונפטר ב־1702. מגדולי האחרונים באשכנז, ונודע בספר השו״ת ״חוות יאיר״, שיצא לאור ב־1699 ונחשב לאחד מספרי ההלכה החשובים ביותר באשכנז. חיבר כארבעים ספרים בהלכה, ובהם ״מקור חיים״ על שולחן ערוך אורח חיים; ספרו ״חוט השני״ מכיל בעיקר תשובות של אביו וסבו.</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>פסיקה עצמאית שמחויבת לאמת: הוא חולק על הרמב״ם וקובע שייתכנו שכחה ומחלוקת גם בהלכה למשה מסיני, ושהכרעת חכמי הדור קובעת הלכה גם נגד המסורת המקורית. הוא מתנגד בחריפות לפלפול מוגזם, ובמקום לעסוק בתורת הנסתר, שהעריך את חשיבותה, מעדיף ״לעמוד על עקרי הדת ומשפטי המצוות״.</t>
+        </is>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>המהר״ל מפראג, רבי דוד הלוי סגל (הט״ז), רבי אברהם אבלי גומבינר (המגן אברהם)</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>רבי אליהו הכהן האתמרי (בעל שבט מוסר)</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>כ־1659–1729</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>איזמיר</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>מוסר, דרשנות וקבלה</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>שבט מוסר, מדרש תלפיות, ילקוט האתמרי, איזמיר, סגפנות, צדקה, אפוטרופוסים לעניים, אגדת אליהו, ספרות המוסר</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>דיין, דרשן ומקובל מחכמי איזמיר, שנולד בעיר וישב בה כל חייו. ספרו המוסרי ״שבט מוסר״ יצא לאור לראשונה בקושטא בשנת ה׳תע״ב, נדפס מאז בעשרות מהדורות ותורגם ליידיש, ללדינו ולערבית יהודית. חיבר עשרות ספרים, בעיקר ספרי מוסר, מדרש ופרשנות המקרא, ובהם ״מדרש תלפיות״.</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>המוסר אינו עניין של הפרט בלבד: בדרשותיו הטיף לסגפנות ולהתרחקות מתענוגות העולם הזה, וראה בעוני ובאי־השוויון החברתי בעיה דתית ומוסרית שהקהילה כולה צריכה לתקן. את עשירי הקהילה ראה כ״אפוטרופוסים״ על כספי העניים וקרא להם לפזר את כספם לצדקה.</t>
+        </is>
+      </c>
+      <c r="K659" t="inlineStr"/>
+      <c r="L659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>רבי עזריה פיגו (בעל גידולי תרומה)</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>1579–1647</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>ונציה; פיזה</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>הלכה, דרשנות</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>גידולי תרומה, בינה לעתים, ספר התרומות, רבי שמואל הסרדי, פיזה, ונציה, דרשנות, סופר סת״ם, הש״ך, יהדות איטליה</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>רב, פוסק ודרשן יליד ונציה, מחכמי איטליה במאה ה־17, שלמד תורה בעירו ורכש גם השכלה כללית באוניברסיטה. שימש כרב קהילת פיזה כעשרים שנה, ואחר כך שב לוונציה והיה בה דרשן בבתי הכנסת. את פירושו ״גידולי תרומה״ לספר התרומות של רבי שמואל הסרדי כתב כמעט ללא ספרים, ודרשותיו נדפסו בספרו ״בינה לעתים״, שיצא לאור אחרי מותו.</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>הדרשה צריכה להישאר קרובה לפשט ולעולם המעשה: לדברי מי שהוציא את דרשותיו לאור, הוא נמנע מעיונים מופשטים ומרעיונות פילוסופיים שאין להם אחיזה בעולם המעשה, שהיו דרכם של דרשני איטליה בימיו, ומבקש את פשט הדברים. ספרו נדפס עשרות פעמים וזכה לפופולריות רבה בקרב הדרשנים והמון העם. בהלכה ברר את דברי ספר התרומות ואת מקורותיו והשווה אותם לדברי פוסקים אחרים.</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>רבנו שמואל הסרדי, רבי שבתאי הכהן (הש״ך)</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>רבי יעקב ריישר (בעל שבות יעקב)</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>כ־1661–1733</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>פראג; וורמייזא; מץ</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, אגדה</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>שבות יעקב, חק יעקב, מנחת יעקב, עיון יעקב, תורת השלמים, עין יעקב, פראג, מץ, וורמייזא, הש״ך</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>מרבני אשכנז, פוסק ומחבר ספרי הלכה ואגדה. נולד בפראג, שימש בה כדיין ובהמשך כראש בית הדין הגדול, ואחר כך כיהן כרב וכראש ישיבה בוורמייזא ובמץ, ושם נפטר. מחיבוריו שו״ת ״שבות יעקב״, ״חק יעקב״ על הלכות פסח, ״מנחת יעקב״ ו״עיון יעקב״, פירוש לאגדות שבספר עין יעקב.</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>הלכה ואגדה יחד: הוא חיבר שו״ת וחידושים על שולחן ערוך, וחיבור על כללי הספיקות של הש״ך, וגם פירוש לאגדות התלמוד שבספר עין יעקב. הוא נהג לעמוד עם גיסיו, רבי אליה שפירא ורבי דוד אופנהיים, במשא ומתן הלכתי.</t>
+        </is>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>רבי אליה שפירא (בעל אליה רבה), רבי שבתאי הכהן (הש״ך)</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>רבי שמשון חיים נחמני (בעל זרע שמשון)</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>1706–1779</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>מודינה; רג׳ו אמיליה; צפון איטליה</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>קבלה, הלכה, דרשנות ושירה</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>זרע שמשון, תולדות שמשון, קרבן קטורת, מודינה, רג׳ו אמיליה, רבי אביעד שר שלום באזילה, קבלה מעשית, גניזת כתבים, דרשנות</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>רב, מקובל, דרשן ומשורר יהודי איטלקי, יליד מודינה, שכיהן כרב בכמה קהילות בצפון איטליה ונחשב לאחד מגדולי רבני המדינה. למד תורה במודינה ובמנטובה וקבלה ברג׳ו אמיליה, ובשנת 1739 החל לכהן שם כרב ושם נפטר. מספריו נדפסו ״זרע שמשון״ על התורה והמגילות ו״תולדות שמשון״ על מסכת אבות, וציווה לגנוז עמו את ספריו, בעיקר בקבלה.</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>נגלה ונסתר יחד: הוא נחשב לבקי בכל חלקי התורה, נגלה ונסתר, בדרשותיו על התורה ביאר גם מאמרים תמוהים, ובהלכה נקט גישה מחמירה וראה בנטייה להקל ״כוח הטומאה״. שאיפתו, כפי שהצהיר בצוואתו, הייתה לזכות את הרבים, להעמיד תלמידים ולחדש חידושי תורה אמיתיים.</t>
+        </is>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>רבי אביעד שר שלום באזילה</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>רבי יצחק דמן עכו (בעל מאירת עיניים)</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>כ־1250–1340</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>עכו; ספרד</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>קבלה, פרשנות</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>מאירת עיניים, אוצר החיים, הרמב״ן, ספר הזוהר, רבי משה די ליאון, כיבוש עכו, חכמת הצירוף, פירוש לספר יצירה, ראשית חכמה</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>מקובל יליד עכו, שנחשב לאחד מגדולי חכמי העיר בדורו. בכיבוש עכו בידי הממלוכים ב־1291 נפל בשבי, ואחר כך נסע לספרד כדי להתחקות אחר מקורו של ספר הזוהר, ושם נפטר. בספרו ״מאירת עיניים״ ביאר את הסודות שבפירוש הרמב״ן לתורה, והחיד״א מכנה אותו תלמידו ואיש סודו של הרמב״ן, אך הדבר מסופק.</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>חקירת מקורותיו של ספר הזוהר: הוא נסע לספרד כדי להתחקות אחר מקורו של ספר הזוהר, ובמאירת עיניים ביאר את הסודות שבפירוש הרמב״ן לתורה והאריך בגנות הפילוסופיה. בספרו ״אוצר החיים״, יומן מיסטי של חוויות אקסטטיות, פירש את תורת השמיטות הקבלית.</t>
+        </is>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>הרמב״ן (רבי משה בן נחמן), רבי אליהו די וידאש</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>רבי שמואל אבוהב (בעל דבר שמואל)</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>1610–1694</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>ונציה; ורונה</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, מנהיגות קהילתית</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>דבר שמואל, ספר הזכרונות, ורונה, ונציה, רבי דוד פרנקו, שבתי צבי, סתם יינם, רבי משה זכות, יהדות איטליה</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>רב ופוסק הלכה בוונציה ומגדולי חכמי איטליה, יליד המבורג, שנשלח בגיל שלוש עשרה ללמוד בוונציה אצל הרב דוד פרנקו. ייסד בוורונה ישיבה שנודעה בערי איטליה, ומשנת 1650 שימש רב ואב״ד של ונציה עד סוף ימיו, והיה מראשי הלוחמים באיטליה במשיחיותו של שבתי צבי. נודע בספר תשובותיו ״דבר שמואל״ ובספר ״הזכרונות״.</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>הוא ביקש להשיב את העם אל קיום ההלכה: ב״ספר הזכרונות״, שנדפס בעילום שם, הוכיח על איסורים שרגילים לזלזל בהם, כמו ״סתם יינם״ ושעטנז, בימים שבהם יהדות איטליה הייתה פרוצה ליחסים קרובים עם תושביה הגויים. בתשובותיו לא חתם בשמו מתוך ענווה אלא צירף את שמות חכמי הישיבה.</t>
+        </is>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>רבי יעקב חגיז, רבי משה זכות (הרמ״ז)</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>רבי יונה לנדסופר (בעל מעיל צדקה)</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>1678–1712</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>פראג</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, הלכות סת״ם</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>מעיל צדקה, בני יונה, כנפי יונה, מאורי אור, רבי אברהם ברודא, שיעור הגריס, סופר סת״ם, הנדסה, המהר״ל מפראג</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>רב ופוסק, מגדולי רבני בוהמיה, יליד פראג, שנפטר בגיל צעיר ובכל זאת עשה רושם גדול בעולם ההלכה עוד בחייו. היה סופר סת״ם במקצועו ורכש לעצמו ידע רחב במדעים. שלושה מספריו הרבים נדפסו לאחר מותו: שו״ת ״מעיל צדקה״, שעל שמו כונה, ״בני יונה״ על הלכות ספר תורה ו״כנפי יונה״ על יורה דעה.</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>הלכה שנשענת על ידע מדעי: ב״מעיל צדקה״ קבע את שיעור ה״גריס״ בדיני כתמים; לספר מצורף שרטוט בגודל אמיתי שמודדים לפיו, ובסופו קונטרס בהנדסה, מלוקט מדברי אוקלידס, שכתב בתשובה לשאלה שנשאל מחכמי ההנדסה בדורו. ב״בני יונה״, שמעמדו כספר יסוד בהלכה, פסק שאין נמנעים מלקרוא בחומשים שנדפסו בידי גויים.</t>
+        </is>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>המהר״ל מפראג</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>רבי נתנאל וייל (בעל קרבן נתנאל)</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>1687–1769</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>פראג; קרלסרוהה</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, פירוש לפסקי הרא״ש, ראשות ישיבה</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>קרבן נתנאל, פסקי הרא״ש, נתיב חיים, תורת נתנאל, מגן אברהם, רבי אברהם ברודא, קרלסרוהה, פראג, מהר״י וייל, גירוש יהודי בוהמיה</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>ראש ישיבה בפראג ורב קרלסרוהה, יליד שטילינגן שבגרמניה, שלמד בישיבתו של רבי אברהם ברודא. לאחר גירוש יהודי בוהמיה ב־1744 עבר לגרמניה, ובשנת 1750 נתמנה לרבה של קרלסרוהה, ושם סיים את ״קרבן נתנאל״ על פסקי הרא״ש, שנדפס ב־1755. חיבר גם את ״נתיב חיים״ על שולחן ערוך אורח חיים ואת ״תורת נתנאל״, שו״ת ודרשות.</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>ביאור לפסקי הרא״ש שמשלים את החסר: סדרי מועד ונשים נותרו בלי ביאור, והוא חיבר עליהם את ״קרבן נתנאל״, שבו הוא מפרש את דברי הרא״ש, מברר את גרסאותיו ומביא מקורות לדבריו. הפירוש נדפס בצמוד לפסקי הרא״ש בש״ס וילנא.</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>מהר״י וייל</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>666</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>רבי חייא רופא (בעל מעשה חייא)</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>כ־1550–1617</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>צפת; טבריה; ירושלים</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, קבלה, ראשות ישיבה</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>מעשה חייא, צפת, טבריה, רבי שלמה סאגיש, רבי חיים ויטאל, האר״י, סמיכה בצפת, תיקון ליל שבועות, חכמי בית הוועד</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>פוסק ומקובל, מרבני צפת וירושלים, יליד צפת. למד בישיבתו של רבי שלמה סאגיש וקבלה אצל רבי חיים ויטאל, וקיבל גם מהאר״י, ובגיל עשרים ושלוש כיהן כדיין בבית דינו של רבי משה גלאנטי הראשון. הקים ישיבה בטבריה, כיהן כאב בית דין בירושלים וכראש ישיבה בצפת, ותשובותיו וחידושיו על הש״ס נדפסו בספר ״מעשה חייא״.</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>קבלה ופסיקה יחד: את הקבלה למד מרבי חיים ויטאל וקיבל גם מהאר״י, לימד אותה לתלמידיו, ובתיקון ליל שבועות של הרמ״ז מובאת כוונה שהגיעה אל הרמ״ז ממנו דרך רבי בנימין הלוי. בצפת היה מראשי הרבנים ומעשרים ״חכמי בית הוועד״, ורבי משה גלאנטי הראשון כתב בתשובותיו שהנהגת בית המדרש בעיר תהיה על פיו ועל פי חכמים נוספים.</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>רבי חיים ויטאל, האר״י הקדוש, רבי משה זכות (הרמ״ז)</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>רב פלטוי גאון</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>842–858 (ראש ישיבת פומבדיתא)</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>פומבדיתא</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>גאונים</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>הלכה ותשובות הגאונים, הנהגת ישיבה</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>ישיבת פומבדיתא, תשובות הגאונים, רב צמח בן פלטוי, רב שרירא גאון, רב האי גאון, תקנות, ערכאות של גויים, נוסח החרם, יהדות ספרד</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>רב פלטוי בר אביי היה גאון ישיבת פומבדיתא בשנים 842–858, ואחד הגאונים הפעילים ביותר שהקימה הישיבה. הוא התמנה בגיל צעיר יחסית ובלי מחלוקות, אף שלא בא ממשפחה מיוחסת, והשיב יותר תשובות הלכתיות מכל גאוני פומבדיתא שקדמו לו. בנו רב צמח בן פלטוי היה אף הוא גאון, ומצאצאיו רב שרירא גאון ובנו רב האי גאון.</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>גאון שחיבר את הישיבה אל הגולה: הוא יצר וביסס קשרים עם התפוצות במערב ובמיוחד עם ספרד, ולדברי אחד החוקרים הגביר את הפצת התלמוד והוראתו יותר מכל גאוני פומבדיתא שקדמו לו, ותיקן תקנות חשובות במשפט, ובהן היתר לפנות לערכאות של גויים כשהנתבע מסרב לידון בבית הדין היהודי.</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>רב שרירא גאון, רב האי גאון</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>668</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>רבי יעקב הלוי ממרויש (בעל שו״ת מן השמים)</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>המאה ה־13 (נפטר 1233)</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>פרובנס</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, קבלה</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>שו״ת מן השמים, שאילת חלום, מרויש, פרובנס, התבודדות, הרדב״ז, רבי יעקב החסיד, הכרעה בין הפוסקים</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>רב ומקובל מחכמי יהדות פרובנס בתקופת הראשונים, בנו של רבי לוי, שנפטר בשנת 1233. התגורר במרויש, שימש כפוסק, כונה בעבר ״החסיד״ או ״הקדוש״, ולדברי הרדב״ז, שהיו בידיו קצת מתשובותיו, היה ״חכם גדול מקובל״. נודע בחיבורו ״שו״ת מן השמים״, שבו שאל את שאלותיו ההלכתיות מן השמים.</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>ההכרעה ההלכתית נשענת גם על שאלה מן השמים: כשהלכה הייתה מסופקת לו, שאל, לפי הרדב״ז, בהתבודדות, בתפילה ובהזכרת שמות, והיו משיבים לו. שאלותיו נשאלו בדרך של שאלת חלום, כשאלות לבית דין של מעלה, כדי להכריע בין הפוסקים.</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr"/>
+      <c r="L669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>רבי אברהם סבע (בעל צרור המור)</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>1440–1508</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>קסטיליה; פורטוגל; פאס; אדריאנופול</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>פרשנות התורה, קבלה והגות</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>צרור המור, אשכול הכופר, צרור החיים, תפארת בנים, גירוש ספרד, שמד פורטוגל, רבי יצחק די ליאון, פאס, אדריאנופול, פשט</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>רב, מקובל ופרשן מדור גירוש ספרד, יליד קסטיליה ותלמידו של רבי יצחק די ליאון. בגזירות השמד בפורטוגל ב־1497 נחטפו שני ילדיו והוטבלו לנצרות, והוא עצמו נאסר ועונה ונמלט לפאס שבמרוקו. את ספריו קבר בפורטוגל וכתב מחדש מזיכרונו, ובהם ״צרור המור״ על התורה ו״אשכול הכופר״ על רות ואסתר; הוא נפטר בדרכו לאיטליה בשנת 1508.</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>פירושו לתורה ״צרור המור״ מצרף פשט, דרוש וקבלה בביאור אחד. הוא גם עדות אישית לגירוש ספרד ולשמד פורטוגל: בפרשת ויצא מגולל סבע את תלאותיו בקונטרס ״תפארת בנים״.</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>רבי יוסף קארו</t>
+        </is>
+      </c>
+      <c r="L670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>רבי אליעזר אשכנזי (בעל מעשי ה׳)</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>כ־1513–1585</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>קהיר; ונציה; פוזנא; קרקוב</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>פרשנות המקרא, פילוסופיה והלכה</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>מעשי ה׳, יוסף לקח, פירוש ההגדה של פסח, פשוטו של מקרא, סליחות ופזמונים, רבי יוסף טאיטצאק, קפריסין, קרימונה, פוזנא, קרקוב</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>רב, פרשן מקרא, פייטן ופילוסוף, ככל הנראה יליד ונציה, שלמד בסלוניקי אצל רבי יוסף טאיטצאק. שימש דיין בקהיר, חי בקפריסין ובאיטליה, ולבסוף היה רב העיר ורב המדינה בפוזנא ועבר לקרקוב, שבה נפטר ב־1585. ספרו העיקרי ״מעשי ה׳״ הוא פירוש לחמשה חומשי תורה ובתוכו פירוש להגדה של פסח, והוא חיבר גם את ״יוסף לקח״ על מגילת אסתר.</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>כפרשן דבק בפשוטו של מקרא, אך אינו נרתע מלחלוק על רש״י, האבן עזרא, הרמב״ם והרמב״ן ולהציע פירושים עצמאיים. בהקדמתו כתב שהוא מקבל את הטוב ודוחה את הרע בלי להתחשב בשם האומר.</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>רבי יוסף טאיטצאק</t>
+        </is>
+      </c>
+      <c r="L671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>רבי משה גלאנטי (המג״ן)</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>כ־1620–1689</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>ירושלים; צפת</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>הלכה, מנהיגות ופרשנות</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>אלף המגן, זבח השלמים, קרבן חגיגה, פרפראות לחכמה, הראשון לציון, שד״ר, כספי החלוקה, ישיבת בית יעקב, רבי משה גלאנטי הראשון, רבי משה חגיז</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>הראשון לציון הראשון וראש רבני ירושלים במאה ה־17, שכונה לעיתים ״המג״ן״, יליד צפת ונכד רבי משה גלאנטי הראשון. למד בצפת אצל רבי ברוך ברזילי ורבי גבריאל איספיראנסה, ובגיל 34 עבר לירושלים, שם עמד בראש ישיבת בית יעקב ונשלח כשד״ר לחוץ לארץ. חיבר את ״אלף המגן״, אוסף שו״ת ובו אלף תשובות, ואת ״זבח השלמים״ על התורה, ונפטר בירושלים ב־1689.</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>הסכים להתמנות לרבה של ירושלים רק בתואר שאינו שררתי, ״ראשון לציון״ ולא ״רב״, כי ראה את עצמו שווה בין שווים בגדלותו בתורה. הוא תיקן לחלק את כספי החלוקה לעשרים וארבעה חלקים: שנים־עשר לירושלים, שמונה לצפת וארבעה לחברון.</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>רבי משה חגיז, רבנו חזקיה די סילוה, הרב אברהם יצחקי</t>
+        </is>
+      </c>
+      <c r="L672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>רבי אברהם גלאנטי (בעל קול בוכים)</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>תחילת המאה ה־16 – 1560</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>צפת; רומא</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>קבלה ופרשנות</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>קינת סתרים, קול בוכים, ירח יקר, זכות אבות, הרמ״ק, הזוהר, מגילת איכה, זהרי חמה, אור יקר, צפת</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>מקובל, יליד רומא בתחילת המאה ה־16, שעלה לצפת והיה מתלמידי הרמ״ק. כמו אביו מרדכי ואחיו המבוגר ממנו, רבי משה גלאנטי הראשון, חי חיי סגפנות וקדושה. חיבר את ״קינת סתרים״ (״קול בוכים״), פירוש קבלי למגילת איכה שהודפס בוונציה ב־1589 בעריכת בנו שמואל, את ״ירח יקר״ על הזוהר ואת ״זכות אבות״ על מסכת אבות, ונפטר ב־1560.</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>פירושו לזוהר, ״ירח יקר״, נקרא כך על שם ״אור יקר״ של רבו הרמ״ק, כמאמר ״פני משה כפני חמה״, ורבי אברהם אזולאי קיצר אותו ב״זהרי חמה״. את מגילת איכה פירש ״על דרך האמת״, כלומר בקבלה, ב״קינת סתרים״ שהודפס כמה פעמים.</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>רבי משה קורדובירו (הרמ״ק), רבי אברהם אזולאי</t>
+        </is>
+      </c>
+      <c r="L673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>רבי יעקב קשטרו (מהריק״ש)</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>כ־1525–1612</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>קהיר; אלכסנדריה; ירושלים</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>ערך לחם, אהלי יעקב, תולדות יעקב, קול יעקב, מרא דאתרא, הרדב״ז, המהרלב״ח, שולחן ערוך, קהיר, יהדות מצרים</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>מרבניה הנודעים של יהדות מצרים, יליד מצרים בסביבות 1525, ששימש כרבו של קהל המוסתערבים בקהיר. למד בירושלים אצל הרלב״ח, אך רבו המובהק היה הרדב״ז, ובמצרים ראו בו גדול הדור, ״מרא דאתרא״. נתפרסם בעיקר בספרו ״ערך לחם״, הגהות על השולחן ערוך, וחיבר גם את שו״ת ״אהלי יעקב״; ככל הנראה נפטר בקהיר ב־1610 או ב־1612.</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>ב״ערך לחם״ הגיה את השולחן ערוך, והגהותיו תואמות פעמים רבות את הגהות הרמ״א. הספרדים בכל ארץ מצרים פסקו כמותו גם במקום שחלק על מרן הבית יוסף.</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>הרדב״ז, רבי לוי בן חביב (המהרלב״ח)</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>רבי חיים כפוסי (בעל הנס)</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>כ־1540–1631</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>קהיר; אלכסנדריה; אלג׳יר</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, פרשנות התורה</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>ספרי חיים, באור החיים, בעל הנס, מכילתא דרשב״י, קהיר, אלכסנדריה, דמיאט, אלג׳יר, יהדות מצרים, המהריק״ש</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>פוסק הלכה ופרשן, מגדולי חכמי מצרים במאות ה־16 וה־17, יליד אלג׳יר למשפחה שמוצאה מספרד. חייו היו מלאי סבל ונדודים בין קהיר, אלכסנדריה ודמיאט, ולפי אגדה נפקחו עיניו בנס אחרי שלקה בעיוורון, ומאז כונה ״בעל הנס״. תשובותיו נשארו בכתב יד מאות שנים; חיבר גם את ״באור החיים״ על התורה ואת ״ספרי חיים״ על המכילתא, ונפטר ב־1631.</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>תשובותיו משקפות את חיי היהודים במצרים ובאימפריה העות׳מאנית במשך יותר מ־60 שנה, ובהן מחלוקות הלכתיות עם רבה של מצרים, המהריק״ש. בביאורו לתורה, ״באור החיים״, הוא מפרש בדרך פשט ורמז.</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr"/>
+      <c r="L675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>רבי שמואל ויטאל (בן רבי חיים)</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>1598–1677</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>דמשק; מצרים</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>קבלה והלכה</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>שער הגלגולים, כתבי האר״י, שמונה שערים, באר מים חיים, מקור חיים, תוצאות חיים, חמדת ישראל, דמשק, קבלת האר״י, רבי חיים ויטאל</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>מרבני ומקובלי דמשק ובנו של רבי חיים ויטאל: נולד בדמשק, שימש בה רב ודיין והקים ישיבה גדולה שלמדו בה גם קבלה. היה מגדולי תלמידי אביו, העתיק וסידר את כתבי אביו ואת כתבי האר״י, ובהם ״שער הגלגולים״, ובהמשך חייו עבר למצרים והקים שם ישיבה. כתב תשובות בהלכה ובקבלה ודרשות לראש חודש, ונפטר במצרים ב־1677.</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>כמעתיק ומסדר של כתבי אביו ושל כתבי האר״י שימר את תורת האר״י, וספריו נחשבו, כפי שכתב החיד״א, למדויקים והמוסמכים ביותר לכתבי קבלת האר״י. את תשובותיו בהלכה ובקבלה כתב לשואלים ממצרים, מארץ ישראל ומרחבי סוריה.</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>רבי חיים ויטאל</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>רבי אהרן שמואל קאיידנובר (המהרש״ק)</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>1614–1676</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>קרקוב; בריסק; פרנקפורט</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>הלכה ופרשנות התלמוד</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>ברכת הזבח, תפארת שמואל, אמונת שמואל, ברכת שמואל, סדר קדשים, גזירות ת״ח ת״ט, פסקי הרא״ש, המהרש״א, בריסק, קרקוב</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>רב אשכנזי מראשוני האחרונים, שנולד ככל הנראה בקוידנוב שבבלארוס, למד אצל רבי יעקב מלובלין ואחר כך אצל בנו והיה דיין בבית דינו של רבי משה לימא. בגזירות ת״ח ת״ט נרצחו שתי בנותיו ואבדו רוב כתביו, ולאחר מכן כיהן ברבנות בערים רבות, בהן בריסק, פרנקפורט וקרקוב. חיבר את ״ברכת הזבח״ על סדר קדשים ואת ״תפארת שמואל״ על פסקי הרא״ש ואת שו״ת ״אמונת שמואל״, ונפטר ב־1676.</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>כתב ״בדרך קצרה וכשרה״, כלשון החיד״א. הגהותיו על הרא״ש והשגותיו על המהרש״א נדפסו בתוך הש״ס בכל מהדורותיו עד ש״ס וילנה, והמגן אברהם קורא לו ״גאון״. הוא התנגד לפסוק לפי השולחן ערוך ונושאי כליו ותמך בפסיקה לפי ארבעה טורים עם הבית יוסף.</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>רבי אברהם אבלי גומבינר (המגן אברהם)</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>677</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>רבי יהודה בן עטר (בעל מנחת יהודה)</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>1655–1733</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>פאס; מקנס</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>הלכה, דרשנות ופרשנות המקרא</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>מנחת יהודה, שיר מכתם, דרשנות, תקנות הקהילה, צורף, פאס, מקנס, יהדות מרוקו</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>אב בית דין ודיין בפאס ובמקנס שבמרוקו, פרשן מקרא ומרבניה הגדולים של המדינה, יליד פאס. התפרנס כצורף מיגיע כפיו ולא רצה שכר מקופת הציבור, למד מרבי וידאל הצרפתי השלישי ומרבי מנחם סירירו, ובשנת 1698 מונה לדיין בפאס. חיבר את ״מנחת יהודה״, דרשות על התורה, ואת ״שיר מכתם״ על הלכות שחיטה, ונפטר ב־1733.</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>ראה שתלמידיו, על גדלותם בתורה, אינם יודעים לדרוש, ולימד אותם נאום ודרוש: ״מנחת יהודה״ מקורו בדרשות שבת במנחה, שאחריהן דרש תלמיד אחר. כל חייו התפרנס מיגיע כפיו, ותיקן לקהילתו תקנות במיסים, במסחר ובהלוואות מגויים.</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr"/>
+      <c r="L678" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>רבי מנחם ציוני (בעל ספר ציוני)</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>כ־1340–1410</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>שפיירא; קלן; ירושלים; ונציה; גרמניה</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>קבלה, פיוט ופרשנות התורה</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>ציוני, צפוני ציוני, ספר הבהיר, הזוהר, הרמב״ן, קינות, ציון מעון חשקי, רבי יצחק מבילשטיין, שפיירא, קרימונה</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>מקובל ופייטן מחכמי אשכנז, יליד שפיירא, שנסע בצעירותו לירושלים ולמד בישיבתו של רבי יצחק מבילשטיין. הוא האדם הראשון הידוע שבחר לכנות עצמו ״ציוני״, על שם לימודיו בירושלים. חיבר את הספר ״ציוני״ על התורה, שנדפס בקרימונה ב־1559, ואת ״צפוני ציוני״, וכתב עשרות שירים.</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>ספרו ״ציוני״ מצרף את הזוהר וספר הבהיר עם דברי הראשונים, כסעדיה גאון, הרמב״ם, אבן עזרא והרמב״ן, לפירוש התורה ״על דרך האמת״, ובראשי פרקיו ובסופיהם חרוזים ובפתיחתו ובסיומו שירים. החיד״א שיבח אותו ב״שם הגדולים״, וגדולי האחרונים כהשל״ה והמגן אברהם הביאו דברים בשמו.</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>רבי יוסף שלמה דלמדיגו – יש״ר מקנדיה, רבי ישעיה הלוי הורוויץ (השל״ה הקדוש), רבי אברהם אבלי גומבינר (המגן אברהם)</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>רבי אליהו בחור (בעל מסורת המסורת)</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>1469–1549</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>גרמניה; ונציה; פדובה; רומא</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>דקדוק עברי, מסורה ומילונאות</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>הבחור, התשבי, מסורת המסורת, טוב טעם, המתורגמן, סבסטיאן מינסטר, פאולוס פאגיוס, אג׳ידיו דה ויטרבו, ספרות יידיש, מלומדים נוצרים</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>בלשן עברי וחוקר המסורה בתקופת הרנסאנס, יליד נוישטאדט שבבוואריה, שעבר בצעירותו לאיטליה והתגורר בוונציה, בפדובה וברומא. לימד עברית למלומדים נוצרים, עבד כמגיה בבית דפוס בוונציה ופיקח על בית דפוס באיזנא וחיבר ספרי דקדוק ומילונים, ובהם ״הבחור״ ו״התשבי״, וכן את ״מסורת המסורת״ ו״טוב טעם״. מת בוונציה ב־1549.</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>בספרו ״מסורת המסורת״ טען שסימני הניקוד והטעמים חודשו בידי בעלי המסורה ואינם מזמן התלמוד, דעה שהחיד״א מביא ומסתייג ממנה. בספריו ובהוראתו הנחיל את הדקדוק העברי למלומדים נוצרים, שתרגמו את חיבוריו ללטינית.</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr"/>
+      <c r="L680" t="inlineStr"/>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L680"/>
+  <dimension ref="A1:L697"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="3" min="1" max="1"/>
@@ -38162,2884 +38162,3768 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" t="inlineStr">
+      <c r="A631" s="3" t="inlineStr">
         <is>
           <t>630</t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C631" t="inlineStr">
+      <c r="B631" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C631" s="3" t="inlineStr">
         <is>
           <t>רבי משה אלשיך (האלשיך הקדוש)</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr">
+      <c r="D631" s="3" t="inlineStr">
         <is>
           <t>כ־1507–1600</t>
         </is>
       </c>
-      <c r="E631" t="inlineStr">
+      <c r="E631" s="3" t="inlineStr">
         <is>
           <t>צפת; אדריאנופול</t>
         </is>
       </c>
-      <c r="F631" t="inlineStr">
+      <c r="F631" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G631" t="inlineStr">
+      <c r="G631" s="3" t="inlineStr">
         <is>
           <t>דרשנות ופרשנות המקרא, הלכה ושו״ת</t>
         </is>
       </c>
-      <c r="H631" t="inlineStr">
+      <c r="H631" s="3" t="inlineStr">
         <is>
           <t>תורת משה, האלשיך הקדוש, רבי יוסף קארו, רבי חיים ויטאל, מראות הצובאות, שושנת העמקים, שו״ת מהר״ם אלשיך, שד״ר, דרשות שבת</t>
         </is>
       </c>
-      <c r="I631" t="inlineStr">
+      <c r="I631" s="3" t="inlineStr">
         <is>
           <t>דרשן, פרשן ופוסק בצפת, הנודע בכינוי ״האלשיך הקדוש״. נולד באדריאנופול ולמד בישיבת רבי יוסף קארו ובישיבת רבי יוסף טאיטצאק בסלוניקי, עלה לצפת ועמד בראש שתי ישיבות, ורבי חיים ויטאל היה תלמידו. חיבר את ״תורת משה״ על התורה, פירושים לנביאים, למגילות ולחלק מהכתובים, וקובץ שו״ת.</t>
         </is>
       </c>
-      <c r="J631" t="inlineStr">
+      <c r="J631" s="3" t="inlineStr">
         <is>
           <t>פירושיו צמחו מדרשות שנשא מדי שבת: בראש כל יחידה הוא מעלה שאלות וקשיים בלשון הכתוב, ובסופה משיב על כולם בזה אחר זה. בכל פסוק ובכל מילה הוא מבקש לקח מוסרי וחיזוק באמונה, ודבריו נלמדים עד היום.</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr">
+      <c r="K631" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף קארו, רבי יוסף טאיטצאק, רבי חיים ויטאל</t>
         </is>
       </c>
-      <c r="L631" t="inlineStr">
+      <c r="L631" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/7xXl4sOy18MABmQdtXzrQu</t>
         </is>
       </c>
     </row>
     <row r="632">
-      <c r="A632" t="inlineStr">
+      <c r="A632" s="3" t="inlineStr">
         <is>
           <t>631</t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C632" t="inlineStr">
+      <c r="B632" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C632" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל די אוזידא (בעל מדרש שמואל)</t>
         </is>
       </c>
-      <c r="D632" t="inlineStr">
+      <c r="D632" s="3" t="inlineStr">
         <is>
           <t>1545–1604</t>
         </is>
       </c>
-      <c r="E632" t="inlineStr">
+      <c r="E632" s="3" t="inlineStr">
         <is>
           <t>צפת; קושטא</t>
         </is>
       </c>
-      <c r="F632" t="inlineStr">
+      <c r="F632" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G632" t="inlineStr">
+      <c r="G632" s="3" t="inlineStr">
         <is>
           <t>דרשנות, פרשנות משנה ומקרא, קבלה</t>
         </is>
       </c>
-      <c r="H632" t="inlineStr">
+      <c r="H632" s="3" t="inlineStr">
         <is>
           <t>מדרש שמואל, פרקי אבות, האר״י, רבי חיים ויטאל, לחם דמעה, אגרת שמואל, ישיבת צפת, שיטה מקובצת, שליחות לקושטא</t>
         </is>
       </c>
-      <c r="I632" t="inlineStr">
+      <c r="I632" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבה, מקובל ודרשן, יליד צפת ומתלמידיו הראשונים של האר״י, שאחרי פטירתו המשיך ללמוד קבלה אצל רבי חיים ויטאל. ייסד בצפת ישיבה גדולה שעסקו בה בנגלה ובנסתר, ויצא לשליחות בקושטא. נודע בחיבורו ״מדרש שמואל״ על פרקי אבות, שנדפס לראשונה בוונציה בשנת 1579, וכתב גם פירושים למגילות איכה ורות.</t>
         </is>
       </c>
-      <c r="J632" t="inlineStr">
+      <c r="J632" s="3" t="inlineStr">
         <is>
           <t>״מדרש שמואל״ הוא ליקוט פרשני: מעין ״שיטה מקובצת״ לפירושים אחרים על אבות, בתוספת דרשותיו שלו, ולכן שימר גם פירושים שאינם בידינו כיום. אף שהיה מתלמידי האר״י, עסק בספריו בעיקר בדרש ולא בקבלה, והשתמש בתובנות קבליות כתשתית סמויה לדברי מוסר שנועדו לכלל הציבור.</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr">
+      <c r="K632" s="3" t="inlineStr">
         <is>
           <t>האר״י הקדוש, רבי חיים ויטאל</t>
         </is>
       </c>
-      <c r="L632" t="inlineStr">
+      <c r="L632" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/6Umixwtvl1Jh3iq0E1sCHW</t>
         </is>
       </c>
     </row>
     <row r="633">
-      <c r="A633" t="inlineStr">
+      <c r="A633" s="3" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C633" t="inlineStr">
+      <c r="B633" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C633" s="3" t="inlineStr">
         <is>
           <t>רבי משה מטראני (המבי״ט)</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr">
+      <c r="D633" s="3" t="inlineStr">
         <is>
           <t>כ־1500–1580</t>
         </is>
       </c>
-      <c r="E633" t="inlineStr">
+      <c r="E633" s="3" t="inlineStr">
         <is>
           <t>צפת; סלוניקי</t>
         </is>
       </c>
-      <c r="F633" t="inlineStr">
+      <c r="F633" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G633" t="inlineStr">
+      <c r="G633" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, הגות ומוסר</t>
         </is>
       </c>
-      <c r="H633" t="inlineStr">
+      <c r="H633" s="3" t="inlineStr">
         <is>
           <t>קרית ספר, בית אלהים, שו״ת המבי״ט, רבי יעקב בירב, רבי יוסף קארו, פרק שירה, משנה תורה, בית הדין בצפת</t>
         </is>
       </c>
-      <c r="I633" t="inlineStr">
+      <c r="I633" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבה, דיין ופוסק, מחכמי צפת במאה ה־16. נולד בסלוניקי, למד באדריאנופול אצל דודו רבי אהרן מטראני, עלה לצפת והיה תלמידו המובהק של רבי יעקב בירב, ויותר מחמישים שנה ישב בבית הדין בעיר. חיבר את ״קרית ספר״ על ״משנה תורה״ לרמב״ם, את ״בית אלהים״ ושני כרכי תשובות שנדפסו אחרי מותו.</t>
         </is>
       </c>
-      <c r="J633" t="inlineStr">
+      <c r="J633" s="3" t="inlineStr">
         <is>
           <t>ב״קרית ספר״ הוא בירר בכל דין ב״משנה תורה״ אם הוא מן התורה, ממידות שהתורה נדרשת בהן, מהלכה למשה מסיני או מדברי חכמים ותקנותיהם. ב״בית אלהים״ הוא ביאר את יסודות הדת בשערי התפילה, התשובה והעיקרים, ולספר צורף גם הפירוש הראשון שנדפס על פרק שירה.</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr">
+      <c r="K633" s="3" t="inlineStr">
         <is>
           <t>מהר״י בירב (רבי יעקב בירב), רבי יוסף מטראני (המהרי״ט)</t>
         </is>
       </c>
-      <c r="L633" t="inlineStr">
+      <c r="L633" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/0V7vkwok6itxSw9niOhmW0</t>
         </is>
       </c>
     </row>
     <row r="634">
-      <c r="A634" t="inlineStr">
+      <c r="A634" s="3" t="inlineStr">
         <is>
           <t>633</t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C634" t="inlineStr">
+      <c r="B634" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C634" s="3" t="inlineStr">
         <is>
           <t>רבי חזקיה בן מנוח (החזקוני)</t>
         </is>
       </c>
-      <c r="D634" t="inlineStr">
+      <c r="D634" s="3" t="inlineStr">
         <is>
           <t>כ־1250–1310</t>
         </is>
       </c>
-      <c r="E634" t="inlineStr">
+      <c r="E634" s="3" t="inlineStr">
         <is>
           <t>צרפת</t>
         </is>
       </c>
-      <c r="F634" t="inlineStr">
+      <c r="F634" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G634" t="inlineStr">
+      <c r="G634" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא</t>
         </is>
       </c>
-      <c r="H634" t="inlineStr">
+      <c r="H634" s="3" t="inlineStr">
         <is>
           <t>החזקוני, פירוש לתורה, פשט, רש״י, רבי יוסף בכור שור, רשב״ם, אבן עזרא, מנחת יהודה</t>
         </is>
       </c>
-      <c r="I634" t="inlineStr">
+      <c r="I634" s="3" t="inlineStr">
         <is>
           <t>רב ופרשן מקרא צרפתי מהמאה ה־13, שנודע על שם ספרו ״החזקוני״ על חמשה חומשי תורה. פרטי חייו המדויקים אינם ידועים, ומקובל להעריך שנולד בצרפת בסביבות 1250 ונפטר בסביבות 1310. פירושו נדפס לראשונה בוונציה בשנת ה׳רפ״ד, בתוך חמישה חומשי תורה עם רש״י, ובהקדמתו הוא מבקש מקוראיו שיזכרו אותו ויחזקוהו.</t>
         </is>
       </c>
-      <c r="J634" t="inlineStr">
+      <c r="J634" s="3" t="inlineStr">
         <is>
           <t>פירושו הוא ליקוט מכוון: אחרי ששוטט במדינות רבות בחיפוש אחר פירושים ישרים לתורה, הוא הוציא את המיטב מעשרים חיבורים, ובהם רש״י, רשב״ם ואבן עזרא, ובדרך כלל אינו מציין את שמות מקורותיו. הוא נוטה לדרך הפשט הריאלית של רבי יוסף בכור שור, ומביא ממנו גם קטעי הגות בטעמי המצוות.</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr">
+      <c r="K634" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף בכור שור, רש״י (רבי שלמה יצחקי), הרשב״ם, אברהם אבן עזרא</t>
         </is>
       </c>
-      <c r="L634" t="inlineStr">
+      <c r="L634" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/6VBVggnMCgZu86mq2JMniv</t>
         </is>
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr">
+      <c r="A635" s="3" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
+      <c r="B635" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C635" s="3" t="inlineStr">
         <is>
           <t>הרב יוסף בא-גד</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr">
+      <c r="D635" s="3" t="inlineStr">
         <is>
           <t>נולד ב־1932</t>
         </is>
       </c>
-      <c r="E635" t="inlineStr">
+      <c r="E635" s="3" t="inlineStr">
         <is>
           <t>פתח תקווה; ירושלים</t>
         </is>
       </c>
-      <c r="F635" t="inlineStr">
+      <c r="F635" s="3" t="inlineStr">
         <is>
           <t>העת החדשה</t>
         </is>
       </c>
-      <c r="G635" t="inlineStr">
+      <c r="G635" s="3" t="inlineStr">
         <is>
           <t>לימוד התלמוד, חינוך תורני</t>
         </is>
       </c>
-      <c r="H635" t="inlineStr">
+      <c r="H635" s="3" t="inlineStr">
         <is>
           <t>ש״ס בש״ס, שיטת הסוגיות, ישיבת נחלים, נחל יצחק, אוגדן הסוגיות, נחלי לימוד, תלמוד בבלי וירושלמי, תורה ומדע</t>
         </is>
       </c>
-      <c r="I635" t="inlineStr">
+      <c r="I635" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבה ומחבר ספרי לימוד, יליד מוצא תחתית (1932). למד בישיבות כפר הרוא״ה, היישוב החדש וחברון, ובשנת 1955 ייסד את הישיבה התיכונית ״נחל יצחק״ בנחלים, שבראשה עמד עד 2004 ושבה הוא משמש מאז נשיא הישיבה. פיתח את שיטת הלימוד ״ש״ס בש״ס״, המכונה גם ״שיטת הסוגיות״, וחיבר את ״אוגדן הסוגיות״ ו״נחלי לימוד״, שזכו בפרס הרב טולידאנו; בשנים 1992–1996 היה גם חבר הכנסת.</t>
         </is>
       </c>
-      <c r="J635" t="inlineStr">
+      <c r="J635" s="3" t="inlineStr">
         <is>
           <t>שיטתו מלמדת תלמוד לפי סוגיות ולא לפי סדר הדפים: כל סוגיה נבחנת בבבלי ומיד אחריה מובאת מקבילתה מהירושלמי, תוך הצלבת מקורות ושילוב תורה ומדע. בחינוך הוא דגל בלמידה עצמאית, ביום לימודים ארוך, באישיות תורנית כמחנך הכיתה ובשילוב הרגש והשכל, והמליץ להעתיק מרכיבים אלה אל בתי הספר הדתיים.</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr">
+      <c r="K635" s="3" t="inlineStr">
         <is>
           <t>הרב אברהם יצחק הכהן קוק</t>
         </is>
       </c>
-      <c r="L635" t="inlineStr"/>
+      <c r="L635" s="3" t="inlineStr"/>
     </row>
     <row r="636">
-      <c r="A636" t="inlineStr">
+      <c r="A636" s="3" t="inlineStr">
         <is>
           <t>635</t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
+      <c r="B636" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C636" s="3" t="inlineStr">
         <is>
           <t>רבי עובדיה ספורנו</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr">
+      <c r="D636" s="3" t="inlineStr">
         <is>
           <t>כ־1470–1549</t>
         </is>
       </c>
-      <c r="E636" t="inlineStr">
+      <c r="E636" s="3" t="inlineStr">
         <is>
           <t>בולוניה; רומא</t>
         </is>
       </c>
-      <c r="F636" t="inlineStr">
+      <c r="F636" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G636" t="inlineStr">
+      <c r="G636" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא, הגות ורפואה</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr">
+      <c r="H636" s="3" t="inlineStr">
         <is>
           <t>ספורנו, ביאור לתורה, כוונות התורה, אור עמים, פשט, בולוניה, רופא, פרקי אבות</t>
         </is>
       </c>
-      <c r="I636" t="inlineStr">
+      <c r="I636" s="3" t="inlineStr">
         <is>
           <t>פרשן מקרא, רב ורופא איטלקי, יליד צ׳זנה, מראשי קהילת רומא וקהילת בולוניה, שבה יסד בית דפוס עברי ושימש רופא. חיבורו החשוב והנפוץ ביותר הוא ביאורו לתורה, והוא חיבר גם פירושים לתהילים, לשיר השירים, לקהלת, לאיוב ולפרקי אבות, ואת הספר הפילוסופי ״אור עמים״.</t>
         </is>
       </c>
-      <c r="J636" t="inlineStr">
+      <c r="J636" s="3" t="inlineStr">
         <is>
           <t>פירושו מבוסס על הפשט, בלשון קצרה ובהירה, והוא נכתב לעם ולא כדי להרשים משכילים. בהקדמה לפירושו לתורה הוא קובע שמטרת התורה להדריך את האדם באשר הוא אדם; הוא חוזר ומדגיש שהבחירה בישראל היא אחריות וחובה ולא זכות, וקושר את הידיעות המדעיות לתיקון המידות.</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr">
+      <c r="K636" s="3" t="inlineStr">
         <is>
           <t>רש״י (רבי שלמה יצחקי), אברהם אבן עזרא, הרשב״ם, הרמב״ן (רבי משה בן נחמן)</t>
         </is>
       </c>
-      <c r="L636" t="inlineStr"/>
+      <c r="L636" s="3" t="inlineStr"/>
     </row>
     <row r="637">
-      <c r="A637" t="inlineStr">
+      <c r="A637" s="3" t="inlineStr">
         <is>
           <t>636</t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C637" t="inlineStr">
+      <c r="B637" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C637" s="3" t="inlineStr">
         <is>
           <t>רבנו ירוחם בן משולם</t>
         </is>
       </c>
-      <c r="D637" t="inlineStr">
+      <c r="D637" s="3" t="inlineStr">
         <is>
           <t>כ־1290–1350</t>
         </is>
       </c>
-      <c r="E637" t="inlineStr">
+      <c r="E637" s="3" t="inlineStr">
         <is>
           <t>טולדו; פרובנס</t>
         </is>
       </c>
-      <c r="F637" t="inlineStr">
+      <c r="F637" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G637" t="inlineStr">
+      <c r="G637" s="3" t="inlineStr">
         <is>
           <t>הלכה ופסיקה</t>
         </is>
       </c>
-      <c r="H637" t="inlineStr">
+      <c r="H637" s="3" t="inlineStr">
         <is>
           <t>מישרים, תולדות אדם וחוה, הרא״ש, רבי אברהם בן אסמעאל, בית יוסף, שולחן ערוך, גירוש צרפת, דיני ממונות</t>
         </is>
       </c>
-      <c r="I637" t="inlineStr">
+      <c r="I637" s="3" t="inlineStr">
         <is>
           <t>רב ופוסק מגדולי הראשונים, שנולד בפרובנס ועבר לטולדו אחרי גירוש יהודי צרפת; פרטים בחייו שנויים במחלוקת. למד אצל הרא״ש ואחר כך אצל רבי אברהם בן אסמעאל, תלמיד הרשב״א והרא״ש, שהיה רבו המובהק. חיבר את ״מישרים״ על דיני ממונות ואת ״תולדות אדם וחוה״ על דינים הנוהגים בגלות, ושני החיבורים נודעים יחד בשם ״רבנו ירוחם״.</t>
         </is>
       </c>
-      <c r="J637" t="inlineStr">
+      <c r="J637" s="3" t="inlineStr">
         <is>
           <t>את ההלכה הנוהגת בגלות הוא ארגן ב״תולדות אדם וחוה״ לפי מהלך חייו של האדם: ב״אדם״ הדינים מלידתו ועד נישואיו, לצד ברכות, תפילות ומנהגים, וב״חוה״ מנישואיו ועד פטירתו. פסקיו מוזכרים פעמים רבות ב״בית יוסף״ והשפיעו על פסיקתו של רבי יוסף קארו בשולחן ערוך, ומתוך כך על הלכות רבות הנהוגות גם בימינו.</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr">
+      <c r="K637" s="3" t="inlineStr">
         <is>
           <t>רבנו אשר בן יחיאל (הרא״ש), רבי יוסף קארו</t>
         </is>
       </c>
-      <c r="L637" t="inlineStr"/>
+      <c r="L637" s="3" t="inlineStr"/>
     </row>
     <row r="638">
-      <c r="A638" t="inlineStr">
+      <c r="A638" s="3" t="inlineStr">
         <is>
           <t>637</t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
+      <c r="B638" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C638" s="3" t="inlineStr">
         <is>
           <t>רבי ברוך בן יצחק (בעל התרומה)</t>
         </is>
       </c>
-      <c r="D638" t="inlineStr">
+      <c r="D638" s="3" t="inlineStr">
         <is>
           <t>כ־1140–1211</t>
         </is>
       </c>
-      <c r="E638" t="inlineStr">
+      <c r="E638" s="3" t="inlineStr">
         <is>
           <t>פריז; ארץ ישראל</t>
         </is>
       </c>
-      <c r="F638" t="inlineStr">
+      <c r="F638" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G638" t="inlineStr">
+      <c r="G638" s="3" t="inlineStr">
         <is>
           <t>הלכה ופסיקה, תוספות</t>
         </is>
       </c>
-      <c r="H638" t="inlineStr">
+      <c r="H638" s="3" t="inlineStr">
         <is>
           <t>ספר התרומה, ר״י הזקן, בעלי התוספות, הלכות ארץ ישראל, עליית בעלי התוספות, בית המדרש הצרפתי, בית יוסף, תוספות על זבחים</t>
         </is>
       </c>
-      <c r="I638" t="inlineStr">
+      <c r="I638" s="3" t="inlineStr">
         <is>
           <t>תלמיד חכם ופוסק מבעלי התוספות ותלמידו המובהק של ר״י הזקן, שחי ופעל בצרפת, ובין היתר בפריז. נודע בכינוי בעל התרומה על שם ספרו ״ספר התרומה״, קובץ פסקי הלכה בלשון קצרה שנכתב בראשית המאה ה־13. לקראת פטירתו עלה לארץ ישראל, בתקופת עליית בעלי התוספות, ושם נפטר ונקבר.</t>
         </is>
       </c>
-      <c r="J638" t="inlineStr">
+      <c r="J638" s="3" t="inlineStr">
         <is>
           <t>ספרו הולך אחר בית המדרש הצרפתי: הוא פוסק הלכה בלשון קצרה במגוון נושאים, אינו עוסק במנהגי הקהילות ומסתיים במפתחות המסכמים את הפרקים. הוא כולל גם פרק מיוחד על ״הלכות ארץ ישראל״, ופוסקים רבים בססו עליו את פסיקתם; הבית יוסף מביא את דבריו רבות.</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr">
+      <c r="K638" s="3" t="inlineStr">
         <is>
           <t>ר״י הזקן מדמפייר, יעקב בן אשר, רבי יוסף קארו, רבי אלעזר מגרמייזא (בעל הרוקח)</t>
         </is>
       </c>
-      <c r="L638" t="inlineStr"/>
+      <c r="L638" s="3" t="inlineStr"/>
     </row>
     <row r="639">
-      <c r="A639" t="inlineStr">
+      <c r="A639" s="3" t="inlineStr">
         <is>
           <t>638</t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr">
+      <c r="B639" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C639" s="3" t="inlineStr">
         <is>
           <t>רבי יהושע פלק כ״ץ (הסמ״ע)</t>
         </is>
       </c>
-      <c r="D639" t="inlineStr">
+      <c r="D639" s="3" t="inlineStr">
         <is>
           <t>כ־1555–1614</t>
         </is>
       </c>
-      <c r="E639" t="inlineStr">
+      <c r="E639" s="3" t="inlineStr">
         <is>
           <t>קרקוב; לבוב</t>
         </is>
       </c>
-      <c r="F639" t="inlineStr">
+      <c r="F639" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G639" t="inlineStr">
+      <c r="G639" s="3" t="inlineStr">
         <is>
           <t>הלכה, פרשנות הטור, פרשנות השולחן ערוך</t>
         </is>
       </c>
-      <c r="H639" t="inlineStr">
+      <c r="H639" s="3" t="inlineStr">
         <is>
           <t>מאירת עינים, הסמ״ע, דרישה ופרישה, בית ישראל, ארבעה טורים, שולחן ערוך, המהרש״ל, הרמ״א, ישיבת לבוב, ועד ארבע הארצות</t>
         </is>
       </c>
-      <c r="I639" t="inlineStr">
+      <c r="I639" s="3" t="inlineStr">
         <is>
           <t>מגדולי האחרונים בפולין, יליד קראקא ותלמידם של המהרש״ל והרמ״א. עמד בראש ישיבה בלבוב, שם נפטר בשנת 1614, והעמיד תלמידים רבים. חיבר את ״דרישה ופרישה״ על הטור ואת ״מאירת עינים״ (הסמ״ע) על חושן משפט שבשולחן ערוך, ושניהם נדפסו אחר כך ברוב מהדורות הטור והשולחן ערוך.</t>
         </is>
       </c>
-      <c r="J639" t="inlineStr">
+      <c r="J639" s="3" t="inlineStr">
         <is>
           <t>הסמ״ע התנגד להישענות על ספרי הפסק תוך זניחת העיון במקורות המקוריים, ולכן חיבר פירושים לטור ולשולחן ערוך. ב״פרישה״ הוא מתחקה אחר הכרעות הטור עד מקורותיהן בתלמוד ובראשונים, וב״דרישה״ הוא דן בהרחבה בשיטות השונות.</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr">
+      <c r="K639" s="3" t="inlineStr">
         <is>
           <t>המהרש״ל (רבי שלמה לוריא), הרמ״א (רבי משה איסרליש)</t>
         </is>
       </c>
-      <c r="L639" t="inlineStr"/>
+      <c r="L639" s="3" t="inlineStr"/>
     </row>
     <row r="640">
-      <c r="A640" t="inlineStr">
+      <c r="A640" s="3" t="inlineStr">
         <is>
           <t>639</t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
+      <c r="B640" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C640" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל די מדינה (המהרשד״ם)</t>
         </is>
       </c>
-      <c r="D640" t="inlineStr">
+      <c r="D640" s="3" t="inlineStr">
         <is>
           <t>כ־1505–1589</t>
         </is>
       </c>
-      <c r="E640" t="inlineStr">
+      <c r="E640" s="3" t="inlineStr">
         <is>
           <t>סלוניקי</t>
         </is>
       </c>
-      <c r="F640" t="inlineStr">
+      <c r="F640" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G640" t="inlineStr">
+      <c r="G640" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H640" t="inlineStr">
+      <c r="H640" s="3" t="inlineStr">
         <is>
           <t>שו״ת מהרשד״ם, בן שמואל, רבי יוסף טאיטצאק, המהרלב״ח, לחם משנה, סלוניקי, האימפריה העות׳מאנית, תקנות קהל, אנוסים, פסיקה</t>
         </is>
       </c>
-      <c r="I640" t="inlineStr">
+      <c r="I640" s="3" t="inlineStr">
         <is>
           <t>מן הפוסקים המרכזיים באימפריה העות׳מאנית במאה ה־16, יליד סלוניקי, דיין וראש ישיבה בעירו. תלמידם של רבי יוסף טאיטצאק ורבי לוי בן חביב, ורבו של רבי אברהם די בוטון, בעל ״לחם משנה״. שאלות הלכתיות נשלחו אליו מקהילות רבות, וכאלף מתשובותיו נדפסו ב״שו״ת מהרשד״ם״, ודרשותיו בספר ״בן שמואל״.</t>
         </is>
       </c>
-      <c r="J640" t="inlineStr">
+      <c r="J640" s="3" t="inlineStr">
         <is>
           <t>תשובותיו קושרות את ההלכה לחיי הקהילה: לצד איסור והיתר, קידושין וגירושין הן עוסקות בתקנות קהל, במנהגי קהילות, בחלוקת נטל המיסים, בענייני מסחר ובמעמד האנוסים וצאצאיהם. שו״ת מהרשד״ם נמנה עם ספרי הפסיקה שחכמי המזרח הסתמכו עליהם, והוא משמש גם מקור היסטורי חשוב לחיי היהודים בסלוניקי.</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr">
+      <c r="K640" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף טאיטצאק, רבי לוי בן חביב (המהרלב״ח), רבי אברהם די בוטון, רבי מנחם די לונזאנו</t>
         </is>
       </c>
-      <c r="L640" t="inlineStr"/>
+      <c r="L640" s="3" t="inlineStr"/>
     </row>
     <row r="641">
-      <c r="A641" t="inlineStr">
+      <c r="A641" s="3" t="inlineStr">
         <is>
           <t>640</t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C641" t="inlineStr">
+      <c r="B641" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C641" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף בן לב (מהריב״ל)</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr">
+      <c r="D641" s="3" t="inlineStr">
         <is>
           <t>כ־1503–1580</t>
         </is>
       </c>
-      <c r="E641" t="inlineStr">
+      <c r="E641" s="3" t="inlineStr">
         <is>
           <t>סלוניקי; קושטא</t>
         </is>
       </c>
-      <c r="F641" t="inlineStr">
+      <c r="F641" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G641" t="inlineStr">
+      <c r="G641" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H641" t="inlineStr">
+      <c r="H641" s="3" t="inlineStr">
         <is>
           <t>שו״ת מהריב״ל, מונסטיר, סלוניקי, קושטא, דונה גרציה, רבי יוסף קארו, רבי יוסף טאיטצאק, אנוסים, לימוד לפי סוגיות, ישיבת קושטא</t>
         </is>
       </c>
-      <c r="I641" t="inlineStr">
+      <c r="I641" s="3" t="inlineStr">
         <is>
           <t>מחכמי מונסטיר שבאימפריה העות׳מאנית במאה ה־16, דיין ופוסק וראש ישיבה בסלוניקי ובקושטא, שנודע באישיותו התקיפה ובפסיקת הלכה בלתי מתפשרת. בקושטא מינתה אותו דונה גרציה מנדס לראש הישיבה שהקימה. תשובותיו, ״שו״ת מהריב״ל״, נדפסו עוד בחייו, ובהן גם חידושיו לכמה מסכתות בתלמוד הבבלי.</t>
         </is>
       </c>
-      <c r="J641" t="inlineStr">
+      <c r="J641" s="3" t="inlineStr">
         <is>
           <t>דרך לימודו מיזגה את הדרך הספרדית, המצטיינת בבקיאות ועוסקת בעיקר בבירור ההלכה, עם הדרך האשכנזית, המצטיינת בחריפות ועוסקת רבות גם בפלפול. בישיבתו הנהיג, כבישיבות האשכנזיות, לימוד לפי נושאים וסוגיות ולא לפי סדר התלמוד.</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
-      <c r="L641" t="inlineStr"/>
+      <c r="K641" s="3" t="inlineStr"/>
+      <c r="L641" s="3" t="inlineStr"/>
     </row>
     <row r="642">
-      <c r="A642" t="inlineStr">
+      <c r="A642" s="3" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C642" t="inlineStr">
+      <c r="B642" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C642" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף מטראני (המהרי״ט)</t>
         </is>
       </c>
-      <c r="D642" t="inlineStr">
+      <c r="D642" s="3" t="inlineStr">
         <is>
           <t>1568–1639</t>
         </is>
       </c>
-      <c r="E642" t="inlineStr">
+      <c r="E642" s="3" t="inlineStr">
         <is>
           <t>צפת; קושטא</t>
         </is>
       </c>
-      <c r="F642" t="inlineStr">
+      <c r="F642" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G642" t="inlineStr">
+      <c r="G642" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, ראשות ישיבה, פרשנות לתורה</t>
         </is>
       </c>
-      <c r="H642" t="inlineStr">
+      <c r="H642" s="3" t="inlineStr">
         <is>
           <t>שו״ת המהרי״ט, צפנת פענח, חידושי מהרי״ט, החכם באשי, המבי״ט, רבי חיים בנבנשתי, דינא דחיי, צפת, קושטא, הסמ״ג</t>
         </is>
       </c>
-      <c r="I642" t="inlineStr">
+      <c r="I642" s="3" t="inlineStr">
         <is>
           <t>מגדולי הפוסקים, בנו של רבי משה מטראני (המבי״ט), יליד צפת ומרבניה. עבר לקושטא, ייסד בה בית דין לענייני איסור והיתר ונתמנה לחכם באשי של טורקיה, ולישיבתו נהרו תלמידים מכל טורקיה ואף מעבר לה. נודע בשו״ת המהרי״ט ובחידושיו, וכן בפירושו ״צפנת פענח״ על התורה והמועדים.</t>
         </is>
       </c>
-      <c r="J642" t="inlineStr">
+      <c r="J642" s="3" t="inlineStr">
         <is>
           <t>הוא היה פוסק ומרביץ תורה גם יחד: קיבל אלפי שאלות והשיב עליהן, חיבר פירושים על הר״ן, הרי״ף והרמב״ם, והעמיד תלמידים. אחד מהם, בעל ״כנסת הגדולה״, זכה לברכתו שיחבר חיבור על הסמ״ג.</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr">
+      <c r="K642" s="3" t="inlineStr">
         <is>
           <t>רבי משה מטראני (המבי״ט), רבי חיים בנבנשתי (בעל כנסת הגדולה)</t>
         </is>
       </c>
-      <c r="L642" t="inlineStr"/>
+      <c r="L642" s="3" t="inlineStr"/>
     </row>
     <row r="643">
-      <c r="A643" t="inlineStr">
+      <c r="A643" s="3" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C643" t="inlineStr">
+      <c r="B643" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C643" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם די בוטון (בעל לחם משנה)</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr">
+      <c r="D643" s="3" t="inlineStr">
         <is>
           <t>המאה ה־16</t>
         </is>
       </c>
-      <c r="E643" t="inlineStr">
+      <c r="E643" s="3" t="inlineStr">
         <is>
           <t>סלוניקי</t>
         </is>
       </c>
-      <c r="F643" t="inlineStr">
+      <c r="F643" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G643" t="inlineStr">
+      <c r="G643" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, פרשנות הרמב״ם</t>
         </is>
       </c>
-      <c r="H643" t="inlineStr">
+      <c r="H643" s="3" t="inlineStr">
         <is>
           <t>לחם משנה, לחם רב, משנה תורה, הרמב״ם, המהרשד״ם, המגיד משנה, כסף משנה, סלוניקי, ראשות ישיבה, מגפה</t>
         </is>
       </c>
-      <c r="I643" t="inlineStr">
+      <c r="I643" s="3" t="inlineStr">
         <is>
           <t>רב, פוסק וראש ישיבה, מצאצאי מגורשי ספרד ומחכמי סלוניקי במאה ה־16, תלמידו של המהרשד״ם. פירש את משנה תורה של הרמב״ם בספרו ״לחם משנה״, שזכה לתפוצה רחבה והודפס במהדורה הסטנדרטית של הספר, וחיבר גם ספר שו״ת בשם ״לחם רב״. בשעת מחלתו נוסף לו השם חייא, ולפעמים היה חותם בשם זה.</t>
         </is>
       </c>
-      <c r="J643" t="inlineStr">
+      <c r="J643" s="3" t="inlineStr">
         <is>
           <t>בפירושו הוא מעמיק בדברי הרמב״ם ומשווה אותם לראשונים אחרים ולמפרשי הרמב״ם שקדמו לו, המגיד משנה והכסף משנה. החיד״א כתב שהחל לכתוב את חיבורו לפני שהתוודע לפירוש ״כסף משנה״, ולאחר שהתוודע אליו ציין אותו גם בו.</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr">
+      <c r="K643" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל די מדינה (המהרשד״ם)</t>
         </is>
       </c>
-      <c r="L643" t="inlineStr"/>
+      <c r="L643" s="3" t="inlineStr"/>
     </row>
     <row r="644">
-      <c r="A644" t="inlineStr">
+      <c r="A644" s="3" t="inlineStr">
         <is>
           <t>643</t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C644" t="inlineStr">
+      <c r="B644" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C644" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל בן אורי שרגא פייבוש (בעל בית שמואל)</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr">
+      <c r="D644" s="3" t="inlineStr">
         <is>
           <t>כ־1650–1706</t>
         </is>
       </c>
-      <c r="E644" t="inlineStr">
+      <c r="E644" s="3" t="inlineStr">
         <is>
           <t>פולין; גרמניה</t>
         </is>
       </c>
-      <c r="F644" t="inlineStr">
+      <c r="F644" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G644" t="inlineStr">
+      <c r="G644" s="3" t="inlineStr">
         <is>
           <t>הלכה, פרשנות השולחן ערוך, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H644" t="inlineStr">
+      <c r="H644" s="3" t="inlineStr">
         <is>
           <t>בית שמואל, אבן העזר, שולחן ערוך, חלקת מחוקק, אפי רברבי, פיורדא, שידלוב, ישיבת קרקוב, דירנפורט, מהדורא בתרא</t>
         </is>
       </c>
-      <c r="I644" t="inlineStr">
+      <c r="I644" s="3" t="inlineStr">
         <is>
           <t>רבן של שידלוב ופיורדא, יליד פולין באמצע המאה ה־17, שלמד בישיבת קרקוב. נודע בזכות ״בית שמואל״, מ״נושאי הכלים״ לחלק אבן העזר בשולחן ערוך. את המהדורה הראשונה הדפיס בדירנפורט, ואחרי שעבר עליה בפיורדא עם תלמידיו הוציא מהדורה שנייה מתוקנת, שמודפסת מאז ברוב מהדורות השולחן ערוך.</t>
         </is>
       </c>
-      <c r="J644" t="inlineStr">
+      <c r="J644" s="3" t="inlineStr">
         <is>
           <t>״בית שמואל״ נכתב כדי ״לגאול״ את חלק אבן העזר, שתלמידי החכמים זנחו, ולהפוך אותו מ״אבן מאסו הבונים״ ל״ראש פינה״ ולמרכז העיסוק הלימודי. המהדורה השנייה, שהמחבר הוסיף וגרע ושינה בה בעצמו יחד עם תלמידיו, היא העיקרית: שם הגדולים קובע ש״מהדורא קמא אין להשגיח בו״.</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
-      <c r="L644" t="inlineStr"/>
+      <c r="K644" s="3" t="inlineStr"/>
+      <c r="L644" s="3" t="inlineStr"/>
     </row>
     <row r="645">
-      <c r="A645" t="inlineStr">
+      <c r="A645" s="3" t="inlineStr">
         <is>
           <t>644</t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
+      <c r="B645" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C645" s="3" t="inlineStr">
         <is>
           <t>רבי יהושע בועז (בעל שלטי הגיבורים)</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr">
+      <c r="D645" s="3" t="inlineStr">
         <is>
           <t>המאה ה־16</t>
         </is>
       </c>
-      <c r="E645" t="inlineStr">
+      <c r="E645" s="3" t="inlineStr">
         <is>
           <t>איטליה</t>
         </is>
       </c>
-      <c r="F645" t="inlineStr">
+      <c r="F645" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G645" t="inlineStr">
+      <c r="G645" s="3" t="inlineStr">
         <is>
           <t>הלכה, פרשנות הרי״ף, עריכת הש״ס</t>
         </is>
       </c>
-      <c r="H645" t="inlineStr">
+      <c r="H645" s="3" t="inlineStr">
         <is>
           <t>שלטי הגיבורים, מסורת הש״ס, עין משפט נר מצווה, תורה אור, הרי״ף, ריא״ז, הרמ״א, הגהות אלפסי, ש״ס ונציה, איטליה</t>
         </is>
       </c>
-      <c r="I645" t="inlineStr">
+      <c r="I645" s="3" t="inlineStr">
         <is>
           <t>מגדולי הפוסקים האחרונים, נולד באיטליה לרבי שמעון לבית ברוך, ממשפחה ממגורשי ספרד. חיבר את ״מסורת הש״ס״, הפניות למקבילות בתלמוד שנדפסו כמעט בכל מהדורותיו, את ״עין משפט נר מצווה״, הפניות להלכה שבדברי הרמב״ם והסמ״ג, ואת ״שלטי הגיבורים״ על הרי״ף, שהרמ״א הרבה להביא ממנו פסקים.</t>
         </is>
       </c>
-      <c r="J645" t="inlineStr">
+      <c r="J645" s="3" t="inlineStr">
         <is>
           <t>ספריו קושרים את הלימוד בגמרא להלכה: ״עין משפט״ מפנה ממקום הדין בגמרא לדברי הרמב״ם והסמ״ג, ולאחר מכן גם לשולחן ערוך ולארבעה טורים, והוא כלי עזר חשוב ללומדי הגמרא ״אליבא דהלכתא״. ״שלטי הגיבורים״ מתמצת את פסקי ההלכה הנובעים מדברי הרי״ף ומהתייחסות הראשונים אליהם, ובו גם מעט מחידושיו.</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr">
+      <c r="K645" s="3" t="inlineStr">
         <is>
           <t>הרמ״א (רבי משה איסרליש)</t>
         </is>
       </c>
-      <c r="L645" t="inlineStr"/>
+      <c r="L645" s="3" t="inlineStr"/>
     </row>
     <row r="646">
-      <c r="A646" t="inlineStr">
+      <c r="A646" s="3" t="inlineStr">
         <is>
           <t>645</t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
+      <c r="B646" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C646" s="3" t="inlineStr">
         <is>
           <t>רבי שלמה סיריליו</t>
         </is>
       </c>
-      <c r="D646" t="inlineStr">
+      <c r="D646" s="3" t="inlineStr">
         <is>
           <t>1485–1554</t>
         </is>
       </c>
-      <c r="E646" t="inlineStr">
+      <c r="E646" s="3" t="inlineStr">
         <is>
           <t>צפת; ירושלים; סלוניקי</t>
         </is>
       </c>
-      <c r="F646" t="inlineStr">
+      <c r="F646" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G646" t="inlineStr">
+      <c r="G646" s="3" t="inlineStr">
         <is>
           <t>פרשנות התלמוד הירושלמי, הלכה, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H646" t="inlineStr">
+      <c r="H646" s="3" t="inlineStr">
         <is>
           <t>תלמוד ירושלמי, פירוש לירושלמי, סדר זרעים, מסכת שקלים, מסכת עדויות, מגורשי ספרד, צפת, ירושלים, סלוניקי, המצוות התלויות בארץ</t>
         </is>
       </c>
-      <c r="I646" t="inlineStr">
+      <c r="I646" s="3" t="inlineStr">
         <is>
           <t>ממגורשי ספרד ומחכמי צפת וירושלים במחצית הראשונה של המאה ה־16, מראשוני פרשני התלמוד הירושלמי. למד בקושטא ובסלוניקי, עלה לצפת ב־1532 ולימים עבר לירושלים והקים בה ישיבה. פירש את כל סדר זרעים ואת מסכת שקלים, ופירושו לסדר זרעים הוא הפירוש הרציף הראשון הידוע לירושלמי, וכן ערך מעין גמרא על מסכת עדויות.</t>
         </is>
       </c>
-      <c r="J646" t="inlineStr">
+      <c r="J646" s="3" t="inlineStr">
         <is>
           <t>ברוב הסוגיות לא עמד לפניו פירוש קדום, ופירושו לירושלמי מקורי ברובו, והוא לא נרתע מלחלוק על הראשונים ולעיתים אף על הרמב״ם. הוא שילב בפירושו פסקי הלכה הנובעים מן הסוגיות, ופסקים אלה הם מאבני היסוד בפסיקת ההלכה בימינו בנושא המצוות התלויות בארץ.</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr">
+      <c r="K646" s="3" t="inlineStr">
         <is>
           <t>רבי לוי בן חביב (המהרלב״ח), רבי יעקב אבן חביב (עין יעקב), רבי שלמה עדני (בעל מלאכת שלמה)</t>
         </is>
       </c>
-      <c r="L646" t="inlineStr"/>
+      <c r="L646" s="3" t="inlineStr"/>
     </row>
     <row r="647">
-      <c r="A647" t="inlineStr">
+      <c r="A647" s="3" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C647" t="inlineStr">
+      <c r="B647" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C647" s="3" t="inlineStr">
         <is>
           <t>רבי חיים בנבנשתי (בעל כנסת הגדולה)</t>
         </is>
       </c>
-      <c r="D647" t="inlineStr">
+      <c r="D647" s="3" t="inlineStr">
         <is>
           <t>1603–1673</t>
         </is>
       </c>
-      <c r="E647" t="inlineStr">
+      <c r="E647" s="3" t="inlineStr">
         <is>
           <t>איזמיר; קושטא</t>
         </is>
       </c>
-      <c r="F647" t="inlineStr">
+      <c r="F647" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G647" t="inlineStr">
+      <c r="G647" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, ראשות ישיבה, פרשנות הטור</t>
         </is>
       </c>
-      <c r="H647" t="inlineStr">
+      <c r="H647" s="3" t="inlineStr">
         <is>
           <t>ספר כנסת הגדולה, שיירי כנסת הגדולה, דינא דחיי, בעי חיי, פסח מעובין, חמרא וחיי, המהרי״ט, הסמ״ג, בית יוסף, איזמיר</t>
         </is>
       </c>
-      <c r="I647" t="inlineStr">
+      <c r="I647" s="3" t="inlineStr">
         <is>
           <t>רב ופוסק באיזמיר, יליד קושטא ותלמידו של רבי יוסף מטראני (המהרי״ט), שבירך אותו לחבר חיבור על הסמ״ג. בגיל 21 חיבר את ספרו הראשון, ״דינא דחיי״ על הסמ״ג. כיהן ברבנות בטירה הסמוכה לאיזמיר ואחר כך באיזמיר, כדיין וכראש ישיבה, ונודע בעיקר בספרו ״כנסת הגדולה״ על הטור והבית יוסף.</t>
         </is>
       </c>
-      <c r="J647" t="inlineStr">
+      <c r="J647" s="3" t="inlineStr">
         <is>
           <t>״כנסת הגדולה״ על הטור והבית יוסף הפך לאחד מספרי היסוד בפסיקה, ועל שמו נקרא מחברו. החיד״א כתב שאיש מורה הוראה בקי אינו מרים יד בשום הוראה בלי שיעיין בו תחילה.</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr">
+      <c r="K647" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף מטראני (המהרי״ט)</t>
         </is>
       </c>
-      <c r="L647" t="inlineStr"/>
+      <c r="L647" s="3" t="inlineStr"/>
     </row>
     <row r="648">
-      <c r="A648" t="inlineStr">
+      <c r="A648" s="3" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C648" t="inlineStr">
+      <c r="B648" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C648" s="3" t="inlineStr">
         <is>
           <t>רבי אליהו די וידאש (בעל ראשית חכמה)</t>
         </is>
       </c>
-      <c r="D648" t="inlineStr">
+      <c r="D648" s="3" t="inlineStr">
         <is>
           <t>המאה ה־16</t>
         </is>
       </c>
-      <c r="E648" t="inlineStr">
+      <c r="E648" s="3" t="inlineStr">
         <is>
           <t>צפת; חברון</t>
         </is>
       </c>
-      <c r="F648" t="inlineStr">
+      <c r="F648" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G648" t="inlineStr">
+      <c r="G648" s="3" t="inlineStr">
         <is>
           <t>קבלה ומוסר, הגות</t>
         </is>
       </c>
-      <c r="H648" t="inlineStr">
+      <c r="H648" s="3" t="inlineStr">
         <is>
           <t>ראשית חכמה, תוצאות חיים, הרמ״ק, האר״י, רבי שלמה אלקבץ, רבי יצחק דמן עכו, ראשות רבני חברון, תיקון המידות, הזוהר, קבלה ומוסר</t>
         </is>
       </c>
-      <c r="I648" t="inlineStr">
+      <c r="I648" s="3" t="inlineStr">
         <is>
           <t>מקובל והוגה דעות, יליד צפת ותלמידו של הרמ״ק, שלמד גם מפי האר״י. עבר לחברון והתמנה לראש רבניה, ושם נקבר. בשנת 1575 סיים את כתיבת ספרו ״ראשית חכמה״, העוסק בהיבטים השונים של חיי האדם על פי המשמעות הקבלית, והספר זכה למהדורות רבות, למהדורה מקוצרת ולתרגום ליידיש.</t>
         </is>
       </c>
-      <c r="J648" t="inlineStr">
+      <c r="J648" s="3" t="inlineStr">
         <is>
           <t>״ראשית חכמה״ הוא ספר קבלי על מידות האדם הראויות, המבוסס ברובו על הזוהר. לדברי שם הגדולים, מי שיקבע בו שיעור יומי ודאי יתנוצצו בו קדושה וטהרה.</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr">
+      <c r="K648" s="3" t="inlineStr">
         <is>
           <t>הרמ״ק (רבי משה קורדובירו), האר״י הקדוש, רבי יצחק דמן עכו</t>
         </is>
       </c>
-      <c r="L648" t="inlineStr"/>
+      <c r="L648" s="3" t="inlineStr"/>
     </row>
     <row r="649">
-      <c r="A649" t="inlineStr">
+      <c r="A649" s="3" t="inlineStr">
         <is>
           <t>648</t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C649" t="inlineStr">
+      <c r="B649" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C649" s="3" t="inlineStr">
         <is>
           <t>רבי אליה שפירא (בעל אליה רבה)</t>
         </is>
       </c>
-      <c r="D649" t="inlineStr">
+      <c r="D649" s="3" t="inlineStr">
         <is>
           <t>כ־1660–1712</t>
         </is>
       </c>
-      <c r="E649" t="inlineStr">
+      <c r="E649" s="3" t="inlineStr">
         <is>
           <t>פראג</t>
         </is>
       </c>
-      <c r="F649" t="inlineStr">
+      <c r="F649" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G649" t="inlineStr">
+      <c r="G649" s="3" t="inlineStr">
         <is>
           <t>הלכה, פסיקה ודרשנות</t>
         </is>
       </c>
-      <c r="H649" t="inlineStr">
+      <c r="H649" s="3" t="inlineStr">
         <is>
           <t>אליה רבה, אליה זוטא, הלבושים, רבי מרדכי יפה, מגן אברהם, משנה ברורה, פסיקה אשכנזית, פראג, שולחן ערוך</t>
         </is>
       </c>
-      <c r="I649" t="inlineStr">
+      <c r="I649" s="3" t="inlineStr">
         <is>
           <t>דיין, ראש ישיבה ודרשן בפראג, יליד העיר בסביבות שנת 1660, שנפטר ב־1712 בחיי אביו. למד אצל סבו, רבי אהרן שמעון מפראג, ובפולין למד מפי בעל ״מגן אברהם״. חיבר את ״אליה זוטא״ ואת ״אליה רבה״, פירושים לחלק אורח חיים בספרי ״הלבוש״ של רבי מרדכי יפה; שני הפירושים נחשבים לספרי יסוד בפסיקה האשכנזית.</t>
         </is>
       </c>
-      <c r="J649" t="inlineStr">
+      <c r="J649" s="3" t="inlineStr">
         <is>
           <t>פסיקה דרך פירוש: ״אליה רבה״ נכתב על סדר ״הלבוש״ של רבי מרדכי יפה ונעשה אחד מספרי היסוד בפסיקה האשכנזית. המשנה ברורה מביא אותו תדיר כמקור הפסיקה ההלכתית שלו.</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr">
+      <c r="K649" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם אבלי גומבינר (המגן אברהם), רבי מרדכי יפה, רבי יעקב ריישר</t>
         </is>
       </c>
-      <c r="L649" t="inlineStr"/>
+      <c r="L649" s="3" t="inlineStr"/>
     </row>
     <row r="650">
-      <c r="A650" t="inlineStr">
+      <c r="A650" s="3" t="inlineStr">
         <is>
           <t>649</t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C650" t="inlineStr">
+      <c r="B650" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C650" s="3" t="inlineStr">
         <is>
           <t>רבי דוד אלטשולר (בעל מצודת דוד)</t>
         </is>
       </c>
-      <c r="D650" t="inlineStr">
+      <c r="D650" s="3" t="inlineStr">
         <is>
           <t>1687–1769</t>
         </is>
       </c>
-      <c r="E650" t="inlineStr">
+      <c r="E650" s="3" t="inlineStr">
         <is>
           <t>יאברוב; גליציה</t>
         </is>
       </c>
-      <c r="F650" t="inlineStr">
+      <c r="F650" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G650" t="inlineStr">
+      <c r="G650" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא</t>
         </is>
       </c>
-      <c r="H650" t="inlineStr">
+      <c r="H650" s="3" t="inlineStr">
         <is>
           <t>מצודת דוד, מצודת ציון, פירוש לנביאים ולכתובים, פשט, מקראות גדולות, רד״ק, יאברוב, זאלקווא</t>
         </is>
       </c>
-      <c r="I650" t="inlineStr">
+      <c r="I650" s="3" t="inlineStr">
         <is>
           <t>פרשן מקרא ממשפחת אלטשולר, יליד יאברוב שבגליציה, שנזכר בה כדיין או כרב. כדי להנגיש את התנ״ך גם למלמדי תינוקות וילדים כתב את ״מצודת דוד״, ביאור פשוט וברור על התנ״ך (חוץ ממגילות רות, איכה ואסתר) שליקט מפירושי הראשונים, והדפיס ב־1753 בזאלקווא את הפירוש לאיוב, למשלי ולתהילים. בנו, רבי יחיאל הלל, השלים את הפירוש והדפיסו.</t>
         </is>
       </c>
-      <c r="J650" t="inlineStr">
+      <c r="J650" s="3" t="inlineStr">
         <is>
           <t>הנגשת המקרא לכל לומד: ״מצודת דוד״ מלקט בעברית פשוטה וצחה את פירושי הראשונים, כך שתלמידי החכמים חוסכים זמן יקר של עיון בהם והיהודים הפשוטים מבינים את המקרא על פי פשוטו. הפירוש זכה לאהדה רבה מפני שהוא ברור ומובן לכל, והוא נדפס כמעט בכל מהדורות ״מקראות גדולות״.</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr">
+      <c r="K650" s="3" t="inlineStr">
         <is>
           <t>רבי דוד קמחי (הרד״ק), רבי יחיאל הלל אלטשולר</t>
         </is>
       </c>
-      <c r="L650" t="inlineStr"/>
+      <c r="L650" s="3" t="inlineStr"/>
     </row>
     <row r="651">
-      <c r="A651" t="inlineStr">
+      <c r="A651" s="3" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr">
+      <c r="B651" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C651" s="3" t="inlineStr">
         <is>
           <t>רבי יחיאל הלל אלטשולר (בעל מצודת ציון)</t>
         </is>
       </c>
-      <c r="D651" t="inlineStr">
+      <c r="D651" s="3" t="inlineStr">
         <is>
           <t>המאה ה־18</t>
         </is>
       </c>
-      <c r="E651" t="inlineStr">
+      <c r="E651" s="3" t="inlineStr">
         <is>
           <t>יאברוב; עמדין; גליציה</t>
         </is>
       </c>
-      <c r="F651" t="inlineStr">
+      <c r="F651" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G651" t="inlineStr">
+      <c r="G651" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא והלכה</t>
         </is>
       </c>
-      <c r="H651" t="inlineStr">
+      <c r="H651" s="3" t="inlineStr">
         <is>
           <t>מצודת ציון, מצודת דוד, בנין הבית, בית המקדש השלישי, נבואת יחזקאל, מקראות גדולות, ליוורנו, יאברוב, עמדין</t>
         </is>
       </c>
-      <c r="I651" t="inlineStr">
+      <c r="I651" s="3" t="inlineStr">
         <is>
           <t>פרשן מקרא ופוסק, בנו של רבי דוד אלטשולר, יליד יאברוב שבגליציה, שכיהן כרב בעמדין וביאברוב. השלים וערך את ״המצודות״ של אביו על התנ״ך, חילק אותן ל״מצודת דוד״ ול״מצודת ציון״, ונדד לברלין, להולנד ולאיטליה כדי להדפיסן, עד שהודפסו בליוורנו. כתב גם את ״בנין הבית״ על צורת בית המקדש השלישי.</t>
         </is>
       </c>
-      <c r="J651" t="inlineStr">
+      <c r="J651" s="3" t="inlineStr">
         <is>
           <t>עריכה שהופכת כתבי אב לפירוש מקיף: ״מצודת דוד״ מבארת את ענייני הפסוקים ופשטם, ו״מצודת ציון״ מפרשת מילים וביטויים בתנ״ך, והוא שכלל והוסיף הוספות משלו. הפירוש המוגמר זכה לאהדה רבה מפני שהוא ברור ומובן לכל, ובמהרה נעשה אבן יסוד של פרשנות התנ״ך.</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr">
+      <c r="K651" s="3" t="inlineStr">
         <is>
           <t>רבי דוד אלטשולר</t>
         </is>
       </c>
-      <c r="L651" t="inlineStr"/>
+      <c r="L651" s="3" t="inlineStr"/>
     </row>
     <row r="652">
-      <c r="A652" t="inlineStr">
+      <c r="A652" s="3" t="inlineStr">
         <is>
           <t>651</t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
+      <c r="B652" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C652" s="3" t="inlineStr">
         <is>
           <t>רבי שלמה עדני (בעל מלאכת שלמה)</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr">
+      <c r="D652" s="3" t="inlineStr">
         <is>
           <t>כ־1567–1630</t>
         </is>
       </c>
-      <c r="E652" t="inlineStr">
+      <c r="E652" s="3" t="inlineStr">
         <is>
           <t>חברון; ירושלים; צנעא</t>
         </is>
       </c>
-      <c r="F652" t="inlineStr">
+      <c r="F652" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G652" t="inlineStr">
+      <c r="G652" s="3" t="inlineStr">
         <is>
           <t>פרשנות משנה</t>
         </is>
       </c>
-      <c r="H652" t="inlineStr">
+      <c r="H652" s="3" t="inlineStr">
         <is>
           <t>מלאכת שלמה, פירוש המשנה, נוסח המשנה, רבי חיים ויטאל, רבי בצלאל אשכנזי, בנין שלמה לחכמת בצלאל, דברי אמת, יהדות תימן</t>
         </is>
       </c>
-      <c r="I652" t="inlineStr">
+      <c r="I652" s="3" t="inlineStr">
         <is>
           <t>מגדולי מפרשי המשנה, יליד צנעא שבתימן, שעלה עם משפחתו לארץ ישראל והתיישב בצפת ואחר כך בירושלים, ובירושלים למד לפני רבי חיים ויטאל ורבי בצלאל אשכנזי. עבר לחברון וכתב בה במשך שלושים שנה את ״מלאכת שלמה״, פירוש על ששת סדרי משנה. חיבר גם את ״בנין שלמה לחכמת בצלאל״ ואת ״דברי אמת״, הגהות למקרא.</t>
         </is>
       </c>
-      <c r="J652" t="inlineStr">
+      <c r="J652" s="3" t="inlineStr">
         <is>
           <t>פירוש למשנה שמברר את נוסח המשנה וניקודה, ומתוך בקיאות בשני התלמודים, במפרשים ובפוסקים הוא דן בדבריהם עד לפסיקת ההלכה. בפירושו ניכרת חיבתו לרמב״ם, שאותו הוא מכנה ״גדול הפוסקים״.</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr">
+      <c r="K652" s="3" t="inlineStr">
         <is>
           <t>רבי בצלאל אשכנזי, רבי חיים ויטאל</t>
         </is>
       </c>
-      <c r="L652" t="inlineStr"/>
+      <c r="L652" s="3" t="inlineStr"/>
     </row>
     <row r="653">
-      <c r="A653" t="inlineStr">
+      <c r="A653" s="3" t="inlineStr">
         <is>
           <t>652</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
+      <c r="B653" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C653" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב יהושע פלק (בעל פני יהושע)</t>
         </is>
       </c>
-      <c r="D653" t="inlineStr">
+      <c r="D653" s="3" t="inlineStr">
         <is>
           <t>1680–1756</t>
         </is>
       </c>
-      <c r="E653" t="inlineStr">
+      <c r="E653" s="3" t="inlineStr">
         <is>
           <t>לבוב; ברלין; מץ; פרנקפורט; גרמניה; גליציה</t>
         </is>
       </c>
-      <c r="F653" t="inlineStr">
+      <c r="F653" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G653" t="inlineStr">
+      <c r="G653" s="3" t="inlineStr">
         <is>
           <t>פרשנות התלמוד</t>
         </is>
       </c>
-      <c r="H653" t="inlineStr">
+      <c r="H653" s="3" t="inlineStr">
         <is>
           <t>פני יהושע, מגיני שלמה, תוספות, רש״י, עיון ופלפול, לבוב, ברלין, מץ, פרנקפורט, מחלוקת עמדין־אייבשיץ</t>
         </is>
       </c>
-      <c r="I653" t="inlineStr">
+      <c r="I653" s="3" t="inlineStr">
         <is>
           <t>נולד בקרקוב ב־1680, כיהן כרבן של לבוב, ברלין, מץ ופרנקפורט על המיין, ונפטר ב־1756 באופנבך. כתב את סדרת ספרי ״פני יהושע״ על התלמוד הבבלי, שבהם הוא מבאר את סוגיות הש״ס על פי התוספות ורש״י בדרך העיון, החקירה, הסברה והפלפול. לפי הקדמתו התחיל לכתוב את הספר בנדר, אחרי שניצל מפיצוץ מחסן חומר נפץ.</t>
         </is>
       </c>
-      <c r="J653" t="inlineStr">
+      <c r="J653" s="3" t="inlineStr">
         <is>
           <t>הגנה על רש״י דרך עיון: ״פני יהושע״ ממשיך את דרכו של ״מגיני שלמה״ ומיישב את קושיות בעלי התוספות על פירוש רש״י, ויורד לפרטי הפרטים של כל סוגיה. אף ששיטת הלימוד שהתקבלה בדורות האחרונים רחוקה מדרכו, הספר זוכה לפופולריות רבה בישיבות.</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
-      <c r="L653" t="inlineStr"/>
+      <c r="K653" s="3" t="inlineStr"/>
+      <c r="L653" s="3" t="inlineStr"/>
     </row>
     <row r="654">
-      <c r="A654" t="inlineStr">
+      <c r="A654" s="3" t="inlineStr">
         <is>
           <t>653</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
+      <c r="B654" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C654" s="3" t="inlineStr">
         <is>
           <t>רבי יהונתן אייבשיץ</t>
         </is>
       </c>
-      <c r="D654" t="inlineStr">
+      <c r="D654" s="3" t="inlineStr">
         <is>
           <t>כ־1690–1764</t>
         </is>
       </c>
-      <c r="E654" t="inlineStr">
+      <c r="E654" s="3" t="inlineStr">
         <is>
           <t>פראג; מץ; אלטונה; המבורג</t>
         </is>
       </c>
-      <c r="F654" t="inlineStr">
+      <c r="F654" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G654" t="inlineStr">
+      <c r="G654" s="3" t="inlineStr">
         <is>
           <t>הלכה, קבלה ודרשנות</t>
         </is>
       </c>
-      <c r="H654" t="inlineStr">
+      <c r="H654" s="3" t="inlineStr">
         <is>
           <t>כרתי ופלתי, אורים ותומים, יערות דבש, מחלוקת עמדין־אייבשיץ, קמעות, שבתאות, לוחות עדות, פלפול, פראג, מץ</t>
         </is>
       </c>
-      <c r="I654" t="inlineStr">
+      <c r="I654" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבה ודרשן בפראג, ולימים רבה של מץ ורבן של קהילות אלטונה, המבורג ואנדסבק, ומגדולי פוסקי ההלכה ביהדות אשכנז בזמנו. חיבר את ״כרתי ופלתי״ על יורה דעה, את ״אורים ותומים״ על חושן משפט ואת ספר הדרשות ״יערות דבש״. עיסוקו בקבלה ובקמעות עורר נגדו פולמוס, שפתח רבי יעקב עמדין שמצא רמזים שבתאיים בכתביו; רוב רבני דורו תמכו בו והפולמוס דעך.</t>
         </is>
       </c>
-      <c r="J654" t="inlineStr">
+      <c r="J654" s="3" t="inlineStr">
         <is>
           <t>פלפול מחוכם שמלווה גם את ההלכה וגם את המוסר: חיבור של רעיונות שונים זה מזה מאפשר לו לפתור קושיות ולהתמודד עם סתירות. כפוסק הוא מחמיר, ודבקותו בשולחן ערוך גדולה, והוא מציע להתעלם מדעות שאינן מוזכרות בו.</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr">
+      <c r="K654" s="3" t="inlineStr">
         <is>
           <t>רבי אליה שפירא (בעל אליה רבה), רבי יעקב ריישר</t>
         </is>
       </c>
-      <c r="L654" t="inlineStr"/>
+      <c r="L654" s="3" t="inlineStr"/>
     </row>
     <row r="655">
-      <c r="A655" t="inlineStr">
+      <c r="A655" s="3" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C655" t="inlineStr">
+      <c r="B655" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C655" s="3" t="inlineStr">
         <is>
           <t>רבי מנחם די לונזאנו</t>
         </is>
       </c>
-      <c r="D655" t="inlineStr">
+      <c r="D655" s="3" t="inlineStr">
         <is>
           <t>כ־1550–1626</t>
         </is>
       </c>
-      <c r="E655" t="inlineStr">
+      <c r="E655" s="3" t="inlineStr">
         <is>
           <t>ירושלים; קושטא; איטליה</t>
         </is>
       </c>
-      <c r="F655" t="inlineStr">
+      <c r="F655" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G655" t="inlineStr">
+      <c r="G655" s="3" t="inlineStr">
         <is>
           <t>נוסח המקרא, מילונאות, קבלה ושירה</t>
         </is>
       </c>
-      <c r="H655" t="inlineStr">
+      <c r="H655" s="3" t="inlineStr">
         <is>
           <t>שתי ידות, אור תורה, מעריך, עבודת המקדש, דרך חיים, נוסח המקרא, מסורה, מדרש אגור, הרמד״ל</t>
         </is>
       </c>
-      <c r="I655" t="inlineStr">
+      <c r="I655" s="3" t="inlineStr">
         <is>
           <t>רב, מקובל, משורר, חוקר המסורה ומהדיר ספרי מדרש, ומן העולים הקדמונים לארץ ישראל. נולד, לפי אגרת המלצה, בפיסארו שבאיטליה, עלה לירושלים אחרי 1575 ונפטר בה לפני 1626. חיבר את ״שתי ידות״ (ונציה, 1618), ספר הכולל עשרה חיבורים: חמישה משלו, ובהם ״אור תורה״ לבירור נוסח המקרא לפי המסורה ו״מעריך״, תשלום לספר הערוך, וחמישה חיבורים קדומים של חז״ל שהדיר.</t>
         </is>
       </c>
-      <c r="J655" t="inlineStr">
+      <c r="J655" s="3" t="inlineStr">
         <is>
           <t>הכרעה בנוסח המקרא לפי כתבי היד והמסורה: ״אור תורה״ נשען על יותר מעשרה כתבי יד של המקרא ועל ספרי מגיהי המקרא שקדמוהו, ויחד עם דברי הרמ״ה (רבי מאיר הלוי אבולעפיה) ובעל ״מנחת שי״ נעשה לקובע נוסח המקרא המקובל. בנדודיו נחשף לכתבי יד עתיקים של מדרשי חז״ל והשתדל להוציאם לאור.</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr">
+      <c r="K655" s="3" t="inlineStr">
         <is>
           <t>רבי נתן מרומי, רבי שמואל די מדינה (המהרשד״ם)</t>
         </is>
       </c>
-      <c r="L655" t="inlineStr"/>
+      <c r="L655" s="3" t="inlineStr"/>
     </row>
     <row r="656">
-      <c r="A656" t="inlineStr">
+      <c r="A656" s="3" t="inlineStr">
         <is>
           <t>655</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C656" t="inlineStr">
+      <c r="B656" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C656" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב חגיז (בעל הלכות קטנות)</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr">
+      <c r="D656" s="3" t="inlineStr">
         <is>
           <t>1620–1674</t>
         </is>
       </c>
-      <c r="E656" t="inlineStr">
+      <c r="E656" s="3" t="inlineStr">
         <is>
           <t>ירושלים; ליוורנו; קושטא; פאס</t>
         </is>
       </c>
-      <c r="F656" t="inlineStr">
+      <c r="F656" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G656" t="inlineStr">
+      <c r="G656" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, פרשנות משנה וראשות ישיבה</t>
         </is>
       </c>
-      <c r="H656" t="inlineStr">
+      <c r="H656" s="3" t="inlineStr">
         <is>
           <t>הלכות קטנות, עץ חיים, ישיבת בית יעקב, פתיל תכלת, תחילת חכמה, שבתי צבי, שבתאות, ליוורנו, פאס</t>
         </is>
       </c>
-      <c r="I656" t="inlineStr">
+      <c r="I656" s="3" t="inlineStr">
         <is>
           <t>נולד בפאס שבמרוקו ב־1620, עבר בצעירותו לאיטליה והדפיס שם חיבורים, ובשנת 1658 עלה לירושלים והקים בה את בית המדרש ״בית יעקב״. חיבר את שו״ת ״הלכות קטנות״, את ״עץ חיים״ על המשנה ואת ״פתיל תכלת״ על אזהרות אבן גבירול. בראש רבני ירושלים נקט קו תקיף נגד שבתי צבי, ורבני העיר בראשותו פרסמו נגדו חרם; הוא נפטר בקושטא ב־1674.</t>
         </is>
       </c>
-      <c r="J656" t="inlineStr">
+      <c r="J656" s="3" t="inlineStr">
         <is>
           <t>הכשרת דיינים ורבנים דרך התנסות: בישיבת ״בית יעקב״ קבע סדרי לימוד חדשים, ובהם מקום לתלמידים צעירים ולתלמידי חכמים; התלמידים למדו בחמישה ״שולחנות״, ואחר כך התמחו בפסיקה ובדיינות לצד עשרה חכמים, עד מינוי לדיינים בקהילות שבחוץ לארץ. גם את תשובותיו ב״הלכות קטנות״ כתב, לפי החיד״א, בדרך קצרה כדי לחדד את התלמידים.</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr">
+      <c r="K656" s="3" t="inlineStr">
         <is>
           <t>רבי משה חגיז, רבי משה גלאנטי (המג״ן)</t>
         </is>
       </c>
-      <c r="L656" t="inlineStr"/>
+      <c r="L656" s="3" t="inlineStr"/>
     </row>
     <row r="657">
-      <c r="A657" t="inlineStr">
+      <c r="A657" s="3" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C657" t="inlineStr">
+      <c r="B657" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C657" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם הלוי (בעל גינת ורדים)</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr">
+      <c r="D657" s="3" t="inlineStr">
         <is>
           <t>כ־1650–1712</t>
         </is>
       </c>
-      <c r="E657" t="inlineStr">
+      <c r="E657" s="3" t="inlineStr">
         <is>
           <t>קהיר; רוזטה; מצרים</t>
         </is>
       </c>
-      <c r="F657" t="inlineStr">
+      <c r="F657" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G657" t="inlineStr">
+      <c r="G657" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת</t>
         </is>
       </c>
-      <c r="H657" t="inlineStr">
+      <c r="H657" s="3" t="inlineStr">
         <is>
           <t>גינת ורדים, גן המלך, דרכי נועם, רבני מצרים, רוזטה, קהיר, באר היטב</t>
         </is>
       </c>
-      <c r="I657" t="inlineStr">
+      <c r="I657" s="3" t="inlineStr">
         <is>
           <t>מרבני מצרים במאה ה־17, נולד בה בסביבות 1650 ונפטר ב־1712. שימש בדיינות ואחר כך נבחר לראש רבני מצרים בקהיר, ומילא את מקום אביו, רבי מרדכי הלוי בעל ״דרכי נועם״, כראש הישיבה ואב בית הדין ברוזטה. חיבר את שו״ת ״גינת ורדים״, בסדר ארבעה טורים, שנתפרסמו אחרי מותו והשפיעו רבות בכל המזרח וגם על חכמים אשכנזים.</t>
         </is>
       </c>
-      <c r="J657" t="inlineStr">
+      <c r="J657" s="3" t="inlineStr">
         <is>
           <t>שו״ת מסודר לפי ארבעה טורים, הכולל גם תשובות של חכמי התקופה ומכתבים עם חברו ובר פלוגתא רבי יעקב פראג׳י. השפעת הספר הייתה רבה בכל המזרח וגם על חכמים אשכנזים, ובעל ״באר היטב״ מביאו פעמים רבות.</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
-      <c r="L657" t="inlineStr"/>
+      <c r="K657" s="3" t="inlineStr"/>
+      <c r="L657" s="3" t="inlineStr"/>
     </row>
     <row r="658">
-      <c r="A658" t="inlineStr">
+      <c r="A658" s="3" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C658" t="inlineStr">
+      <c r="B658" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C658" s="3" t="inlineStr">
         <is>
           <t>רבי יאיר חיים בכרך (בעל חוות יאיר)</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr">
+      <c r="D658" s="3" t="inlineStr">
         <is>
           <t>1638–1702</t>
         </is>
       </c>
-      <c r="E658" t="inlineStr">
+      <c r="E658" s="3" t="inlineStr">
         <is>
           <t>וורמייזא; מגנצא; קובלנץ; פרנקפורט</t>
         </is>
       </c>
-      <c r="F658" t="inlineStr">
+      <c r="F658" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G658" t="inlineStr">
+      <c r="G658" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת</t>
         </is>
       </c>
-      <c r="H658" t="inlineStr">
+      <c r="H658" s="3" t="inlineStr">
         <is>
           <t>חוות יאיר, מקור חיים, חוט השני, המהר״ל, וורמייזא, מגן אברהם, הט״ז, אחרי רבים להטות, פסיקה אשכנזית</t>
         </is>
       </c>
-      <c r="I658" t="inlineStr">
+      <c r="I658" s="3" t="inlineStr">
         <is>
           <t>נולד בלייפניק שבמוראביה ב־1638, כיהן כרב בקובלנץ ובמגנצא ובסוף ימיו בוורמייזא, ונפטר ב־1702. מגדולי האחרונים באשכנז, ונודע בספר השו״ת ״חוות יאיר״, שיצא לאור ב־1699 ונחשב לאחד מספרי ההלכה החשובים ביותר באשכנז. חיבר כארבעים ספרים בהלכה, ובהם ״מקור חיים״ על שולחן ערוך אורח חיים; ספרו ״חוט השני״ מכיל בעיקר תשובות של אביו וסבו.</t>
         </is>
       </c>
-      <c r="J658" t="inlineStr">
+      <c r="J658" s="3" t="inlineStr">
         <is>
           <t>פסיקה עצמאית שמחויבת לאמת: הוא חולק על הרמב״ם וקובע שייתכנו שכחה ומחלוקת גם בהלכה למשה מסיני, ושהכרעת חכמי הדור קובעת הלכה גם נגד המסורת המקורית. הוא מתנגד בחריפות לפלפול מוגזם, ובמקום לעסוק בתורת הנסתר, שהעריך את חשיבותה, מעדיף ״לעמוד על עקרי הדת ומשפטי המצוות״.</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr">
+      <c r="K658" s="3" t="inlineStr">
         <is>
           <t>המהר״ל מפראג, רבי דוד הלוי סגל (הט״ז), רבי אברהם אבלי גומבינר (המגן אברהם)</t>
         </is>
       </c>
-      <c r="L658" t="inlineStr"/>
+      <c r="L658" s="3" t="inlineStr"/>
     </row>
     <row r="659">
-      <c r="A659" t="inlineStr">
+      <c r="A659" s="3" t="inlineStr">
         <is>
           <t>658</t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C659" t="inlineStr">
+      <c r="B659" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C659" s="3" t="inlineStr">
         <is>
           <t>רבי אליהו הכהן האתמרי (בעל שבט מוסר)</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr">
+      <c r="D659" s="3" t="inlineStr">
         <is>
           <t>כ־1659–1729</t>
         </is>
       </c>
-      <c r="E659" t="inlineStr">
+      <c r="E659" s="3" t="inlineStr">
         <is>
           <t>איזמיר</t>
         </is>
       </c>
-      <c r="F659" t="inlineStr">
+      <c r="F659" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G659" t="inlineStr">
+      <c r="G659" s="3" t="inlineStr">
         <is>
           <t>מוסר, דרשנות וקבלה</t>
         </is>
       </c>
-      <c r="H659" t="inlineStr">
+      <c r="H659" s="3" t="inlineStr">
         <is>
           <t>שבט מוסר, מדרש תלפיות, ילקוט האתמרי, איזמיר, סגפנות, צדקה, אפוטרופוסים לעניים, אגדת אליהו, ספרות המוסר</t>
         </is>
       </c>
-      <c r="I659" t="inlineStr">
+      <c r="I659" s="3" t="inlineStr">
         <is>
           <t>דיין, דרשן ומקובל מחכמי איזמיר, שנולד בעיר וישב בה כל חייו. ספרו המוסרי ״שבט מוסר״ יצא לאור לראשונה בקושטא בשנת ה׳תע״ב, נדפס מאז בעשרות מהדורות ותורגם ליידיש, ללדינו ולערבית יהודית. חיבר עשרות ספרים, בעיקר ספרי מוסר, מדרש ופרשנות המקרא, ובהם ״מדרש תלפיות״.</t>
         </is>
       </c>
-      <c r="J659" t="inlineStr">
+      <c r="J659" s="3" t="inlineStr">
         <is>
           <t>המוסר אינו עניין של הפרט בלבד: בדרשותיו הטיף לסגפנות ולהתרחקות מתענוגות העולם הזה, וראה בעוני ובאי־השוויון החברתי בעיה דתית ומוסרית שהקהילה כולה צריכה לתקן. את עשירי הקהילה ראה כ״אפוטרופוסים״ על כספי העניים וקרא להם לפזר את כספם לצדקה.</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
-      <c r="L659" t="inlineStr"/>
+      <c r="K659" s="3" t="inlineStr"/>
+      <c r="L659" s="3" t="inlineStr"/>
     </row>
     <row r="660">
-      <c r="A660" t="inlineStr">
+      <c r="A660" s="3" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C660" t="inlineStr">
+      <c r="B660" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C660" s="3" t="inlineStr">
         <is>
           <t>רבי עזריה פיגו (בעל גידולי תרומה)</t>
         </is>
       </c>
-      <c r="D660" t="inlineStr">
+      <c r="D660" s="3" t="inlineStr">
         <is>
           <t>1579–1647</t>
         </is>
       </c>
-      <c r="E660" t="inlineStr">
+      <c r="E660" s="3" t="inlineStr">
         <is>
           <t>ונציה; פיזה</t>
         </is>
       </c>
-      <c r="F660" t="inlineStr">
+      <c r="F660" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G660" t="inlineStr">
+      <c r="G660" s="3" t="inlineStr">
         <is>
           <t>הלכה, דרשנות</t>
         </is>
       </c>
-      <c r="H660" t="inlineStr">
+      <c r="H660" s="3" t="inlineStr">
         <is>
           <t>גידולי תרומה, בינה לעתים, ספר התרומות, רבי שמואל הסרדי, פיזה, ונציה, דרשנות, סופר סת״ם, הש״ך, יהדות איטליה</t>
         </is>
       </c>
-      <c r="I660" t="inlineStr">
+      <c r="I660" s="3" t="inlineStr">
         <is>
           <t>רב, פוסק ודרשן יליד ונציה, מחכמי איטליה במאה ה־17, שלמד תורה בעירו ורכש גם השכלה כללית באוניברסיטה. שימש כרב קהילת פיזה כעשרים שנה, ואחר כך שב לוונציה והיה בה דרשן בבתי הכנסת. את פירושו ״גידולי תרומה״ לספר התרומות של רבי שמואל הסרדי כתב כמעט ללא ספרים, ודרשותיו נדפסו בספרו ״בינה לעתים״, שיצא לאור אחרי מותו.</t>
         </is>
       </c>
-      <c r="J660" t="inlineStr">
+      <c r="J660" s="3" t="inlineStr">
         <is>
           <t>הדרשה צריכה להישאר קרובה לפשט ולעולם המעשה: לדברי מי שהוציא את דרשותיו לאור, הוא נמנע מעיונים מופשטים ומרעיונות פילוסופיים שאין להם אחיזה בעולם המעשה, שהיו דרכם של דרשני איטליה בימיו, ומבקש את פשט הדברים. ספרו נדפס עשרות פעמים וזכה לפופולריות רבה בקרב הדרשנים והמון העם. בהלכה ברר את דברי ספר התרומות ואת מקורותיו והשווה אותם לדברי פוסקים אחרים.</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr">
+      <c r="K660" s="3" t="inlineStr">
         <is>
           <t>רבנו שמואל הסרדי, רבי שבתאי הכהן (הש״ך)</t>
         </is>
       </c>
-      <c r="L660" t="inlineStr"/>
+      <c r="L660" s="3" t="inlineStr"/>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr">
+      <c r="A661" s="3" t="inlineStr">
         <is>
           <t>660</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
+      <c r="B661" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C661" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב ריישר (בעל שבות יעקב)</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr">
+      <c r="D661" s="3" t="inlineStr">
         <is>
           <t>כ־1661–1733</t>
         </is>
       </c>
-      <c r="E661" t="inlineStr">
+      <c r="E661" s="3" t="inlineStr">
         <is>
           <t>פראג; וורמייזא; מץ</t>
         </is>
       </c>
-      <c r="F661" t="inlineStr">
+      <c r="F661" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G661" t="inlineStr">
+      <c r="G661" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, אגדה</t>
         </is>
       </c>
-      <c r="H661" t="inlineStr">
+      <c r="H661" s="3" t="inlineStr">
         <is>
           <t>שבות יעקב, חק יעקב, מנחת יעקב, עיון יעקב, תורת השלמים, עין יעקב, פראג, מץ, וורמייזא, הש״ך</t>
         </is>
       </c>
-      <c r="I661" t="inlineStr">
+      <c r="I661" s="3" t="inlineStr">
         <is>
           <t>מרבני אשכנז, פוסק ומחבר ספרי הלכה ואגדה. נולד בפראג, שימש בה כדיין ובהמשך כראש בית הדין הגדול, ואחר כך כיהן כרב וכראש ישיבה בוורמייזא ובמץ, ושם נפטר. מחיבוריו שו״ת ״שבות יעקב״, ״חק יעקב״ על הלכות פסח, ״מנחת יעקב״ ו״עיון יעקב״, פירוש לאגדות שבספר עין יעקב.</t>
         </is>
       </c>
-      <c r="J661" t="inlineStr">
+      <c r="J661" s="3" t="inlineStr">
         <is>
           <t>הלכה ואגדה יחד: הוא חיבר שו״ת וחידושים על שולחן ערוך, וחיבור על כללי הספיקות של הש״ך, וגם פירוש לאגדות התלמוד שבספר עין יעקב. הוא נהג לעמוד עם גיסיו, רבי אליה שפירא ורבי דוד אופנהיים, במשא ומתן הלכתי.</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr">
+      <c r="K661" s="3" t="inlineStr">
         <is>
           <t>רבי אליה שפירא (בעל אליה רבה), רבי שבתאי הכהן (הש״ך)</t>
         </is>
       </c>
-      <c r="L661" t="inlineStr"/>
+      <c r="L661" s="3" t="inlineStr"/>
     </row>
     <row r="662">
-      <c r="A662" t="inlineStr">
+      <c r="A662" s="3" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C662" t="inlineStr">
+      <c r="B662" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C662" s="3" t="inlineStr">
         <is>
           <t>רבי שמשון חיים נחמני (בעל זרע שמשון)</t>
         </is>
       </c>
-      <c r="D662" t="inlineStr">
+      <c r="D662" s="3" t="inlineStr">
         <is>
           <t>1706–1779</t>
         </is>
       </c>
-      <c r="E662" t="inlineStr">
+      <c r="E662" s="3" t="inlineStr">
         <is>
           <t>מודינה; רג׳ו אמיליה; צפון איטליה</t>
         </is>
       </c>
-      <c r="F662" t="inlineStr">
+      <c r="F662" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G662" t="inlineStr">
+      <c r="G662" s="3" t="inlineStr">
         <is>
           <t>קבלה, הלכה, דרשנות ושירה</t>
         </is>
       </c>
-      <c r="H662" t="inlineStr">
+      <c r="H662" s="3" t="inlineStr">
         <is>
           <t>זרע שמשון, תולדות שמשון, קרבן קטורת, מודינה, רג׳ו אמיליה, רבי אביעד שר שלום באזילה, קבלה מעשית, גניזת כתבים, דרשנות</t>
         </is>
       </c>
-      <c r="I662" t="inlineStr">
+      <c r="I662" s="3" t="inlineStr">
         <is>
           <t>רב, מקובל, דרשן ומשורר יהודי איטלקי, יליד מודינה, שכיהן כרב בכמה קהילות בצפון איטליה ונחשב לאחד מגדולי רבני המדינה. למד תורה במודינה ובמנטובה וקבלה ברג׳ו אמיליה, ובשנת 1739 החל לכהן שם כרב ושם נפטר. מספריו נדפסו ״זרע שמשון״ על התורה והמגילות ו״תולדות שמשון״ על מסכת אבות, וציווה לגנוז עמו את ספריו, בעיקר בקבלה.</t>
         </is>
       </c>
-      <c r="J662" t="inlineStr">
+      <c r="J662" s="3" t="inlineStr">
         <is>
           <t>נגלה ונסתר יחד: הוא נחשב לבקי בכל חלקי התורה, נגלה ונסתר, בדרשותיו על התורה ביאר גם מאמרים תמוהים, ובהלכה נקט גישה מחמירה וראה בנטייה להקל ״כוח הטומאה״. שאיפתו, כפי שהצהיר בצוואתו, הייתה לזכות את הרבים, להעמיד תלמידים ולחדש חידושי תורה אמיתיים.</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr">
+      <c r="K662" s="3" t="inlineStr">
         <is>
           <t>רבי אביעד שר שלום באזילה</t>
         </is>
       </c>
-      <c r="L662" t="inlineStr"/>
+      <c r="L662" s="3" t="inlineStr"/>
     </row>
     <row r="663">
-      <c r="A663" t="inlineStr">
+      <c r="A663" s="3" t="inlineStr">
         <is>
           <t>662</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr">
+      <c r="B663" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C663" s="3" t="inlineStr">
         <is>
           <t>רבי יצחק דמן עכו (בעל מאירת עיניים)</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr">
+      <c r="D663" s="3" t="inlineStr">
         <is>
           <t>כ־1250–1340</t>
         </is>
       </c>
-      <c r="E663" t="inlineStr">
+      <c r="E663" s="3" t="inlineStr">
         <is>
           <t>עכו; ספרד</t>
         </is>
       </c>
-      <c r="F663" t="inlineStr">
+      <c r="F663" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G663" t="inlineStr">
+      <c r="G663" s="3" t="inlineStr">
         <is>
           <t>קבלה, פרשנות</t>
         </is>
       </c>
-      <c r="H663" t="inlineStr">
+      <c r="H663" s="3" t="inlineStr">
         <is>
           <t>מאירת עיניים, אוצר החיים, הרמב״ן, ספר הזוהר, רבי משה די ליאון, כיבוש עכו, חכמת הצירוף, פירוש לספר יצירה, ראשית חכמה</t>
         </is>
       </c>
-      <c r="I663" t="inlineStr">
+      <c r="I663" s="3" t="inlineStr">
         <is>
           <t>מקובל יליד עכו, שנחשב לאחד מגדולי חכמי העיר בדורו. בכיבוש עכו בידי הממלוכים ב־1291 נפל בשבי, ואחר כך נסע לספרד כדי להתחקות אחר מקורו של ספר הזוהר, ושם נפטר. בספרו ״מאירת עיניים״ ביאר את הסודות שבפירוש הרמב״ן לתורה, והחיד״א מכנה אותו תלמידו ואיש סודו של הרמב״ן, אך הדבר מסופק.</t>
         </is>
       </c>
-      <c r="J663" t="inlineStr">
+      <c r="J663" s="3" t="inlineStr">
         <is>
           <t>חקירת מקורותיו של ספר הזוהר: הוא נסע לספרד כדי להתחקות אחר מקורו של ספר הזוהר, ובמאירת עיניים ביאר את הסודות שבפירוש הרמב״ן לתורה והאריך בגנות הפילוסופיה. בספרו ״אוצר החיים״, יומן מיסטי של חוויות אקסטטיות, פירש את תורת השמיטות הקבלית.</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr">
+      <c r="K663" s="3" t="inlineStr">
         <is>
           <t>הרמב״ן (רבי משה בן נחמן), רבי אליהו די וידאש</t>
         </is>
       </c>
-      <c r="L663" t="inlineStr"/>
+      <c r="L663" s="3" t="inlineStr"/>
     </row>
     <row r="664">
-      <c r="A664" t="inlineStr">
+      <c r="A664" s="3" t="inlineStr">
         <is>
           <t>663</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
+      <c r="B664" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C664" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל אבוהב (בעל דבר שמואל)</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr">
+      <c r="D664" s="3" t="inlineStr">
         <is>
           <t>1610–1694</t>
         </is>
       </c>
-      <c r="E664" t="inlineStr">
+      <c r="E664" s="3" t="inlineStr">
         <is>
           <t>ונציה; ורונה</t>
         </is>
       </c>
-      <c r="F664" t="inlineStr">
+      <c r="F664" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G664" t="inlineStr">
+      <c r="G664" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, מנהיגות קהילתית</t>
         </is>
       </c>
-      <c r="H664" t="inlineStr">
+      <c r="H664" s="3" t="inlineStr">
         <is>
           <t>דבר שמואל, ספר הזכרונות, ורונה, ונציה, רבי דוד פרנקו, שבתי צבי, סתם יינם, רבי משה זכות, יהדות איטליה</t>
         </is>
       </c>
-      <c r="I664" t="inlineStr">
+      <c r="I664" s="3" t="inlineStr">
         <is>
           <t>רב ופוסק הלכה בוונציה ומגדולי חכמי איטליה, יליד המבורג, שנשלח בגיל שלוש עשרה ללמוד בוונציה אצל הרב דוד פרנקו. ייסד בוורונה ישיבה שנודעה בערי איטליה, ומשנת 1650 שימש רב ואב״ד של ונציה עד סוף ימיו, והיה מראשי הלוחמים באיטליה במשיחיותו של שבתי צבי. נודע בספר תשובותיו ״דבר שמואל״ ובספר ״הזכרונות״.</t>
         </is>
       </c>
-      <c r="J664" t="inlineStr">
+      <c r="J664" s="3" t="inlineStr">
         <is>
           <t>הוא ביקש להשיב את העם אל קיום ההלכה: ב״ספר הזכרונות״, שנדפס בעילום שם, הוכיח על איסורים שרגילים לזלזל בהם, כמו ״סתם יינם״ ושעטנז, בימים שבהם יהדות איטליה הייתה פרוצה ליחסים קרובים עם תושביה הגויים. בתשובותיו לא חתם בשמו מתוך ענווה אלא צירף את שמות חכמי הישיבה.</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr">
+      <c r="K664" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב חגיז, רבי משה זכות (הרמ״ז)</t>
         </is>
       </c>
-      <c r="L664" t="inlineStr"/>
+      <c r="L664" s="3" t="inlineStr"/>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr">
+      <c r="A665" s="3" t="inlineStr">
         <is>
           <t>664</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr">
+      <c r="B665" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C665" s="3" t="inlineStr">
         <is>
           <t>רבי יונה לנדסופר (בעל מעיל צדקה)</t>
         </is>
       </c>
-      <c r="D665" t="inlineStr">
+      <c r="D665" s="3" t="inlineStr">
         <is>
           <t>1678–1712</t>
         </is>
       </c>
-      <c r="E665" t="inlineStr">
+      <c r="E665" s="3" t="inlineStr">
         <is>
           <t>פראג</t>
         </is>
       </c>
-      <c r="F665" t="inlineStr">
+      <c r="F665" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G665" t="inlineStr">
+      <c r="G665" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, הלכות סת״ם</t>
         </is>
       </c>
-      <c r="H665" t="inlineStr">
+      <c r="H665" s="3" t="inlineStr">
         <is>
           <t>מעיל צדקה, בני יונה, כנפי יונה, מאורי אור, רבי אברהם ברודא, שיעור הגריס, סופר סת״ם, הנדסה, המהר״ל מפראג</t>
         </is>
       </c>
-      <c r="I665" t="inlineStr">
+      <c r="I665" s="3" t="inlineStr">
         <is>
           <t>רב ופוסק, מגדולי רבני בוהמיה, יליד פראג, שנפטר בגיל צעיר ובכל זאת עשה רושם גדול בעולם ההלכה עוד בחייו. היה סופר סת״ם במקצועו ורכש לעצמו ידע רחב במדעים. שלושה מספריו הרבים נדפסו לאחר מותו: שו״ת ״מעיל צדקה״, שעל שמו כונה, ״בני יונה״ על הלכות ספר תורה ו״כנפי יונה״ על יורה דעה.</t>
         </is>
       </c>
-      <c r="J665" t="inlineStr">
+      <c r="J665" s="3" t="inlineStr">
         <is>
           <t>הלכה שנשענת על ידע מדעי: ב״מעיל צדקה״ קבע את שיעור ה״גריס״ בדיני כתמים; לספר מצורף שרטוט בגודל אמיתי שמודדים לפיו, ובסופו קונטרס בהנדסה, מלוקט מדברי אוקלידס, שכתב בתשובה לשאלה שנשאל מחכמי ההנדסה בדורו. ב״בני יונה״, שמעמדו כספר יסוד בהלכה, פסק שאין נמנעים מלקרוא בחומשים שנדפסו בידי גויים.</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr">
+      <c r="K665" s="3" t="inlineStr">
         <is>
           <t>המהר״ל מפראג</t>
         </is>
       </c>
-      <c r="L665" t="inlineStr"/>
+      <c r="L665" s="3" t="inlineStr"/>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr">
+      <c r="A666" s="3" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr">
+      <c r="B666" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C666" s="3" t="inlineStr">
         <is>
           <t>רבי נתנאל וייל (בעל קרבן נתנאל)</t>
         </is>
       </c>
-      <c r="D666" t="inlineStr">
+      <c r="D666" s="3" t="inlineStr">
         <is>
           <t>1687–1769</t>
         </is>
       </c>
-      <c r="E666" t="inlineStr">
+      <c r="E666" s="3" t="inlineStr">
         <is>
           <t>פראג; קרלסרוהה</t>
         </is>
       </c>
-      <c r="F666" t="inlineStr">
+      <c r="F666" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G666" t="inlineStr">
+      <c r="G666" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, פירוש לפסקי הרא״ש, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H666" t="inlineStr">
+      <c r="H666" s="3" t="inlineStr">
         <is>
           <t>קרבן נתנאל, פסקי הרא״ש, נתיב חיים, תורת נתנאל, מגן אברהם, רבי אברהם ברודא, קרלסרוהה, פראג, מהר״י וייל, גירוש יהודי בוהמיה</t>
         </is>
       </c>
-      <c r="I666" t="inlineStr">
+      <c r="I666" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבה בפראג ורב קרלסרוהה, יליד שטילינגן שבגרמניה, שלמד בישיבתו של רבי אברהם ברודא. לאחר גירוש יהודי בוהמיה ב־1744 עבר לגרמניה, ובשנת 1750 נתמנה לרבה של קרלסרוהה, ושם סיים את ״קרבן נתנאל״ על פסקי הרא״ש, שנדפס ב־1755. חיבר גם את ״נתיב חיים״ על שולחן ערוך אורח חיים ואת ״תורת נתנאל״, שו״ת ודרשות.</t>
         </is>
       </c>
-      <c r="J666" t="inlineStr">
+      <c r="J666" s="3" t="inlineStr">
         <is>
           <t>ביאור לפסקי הרא״ש שמשלים את החסר: סדרי מועד ונשים נותרו בלי ביאור, והוא חיבר עליהם את ״קרבן נתנאל״, שבו הוא מפרש את דברי הרא״ש, מברר את גרסאותיו ומביא מקורות לדבריו. הפירוש נדפס בצמוד לפסקי הרא״ש בש״ס וילנא.</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr">
+      <c r="K666" s="3" t="inlineStr">
         <is>
           <t>מהר״י וייל</t>
         </is>
       </c>
-      <c r="L666" t="inlineStr"/>
+      <c r="L666" s="3" t="inlineStr"/>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr">
+      <c r="A667" s="3" t="inlineStr">
         <is>
           <t>666</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
+      <c r="B667" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C667" s="3" t="inlineStr">
         <is>
           <t>רבי חייא רופא (בעל מעשה חייא)</t>
         </is>
       </c>
-      <c r="D667" t="inlineStr">
+      <c r="D667" s="3" t="inlineStr">
         <is>
           <t>כ־1550–1617</t>
         </is>
       </c>
-      <c r="E667" t="inlineStr">
+      <c r="E667" s="3" t="inlineStr">
         <is>
           <t>צפת; טבריה; ירושלים</t>
         </is>
       </c>
-      <c r="F667" t="inlineStr">
+      <c r="F667" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr">
+      <c r="G667" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, קבלה, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H667" t="inlineStr">
+      <c r="H667" s="3" t="inlineStr">
         <is>
           <t>מעשה חייא, צפת, טבריה, רבי שלמה סאגיש, רבי חיים ויטאל, האר״י, סמיכה בצפת, תיקון ליל שבועות, חכמי בית הוועד</t>
         </is>
       </c>
-      <c r="I667" t="inlineStr">
+      <c r="I667" s="3" t="inlineStr">
         <is>
           <t>פוסק ומקובל, מרבני צפת וירושלים, יליד צפת. למד בישיבתו של רבי שלמה סאגיש וקבלה אצל רבי חיים ויטאל, וקיבל גם מהאר״י, ובגיל עשרים ושלוש כיהן כדיין בבית דינו של רבי משה גלאנטי הראשון. הקים ישיבה בטבריה, כיהן כאב בית דין בירושלים וכראש ישיבה בצפת, ותשובותיו וחידושיו על הש״ס נדפסו בספר ״מעשה חייא״.</t>
         </is>
       </c>
-      <c r="J667" t="inlineStr">
+      <c r="J667" s="3" t="inlineStr">
         <is>
           <t>קבלה ופסיקה יחד: את הקבלה למד מרבי חיים ויטאל וקיבל גם מהאר״י, לימד אותה לתלמידיו, ובתיקון ליל שבועות של הרמ״ז מובאת כוונה שהגיעה אל הרמ״ז ממנו דרך רבי בנימין הלוי. בצפת היה מראשי הרבנים ומעשרים ״חכמי בית הוועד״, ורבי משה גלאנטי הראשון כתב בתשובותיו שהנהגת בית המדרש בעיר תהיה על פיו ועל פי חכמים נוספים.</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr">
+      <c r="K667" s="3" t="inlineStr">
         <is>
           <t>רבי חיים ויטאל, האר״י הקדוש, רבי משה זכות (הרמ״ז)</t>
         </is>
       </c>
-      <c r="L667" t="inlineStr"/>
+      <c r="L667" s="3" t="inlineStr"/>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr">
+      <c r="A668" s="3" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C668" t="inlineStr">
+      <c r="B668" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C668" s="3" t="inlineStr">
         <is>
           <t>רב פלטוי גאון</t>
         </is>
       </c>
-      <c r="D668" t="inlineStr">
+      <c r="D668" s="3" t="inlineStr">
         <is>
           <t>842–858 (ראש ישיבת פומבדיתא)</t>
         </is>
       </c>
-      <c r="E668" t="inlineStr">
+      <c r="E668" s="3" t="inlineStr">
         <is>
           <t>פומבדיתא</t>
         </is>
       </c>
-      <c r="F668" t="inlineStr">
+      <c r="F668" s="3" t="inlineStr">
         <is>
           <t>גאונים</t>
         </is>
       </c>
-      <c r="G668" t="inlineStr">
+      <c r="G668" s="3" t="inlineStr">
         <is>
           <t>הלכה ותשובות הגאונים, הנהגת ישיבה</t>
         </is>
       </c>
-      <c r="H668" t="inlineStr">
+      <c r="H668" s="3" t="inlineStr">
         <is>
           <t>ישיבת פומבדיתא, תשובות הגאונים, רב צמח בן פלטוי, רב שרירא גאון, רב האי גאון, תקנות, ערכאות של גויים, נוסח החרם, יהדות ספרד</t>
         </is>
       </c>
-      <c r="I668" t="inlineStr">
+      <c r="I668" s="3" t="inlineStr">
         <is>
           <t>רב פלטוי בר אביי היה גאון ישיבת פומבדיתא בשנים 842–858, ואחד הגאונים הפעילים ביותר שהקימה הישיבה. הוא התמנה בגיל צעיר יחסית ובלי מחלוקות, אף שלא בא ממשפחה מיוחסת, והשיב יותר תשובות הלכתיות מכל גאוני פומבדיתא שקדמו לו. בנו רב צמח בן פלטוי היה אף הוא גאון, ומצאצאיו רב שרירא גאון ובנו רב האי גאון.</t>
         </is>
       </c>
-      <c r="J668" t="inlineStr">
+      <c r="J668" s="3" t="inlineStr">
         <is>
           <t>גאון שחיבר את הישיבה אל הגולה: הוא יצר וביסס קשרים עם התפוצות במערב ובמיוחד עם ספרד, ולדברי אחד החוקרים הגביר את הפצת התלמוד והוראתו יותר מכל גאוני פומבדיתא שקדמו לו, ותיקן תקנות חשובות במשפט, ובהן היתר לפנות לערכאות של גויים כשהנתבע מסרב לידון בבית הדין היהודי.</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr">
+      <c r="K668" s="3" t="inlineStr">
         <is>
           <t>רב שרירא גאון, רב האי גאון</t>
         </is>
       </c>
-      <c r="L668" t="inlineStr"/>
+      <c r="L668" s="3" t="inlineStr"/>
     </row>
     <row r="669">
-      <c r="A669" t="inlineStr">
+      <c r="A669" s="3" t="inlineStr">
         <is>
           <t>668</t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C669" t="inlineStr">
+      <c r="B669" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C669" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב הלוי ממרויש (בעל שו״ת מן השמים)</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr">
+      <c r="D669" s="3" t="inlineStr">
         <is>
           <t>המאה ה־13 (נפטר 1233)</t>
         </is>
       </c>
-      <c r="E669" t="inlineStr">
+      <c r="E669" s="3" t="inlineStr">
         <is>
           <t>פרובנס</t>
         </is>
       </c>
-      <c r="F669" t="inlineStr">
+      <c r="F669" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G669" t="inlineStr">
+      <c r="G669" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, קבלה</t>
         </is>
       </c>
-      <c r="H669" t="inlineStr">
+      <c r="H669" s="3" t="inlineStr">
         <is>
           <t>שו״ת מן השמים, שאילת חלום, מרויש, פרובנס, התבודדות, הרדב״ז, רבי יעקב החסיד, הכרעה בין הפוסקים</t>
         </is>
       </c>
-      <c r="I669" t="inlineStr">
+      <c r="I669" s="3" t="inlineStr">
         <is>
           <t>רב ומקובל מחכמי יהדות פרובנס בתקופת הראשונים, בנו של רבי לוי, שנפטר בשנת 1233. התגורר במרויש, שימש כפוסק, כונה בעבר ״החסיד״ או ״הקדוש״, ולדברי הרדב״ז, שהיו בידיו קצת מתשובותיו, היה ״חכם גדול מקובל״. נודע בחיבורו ״שו״ת מן השמים״, שבו שאל את שאלותיו ההלכתיות מן השמים.</t>
         </is>
       </c>
-      <c r="J669" t="inlineStr">
+      <c r="J669" s="3" t="inlineStr">
         <is>
           <t>ההכרעה ההלכתית נשענת גם על שאלה מן השמים: כשהלכה הייתה מסופקת לו, שאל, לפי הרדב״ז, בהתבודדות, בתפילה ובהזכרת שמות, והיו משיבים לו. שאלותיו נשאלו בדרך של שאלת חלום, כשאלות לבית דין של מעלה, כדי להכריע בין הפוסקים.</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
-      <c r="L669" t="inlineStr"/>
+      <c r="K669" s="3" t="inlineStr"/>
+      <c r="L669" s="3" t="inlineStr"/>
     </row>
     <row r="670">
-      <c r="A670" t="inlineStr">
+      <c r="A670" s="3" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C670" t="inlineStr">
+      <c r="B670" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C670" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם סבע (בעל צרור המור)</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr">
+      <c r="D670" s="3" t="inlineStr">
         <is>
           <t>1440–1508</t>
         </is>
       </c>
-      <c r="E670" t="inlineStr">
+      <c r="E670" s="3" t="inlineStr">
         <is>
           <t>קסטיליה; פורטוגל; פאס; אדריאנופול</t>
         </is>
       </c>
-      <c r="F670" t="inlineStr">
+      <c r="F670" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G670" t="inlineStr">
+      <c r="G670" s="3" t="inlineStr">
         <is>
           <t>פרשנות התורה, קבלה והגות</t>
         </is>
       </c>
-      <c r="H670" t="inlineStr">
+      <c r="H670" s="3" t="inlineStr">
         <is>
           <t>צרור המור, אשכול הכופר, צרור החיים, תפארת בנים, גירוש ספרד, שמד פורטוגל, רבי יצחק די ליאון, פאס, אדריאנופול, פשט</t>
         </is>
       </c>
-      <c r="I670" t="inlineStr">
+      <c r="I670" s="3" t="inlineStr">
         <is>
           <t>רב, מקובל ופרשן מדור גירוש ספרד, יליד קסטיליה ותלמידו של רבי יצחק די ליאון. בגזירות השמד בפורטוגל ב־1497 נחטפו שני ילדיו והוטבלו לנצרות, והוא עצמו נאסר ועונה ונמלט לפאס שבמרוקו. את ספריו קבר בפורטוגל וכתב מחדש מזיכרונו, ובהם ״צרור המור״ על התורה ו״אשכול הכופר״ על רות ואסתר; הוא נפטר בדרכו לאיטליה בשנת 1508.</t>
         </is>
       </c>
-      <c r="J670" t="inlineStr">
+      <c r="J670" s="3" t="inlineStr">
         <is>
           <t>פירושו לתורה ״צרור המור״ מצרף פשט, דרוש וקבלה בביאור אחד. הוא גם עדות אישית לגירוש ספרד ולשמד פורטוגל: בפרשת ויצא מגולל סבע את תלאותיו בקונטרס ״תפארת בנים״.</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr">
+      <c r="K670" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף קארו</t>
         </is>
       </c>
-      <c r="L670" t="inlineStr"/>
+      <c r="L670" s="3" t="inlineStr"/>
     </row>
     <row r="671">
-      <c r="A671" t="inlineStr">
+      <c r="A671" s="3" t="inlineStr">
         <is>
           <t>670</t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
+      <c r="B671" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C671" s="3" t="inlineStr">
         <is>
           <t>רבי אליעזר אשכנזי (בעל מעשי ה׳)</t>
         </is>
       </c>
-      <c r="D671" t="inlineStr">
+      <c r="D671" s="3" t="inlineStr">
         <is>
           <t>כ־1513–1585</t>
         </is>
       </c>
-      <c r="E671" t="inlineStr">
+      <c r="E671" s="3" t="inlineStr">
         <is>
           <t>קהיר; ונציה; פוזנא; קרקוב</t>
         </is>
       </c>
-      <c r="F671" t="inlineStr">
+      <c r="F671" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G671" t="inlineStr">
+      <c r="G671" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא, פילוסופיה והלכה</t>
         </is>
       </c>
-      <c r="H671" t="inlineStr">
+      <c r="H671" s="3" t="inlineStr">
         <is>
           <t>מעשי ה׳, יוסף לקח, פירוש ההגדה של פסח, פשוטו של מקרא, סליחות ופזמונים, רבי יוסף טאיטצאק, קפריסין, קרימונה, פוזנא, קרקוב</t>
         </is>
       </c>
-      <c r="I671" t="inlineStr">
+      <c r="I671" s="3" t="inlineStr">
         <is>
           <t>רב, פרשן מקרא, פייטן ופילוסוף, ככל הנראה יליד ונציה, שלמד בסלוניקי אצל רבי יוסף טאיטצאק. שימש דיין בקהיר, חי בקפריסין ובאיטליה, ולבסוף היה רב העיר ורב המדינה בפוזנא ועבר לקרקוב, שבה נפטר ב־1585. ספרו העיקרי ״מעשי ה׳״ הוא פירוש לחמשה חומשי תורה ובתוכו פירוש להגדה של פסח, והוא חיבר גם את ״יוסף לקח״ על מגילת אסתר.</t>
         </is>
       </c>
-      <c r="J671" t="inlineStr">
+      <c r="J671" s="3" t="inlineStr">
         <is>
           <t>כפרשן דבק בפשוטו של מקרא, אך אינו נרתע מלחלוק על רש״י, האבן עזרא, הרמב״ם והרמב״ן ולהציע פירושים עצמאיים. בהקדמתו כתב שהוא מקבל את הטוב ודוחה את הרע בלי להתחשב בשם האומר.</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr">
+      <c r="K671" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף טאיטצאק</t>
         </is>
       </c>
-      <c r="L671" t="inlineStr"/>
+      <c r="L671" s="3" t="inlineStr"/>
     </row>
     <row r="672">
-      <c r="A672" t="inlineStr">
+      <c r="A672" s="3" t="inlineStr">
         <is>
           <t>671</t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C672" t="inlineStr">
+      <c r="B672" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C672" s="3" t="inlineStr">
         <is>
           <t>רבי משה גלאנטי (המג״ן)</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr">
+      <c r="D672" s="3" t="inlineStr">
         <is>
           <t>כ־1620–1689</t>
         </is>
       </c>
-      <c r="E672" t="inlineStr">
+      <c r="E672" s="3" t="inlineStr">
         <is>
           <t>ירושלים; צפת</t>
         </is>
       </c>
-      <c r="F672" t="inlineStr">
+      <c r="F672" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G672" t="inlineStr">
+      <c r="G672" s="3" t="inlineStr">
         <is>
           <t>הלכה, מנהיגות ופרשנות</t>
         </is>
       </c>
-      <c r="H672" t="inlineStr">
+      <c r="H672" s="3" t="inlineStr">
         <is>
           <t>אלף המגן, זבח השלמים, קרבן חגיגה, פרפראות לחכמה, הראשון לציון, שד״ר, כספי החלוקה, ישיבת בית יעקב, רבי משה גלאנטי הראשון, רבי משה חגיז</t>
         </is>
       </c>
-      <c r="I672" t="inlineStr">
+      <c r="I672" s="3" t="inlineStr">
         <is>
           <t>הראשון לציון הראשון וראש רבני ירושלים במאה ה־17, שכונה לעיתים ״המג״ן״, יליד צפת ונכד רבי משה גלאנטי הראשון. למד בצפת אצל רבי ברוך ברזילי ורבי גבריאל איספיראנסה, ובגיל 34 עבר לירושלים, שם עמד בראש ישיבת בית יעקב ונשלח כשד״ר לחוץ לארץ. חיבר את ״אלף המגן״, אוסף שו״ת ובו אלף תשובות, ואת ״זבח השלמים״ על התורה, ונפטר בירושלים ב־1689.</t>
         </is>
       </c>
-      <c r="J672" t="inlineStr">
+      <c r="J672" s="3" t="inlineStr">
         <is>
           <t>הסכים להתמנות לרבה של ירושלים רק בתואר שאינו שררתי, ״ראשון לציון״ ולא ״רב״, כי ראה את עצמו שווה בין שווים בגדלותו בתורה. הוא תיקן לחלק את כספי החלוקה לעשרים וארבעה חלקים: שנים־עשר לירושלים, שמונה לצפת וארבעה לחברון.</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr">
+      <c r="K672" s="3" t="inlineStr">
         <is>
           <t>רבי משה חגיז, רבנו חזקיה די סילוה, הרב אברהם יצחקי</t>
         </is>
       </c>
-      <c r="L672" t="inlineStr"/>
+      <c r="L672" s="3" t="inlineStr"/>
     </row>
     <row r="673">
-      <c r="A673" t="inlineStr">
+      <c r="A673" s="3" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr">
+      <c r="B673" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C673" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם גלאנטי (בעל קול בוכים)</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr">
+      <c r="D673" s="3" t="inlineStr">
         <is>
           <t>תחילת המאה ה־16 – 1560</t>
         </is>
       </c>
-      <c r="E673" t="inlineStr">
+      <c r="E673" s="3" t="inlineStr">
         <is>
           <t>צפת; רומא</t>
         </is>
       </c>
-      <c r="F673" t="inlineStr">
+      <c r="F673" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G673" t="inlineStr">
+      <c r="G673" s="3" t="inlineStr">
         <is>
           <t>קבלה ופרשנות</t>
         </is>
       </c>
-      <c r="H673" t="inlineStr">
+      <c r="H673" s="3" t="inlineStr">
         <is>
           <t>קינת סתרים, קול בוכים, ירח יקר, זכות אבות, הרמ״ק, הזוהר, מגילת איכה, זהרי חמה, אור יקר, צפת</t>
         </is>
       </c>
-      <c r="I673" t="inlineStr">
+      <c r="I673" s="3" t="inlineStr">
         <is>
           <t>מקובל, יליד רומא בתחילת המאה ה־16, שעלה לצפת והיה מתלמידי הרמ״ק. כמו אביו מרדכי ואחיו המבוגר ממנו, רבי משה גלאנטי הראשון, חי חיי סגפנות וקדושה. חיבר את ״קינת סתרים״ (״קול בוכים״), פירוש קבלי למגילת איכה שהודפס בוונציה ב־1589 בעריכת בנו שמואל, את ״ירח יקר״ על הזוהר ואת ״זכות אבות״ על מסכת אבות, ונפטר ב־1560.</t>
         </is>
       </c>
-      <c r="J673" t="inlineStr">
+      <c r="J673" s="3" t="inlineStr">
         <is>
           <t>פירושו לזוהר, ״ירח יקר״, נקרא כך על שם ״אור יקר״ של רבו הרמ״ק, כמאמר ״פני משה כפני חמה״, ורבי אברהם אזולאי קיצר אותו ב״זהרי חמה״. את מגילת איכה פירש ״על דרך האמת״, כלומר בקבלה, ב״קינת סתרים״ שהודפס כמה פעמים.</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr">
+      <c r="K673" s="3" t="inlineStr">
         <is>
           <t>רבי משה קורדובירו (הרמ״ק), רבי אברהם אזולאי</t>
         </is>
       </c>
-      <c r="L673" t="inlineStr"/>
+      <c r="L673" s="3" t="inlineStr"/>
     </row>
     <row r="674">
-      <c r="A674" t="inlineStr">
+      <c r="A674" s="3" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C674" t="inlineStr">
+      <c r="B674" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C674" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב קשטרו (מהריק״ש)</t>
         </is>
       </c>
-      <c r="D674" t="inlineStr">
+      <c r="D674" s="3" t="inlineStr">
         <is>
           <t>כ־1525–1612</t>
         </is>
       </c>
-      <c r="E674" t="inlineStr">
+      <c r="E674" s="3" t="inlineStr">
         <is>
           <t>קהיר; אלכסנדריה; ירושלים</t>
         </is>
       </c>
-      <c r="F674" t="inlineStr">
+      <c r="F674" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G674" t="inlineStr">
+      <c r="G674" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת</t>
         </is>
       </c>
-      <c r="H674" t="inlineStr">
+      <c r="H674" s="3" t="inlineStr">
         <is>
           <t>ערך לחם, אהלי יעקב, תולדות יעקב, קול יעקב, מרא דאתרא, הרדב״ז, המהרלב״ח, שולחן ערוך, קהיר, יהדות מצרים</t>
         </is>
       </c>
-      <c r="I674" t="inlineStr">
+      <c r="I674" s="3" t="inlineStr">
         <is>
           <t>מרבניה הנודעים של יהדות מצרים, יליד מצרים בסביבות 1525, ששימש כרבו של קהל המוסתערבים בקהיר. למד בירושלים אצל הרלב״ח, אך רבו המובהק היה הרדב״ז, ובמצרים ראו בו גדול הדור, ״מרא דאתרא״. נתפרסם בעיקר בספרו ״ערך לחם״, הגהות על השולחן ערוך, וחיבר גם את שו״ת ״אהלי יעקב״; ככל הנראה נפטר בקהיר ב־1610 או ב־1612.</t>
         </is>
       </c>
-      <c r="J674" t="inlineStr">
+      <c r="J674" s="3" t="inlineStr">
         <is>
           <t>ב״ערך לחם״ הגיה את השולחן ערוך, והגהותיו תואמות פעמים רבות את הגהות הרמ״א. הספרדים בכל ארץ מצרים פסקו כמותו גם במקום שחלק על מרן הבית יוסף.</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr">
+      <c r="K674" s="3" t="inlineStr">
         <is>
           <t>הרדב״ז, רבי לוי בן חביב (המהרלב״ח)</t>
         </is>
       </c>
-      <c r="L674" t="inlineStr"/>
+      <c r="L674" s="3" t="inlineStr"/>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr">
+      <c r="A675" s="3" t="inlineStr">
         <is>
           <t>674</t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C675" t="inlineStr">
+      <c r="B675" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C675" s="3" t="inlineStr">
         <is>
           <t>רבי חיים כפוסי (בעל הנס)</t>
         </is>
       </c>
-      <c r="D675" t="inlineStr">
+      <c r="D675" s="3" t="inlineStr">
         <is>
           <t>כ־1540–1631</t>
         </is>
       </c>
-      <c r="E675" t="inlineStr">
+      <c r="E675" s="3" t="inlineStr">
         <is>
           <t>קהיר; אלכסנדריה; אלג׳יר</t>
         </is>
       </c>
-      <c r="F675" t="inlineStr">
+      <c r="F675" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G675" t="inlineStr">
+      <c r="G675" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, פרשנות התורה</t>
         </is>
       </c>
-      <c r="H675" t="inlineStr">
+      <c r="H675" s="3" t="inlineStr">
         <is>
           <t>ספרי חיים, באור החיים, בעל הנס, מכילתא דרשב״י, קהיר, אלכסנדריה, דמיאט, אלג׳יר, יהדות מצרים, המהריק״ש</t>
         </is>
       </c>
-      <c r="I675" t="inlineStr">
+      <c r="I675" s="3" t="inlineStr">
         <is>
           <t>פוסק הלכה ופרשן, מגדולי חכמי מצרים במאות ה־16 וה־17, יליד אלג׳יר למשפחה שמוצאה מספרד. חייו היו מלאי סבל ונדודים בין קהיר, אלכסנדריה ודמיאט, ולפי אגדה נפקחו עיניו בנס אחרי שלקה בעיוורון, ומאז כונה ״בעל הנס״. תשובותיו נשארו בכתב יד מאות שנים; חיבר גם את ״באור החיים״ על התורה ואת ״ספרי חיים״ על המכילתא, ונפטר ב־1631.</t>
         </is>
       </c>
-      <c r="J675" t="inlineStr">
+      <c r="J675" s="3" t="inlineStr">
         <is>
           <t>תשובותיו משקפות את חיי היהודים במצרים ובאימפריה העות׳מאנית במשך יותר מ־60 שנה, ובהן מחלוקות הלכתיות עם רבה של מצרים, המהריק״ש. בביאורו לתורה, ״באור החיים״, הוא מפרש בדרך פשט ורמז.</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
-      <c r="L675" t="inlineStr"/>
+      <c r="K675" s="3" t="inlineStr"/>
+      <c r="L675" s="3" t="inlineStr"/>
     </row>
     <row r="676">
-      <c r="A676" t="inlineStr">
+      <c r="A676" s="3" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C676" t="inlineStr">
+      <c r="B676" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C676" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל ויטאל (בן רבי חיים)</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr">
+      <c r="D676" s="3" t="inlineStr">
         <is>
           <t>1598–1677</t>
         </is>
       </c>
-      <c r="E676" t="inlineStr">
+      <c r="E676" s="3" t="inlineStr">
         <is>
           <t>דמשק; מצרים</t>
         </is>
       </c>
-      <c r="F676" t="inlineStr">
+      <c r="F676" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G676" t="inlineStr">
+      <c r="G676" s="3" t="inlineStr">
         <is>
           <t>קבלה והלכה</t>
         </is>
       </c>
-      <c r="H676" t="inlineStr">
+      <c r="H676" s="3" t="inlineStr">
         <is>
           <t>שער הגלגולים, כתבי האר״י, שמונה שערים, באר מים חיים, מקור חיים, תוצאות חיים, חמדת ישראל, דמשק, קבלת האר״י, רבי חיים ויטאל</t>
         </is>
       </c>
-      <c r="I676" t="inlineStr">
+      <c r="I676" s="3" t="inlineStr">
         <is>
           <t>מרבני ומקובלי דמשק ובנו של רבי חיים ויטאל: נולד בדמשק, שימש בה רב ודיין והקים ישיבה גדולה שלמדו בה גם קבלה. היה מגדולי תלמידי אביו, העתיק וסידר את כתבי אביו ואת כתבי האר״י, ובהם ״שער הגלגולים״, ובהמשך חייו עבר למצרים והקים שם ישיבה. כתב תשובות בהלכה ובקבלה ודרשות לראש חודש, ונפטר במצרים ב־1677.</t>
         </is>
       </c>
-      <c r="J676" t="inlineStr">
+      <c r="J676" s="3" t="inlineStr">
         <is>
           <t>כמעתיק ומסדר של כתבי אביו ושל כתבי האר״י שימר את תורת האר״י, וספריו נחשבו, כפי שכתב החיד״א, למדויקים והמוסמכים ביותר לכתבי קבלת האר״י. את תשובותיו בהלכה ובקבלה כתב לשואלים ממצרים, מארץ ישראל ומרחבי סוריה.</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr">
+      <c r="K676" s="3" t="inlineStr">
         <is>
           <t>רבי חיים ויטאל</t>
         </is>
       </c>
-      <c r="L676" t="inlineStr"/>
+      <c r="L676" s="3" t="inlineStr"/>
     </row>
     <row r="677">
-      <c r="A677" t="inlineStr">
+      <c r="A677" s="3" t="inlineStr">
         <is>
           <t>676</t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C677" t="inlineStr">
+      <c r="B677" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C677" s="3" t="inlineStr">
         <is>
           <t>רבי אהרן שמואל קאיידנובר (המהרש״ק)</t>
         </is>
       </c>
-      <c r="D677" t="inlineStr">
+      <c r="D677" s="3" t="inlineStr">
         <is>
           <t>1614–1676</t>
         </is>
       </c>
-      <c r="E677" t="inlineStr">
+      <c r="E677" s="3" t="inlineStr">
         <is>
           <t>קרקוב; בריסק; פרנקפורט</t>
         </is>
       </c>
-      <c r="F677" t="inlineStr">
+      <c r="F677" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G677" t="inlineStr">
+      <c r="G677" s="3" t="inlineStr">
         <is>
           <t>הלכה ופרשנות התלמוד</t>
         </is>
       </c>
-      <c r="H677" t="inlineStr">
+      <c r="H677" s="3" t="inlineStr">
         <is>
           <t>ברכת הזבח, תפארת שמואל, אמונת שמואל, ברכת שמואל, סדר קדשים, גזירות ת״ח ת״ט, פסקי הרא״ש, המהרש״א, בריסק, קרקוב</t>
         </is>
       </c>
-      <c r="I677" t="inlineStr">
+      <c r="I677" s="3" t="inlineStr">
         <is>
           <t>רב אשכנזי מראשוני האחרונים, שנולד ככל הנראה בקוידנוב שבבלארוס, למד אצל רבי יעקב מלובלין ואחר כך אצל בנו והיה דיין בבית דינו של רבי משה לימא. בגזירות ת״ח ת״ט נרצחו שתי בנותיו ואבדו רוב כתביו, ולאחר מכן כיהן ברבנות בערים רבות, בהן בריסק, פרנקפורט וקרקוב. חיבר את ״ברכת הזבח״ על סדר קדשים ואת ״תפארת שמואל״ על פסקי הרא״ש ואת שו״ת ״אמונת שמואל״, ונפטר ב־1676.</t>
         </is>
       </c>
-      <c r="J677" t="inlineStr">
+      <c r="J677" s="3" t="inlineStr">
         <is>
           <t>כתב ״בדרך קצרה וכשרה״, כלשון החיד״א. הגהותיו על הרא״ש והשגותיו על המהרש״א נדפסו בתוך הש״ס בכל מהדורותיו עד ש״ס וילנה, והמגן אברהם קורא לו ״גאון״. הוא התנגד לפסוק לפי השולחן ערוך ונושאי כליו ותמך בפסיקה לפי ארבעה טורים עם הבית יוסף.</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr">
+      <c r="K677" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם אבלי גומבינר (המגן אברהם)</t>
         </is>
       </c>
-      <c r="L677" t="inlineStr"/>
+      <c r="L677" s="3" t="inlineStr"/>
     </row>
     <row r="678">
-      <c r="A678" t="inlineStr">
+      <c r="A678" s="3" t="inlineStr">
         <is>
           <t>677</t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C678" t="inlineStr">
+      <c r="B678" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C678" s="3" t="inlineStr">
         <is>
           <t>רבי יהודה בן עטר (בעל מנחת יהודה)</t>
         </is>
       </c>
-      <c r="D678" t="inlineStr">
+      <c r="D678" s="3" t="inlineStr">
         <is>
           <t>1655–1733</t>
         </is>
       </c>
-      <c r="E678" t="inlineStr">
+      <c r="E678" s="3" t="inlineStr">
         <is>
           <t>פאס; מקנס</t>
         </is>
       </c>
-      <c r="F678" t="inlineStr">
+      <c r="F678" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G678" t="inlineStr">
+      <c r="G678" s="3" t="inlineStr">
         <is>
           <t>הלכה, דרשנות ופרשנות המקרא</t>
         </is>
       </c>
-      <c r="H678" t="inlineStr">
+      <c r="H678" s="3" t="inlineStr">
         <is>
           <t>מנחת יהודה, שיר מכתם, דרשנות, תקנות הקהילה, צורף, פאס, מקנס, יהדות מרוקו</t>
         </is>
       </c>
-      <c r="I678" t="inlineStr">
+      <c r="I678" s="3" t="inlineStr">
         <is>
           <t>אב בית דין ודיין בפאס ובמקנס שבמרוקו, פרשן מקרא ומרבניה הגדולים של המדינה, יליד פאס. התפרנס כצורף מיגיע כפיו ולא רצה שכר מקופת הציבור, למד מרבי וידאל הצרפתי השלישי ומרבי מנחם סירירו, ובשנת 1698 מונה לדיין בפאס. חיבר את ״מנחת יהודה״, דרשות על התורה, ואת ״שיר מכתם״ על הלכות שחיטה, ונפטר ב־1733.</t>
         </is>
       </c>
-      <c r="J678" t="inlineStr">
+      <c r="J678" s="3" t="inlineStr">
         <is>
           <t>ראה שתלמידיו, על גדלותם בתורה, אינם יודעים לדרוש, ולימד אותם נאום ודרוש: ״מנחת יהודה״ מקורו בדרשות שבת במנחה, שאחריהן דרש תלמיד אחר. כל חייו התפרנס מיגיע כפיו, ותיקן לקהילתו תקנות במיסים, במסחר ובהלוואות מגויים.</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
-      <c r="L678" t="inlineStr"/>
+      <c r="K678" s="3" t="inlineStr"/>
+      <c r="L678" s="3" t="inlineStr"/>
     </row>
     <row r="679">
-      <c r="A679" t="inlineStr">
+      <c r="A679" s="3" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C679" t="inlineStr">
+      <c r="B679" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C679" s="3" t="inlineStr">
         <is>
           <t>רבי מנחם ציוני (בעל ספר ציוני)</t>
         </is>
       </c>
-      <c r="D679" t="inlineStr">
+      <c r="D679" s="3" t="inlineStr">
         <is>
           <t>כ־1340–1410</t>
         </is>
       </c>
-      <c r="E679" t="inlineStr">
+      <c r="E679" s="3" t="inlineStr">
         <is>
           <t>שפיירא; קלן; ירושלים; ונציה; גרמניה</t>
         </is>
       </c>
-      <c r="F679" t="inlineStr">
+      <c r="F679" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G679" t="inlineStr">
+      <c r="G679" s="3" t="inlineStr">
         <is>
           <t>קבלה, פיוט ופרשנות התורה</t>
         </is>
       </c>
-      <c r="H679" t="inlineStr">
+      <c r="H679" s="3" t="inlineStr">
         <is>
           <t>ציוני, צפוני ציוני, ספר הבהיר, הזוהר, הרמב״ן, קינות, ציון מעון חשקי, רבי יצחק מבילשטיין, שפיירא, קרימונה</t>
         </is>
       </c>
-      <c r="I679" t="inlineStr">
+      <c r="I679" s="3" t="inlineStr">
         <is>
           <t>מקובל ופייטן מחכמי אשכנז, יליד שפיירא, שנסע בצעירותו לירושלים ולמד בישיבתו של רבי יצחק מבילשטיין. הוא האדם הראשון הידוע שבחר לכנות עצמו ״ציוני״, על שם לימודיו בירושלים. חיבר את הספר ״ציוני״ על התורה, שנדפס בקרימונה ב־1559, ואת ״צפוני ציוני״, וכתב עשרות שירים.</t>
         </is>
       </c>
-      <c r="J679" t="inlineStr">
+      <c r="J679" s="3" t="inlineStr">
         <is>
           <t>ספרו ״ציוני״ מצרף את הזוהר וספר הבהיר עם דברי הראשונים, כסעדיה גאון, הרמב״ם, אבן עזרא והרמב״ן, לפירוש התורה ״על דרך האמת״, ובראשי פרקיו ובסופיהם חרוזים ובפתיחתו ובסיומו שירים. החיד״א שיבח אותו ב״שם הגדולים״, וגדולי האחרונים כהשל״ה והמגן אברהם הביאו דברים בשמו.</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr">
+      <c r="K679" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף שלמה דלמדיגו – יש״ר מקנדיה, רבי ישעיה הלוי הורוויץ (השל״ה הקדוש), רבי אברהם אבלי גומבינר (המגן אברהם)</t>
         </is>
       </c>
-      <c r="L679" t="inlineStr"/>
+      <c r="L679" s="3" t="inlineStr"/>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr">
+      <c r="A680" s="3" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C680" t="inlineStr">
+      <c r="B680" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C680" s="3" t="inlineStr">
         <is>
           <t>רבי אליהו בחור (בעל מסורת המסורת)</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr">
+      <c r="D680" s="3" t="inlineStr">
         <is>
           <t>1469–1549</t>
         </is>
       </c>
-      <c r="E680" t="inlineStr">
+      <c r="E680" s="3" t="inlineStr">
         <is>
           <t>גרמניה; ונציה; פדובה; רומא</t>
         </is>
       </c>
-      <c r="F680" t="inlineStr">
+      <c r="F680" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G680" t="inlineStr">
+      <c r="G680" s="3" t="inlineStr">
         <is>
           <t>דקדוק עברי, מסורה ומילונאות</t>
         </is>
       </c>
-      <c r="H680" t="inlineStr">
+      <c r="H680" s="3" t="inlineStr">
         <is>
           <t>הבחור, התשבי, מסורת המסורת, טוב טעם, המתורגמן, סבסטיאן מינסטר, פאולוס פאגיוס, אג׳ידיו דה ויטרבו, ספרות יידיש, מלומדים נוצרים</t>
         </is>
       </c>
-      <c r="I680" t="inlineStr">
+      <c r="I680" s="3" t="inlineStr">
         <is>
           <t>בלשן עברי וחוקר המסורה בתקופת הרנסאנס, יליד נוישטאדט שבבוואריה, שעבר בצעירותו לאיטליה והתגורר בוונציה, בפדובה וברומא. לימד עברית למלומדים נוצרים, עבד כמגיה בבית דפוס בוונציה ופיקח על בית דפוס באיזנא וחיבר ספרי דקדוק ומילונים, ובהם ״הבחור״ ו״התשבי״, וכן את ״מסורת המסורת״ ו״טוב טעם״. מת בוונציה ב־1549.</t>
         </is>
       </c>
-      <c r="J680" t="inlineStr">
+      <c r="J680" s="3" t="inlineStr">
         <is>
           <t>בספרו ״מסורת המסורת״ טען שסימני הניקוד והטעמים חודשו בידי בעלי המסורה ואינם מזמן התלמוד, דעה שהחיד״א מביא ומסתייג ממנה. בספריו ובהוראתו הנחיל את הדקדוק העברי למלומדים נוצרים, שתרגמו את חיבוריו ללטינית.</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
-      <c r="L680" t="inlineStr"/>
+      <c r="K680" s="3" t="inlineStr"/>
+      <c r="L680" s="3" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>רב יהודאי גאון</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>המאה ה־8</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>סורא; פומבדיתא; בבל</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>גאונים</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>הלכה והנהגה</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>הלכות פסוקות, הלכות ראו, תשובות הגאונים, ישיבת סורא, ישיבת פומבדיתא, מנהג שמד, מנהגי ארץ ישראל, פירקוי בן באבוי</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>גאון סורא בן נחמן, שנחשב לאחת הדמויות המרכזיות בראשית תקופת הגאונים, ועמד בראש הישיבה בשנים 757–761 למניינם אף שחינוכו התורני נעשה בישיבת פומבדיתא. היה עיוור, והסתמך על הכתבה לסופרים ועל אמירת תורתו בעל פה. הוא הגאון הראשון שתשובותיו ההלכתיות השתמרו בהיקף משמעותי.</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>ספר ״הלכות פסוקות״, שחובר על ידו או בבית מדרשו, הוא הניסיון הקודיפיקטיבי הראשון לאחר חתימת התלמוד הבבלי; הושמטו בו סבך הדיון התלמודי ושמות האמוראים. הוא נאבק במנהגי ארץ ישראל כדי להשליט את סמכות התלמוד הבבלי, ותלמידיו הפיצו את תורתו בתפוצות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>רב (אבא אריכא)</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>כ־175–247</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>בבל; ארץ ישראל; סורא; ציפורי</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>אמוראים</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>הלכה, הנהגה ותפילה</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>ישיבת סורא, ירחי כלה, תקיעתא דבי רב, עלינו לשבח, הלכה כרב באיסורי, רב ושמואל, ראשון האמוראים, רבי חייא</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>אמורא יליד בבל, ממשפחה מיוחסת, שעלה בצעירותו לארץ ישראל עם דודו רבי חייא ולמד בבית מדרשו של רבי יהודה הנשיא. רבי יהודה הנשיא העניק לו סמיכה חלקית בלבד: הותר לו להורות בענייני איסור והיתר, אך לא להתיר בכור בעל מום. בשנת 219 לערך חזר לבבל, ובהמשך הקים בסורא את ישיבתו וייסד בה את ״ירחי כלה״, כינוסי לימוד המוניים בחודשים אלול ואדר.</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>הכלל ״הלכה כרב באיסורי וכשמואל בממוני״ קובע שבמחלוקות בין רב לשמואל ההלכה כרב בענייני איסור והיתר, וכשמואל בדיני ממונות. הוא נחשב למעצב המרכזי של תפילת מוסף של ראש השנה, ״תקיעתא דבי רב״, שבה סודרו ברכות מלכויות, זכרונות ושופרות ושולבה תפילת ״עלינו לשבח״.</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>רבי אברהם זכות (בעל ספר יוחסין)</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>1452–כ־1515</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>סלמנקה; ליסבון; טוניס</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>אסטרונומיה, מתמטיקה והיסטוריוגרפיה</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>החיבור הגדול, ספר יוחסין, אסטרולאב ימי, אלמנך נצחי, ואסקו דה גאמה, יוסף ויסינו, גירוש ספרד</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>אסטרונום והיסטוריון, יליד סלמנקה שבקסטיליה, שלמד אסטרונומיה באוניברסיטת סלמנקה (ויתכן שאף לימד בה), השלים בעירו ב־1478 את חיבורו האסטרונומי ״החיבור הגדול״ ושימש גם כרב הקהילה. לאחר צו הגירוש מספרד ב־1492 פנה לפורטוגל, ושם מינה אותו המלך ז׳ואאו השני לאסטרונום והיסטוריוגרף מלכותי; כשהוטלו גזירות המרה וגירוש על יהודי פורטוגל בשלהי 1496 סירב להמיר את דתו ונמלט לטוניס. בטוניס חיבר את ״ספר יוחסין״, ולפי מקורות שונים נפטר בירושלים או בדמשק, בסביבות 1515 או ב־1520.</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>הוא ראה במדע חוליה משלימה להבנת התורה וההלכה, ובספר יוחסין העיד שעיסוקו באסטרונומיה לא נועד אלא ״להבין דברי חז״ל וההלכות שכתבו בזה״. לפי הכתוב סיפק לוואסקו דה גאמה טבלאות ניווט ותירגל את מלחיו באסטרולאב ימי משוכלל, ו״ספר יוחסין״ שלו מגולל את שלשלת קבלת התורה ומסירתה ממשה רבנו ועד דורו.</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>רבי אברהם בן נתן הירחי (בעל ספר המנהיג)</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>כ־1155–1215</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>לוניל, פרובנס; דמפייר, צרפת; טולדו, ספרד</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>הלכה ומנהג</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>ספר המנהיג, הירחי, מנהג, לוניל, טולדו, משפחת אבן שושן</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>חכם מפרובנס במאות השתים־עשרה והשלוש־עשרה, הקרוי ״הירחי״ על שם לוניל, ומחבר ״ספר המנהיג״. למד בצפון צרפת בדמפייר, בישיבת ר״י הזקן, ולאחר נדודים ארוכים בקהילות אירופה התיישב בטולדו שבספרד, שם זכה לחסותם של יוסף אבן שושן ובניו. ״ספר המנהיג״, שהחל לכתוב ב־1204 והקדיש לתומכיו, מורכב בצורתו הנוכחית מתשובותיו ומקטעים מחיבורי הרי״ף, רבי יצחק אבן גיאת ורבי יצחק בן אבא מרי, ומתעד מנהגי בתי כנסת שראה בעצמו בארצות רבות.</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>לפי המחקר באתר, ראה בכל מנהג רווח בקהילות ישראל מנהג שיש לו שורש בתלמוד, במדרש או בתשובות הגאונים, ולכן ביקש לגלות את מקורו ולא לבטלו. ספרו כולל ציטוטים מילוליים רבים מן התלמודים ומן מדרשי ההלכה והאגדה, ובהם מאוספי אגדה שאבדו, ולכן הוא תורם לביקורת הנוסח של ספרות זו.</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>רבי אהרן ברכיה ממודינה (בעל מעבר יבק)</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>כ־1549–1639</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>מודינה, איטליה</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>קבלה, הלכה וליטורגיה</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>מעבר יבק, אשמורת הבוקר, חברה קדישא, קבלת האר״י, מודינה, הרמ״ע מפאנו</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>רב ומקובל איטלקי ממודינה, מחבר ״מעבר יבק״ (1626), שנכתב לבקשת החברה קדישא של מנטובה ושימש מקור מרכזי למנהגי הקבורה. היה תלמידם של רבי הלל ממודינה ושל הרמ״ע מפאנו, ולמד גם אצל רבי ישראל סרוג, תלמידו של האר״י. הסידור ״אשמורת הבוקר״ (1624), שחיבר עבור חבורת משכימי קום במודינה, היה חיבורו הראשון.</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>בהקדמה ל״מעבר יבק״, שנקרא על שם חציית נהר היבוק בידי יעקב, הוא מפרש את המעבר כחציית הנשמה את הגבול בין העולם הזה לעולם הבא. הגותו מוצגת במחקר באתר כסינתזה בין קבלת הרמ״ק לקבלת האר״י, ובה הוא נעזר במערכת הספירות והפרצופים הלוריאנית כפי שתורגמה בידי רבי ישראל סרוג.</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>רב אחאי גאון (בעל השאילתות)</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>המאה ה־8</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>פומבדיתא, בבל; ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>גאונים</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>הלכה ודרשנות</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>שאילתות דרב אחאי, משבחא, פומבדיתא, ראש הגולה, נטרונאי כהנא, העמק שאלה</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>חכם בבלי מישיבת פומבדיתא במאה השמינית, מחבר ה״שאילתות״ (אף שלא ידוע אם חיברן בעצמו או ליקט אותן), הספר הראשון שנודע לאחר חתימת התלמוד. הכינוי ״גאון״ הצמוד לשמו אינו מינוי רשמי, שכן לא עמד בראש אחת משתי הישיבות. כשנפטר גאון פומבדיתא עקף ראש הגולה שלמה בר חסדאי, מתוך טינה אישית כלפיו, את אחאי ומינה את נטרונאי כהנא בן אמונה, תלמידו; אחאי עלה לארץ ישראל וחי בה עד מותו.</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>ה״שאילתות״ הן כמאה ותשעים דרשות בארמית על הלכה ומוסר, ובכל אחת מהן נפתחת מצווה, נשאלת שאלה הלכתית, באה דרשה של אגדה ומוסר ובסופה פסק קצר. ספרי פסק גאוניים כ״הלכות פסוקות״ ו״הלכות גדולות״ נשענו על ה״שאילתות״, ראשונים כרש״י, הרי״ף והרמב״ם ציטטו אותן, ועליהן נכתבו הפירושים ״שאילת שלום״ ו״העמק שאלה״.</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>רבי דוד אופנהיים</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>1664–1736</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>וורמייזא; ניקלשבורג; פראג</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, איסוף ספרים</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>נשאל דוד, ספריית אופנהיים, הספרייה הבודליאנית, ניקלשבורג, פראג, וורמייזא, אוקספורד, יהודי החצר, שבות יעקב</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>רב ופוסק יליד וורמייזא, שכיהן כרבה של ניקלשבורג ולאחר מכן כרבה הראשי של פראג וגלילות בוהמיה, ועמד בפראג בראש ישיבה גדולה. הקים אוסף גדול של ספרים וכתבי יד עבריים, שנרכש בשלמותו ב־1829 על ידי הספרייה הבודליאנית באוקספורד. נפטר ב־1736 ונקבר בבית הקברות היהודי העתיק בפראג.</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>בשיעוריו נהג להביא לפני תלמידיו כתבי יד נדירים ומהדורות דפוס עתיקות כדי לברר גרסאות, ואת ספרייתו שמר בהנובר, בבית חמיו. חיבר כעשרים ספרים, ובהם שו״ת ״נשאל דוד״, אך לא הדפיס את מרביתם בחייו.</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>רבי ידידיה שלמה רפאל נורצי (בעל מנחת שי)</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>כ־1560–1626</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>מנטובה</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>פרשנות המקרא ומסורה</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>מנחת שי, גודר פרץ, מסורה, נוסח המקרא, אור תורה, מנחם די לונזאנו, מאיר אבולעפיה, רבי משה קאציס, מנטובה, כתבי יד</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>רב ומפרש המקרא, יליד מנטובה ומרבני העיר, שלמד אצל רבי משה קאציס והוסמך לרבנות ב־1585. את פירושו הביקורתי על כל המקרא, שעניינו המסורה ונוסח הכתוב, סיים ב־1626 וקרא לו ״גודר פרץ״, והוא נדפס במנטובה ב־1742–1744 בשם ״מנחת שי״.</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>בחיבורו ברר את כתיב המקרא, ניקודו וטעמיו על פי ספרי המסורה וכתבי יד, ובמחלוקת בין מדקדק לבעל מסורה פסק כבעל המסורה. נעזר בעבודתו של מנחם די לונזאנו ובחיבורו של רבי מאיר הלוי אבולעפיה, וחיבורו נחשב לחיבור יסוד בנוסח המקרא.</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>רבי מאיר אייזנשטט (בעל פנים מאירות)</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>כ־1670–1744</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>פוזנא; שידלובצא; וורמייזא; פרוסניץ; אייזנשטט</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>פנים מאירות, כתנות אור, אור הגנוז, מאורי אש, שבע קהילות, ישיבת אייזנשטט, הש״ך, רבי יהונתן אייבשיץ, פוזנא, אייזנשטט</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>פוסק וראש ישיבה, יליד פוזנא, שכיהן כרב בשידלובצא ובפרוסניץ, עמד בראש הישיבה בוורמייזא, ולבסוף התיישב באייזנשטט כרבן של ״שבע הקהילות״. ישיבתו באייזנשטט משכה תלמידים מקרוב ומרחוק, ומתלמידיו היה רבי יהונתן אייבשיץ. נפטר באייזנשטט ב־1744.</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>חיבר את שו״ת ״פנים מאירות״, ספר תשובות וחידושים על מסכתות בתלמוד, ואת ״כתנות אור״, פירוש דרשני לתורה ולחמש המגילות. בשאלות הלכה פנו אליו רבנים מטורקיה, מגרמניה ומאיטליה, ושיטתו ההלכתית מתאפיינת בזהירות ובהיצמדות ללשון המקורות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>רבי מאיר שיף (המהר״ם שיף)</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>המאה ה־17</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>גרמניה; פרנקפורט; פולדא</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>הלכה ופרשנות התלמוד</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>חידושי הלכות, ישיבת פולדא, דרוש הדרן, דרושים נחמדים, שריפת פרנקפורט, פלפול</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>ראש ישיבה ופרשן תלמוד בגרמניה במחצית הראשונה של המאה ה־17, יליד פרנקפורט דמיין, שנודע בחריפותו הרבה. כבן שבע עשרה הוזמן לכהן כרב, אב בית דין וראש ישיבה בפולדא, וישיבתו משכה תלמידים מאשכנז, מפולין וממזרח אירופה. בסמוך למותו הוזמן לכהן כרבה של פראג, אך נפטר בפתאומיות בגיל צעיר.</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>חיבורו ״חידושי הלכות״ הוא תמצית דחוסה של השיעורים שלימד בישיבתו בפולדא, ומשתמרים בו חלקים מאחד עשר מסכתות בתלמוד הבבלי. בחידושיו התמקד בהבנה מקומית מעמיקה של הסוגיה ושל דברי התוספות, והם נדפסים בסוף חלק ממסכתות הש״ס בדפוס וילנא.</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>רב נסים גאון</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>כ־990–1062</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>קירואן; מהדיה</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>גאונים</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>פרשנות התלמוד, הלכה ואגדה</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>ספר המפתח, חיבור יפה מהישועה, מגילת סתרים, קירואן, רב האי גאון, שמואל הנגיד, הרי״ף</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>ראש ישיבת קירואן שבצפון אפריקה, יליד קירואן, שכונה ״גאון״ כתואר כבוד אף שלא כיהן כגאון באחת מישיבות בבל. למד בבית מדרשו של אביו, רבי יעקב בן נסים, ואחר כך אצל רבי חושיאל בן אלחנן, וניהל חליפת מכתבים עם רב האי גאון ועם רבי שמואל הנגיד בגרנדה. כאשר קירואן נשדדה ונחרבה בתקופתו, עבר למהדיה, ושם נפטר.</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>בחיבורו ״ספר מפתח מנעולי התלמוד״ ביקש לפענח סוגיות בבליות מקוצרות בהפניית הלומד למקבילות בספרות התלמודית, ובהן התלמוד הירושלמי. חיבר גם את ״חיבור יפה מהישועה״, ספר נחמה בערבית־יהודית, ואת ״מגילת סתרים״, שהתוספות והראשונים הזכירו אותה בכמה מקומות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>רבי נתן נטע שפירא (בעל מגלה עמוקות)</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>כ־1585–1633</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>גרודנה; קרקוב</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>קבלה, דרשנות והלכה</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>מגלה עמוקות, רנ״ב אופנים, חידושי אנשי שם, אלף פירושים, קבלה לוריאנית, ישיבת קראקא</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>ראש הישיבה והדרשן של קהילת קרקוב במחצית הראשונה של המאה ה־17, יליד גרודנה, שנודע בעיקר כמקובל וכמחבר ״מגלה עמוקות״. חותנו, הגביר והפרנס רבי משה בן יעקב, סיפק לו את כל צרכיו, ועל כן מילא את תפקידיו הציבוריים שלא על מנת לקבל שכר. נפטר בדמי ימיו, כבן 48, ונקבר בבית הקברות היהודי העתיק בקרקוב.</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>בספרו ״מגלה עמוקות״ על פרשת ואתחנן הציע רנ״ב אופנים לבאר בדרך הסוד את תפילת משה ״אעברה נא״, ועל שמו נקרא ״בעל מגלה עמוקות״. לצד הקבלה חיבר גם הגהות וחידושים על הרי״ף, המכונים ״חידושי אנשי שם״.</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>רב עמרם גאון</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>המאה ה־9</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>בבל; סורא</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>גאונים</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>תפילה, הלכה ותשובות הגאונים</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>סדר רב עמרם גאון, ישיבת סורא, תשובות הגאונים, שערי צדק, רב נטרונאי גאון, נוסח התפילה, מאה ברכות, הגאונים</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>גאון ישיבת סורא בבבל במאה התשיעית, תלמידו של רב נטרונאי בר הילאי. חיבר את ״סדר רב עמרם גאון״, סידור התפילה השלם והקדום ביותר שהגיע לידינו, שנשלח לקהילה יהודית בספרד שביקשה נוסח מוסמך של התפילות והברכות. הוא מחבר כ־120 תשובות הלכתיות, שרובן נדפסו בקובץ ״שערי צדק״.</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>הראשון הידוע שסידר תפילה שלמה לשימוש בבית הכנסת ובבית, ושילב בנוסחי התפילה את ההלכות והמנהגים הנלווים להם. סידורו הוא מיסודותיהן של הליטורגיה הספרדית ושל האשכנזית, ועליו נשענו חכמי ימי הביניים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>רבי צבי הירש אשכנזי (החכם צבי)</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>כ־1656–1718</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>אמסטרדם; אלטונה; לבוב; סלוניקי; קושטא; סרייבו</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>שו״ת חכם צבי, תרנגולת בלא לב, נחמיה חייא חיון, השבתאות, רבי אליהו קובו, אלטונה, אמסטרדם, לבוב</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>רב ופוסק, יליד מוראביה, שלמד בסלוניקי בבית מדרשו של רבי אליהו קובו ובקושטא נודע בתואר הספרדי ״חכם״. כיהן כרב בסרייבו, באלטונה ובאמסטרדם, ובסוף ימיו נקרא לשמש רבה של לבוב, ושם מת ב־1718. הטיל חרם על נחמיה חייא חיון, שכתביו נחשדו בעקרונות שבתאיים, ובעקבות המחלוקת שנוצרה עזב את אמסטרדם ב־1714.</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>שילב את החריפות האשכנזית עם הבהירות הספרדית, ותשובותיו, בספר ״חכם צבי״ (אמסטרדם, 1712), מצטיינות בקיצור ובחתירה לפשט הסוגיה. בפולמוס ״תרנגולת בלא לב״ הכשיר תרנגולת שלא נמצא בה לב, בנימוק שבעל חיים בעל מערכת דם אינו יכול לחיות בלא לב.</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>רבי שמואל יפה אשכנזי (בעל יפה תואר)</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>כ־1525–1595</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>קושטא; בורסה</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>מדרש ואגדה, פרשנות</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>יפה תואר, יפה מראה, יפה ענף, יפה קול, יפה עיניים, מדרש רבה, תלמוד ירושלמי, הקהילה האשכנזית בקושטא</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>מחכמי האימפריה העות׳מאנית במאה ה־16, יליד בורסה, שכיהן כרבה של הקהילה האשכנזית בקושטא. חיבר את ״יפה תואר״, באור רחב למדרש רבה, ואת ״יפה מראה״ על אגדות התלמוד הירושלמי, שנדפס בוונציה בחייו. כתב גם את ״יפה ענף״ על מדרשי רות, אסתר ואיכה, ואת ״יפה קול״ על שיר השירים רבה.</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>לפי נייר המחקר של האתר, ב״יפה תואר״ וב״יפה מראה״ החדיר ללימוד המדרש והאגדה את דרכי העיון התלמודיות, תוך בירור גרסאות ויישוב תמיהות וקשיים. פירושו ״יפה תואר״ על בראשית רבה נדפס לראשונה בוונציה ב־1597, ולפי נייר המחקר נפרסה הדפסת הפירוש על חומשי התורה על פני יותר ממאתיים שנה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>רבי שמואל אבן תיבון</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>כ־1150–1230</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>לוניל; מונפלייה; בזייה; מרסיי</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>פילוסופיה, תרגום ופרשנות המקרא</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>מורה נבוכים, פירוש המילים הזרות, מאמר יקוו המים, פירוש קהלת, תרגום, פילוסופיה, רמב״ם, משה אבן תיבון, יעקב אנטולי</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>הוגה, מתרגם ופרשן מקרא מדרום צרפת, בנו של רבי יהודה אבן תיבון. פעל בלוניל, במונפלייה, בבזייה ובמרסיי. תרגם מערבית לעברית את ״מורה נבוכים״ של הרמב״ם, ובמהלך העבודה פנה באיגרות אל הרמב״ם וביקש הבהרות לקטעים קשים; התרגום הושלם ב־1204. חיבר את ״פירוש המילים הזרות״, הנחשב למילון הפילוסופי העברי הראשון, ונפטר במרסיי בסביבות 1230.</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>לפי נייר המחקר, בתרגומו ל״מורה נבוכים״ ובמילונו ״פירוש המילים הזרות״ העניק לעם היהודי את הכלים המושגיים והלשוניים לחשוב ולכתוב פילוסופיה בעברית. לפי נייר המחקר ראה ב״מורה נבוכים״ חיבור שנבנה בכוונה על סתירות מכוונות, ולפי אביעזר רביצקי טען שהרמב״ם הסתיר בו עמדה הנוטה לקדמות העולם.</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>רבי שמשון בן אברהם משאנץ (הר״ש משאנץ)</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>כ־1150–1230</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>צרפת; סנס; ירושלים; עכו</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>בעלי התוספות</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>תלמוד, תוספות ופירוש המשנה</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>בעלי התוספות, תוספות שאנץ, פירוש המשניות, זרעים וטהרות, תלמוד ירושלמי, תוספתא, עליית בעלי התוספות, ר״י הזקן, רבנו תם</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>מבעלי התוספות, נולד בצרפת בסביבות 1150, אחיו של הריצב״א, שמע תורה מרבנו תם והיה תלמידו המובהק של ר״י הזקן מדמפייר. קבע את מושבו בסנס ועמד שם בראש ישיבה מפורסמת, חיבר את ״תוספות שאנץ״ ופירוש למשניות סדר זרעים וסדר טהרות. בסביבות 1211, כאחד מראשי עליית בעלי התוספות, עלה לארץ ישראל והתגורר בירושלים ובעכו. נפטר במחצית הראשונה של המאה ה־13: ויקיפדיה העברית מציינת בערך 1214, ויקיפדיה האנגלית בערך 1230.</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>לפי נייר המחקר הביא לשיאה את הגישה הדיאלקטית של בית מדרשם של רש״י, רבנו תם ור״י הזקן. לפי ויקיפדיה האנגלית הקדיש לתלמוד הירושלמי יותר תשומת לב מכל קודמיו ובני דורו, ובפירושו למשנה הרבה לצטט גם את התוספתא. הרא״ש כתב על רבנו תם, ר״י ור׳ שמשון ש״רוב תורתנו על פיהם פרשו״.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -37005,7 +37005,7 @@
       </c>
       <c r="H611" s="3" t="inlineStr">
         <is>
-          <t>חב״ד, ליובאוויטש, משפט הספרים, פעילות מחתרתית, צניעות, כ״ב שבט</t>
+          <t>חב״ד, ליובאוויטש, משפט הספרים, פעילות מחתרתית, צניעות, כ״ב שבט, נשים</t>
         </is>
       </c>
       <c r="I611" s="3" t="inlineStr">
@@ -37063,7 +37063,7 @@
       </c>
       <c r="H612" s="3" t="inlineStr">
         <is>
-          <t>לח״י, תנועת התחיה, המדרשה הלאומית, בית מורשת אורי צבי גרינברג, פרס ישראל</t>
+          <t>לח״י, תנועת התחיה, המדרשה הלאומית, בית מורשת אורי צבי גרינברג, פרס ישראל, נשים</t>
         </is>
       </c>
       <c r="I612" s="3" t="inlineStr">
@@ -37178,7 +37178,7 @@
       </c>
       <c r="H614" s="3" t="inlineStr">
         <is>
-          <t>יעקב אבינו, רחל אמנו, עשו, שבטי ישראל, יהודה, לוי, תפילה, הודיה, עלמא דאתכסיא, מערת המכפלה</t>
+          <t>יעקב אבינו, רחל אמנו, עשו, שבטי ישראל, יהודה, לוי, תפילה, הודיה, עלמא דאתכסיא, מערת המכפלה, נשים</t>
         </is>
       </c>
       <c r="I614" s="3" t="inlineStr">
@@ -37240,7 +37240,7 @@
       </c>
       <c r="H615" s="3" t="inlineStr">
         <is>
-          <t>קידוש השם, מרוקו, צניעות, פיוטים, קבר בפאס</t>
+          <t>קידוש השם, מרוקו, צניעות, פיוטים, קבר בפאס, נשים</t>
         </is>
       </c>
       <c r="I615" s="3" t="inlineStr">
@@ -37843,7 +37843,7 @@
       </c>
       <c r="H625" s="3" t="inlineStr">
         <is>
-          <t>תנורו של עכנאי, רבי אליעזר בן הורקנוס, רבן גמליאל דיבנה, בית הנשיא, אונאת דברים, שערי אונאה, מעשה הפילוסוף, נפילת אפיים, נשים בתלמוד</t>
+          <t>תנורו של עכנאי, רבי אליעזר בן הורקנוס, רבן גמליאל דיבנה, בית הנשיא, אונאת דברים, שערי אונאה, מעשה הפילוסוף, נפילת אפיים, נשים בתלמוד, נשים</t>
         </is>
       </c>
       <c r="I625" s="3" t="inlineStr">
@@ -38141,7 +38141,7 @@
       </c>
       <c r="H630" s="3" t="inlineStr">
         <is>
-          <t>בארה של מרים, שירת הים, התוף והמחול, שלשת הפרנסים, צרעת מרים, לשון הרע, זכירת מעשה מרים, פועה, משה ואהרן, אור חוזר</t>
+          <t>בארה של מרים, שירת הים, התוף והמחול, שלשת הפרנסים, צרעת מרים, לשון הרע, זכירת מעשה מרים, פועה, משה ואהרן, אור חוזר, נשים</t>
         </is>
       </c>
       <c r="I630" s="3" t="inlineStr">

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L680"/>
+  <dimension ref="A1:L686"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="3" min="1" max="1"/>
@@ -38162,2884 +38162,3254 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" t="inlineStr">
+      <c r="A631" s="3" t="inlineStr">
         <is>
           <t>630</t>
         </is>
       </c>
-      <c r="B631" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C631" t="inlineStr">
+      <c r="B631" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C631" s="3" t="inlineStr">
         <is>
           <t>רבי משה אלשיך (האלשיך הקדוש)</t>
         </is>
       </c>
-      <c r="D631" t="inlineStr">
+      <c r="D631" s="3" t="inlineStr">
         <is>
           <t>כ־1507–1600</t>
         </is>
       </c>
-      <c r="E631" t="inlineStr">
+      <c r="E631" s="3" t="inlineStr">
         <is>
           <t>צפת; אדריאנופול</t>
         </is>
       </c>
-      <c r="F631" t="inlineStr">
+      <c r="F631" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G631" t="inlineStr">
+      <c r="G631" s="3" t="inlineStr">
         <is>
           <t>דרשנות ופרשנות המקרא, הלכה ושו״ת</t>
         </is>
       </c>
-      <c r="H631" t="inlineStr">
+      <c r="H631" s="3" t="inlineStr">
         <is>
           <t>תורת משה, האלשיך הקדוש, רבי יוסף קארו, רבי חיים ויטאל, מראות הצובאות, שושנת העמקים, שו״ת מהר״ם אלשיך, שד״ר, דרשות שבת</t>
         </is>
       </c>
-      <c r="I631" t="inlineStr">
+      <c r="I631" s="3" t="inlineStr">
         <is>
           <t>דרשן, פרשן ופוסק בצפת, הנודע בכינוי ״האלשיך הקדוש״. נולד באדריאנופול ולמד בישיבת רבי יוסף קארו ובישיבת רבי יוסף טאיטצאק בסלוניקי, עלה לצפת ועמד בראש שתי ישיבות, ורבי חיים ויטאל היה תלמידו. חיבר את ״תורת משה״ על התורה, פירושים לנביאים, למגילות ולחלק מהכתובים, וקובץ שו״ת.</t>
         </is>
       </c>
-      <c r="J631" t="inlineStr">
+      <c r="J631" s="3" t="inlineStr">
         <is>
           <t>פירושיו צמחו מדרשות שנשא מדי שבת: בראש כל יחידה הוא מעלה שאלות וקשיים בלשון הכתוב, ובסופה משיב על כולם בזה אחר זה. בכל פסוק ובכל מילה הוא מבקש לקח מוסרי וחיזוק באמונה, ודבריו נלמדים עד היום.</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr">
+      <c r="K631" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף קארו, רבי יוסף טאיטצאק, רבי חיים ויטאל</t>
         </is>
       </c>
-      <c r="L631" t="inlineStr">
+      <c r="L631" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/7xXl4sOy18MABmQdtXzrQu</t>
         </is>
       </c>
     </row>
     <row r="632">
-      <c r="A632" t="inlineStr">
+      <c r="A632" s="3" t="inlineStr">
         <is>
           <t>631</t>
         </is>
       </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C632" t="inlineStr">
+      <c r="B632" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C632" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל די אוזידא (בעל מדרש שמואל)</t>
         </is>
       </c>
-      <c r="D632" t="inlineStr">
+      <c r="D632" s="3" t="inlineStr">
         <is>
           <t>1545–1604</t>
         </is>
       </c>
-      <c r="E632" t="inlineStr">
+      <c r="E632" s="3" t="inlineStr">
         <is>
           <t>צפת; קושטא</t>
         </is>
       </c>
-      <c r="F632" t="inlineStr">
+      <c r="F632" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G632" t="inlineStr">
+      <c r="G632" s="3" t="inlineStr">
         <is>
           <t>דרשנות, פרשנות משנה ומקרא, קבלה</t>
         </is>
       </c>
-      <c r="H632" t="inlineStr">
+      <c r="H632" s="3" t="inlineStr">
         <is>
           <t>מדרש שמואל, פרקי אבות, האר״י, רבי חיים ויטאל, לחם דמעה, אגרת שמואל, ישיבת צפת, שיטה מקובצת, שליחות לקושטא</t>
         </is>
       </c>
-      <c r="I632" t="inlineStr">
+      <c r="I632" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבה, מקובל ודרשן, יליד צפת ומתלמידיו הראשונים של האר״י, שאחרי פטירתו המשיך ללמוד קבלה אצל רבי חיים ויטאל. ייסד בצפת ישיבה גדולה שעסקו בה בנגלה ובנסתר, ויצא לשליחות בקושטא. נודע בחיבורו ״מדרש שמואל״ על פרקי אבות, שנדפס לראשונה בוונציה בשנת 1579, וכתב גם פירושים למגילות איכה ורות.</t>
         </is>
       </c>
-      <c r="J632" t="inlineStr">
+      <c r="J632" s="3" t="inlineStr">
         <is>
           <t>״מדרש שמואל״ הוא ליקוט פרשני: מעין ״שיטה מקובצת״ לפירושים אחרים על אבות, בתוספת דרשותיו שלו, ולכן שימר גם פירושים שאינם בידינו כיום. אף שהיה מתלמידי האר״י, עסק בספריו בעיקר בדרש ולא בקבלה, והשתמש בתובנות קבליות כתשתית סמויה לדברי מוסר שנועדו לכלל הציבור.</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr">
+      <c r="K632" s="3" t="inlineStr">
         <is>
           <t>האר״י הקדוש, רבי חיים ויטאל</t>
         </is>
       </c>
-      <c r="L632" t="inlineStr">
+      <c r="L632" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/6Umixwtvl1Jh3iq0E1sCHW</t>
         </is>
       </c>
     </row>
     <row r="633">
-      <c r="A633" t="inlineStr">
+      <c r="A633" s="3" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="B633" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C633" t="inlineStr">
+      <c r="B633" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C633" s="3" t="inlineStr">
         <is>
           <t>רבי משה מטראני (המבי״ט)</t>
         </is>
       </c>
-      <c r="D633" t="inlineStr">
+      <c r="D633" s="3" t="inlineStr">
         <is>
           <t>כ־1500–1580</t>
         </is>
       </c>
-      <c r="E633" t="inlineStr">
+      <c r="E633" s="3" t="inlineStr">
         <is>
           <t>צפת; סלוניקי</t>
         </is>
       </c>
-      <c r="F633" t="inlineStr">
+      <c r="F633" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G633" t="inlineStr">
+      <c r="G633" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, הגות ומוסר</t>
         </is>
       </c>
-      <c r="H633" t="inlineStr">
+      <c r="H633" s="3" t="inlineStr">
         <is>
           <t>קרית ספר, בית אלהים, שו״ת המבי״ט, רבי יעקב בירב, רבי יוסף קארו, פרק שירה, משנה תורה, בית הדין בצפת</t>
         </is>
       </c>
-      <c r="I633" t="inlineStr">
+      <c r="I633" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבה, דיין ופוסק, מחכמי צפת במאה ה־16. נולד בסלוניקי, למד באדריאנופול אצל דודו רבי אהרן מטראני, עלה לצפת והיה תלמידו המובהק של רבי יעקב בירב, ויותר מחמישים שנה ישב בבית הדין בעיר. חיבר את ״קרית ספר״ על ״משנה תורה״ לרמב״ם, את ״בית אלהים״ ושני כרכי תשובות שנדפסו אחרי מותו.</t>
         </is>
       </c>
-      <c r="J633" t="inlineStr">
+      <c r="J633" s="3" t="inlineStr">
         <is>
           <t>ב״קרית ספר״ הוא בירר בכל דין ב״משנה תורה״ אם הוא מן התורה, ממידות שהתורה נדרשת בהן, מהלכה למשה מסיני או מדברי חכמים ותקנותיהם. ב״בית אלהים״ הוא ביאר את יסודות הדת בשערי התפילה, התשובה והעיקרים, ולספר צורף גם הפירוש הראשון שנדפס על פרק שירה.</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr">
+      <c r="K633" s="3" t="inlineStr">
         <is>
           <t>מהר״י בירב (רבי יעקב בירב), רבי יוסף מטראני (המהרי״ט)</t>
         </is>
       </c>
-      <c r="L633" t="inlineStr">
+      <c r="L633" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/0V7vkwok6itxSw9niOhmW0</t>
         </is>
       </c>
     </row>
     <row r="634">
-      <c r="A634" t="inlineStr">
+      <c r="A634" s="3" t="inlineStr">
         <is>
           <t>633</t>
         </is>
       </c>
-      <c r="B634" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C634" t="inlineStr">
+      <c r="B634" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C634" s="3" t="inlineStr">
         <is>
           <t>רבי חזקיה בן מנוח (החזקוני)</t>
         </is>
       </c>
-      <c r="D634" t="inlineStr">
+      <c r="D634" s="3" t="inlineStr">
         <is>
           <t>כ־1250–1310</t>
         </is>
       </c>
-      <c r="E634" t="inlineStr">
+      <c r="E634" s="3" t="inlineStr">
         <is>
           <t>צרפת</t>
         </is>
       </c>
-      <c r="F634" t="inlineStr">
+      <c r="F634" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G634" t="inlineStr">
+      <c r="G634" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא</t>
         </is>
       </c>
-      <c r="H634" t="inlineStr">
+      <c r="H634" s="3" t="inlineStr">
         <is>
           <t>החזקוני, פירוש לתורה, פשט, רש״י, רבי יוסף בכור שור, רשב״ם, אבן עזרא, מנחת יהודה</t>
         </is>
       </c>
-      <c r="I634" t="inlineStr">
+      <c r="I634" s="3" t="inlineStr">
         <is>
           <t>רב ופרשן מקרא צרפתי מהמאה ה־13, שנודע על שם ספרו ״החזקוני״ על חמשה חומשי תורה. פרטי חייו המדויקים אינם ידועים, ומקובל להעריך שנולד בצרפת בסביבות 1250 ונפטר בסביבות 1310. פירושו נדפס לראשונה בוונציה בשנת ה׳רפ״ד, בתוך חמישה חומשי תורה עם רש״י, ובהקדמתו הוא מבקש מקוראיו שיזכרו אותו ויחזקוהו.</t>
         </is>
       </c>
-      <c r="J634" t="inlineStr">
+      <c r="J634" s="3" t="inlineStr">
         <is>
           <t>פירושו הוא ליקוט מכוון: אחרי ששוטט במדינות רבות בחיפוש אחר פירושים ישרים לתורה, הוא הוציא את המיטב מעשרים חיבורים, ובהם רש״י, רשב״ם ואבן עזרא, ובדרך כלל אינו מציין את שמות מקורותיו. הוא נוטה לדרך הפשט הריאלית של רבי יוסף בכור שור, ומביא ממנו גם קטעי הגות בטעמי המצוות.</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr">
+      <c r="K634" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף בכור שור, רש״י (רבי שלמה יצחקי), הרשב״ם, אברהם אבן עזרא</t>
         </is>
       </c>
-      <c r="L634" t="inlineStr">
+      <c r="L634" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/6VBVggnMCgZu86mq2JMniv</t>
         </is>
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr">
+      <c r="A635" s="3" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C635" t="inlineStr">
+      <c r="B635" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C635" s="3" t="inlineStr">
         <is>
           <t>הרב יוסף בא-גד</t>
         </is>
       </c>
-      <c r="D635" t="inlineStr">
+      <c r="D635" s="3" t="inlineStr">
         <is>
           <t>נולד ב־1932</t>
         </is>
       </c>
-      <c r="E635" t="inlineStr">
+      <c r="E635" s="3" t="inlineStr">
         <is>
           <t>פתח תקווה; ירושלים</t>
         </is>
       </c>
-      <c r="F635" t="inlineStr">
+      <c r="F635" s="3" t="inlineStr">
         <is>
           <t>העת החדשה</t>
         </is>
       </c>
-      <c r="G635" t="inlineStr">
+      <c r="G635" s="3" t="inlineStr">
         <is>
           <t>לימוד התלמוד, חינוך תורני</t>
         </is>
       </c>
-      <c r="H635" t="inlineStr">
+      <c r="H635" s="3" t="inlineStr">
         <is>
           <t>ש״ס בש״ס, שיטת הסוגיות, ישיבת נחלים, נחל יצחק, אוגדן הסוגיות, נחלי לימוד, תלמוד בבלי וירושלמי, תורה ומדע</t>
         </is>
       </c>
-      <c r="I635" t="inlineStr">
+      <c r="I635" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבה ומחבר ספרי לימוד, יליד מוצא תחתית (1932). למד בישיבות כפר הרוא״ה, היישוב החדש וחברון, ובשנת 1955 ייסד את הישיבה התיכונית ״נחל יצחק״ בנחלים, שבראשה עמד עד 2004 ושבה הוא משמש מאז נשיא הישיבה. פיתח את שיטת הלימוד ״ש״ס בש״ס״, המכונה גם ״שיטת הסוגיות״, וחיבר את ״אוגדן הסוגיות״ ו״נחלי לימוד״, שזכו בפרס הרב טולידאנו; בשנים 1992–1996 היה גם חבר הכנסת.</t>
         </is>
       </c>
-      <c r="J635" t="inlineStr">
+      <c r="J635" s="3" t="inlineStr">
         <is>
           <t>שיטתו מלמדת תלמוד לפי סוגיות ולא לפי סדר הדפים: כל סוגיה נבחנת בבבלי ומיד אחריה מובאת מקבילתה מהירושלמי, תוך הצלבת מקורות ושילוב תורה ומדע. בחינוך הוא דגל בלמידה עצמאית, ביום לימודים ארוך, באישיות תורנית כמחנך הכיתה ובשילוב הרגש והשכל, והמליץ להעתיק מרכיבים אלה אל בתי הספר הדתיים.</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr">
+      <c r="K635" s="3" t="inlineStr">
         <is>
           <t>הרב אברהם יצחק הכהן קוק</t>
         </is>
       </c>
-      <c r="L635" t="inlineStr"/>
+      <c r="L635" s="3" t="inlineStr"/>
     </row>
     <row r="636">
-      <c r="A636" t="inlineStr">
+      <c r="A636" s="3" t="inlineStr">
         <is>
           <t>635</t>
         </is>
       </c>
-      <c r="B636" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C636" t="inlineStr">
+      <c r="B636" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C636" s="3" t="inlineStr">
         <is>
           <t>רבי עובדיה ספורנו</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr">
+      <c r="D636" s="3" t="inlineStr">
         <is>
           <t>כ־1470–1549</t>
         </is>
       </c>
-      <c r="E636" t="inlineStr">
+      <c r="E636" s="3" t="inlineStr">
         <is>
           <t>בולוניה; רומא</t>
         </is>
       </c>
-      <c r="F636" t="inlineStr">
+      <c r="F636" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G636" t="inlineStr">
+      <c r="G636" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא, הגות ורפואה</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr">
+      <c r="H636" s="3" t="inlineStr">
         <is>
           <t>ספורנו, ביאור לתורה, כוונות התורה, אור עמים, פשט, בולוניה, רופא, פרקי אבות</t>
         </is>
       </c>
-      <c r="I636" t="inlineStr">
+      <c r="I636" s="3" t="inlineStr">
         <is>
           <t>פרשן מקרא, רב ורופא איטלקי, יליד צ׳זנה, מראשי קהילת רומא וקהילת בולוניה, שבה יסד בית דפוס עברי ושימש רופא. חיבורו החשוב והנפוץ ביותר הוא ביאורו לתורה, והוא חיבר גם פירושים לתהילים, לשיר השירים, לקהלת, לאיוב ולפרקי אבות, ואת הספר הפילוסופי ״אור עמים״.</t>
         </is>
       </c>
-      <c r="J636" t="inlineStr">
+      <c r="J636" s="3" t="inlineStr">
         <is>
           <t>פירושו מבוסס על הפשט, בלשון קצרה ובהירה, והוא נכתב לעם ולא כדי להרשים משכילים. בהקדמה לפירושו לתורה הוא קובע שמטרת התורה להדריך את האדם באשר הוא אדם; הוא חוזר ומדגיש שהבחירה בישראל היא אחריות וחובה ולא זכות, וקושר את הידיעות המדעיות לתיקון המידות.</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr">
+      <c r="K636" s="3" t="inlineStr">
         <is>
           <t>רש״י (רבי שלמה יצחקי), אברהם אבן עזרא, הרשב״ם, הרמב״ן (רבי משה בן נחמן)</t>
         </is>
       </c>
-      <c r="L636" t="inlineStr"/>
+      <c r="L636" s="3" t="inlineStr"/>
     </row>
     <row r="637">
-      <c r="A637" t="inlineStr">
+      <c r="A637" s="3" t="inlineStr">
         <is>
           <t>636</t>
         </is>
       </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C637" t="inlineStr">
+      <c r="B637" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C637" s="3" t="inlineStr">
         <is>
           <t>רבנו ירוחם בן משולם</t>
         </is>
       </c>
-      <c r="D637" t="inlineStr">
+      <c r="D637" s="3" t="inlineStr">
         <is>
           <t>כ־1290–1350</t>
         </is>
       </c>
-      <c r="E637" t="inlineStr">
+      <c r="E637" s="3" t="inlineStr">
         <is>
           <t>טולדו; פרובנס</t>
         </is>
       </c>
-      <c r="F637" t="inlineStr">
+      <c r="F637" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G637" t="inlineStr">
+      <c r="G637" s="3" t="inlineStr">
         <is>
           <t>הלכה ופסיקה</t>
         </is>
       </c>
-      <c r="H637" t="inlineStr">
+      <c r="H637" s="3" t="inlineStr">
         <is>
           <t>מישרים, תולדות אדם וחוה, הרא״ש, רבי אברהם בן אסמעאל, בית יוסף, שולחן ערוך, גירוש צרפת, דיני ממונות</t>
         </is>
       </c>
-      <c r="I637" t="inlineStr">
+      <c r="I637" s="3" t="inlineStr">
         <is>
           <t>רב ופוסק מגדולי הראשונים, שנולד בפרובנס ועבר לטולדו אחרי גירוש יהודי צרפת; פרטים בחייו שנויים במחלוקת. למד אצל הרא״ש ואחר כך אצל רבי אברהם בן אסמעאל, תלמיד הרשב״א והרא״ש, שהיה רבו המובהק. חיבר את ״מישרים״ על דיני ממונות ואת ״תולדות אדם וחוה״ על דינים הנוהגים בגלות, ושני החיבורים נודעים יחד בשם ״רבנו ירוחם״.</t>
         </is>
       </c>
-      <c r="J637" t="inlineStr">
+      <c r="J637" s="3" t="inlineStr">
         <is>
           <t>את ההלכה הנוהגת בגלות הוא ארגן ב״תולדות אדם וחוה״ לפי מהלך חייו של האדם: ב״אדם״ הדינים מלידתו ועד נישואיו, לצד ברכות, תפילות ומנהגים, וב״חוה״ מנישואיו ועד פטירתו. פסקיו מוזכרים פעמים רבות ב״בית יוסף״ והשפיעו על פסיקתו של רבי יוסף קארו בשולחן ערוך, ומתוך כך על הלכות רבות הנהוגות גם בימינו.</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr">
+      <c r="K637" s="3" t="inlineStr">
         <is>
           <t>רבנו אשר בן יחיאל (הרא״ש), רבי יוסף קארו</t>
         </is>
       </c>
-      <c r="L637" t="inlineStr"/>
+      <c r="L637" s="3" t="inlineStr"/>
     </row>
     <row r="638">
-      <c r="A638" t="inlineStr">
+      <c r="A638" s="3" t="inlineStr">
         <is>
           <t>637</t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C638" t="inlineStr">
+      <c r="B638" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C638" s="3" t="inlineStr">
         <is>
           <t>רבי ברוך בן יצחק (בעל התרומה)</t>
         </is>
       </c>
-      <c r="D638" t="inlineStr">
+      <c r="D638" s="3" t="inlineStr">
         <is>
           <t>כ־1140–1211</t>
         </is>
       </c>
-      <c r="E638" t="inlineStr">
+      <c r="E638" s="3" t="inlineStr">
         <is>
           <t>פריז; ארץ ישראל</t>
         </is>
       </c>
-      <c r="F638" t="inlineStr">
+      <c r="F638" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G638" t="inlineStr">
+      <c r="G638" s="3" t="inlineStr">
         <is>
           <t>הלכה ופסיקה, תוספות</t>
         </is>
       </c>
-      <c r="H638" t="inlineStr">
+      <c r="H638" s="3" t="inlineStr">
         <is>
           <t>ספר התרומה, ר״י הזקן, בעלי התוספות, הלכות ארץ ישראל, עליית בעלי התוספות, בית המדרש הצרפתי, בית יוסף, תוספות על זבחים</t>
         </is>
       </c>
-      <c r="I638" t="inlineStr">
+      <c r="I638" s="3" t="inlineStr">
         <is>
           <t>תלמיד חכם ופוסק מבעלי התוספות ותלמידו המובהק של ר״י הזקן, שחי ופעל בצרפת, ובין היתר בפריז. נודע בכינוי בעל התרומה על שם ספרו ״ספר התרומה״, קובץ פסקי הלכה בלשון קצרה שנכתב בראשית המאה ה־13. לקראת פטירתו עלה לארץ ישראל, בתקופת עליית בעלי התוספות, ושם נפטר ונקבר.</t>
         </is>
       </c>
-      <c r="J638" t="inlineStr">
+      <c r="J638" s="3" t="inlineStr">
         <is>
           <t>ספרו הולך אחר בית המדרש הצרפתי: הוא פוסק הלכה בלשון קצרה במגוון נושאים, אינו עוסק במנהגי הקהילות ומסתיים במפתחות המסכמים את הפרקים. הוא כולל גם פרק מיוחד על ״הלכות ארץ ישראל״, ופוסקים רבים בססו עליו את פסיקתם; הבית יוסף מביא את דבריו רבות.</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr">
+      <c r="K638" s="3" t="inlineStr">
         <is>
           <t>ר״י הזקן מדמפייר, יעקב בן אשר, רבי יוסף קארו, רבי אלעזר מגרמייזא (בעל הרוקח)</t>
         </is>
       </c>
-      <c r="L638" t="inlineStr"/>
+      <c r="L638" s="3" t="inlineStr"/>
     </row>
     <row r="639">
-      <c r="A639" t="inlineStr">
+      <c r="A639" s="3" t="inlineStr">
         <is>
           <t>638</t>
         </is>
       </c>
-      <c r="B639" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C639" t="inlineStr">
+      <c r="B639" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C639" s="3" t="inlineStr">
         <is>
           <t>רבי יהושע פלק כ״ץ (הסמ״ע)</t>
         </is>
       </c>
-      <c r="D639" t="inlineStr">
+      <c r="D639" s="3" t="inlineStr">
         <is>
           <t>כ־1555–1614</t>
         </is>
       </c>
-      <c r="E639" t="inlineStr">
+      <c r="E639" s="3" t="inlineStr">
         <is>
           <t>קרקוב; לבוב</t>
         </is>
       </c>
-      <c r="F639" t="inlineStr">
+      <c r="F639" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G639" t="inlineStr">
+      <c r="G639" s="3" t="inlineStr">
         <is>
           <t>הלכה, פרשנות הטור, פרשנות השולחן ערוך</t>
         </is>
       </c>
-      <c r="H639" t="inlineStr">
+      <c r="H639" s="3" t="inlineStr">
         <is>
           <t>מאירת עינים, הסמ״ע, דרישה ופרישה, בית ישראל, ארבעה טורים, שולחן ערוך, המהרש״ל, הרמ״א, ישיבת לבוב, ועד ארבע הארצות</t>
         </is>
       </c>
-      <c r="I639" t="inlineStr">
+      <c r="I639" s="3" t="inlineStr">
         <is>
           <t>מגדולי האחרונים בפולין, יליד קראקא ותלמידם של המהרש״ל והרמ״א. עמד בראש ישיבה בלבוב, שם נפטר בשנת 1614, והעמיד תלמידים רבים. חיבר את ״דרישה ופרישה״ על הטור ואת ״מאירת עינים״ (הסמ״ע) על חושן משפט שבשולחן ערוך, ושניהם נדפסו אחר כך ברוב מהדורות הטור והשולחן ערוך.</t>
         </is>
       </c>
-      <c r="J639" t="inlineStr">
+      <c r="J639" s="3" t="inlineStr">
         <is>
           <t>הסמ״ע התנגד להישענות על ספרי הפסק תוך זניחת העיון במקורות המקוריים, ולכן חיבר פירושים לטור ולשולחן ערוך. ב״פרישה״ הוא מתחקה אחר הכרעות הטור עד מקורותיהן בתלמוד ובראשונים, וב״דרישה״ הוא דן בהרחבה בשיטות השונות.</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr">
+      <c r="K639" s="3" t="inlineStr">
         <is>
           <t>המהרש״ל (רבי שלמה לוריא), הרמ״א (רבי משה איסרליש)</t>
         </is>
       </c>
-      <c r="L639" t="inlineStr"/>
+      <c r="L639" s="3" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/3sBHDuG9aT7dx4zmtYyDjH</t>
+        </is>
+      </c>
     </row>
     <row r="640">
-      <c r="A640" t="inlineStr">
+      <c r="A640" s="3" t="inlineStr">
         <is>
           <t>639</t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
+      <c r="B640" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C640" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל די מדינה (המהרשד״ם)</t>
         </is>
       </c>
-      <c r="D640" t="inlineStr">
+      <c r="D640" s="3" t="inlineStr">
         <is>
           <t>כ־1505–1589</t>
         </is>
       </c>
-      <c r="E640" t="inlineStr">
+      <c r="E640" s="3" t="inlineStr">
         <is>
           <t>סלוניקי</t>
         </is>
       </c>
-      <c r="F640" t="inlineStr">
+      <c r="F640" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G640" t="inlineStr">
+      <c r="G640" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H640" t="inlineStr">
+      <c r="H640" s="3" t="inlineStr">
         <is>
           <t>שו״ת מהרשד״ם, בן שמואל, רבי יוסף טאיטצאק, המהרלב״ח, לחם משנה, סלוניקי, האימפריה העות׳מאנית, תקנות קהל, אנוסים, פסיקה</t>
         </is>
       </c>
-      <c r="I640" t="inlineStr">
+      <c r="I640" s="3" t="inlineStr">
         <is>
           <t>מן הפוסקים המרכזיים באימפריה העות׳מאנית במאה ה־16, יליד סלוניקי, דיין וראש ישיבה בעירו. תלמידם של רבי יוסף טאיטצאק ורבי לוי בן חביב, ורבו של רבי אברהם די בוטון, בעל ״לחם משנה״. שאלות הלכתיות נשלחו אליו מקהילות רבות, וכאלף מתשובותיו נדפסו ב״שו״ת מהרשד״ם״, ודרשותיו בספר ״בן שמואל״.</t>
         </is>
       </c>
-      <c r="J640" t="inlineStr">
+      <c r="J640" s="3" t="inlineStr">
         <is>
           <t>תשובותיו קושרות את ההלכה לחיי הקהילה: לצד איסור והיתר, קידושין וגירושין הן עוסקות בתקנות קהל, במנהגי קהילות, בחלוקת נטל המיסים, בענייני מסחר ובמעמד האנוסים וצאצאיהם. שו״ת מהרשד״ם נמנה עם ספרי הפסיקה שחכמי המזרח הסתמכו עליהם, והוא משמש גם מקור היסטורי חשוב לחיי היהודים בסלוניקי.</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr">
+      <c r="K640" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף טאיטצאק, רבי לוי בן חביב (המהרלב״ח), רבי אברהם די בוטון, רבי מנחם די לונזאנו</t>
         </is>
       </c>
-      <c r="L640" t="inlineStr"/>
+      <c r="L640" s="3" t="inlineStr"/>
     </row>
     <row r="641">
-      <c r="A641" t="inlineStr">
+      <c r="A641" s="3" t="inlineStr">
         <is>
           <t>640</t>
         </is>
       </c>
-      <c r="B641" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C641" t="inlineStr">
+      <c r="B641" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C641" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף בן לב (מהריב״ל)</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr">
+      <c r="D641" s="3" t="inlineStr">
         <is>
           <t>כ־1503–1580</t>
         </is>
       </c>
-      <c r="E641" t="inlineStr">
+      <c r="E641" s="3" t="inlineStr">
         <is>
           <t>סלוניקי; קושטא</t>
         </is>
       </c>
-      <c r="F641" t="inlineStr">
+      <c r="F641" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G641" t="inlineStr">
+      <c r="G641" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H641" t="inlineStr">
+      <c r="H641" s="3" t="inlineStr">
         <is>
           <t>שו״ת מהריב״ל, מונסטיר, סלוניקי, קושטא, דונה גרציה, רבי יוסף קארו, רבי יוסף טאיטצאק, אנוסים, לימוד לפי סוגיות, ישיבת קושטא</t>
         </is>
       </c>
-      <c r="I641" t="inlineStr">
+      <c r="I641" s="3" t="inlineStr">
         <is>
           <t>מחכמי מונסטיר שבאימפריה העות׳מאנית במאה ה־16, דיין ופוסק וראש ישיבה בסלוניקי ובקושטא, שנודע באישיותו התקיפה ובפסיקת הלכה בלתי מתפשרת. בקושטא מינתה אותו דונה גרציה מנדס לראש הישיבה שהקימה. תשובותיו, ״שו״ת מהריב״ל״, נדפסו עוד בחייו, ובהן גם חידושיו לכמה מסכתות בתלמוד הבבלי.</t>
         </is>
       </c>
-      <c r="J641" t="inlineStr">
+      <c r="J641" s="3" t="inlineStr">
         <is>
           <t>דרך לימודו מיזגה את הדרך הספרדית, המצטיינת בבקיאות ועוסקת בעיקר בבירור ההלכה, עם הדרך האשכנזית, המצטיינת בחריפות ועוסקת רבות גם בפלפול. בישיבתו הנהיג, כבישיבות האשכנזיות, לימוד לפי נושאים וסוגיות ולא לפי סדר התלמוד.</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
-      <c r="L641" t="inlineStr"/>
+      <c r="K641" s="3" t="inlineStr"/>
+      <c r="L641" s="3" t="inlineStr"/>
     </row>
     <row r="642">
-      <c r="A642" t="inlineStr">
+      <c r="A642" s="3" t="inlineStr">
         <is>
           <t>641</t>
         </is>
       </c>
-      <c r="B642" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C642" t="inlineStr">
+      <c r="B642" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C642" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף מטראני (המהרי״ט)</t>
         </is>
       </c>
-      <c r="D642" t="inlineStr">
+      <c r="D642" s="3" t="inlineStr">
         <is>
           <t>1568–1639</t>
         </is>
       </c>
-      <c r="E642" t="inlineStr">
+      <c r="E642" s="3" t="inlineStr">
         <is>
           <t>צפת; קושטא</t>
         </is>
       </c>
-      <c r="F642" t="inlineStr">
+      <c r="F642" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G642" t="inlineStr">
+      <c r="G642" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, ראשות ישיבה, פרשנות לתורה</t>
         </is>
       </c>
-      <c r="H642" t="inlineStr">
+      <c r="H642" s="3" t="inlineStr">
         <is>
           <t>שו״ת המהרי״ט, צפנת פענח, חידושי מהרי״ט, החכם באשי, המבי״ט, רבי חיים בנבנשתי, דינא דחיי, צפת, קושטא, הסמ״ג</t>
         </is>
       </c>
-      <c r="I642" t="inlineStr">
+      <c r="I642" s="3" t="inlineStr">
         <is>
           <t>מגדולי הפוסקים, בנו של רבי משה מטראני (המבי״ט), יליד צפת ומרבניה. עבר לקושטא, ייסד בה בית דין לענייני איסור והיתר ונתמנה לחכם באשי של טורקיה, ולישיבתו נהרו תלמידים מכל טורקיה ואף מעבר לה. נודע בשו״ת המהרי״ט ובחידושיו, וכן בפירושו ״צפנת פענח״ על התורה והמועדים.</t>
         </is>
       </c>
-      <c r="J642" t="inlineStr">
+      <c r="J642" s="3" t="inlineStr">
         <is>
           <t>הוא היה פוסק ומרביץ תורה גם יחד: קיבל אלפי שאלות והשיב עליהן, חיבר פירושים על הר״ן, הרי״ף והרמב״ם, והעמיד תלמידים. אחד מהם, בעל ״כנסת הגדולה״, זכה לברכתו שיחבר חיבור על הסמ״ג.</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr">
+      <c r="K642" s="3" t="inlineStr">
         <is>
           <t>רבי משה מטראני (המבי״ט), רבי חיים בנבנשתי (בעל כנסת הגדולה)</t>
         </is>
       </c>
-      <c r="L642" t="inlineStr"/>
+      <c r="L642" s="3" t="inlineStr"/>
     </row>
     <row r="643">
-      <c r="A643" t="inlineStr">
+      <c r="A643" s="3" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C643" t="inlineStr">
+      <c r="B643" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C643" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם די בוטון (בעל לחם משנה)</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr">
+      <c r="D643" s="3" t="inlineStr">
         <is>
           <t>המאה ה־16</t>
         </is>
       </c>
-      <c r="E643" t="inlineStr">
+      <c r="E643" s="3" t="inlineStr">
         <is>
           <t>סלוניקי</t>
         </is>
       </c>
-      <c r="F643" t="inlineStr">
+      <c r="F643" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G643" t="inlineStr">
+      <c r="G643" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, פרשנות הרמב״ם</t>
         </is>
       </c>
-      <c r="H643" t="inlineStr">
+      <c r="H643" s="3" t="inlineStr">
         <is>
           <t>לחם משנה, לחם רב, משנה תורה, הרמב״ם, המהרשד״ם, המגיד משנה, כסף משנה, סלוניקי, ראשות ישיבה, מגפה</t>
         </is>
       </c>
-      <c r="I643" t="inlineStr">
+      <c r="I643" s="3" t="inlineStr">
         <is>
           <t>רב, פוסק וראש ישיבה, מצאצאי מגורשי ספרד ומחכמי סלוניקי במאה ה־16, תלמידו של המהרשד״ם. פירש את משנה תורה של הרמב״ם בספרו ״לחם משנה״, שזכה לתפוצה רחבה והודפס במהדורה הסטנדרטית של הספר, וחיבר גם ספר שו״ת בשם ״לחם רב״. בשעת מחלתו נוסף לו השם חייא, ולפעמים היה חותם בשם זה.</t>
         </is>
       </c>
-      <c r="J643" t="inlineStr">
+      <c r="J643" s="3" t="inlineStr">
         <is>
           <t>בפירושו הוא מעמיק בדברי הרמב״ם ומשווה אותם לראשונים אחרים ולמפרשי הרמב״ם שקדמו לו, המגיד משנה והכסף משנה. החיד״א כתב שהחל לכתוב את חיבורו לפני שהתוודע לפירוש ״כסף משנה״, ולאחר שהתוודע אליו ציין אותו גם בו.</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr">
+      <c r="K643" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל די מדינה (המהרשד״ם)</t>
         </is>
       </c>
-      <c r="L643" t="inlineStr"/>
+      <c r="L643" s="3" t="inlineStr"/>
     </row>
     <row r="644">
-      <c r="A644" t="inlineStr">
+      <c r="A644" s="3" t="inlineStr">
         <is>
           <t>643</t>
         </is>
       </c>
-      <c r="B644" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C644" t="inlineStr">
+      <c r="B644" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C644" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל בן אורי שרגא פייבוש (בעל בית שמואל)</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr">
+      <c r="D644" s="3" t="inlineStr">
         <is>
           <t>כ־1650–1706</t>
         </is>
       </c>
-      <c r="E644" t="inlineStr">
+      <c r="E644" s="3" t="inlineStr">
         <is>
           <t>פולין; גרמניה</t>
         </is>
       </c>
-      <c r="F644" t="inlineStr">
+      <c r="F644" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G644" t="inlineStr">
+      <c r="G644" s="3" t="inlineStr">
         <is>
           <t>הלכה, פרשנות השולחן ערוך, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H644" t="inlineStr">
+      <c r="H644" s="3" t="inlineStr">
         <is>
           <t>בית שמואל, אבן העזר, שולחן ערוך, חלקת מחוקק, אפי רברבי, פיורדא, שידלוב, ישיבת קרקוב, דירנפורט, מהדורא בתרא</t>
         </is>
       </c>
-      <c r="I644" t="inlineStr">
+      <c r="I644" s="3" t="inlineStr">
         <is>
           <t>רבן של שידלוב ופיורדא, יליד פולין באמצע המאה ה־17, שלמד בישיבת קרקוב. נודע בזכות ״בית שמואל״, מ״נושאי הכלים״ לחלק אבן העזר בשולחן ערוך. את המהדורה הראשונה הדפיס בדירנפורט, ואחרי שעבר עליה בפיורדא עם תלמידיו הוציא מהדורה שנייה מתוקנת, שמודפסת מאז ברוב מהדורות השולחן ערוך.</t>
         </is>
       </c>
-      <c r="J644" t="inlineStr">
+      <c r="J644" s="3" t="inlineStr">
         <is>
           <t>״בית שמואל״ נכתב כדי ״לגאול״ את חלק אבן העזר, שתלמידי החכמים זנחו, ולהפוך אותו מ״אבן מאסו הבונים״ ל״ראש פינה״ ולמרכז העיסוק הלימודי. המהדורה השנייה, שהמחבר הוסיף וגרע ושינה בה בעצמו יחד עם תלמידיו, היא העיקרית: שם הגדולים קובע ש״מהדורא קמא אין להשגיח בו״.</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
-      <c r="L644" t="inlineStr"/>
+      <c r="K644" s="3" t="inlineStr"/>
+      <c r="L644" s="3" t="inlineStr"/>
     </row>
     <row r="645">
-      <c r="A645" t="inlineStr">
+      <c r="A645" s="3" t="inlineStr">
         <is>
           <t>644</t>
         </is>
       </c>
-      <c r="B645" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C645" t="inlineStr">
+      <c r="B645" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C645" s="3" t="inlineStr">
         <is>
           <t>רבי יהושע בועז (בעל שלטי הגיבורים)</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr">
+      <c r="D645" s="3" t="inlineStr">
         <is>
           <t>המאה ה־16</t>
         </is>
       </c>
-      <c r="E645" t="inlineStr">
+      <c r="E645" s="3" t="inlineStr">
         <is>
           <t>איטליה</t>
         </is>
       </c>
-      <c r="F645" t="inlineStr">
+      <c r="F645" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G645" t="inlineStr">
+      <c r="G645" s="3" t="inlineStr">
         <is>
           <t>הלכה, פרשנות הרי״ף, עריכת הש״ס</t>
         </is>
       </c>
-      <c r="H645" t="inlineStr">
+      <c r="H645" s="3" t="inlineStr">
         <is>
           <t>שלטי הגיבורים, מסורת הש״ס, עין משפט נר מצווה, תורה אור, הרי״ף, ריא״ז, הרמ״א, הגהות אלפסי, ש״ס ונציה, איטליה</t>
         </is>
       </c>
-      <c r="I645" t="inlineStr">
+      <c r="I645" s="3" t="inlineStr">
         <is>
           <t>מגדולי הפוסקים האחרונים, נולד באיטליה לרבי שמעון לבית ברוך, ממשפחה ממגורשי ספרד. חיבר את ״מסורת הש״ס״, הפניות למקבילות בתלמוד שנדפסו כמעט בכל מהדורותיו, את ״עין משפט נר מצווה״, הפניות להלכה שבדברי הרמב״ם והסמ״ג, ואת ״שלטי הגיבורים״ על הרי״ף, שהרמ״א הרבה להביא ממנו פסקים.</t>
         </is>
       </c>
-      <c r="J645" t="inlineStr">
+      <c r="J645" s="3" t="inlineStr">
         <is>
           <t>ספריו קושרים את הלימוד בגמרא להלכה: ״עין משפט״ מפנה ממקום הדין בגמרא לדברי הרמב״ם והסמ״ג, ולאחר מכן גם לשולחן ערוך ולארבעה טורים, והוא כלי עזר חשוב ללומדי הגמרא ״אליבא דהלכתא״. ״שלטי הגיבורים״ מתמצת את פסקי ההלכה הנובעים מדברי הרי״ף ומהתייחסות הראשונים אליהם, ובו גם מעט מחידושיו.</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr">
+      <c r="K645" s="3" t="inlineStr">
         <is>
           <t>הרמ״א (רבי משה איסרליש)</t>
         </is>
       </c>
-      <c r="L645" t="inlineStr"/>
+      <c r="L645" s="3" t="inlineStr"/>
     </row>
     <row r="646">
-      <c r="A646" t="inlineStr">
+      <c r="A646" s="3" t="inlineStr">
         <is>
           <t>645</t>
         </is>
       </c>
-      <c r="B646" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr">
+      <c r="B646" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C646" s="3" t="inlineStr">
         <is>
           <t>רבי שלמה סיריליו</t>
         </is>
       </c>
-      <c r="D646" t="inlineStr">
+      <c r="D646" s="3" t="inlineStr">
         <is>
           <t>1485–1554</t>
         </is>
       </c>
-      <c r="E646" t="inlineStr">
+      <c r="E646" s="3" t="inlineStr">
         <is>
           <t>צפת; ירושלים; סלוניקי</t>
         </is>
       </c>
-      <c r="F646" t="inlineStr">
+      <c r="F646" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G646" t="inlineStr">
+      <c r="G646" s="3" t="inlineStr">
         <is>
           <t>פרשנות התלמוד הירושלמי, הלכה, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H646" t="inlineStr">
+      <c r="H646" s="3" t="inlineStr">
         <is>
           <t>תלמוד ירושלמי, פירוש לירושלמי, סדר זרעים, מסכת שקלים, מסכת עדויות, מגורשי ספרד, צפת, ירושלים, סלוניקי, המצוות התלויות בארץ</t>
         </is>
       </c>
-      <c r="I646" t="inlineStr">
+      <c r="I646" s="3" t="inlineStr">
         <is>
           <t>ממגורשי ספרד ומחכמי צפת וירושלים במחצית הראשונה של המאה ה־16, מראשוני פרשני התלמוד הירושלמי. למד בקושטא ובסלוניקי, עלה לצפת ב־1532 ולימים עבר לירושלים והקים בה ישיבה. פירש את כל סדר זרעים ואת מסכת שקלים, ופירושו לסדר זרעים הוא הפירוש הרציף הראשון הידוע לירושלמי, וכן ערך מעין גמרא על מסכת עדויות.</t>
         </is>
       </c>
-      <c r="J646" t="inlineStr">
+      <c r="J646" s="3" t="inlineStr">
         <is>
           <t>ברוב הסוגיות לא עמד לפניו פירוש קדום, ופירושו לירושלמי מקורי ברובו, והוא לא נרתע מלחלוק על הראשונים ולעיתים אף על הרמב״ם. הוא שילב בפירושו פסקי הלכה הנובעים מן הסוגיות, ופסקים אלה הם מאבני היסוד בפסיקת ההלכה בימינו בנושא המצוות התלויות בארץ.</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr">
+      <c r="K646" s="3" t="inlineStr">
         <is>
           <t>רבי לוי בן חביב (המהרלב״ח), רבי יעקב אבן חביב (עין יעקב), רבי שלמה עדני (בעל מלאכת שלמה)</t>
         </is>
       </c>
-      <c r="L646" t="inlineStr"/>
+      <c r="L646" s="3" t="inlineStr"/>
     </row>
     <row r="647">
-      <c r="A647" t="inlineStr">
+      <c r="A647" s="3" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="B647" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C647" t="inlineStr">
+      <c r="B647" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C647" s="3" t="inlineStr">
         <is>
           <t>רבי חיים בנבנשתי (בעל כנסת הגדולה)</t>
         </is>
       </c>
-      <c r="D647" t="inlineStr">
+      <c r="D647" s="3" t="inlineStr">
         <is>
           <t>1603–1673</t>
         </is>
       </c>
-      <c r="E647" t="inlineStr">
+      <c r="E647" s="3" t="inlineStr">
         <is>
           <t>איזמיר; קושטא</t>
         </is>
       </c>
-      <c r="F647" t="inlineStr">
+      <c r="F647" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G647" t="inlineStr">
+      <c r="G647" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, ראשות ישיבה, פרשנות הטור</t>
         </is>
       </c>
-      <c r="H647" t="inlineStr">
+      <c r="H647" s="3" t="inlineStr">
         <is>
           <t>ספר כנסת הגדולה, שיירי כנסת הגדולה, דינא דחיי, בעי חיי, פסח מעובין, חמרא וחיי, המהרי״ט, הסמ״ג, בית יוסף, איזמיר</t>
         </is>
       </c>
-      <c r="I647" t="inlineStr">
+      <c r="I647" s="3" t="inlineStr">
         <is>
           <t>רב ופוסק באיזמיר, יליד קושטא ותלמידו של רבי יוסף מטראני (המהרי״ט), שבירך אותו לחבר חיבור על הסמ״ג. בגיל 21 חיבר את ספרו הראשון, ״דינא דחיי״ על הסמ״ג. כיהן ברבנות בטירה הסמוכה לאיזמיר ואחר כך באיזמיר, כדיין וכראש ישיבה, ונודע בעיקר בספרו ״כנסת הגדולה״ על הטור והבית יוסף.</t>
         </is>
       </c>
-      <c r="J647" t="inlineStr">
+      <c r="J647" s="3" t="inlineStr">
         <is>
           <t>״כנסת הגדולה״ על הטור והבית יוסף הפך לאחד מספרי היסוד בפסיקה, ועל שמו נקרא מחברו. החיד״א כתב שאיש מורה הוראה בקי אינו מרים יד בשום הוראה בלי שיעיין בו תחילה.</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr">
+      <c r="K647" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף מטראני (המהרי״ט)</t>
         </is>
       </c>
-      <c r="L647" t="inlineStr"/>
+      <c r="L647" s="3" t="inlineStr"/>
     </row>
     <row r="648">
-      <c r="A648" t="inlineStr">
+      <c r="A648" s="3" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="B648" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C648" t="inlineStr">
+      <c r="B648" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C648" s="3" t="inlineStr">
         <is>
           <t>רבי אליהו די וידאש (בעל ראשית חכמה)</t>
         </is>
       </c>
-      <c r="D648" t="inlineStr">
+      <c r="D648" s="3" t="inlineStr">
         <is>
           <t>המאה ה־16</t>
         </is>
       </c>
-      <c r="E648" t="inlineStr">
+      <c r="E648" s="3" t="inlineStr">
         <is>
           <t>צפת; חברון</t>
         </is>
       </c>
-      <c r="F648" t="inlineStr">
+      <c r="F648" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G648" t="inlineStr">
+      <c r="G648" s="3" t="inlineStr">
         <is>
           <t>קבלה ומוסר, הגות</t>
         </is>
       </c>
-      <c r="H648" t="inlineStr">
+      <c r="H648" s="3" t="inlineStr">
         <is>
           <t>ראשית חכמה, תוצאות חיים, הרמ״ק, האר״י, רבי שלמה אלקבץ, רבי יצחק דמן עכו, ראשות רבני חברון, תיקון המידות, הזוהר, קבלה ומוסר</t>
         </is>
       </c>
-      <c r="I648" t="inlineStr">
+      <c r="I648" s="3" t="inlineStr">
         <is>
           <t>מקובל והוגה דעות, יליד צפת ותלמידו של הרמ״ק, שלמד גם מפי האר״י. עבר לחברון והתמנה לראש רבניה, ושם נקבר. בשנת 1575 סיים את כתיבת ספרו ״ראשית חכמה״, העוסק בהיבטים השונים של חיי האדם על פי המשמעות הקבלית, והספר זכה למהדורות רבות, למהדורה מקוצרת ולתרגום ליידיש.</t>
         </is>
       </c>
-      <c r="J648" t="inlineStr">
+      <c r="J648" s="3" t="inlineStr">
         <is>
           <t>״ראשית חכמה״ הוא ספר קבלי על מידות האדם הראויות, המבוסס ברובו על הזוהר. לדברי שם הגדולים, מי שיקבע בו שיעור יומי ודאי יתנוצצו בו קדושה וטהרה.</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr">
+      <c r="K648" s="3" t="inlineStr">
         <is>
           <t>הרמ״ק (רבי משה קורדובירו), האר״י הקדוש, רבי יצחק דמן עכו</t>
         </is>
       </c>
-      <c r="L648" t="inlineStr"/>
+      <c r="L648" s="3" t="inlineStr"/>
     </row>
     <row r="649">
-      <c r="A649" t="inlineStr">
+      <c r="A649" s="3" t="inlineStr">
         <is>
           <t>648</t>
         </is>
       </c>
-      <c r="B649" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C649" t="inlineStr">
+      <c r="B649" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C649" s="3" t="inlineStr">
         <is>
           <t>רבי אליה שפירא (בעל אליה רבה)</t>
         </is>
       </c>
-      <c r="D649" t="inlineStr">
+      <c r="D649" s="3" t="inlineStr">
         <is>
           <t>כ־1660–1712</t>
         </is>
       </c>
-      <c r="E649" t="inlineStr">
+      <c r="E649" s="3" t="inlineStr">
         <is>
           <t>פראג</t>
         </is>
       </c>
-      <c r="F649" t="inlineStr">
+      <c r="F649" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G649" t="inlineStr">
+      <c r="G649" s="3" t="inlineStr">
         <is>
           <t>הלכה, פסיקה ודרשנות</t>
         </is>
       </c>
-      <c r="H649" t="inlineStr">
+      <c r="H649" s="3" t="inlineStr">
         <is>
           <t>אליה רבה, אליה זוטא, הלבושים, רבי מרדכי יפה, מגן אברהם, משנה ברורה, פסיקה אשכנזית, פראג, שולחן ערוך</t>
         </is>
       </c>
-      <c r="I649" t="inlineStr">
+      <c r="I649" s="3" t="inlineStr">
         <is>
           <t>דיין, ראש ישיבה ודרשן בפראג, יליד העיר בסביבות שנת 1660, שנפטר ב־1712 בחיי אביו. למד אצל סבו, רבי אהרן שמעון מפראג, ובפולין למד מפי בעל ״מגן אברהם״. חיבר את ״אליה זוטא״ ואת ״אליה רבה״, פירושים לחלק אורח חיים בספרי ״הלבוש״ של רבי מרדכי יפה; שני הפירושים נחשבים לספרי יסוד בפסיקה האשכנזית.</t>
         </is>
       </c>
-      <c r="J649" t="inlineStr">
+      <c r="J649" s="3" t="inlineStr">
         <is>
           <t>פסיקה דרך פירוש: ״אליה רבה״ נכתב על סדר ״הלבוש״ של רבי מרדכי יפה ונעשה אחד מספרי היסוד בפסיקה האשכנזית. המשנה ברורה מביא אותו תדיר כמקור הפסיקה ההלכתית שלו.</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr">
+      <c r="K649" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם אבלי גומבינר (המגן אברהם), רבי מרדכי יפה, רבי יעקב ריישר</t>
         </is>
       </c>
-      <c r="L649" t="inlineStr"/>
+      <c r="L649" s="3" t="inlineStr"/>
     </row>
     <row r="650">
-      <c r="A650" t="inlineStr">
+      <c r="A650" s="3" t="inlineStr">
         <is>
           <t>649</t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C650" t="inlineStr">
+      <c r="B650" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C650" s="3" t="inlineStr">
         <is>
           <t>רבי דוד אלטשולר (בעל מצודת דוד)</t>
         </is>
       </c>
-      <c r="D650" t="inlineStr">
+      <c r="D650" s="3" t="inlineStr">
         <is>
           <t>1687–1769</t>
         </is>
       </c>
-      <c r="E650" t="inlineStr">
+      <c r="E650" s="3" t="inlineStr">
         <is>
           <t>יאברוב; גליציה</t>
         </is>
       </c>
-      <c r="F650" t="inlineStr">
+      <c r="F650" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G650" t="inlineStr">
+      <c r="G650" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא</t>
         </is>
       </c>
-      <c r="H650" t="inlineStr">
+      <c r="H650" s="3" t="inlineStr">
         <is>
           <t>מצודת דוד, מצודת ציון, פירוש לנביאים ולכתובים, פשט, מקראות גדולות, רד״ק, יאברוב, זאלקווא</t>
         </is>
       </c>
-      <c r="I650" t="inlineStr">
+      <c r="I650" s="3" t="inlineStr">
         <is>
           <t>פרשן מקרא ממשפחת אלטשולר, יליד יאברוב שבגליציה, שנזכר בה כדיין או כרב. כדי להנגיש את התנ״ך גם למלמדי תינוקות וילדים כתב את ״מצודת דוד״, ביאור פשוט וברור על התנ״ך (חוץ ממגילות רות, איכה ואסתר) שליקט מפירושי הראשונים, והדפיס ב־1753 בזאלקווא את הפירוש לאיוב, למשלי ולתהילים. בנו, רבי יחיאל הלל, השלים את הפירוש והדפיסו.</t>
         </is>
       </c>
-      <c r="J650" t="inlineStr">
+      <c r="J650" s="3" t="inlineStr">
         <is>
           <t>הנגשת המקרא לכל לומד: ״מצודת דוד״ מלקט בעברית פשוטה וצחה את פירושי הראשונים, כך שתלמידי החכמים חוסכים זמן יקר של עיון בהם והיהודים הפשוטים מבינים את המקרא על פי פשוטו. הפירוש זכה לאהדה רבה מפני שהוא ברור ומובן לכל, והוא נדפס כמעט בכל מהדורות ״מקראות גדולות״.</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr">
+      <c r="K650" s="3" t="inlineStr">
         <is>
           <t>רבי דוד קמחי (הרד״ק), רבי יחיאל הלל אלטשולר</t>
         </is>
       </c>
-      <c r="L650" t="inlineStr"/>
+      <c r="L650" s="3" t="inlineStr"/>
     </row>
     <row r="651">
-      <c r="A651" t="inlineStr">
+      <c r="A651" s="3" t="inlineStr">
         <is>
           <t>650</t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C651" t="inlineStr">
+      <c r="B651" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C651" s="3" t="inlineStr">
         <is>
           <t>רבי יחיאל הלל אלטשולר (בעל מצודת ציון)</t>
         </is>
       </c>
-      <c r="D651" t="inlineStr">
+      <c r="D651" s="3" t="inlineStr">
         <is>
           <t>המאה ה־18</t>
         </is>
       </c>
-      <c r="E651" t="inlineStr">
+      <c r="E651" s="3" t="inlineStr">
         <is>
           <t>יאברוב; עמדין; גליציה</t>
         </is>
       </c>
-      <c r="F651" t="inlineStr">
+      <c r="F651" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G651" t="inlineStr">
+      <c r="G651" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא והלכה</t>
         </is>
       </c>
-      <c r="H651" t="inlineStr">
+      <c r="H651" s="3" t="inlineStr">
         <is>
           <t>מצודת ציון, מצודת דוד, בנין הבית, בית המקדש השלישי, נבואת יחזקאל, מקראות גדולות, ליוורנו, יאברוב, עמדין</t>
         </is>
       </c>
-      <c r="I651" t="inlineStr">
+      <c r="I651" s="3" t="inlineStr">
         <is>
           <t>פרשן מקרא ופוסק, בנו של רבי דוד אלטשולר, יליד יאברוב שבגליציה, שכיהן כרב בעמדין וביאברוב. השלים וערך את ״המצודות״ של אביו על התנ״ך, חילק אותן ל״מצודת דוד״ ול״מצודת ציון״, ונדד לברלין, להולנד ולאיטליה כדי להדפיסן, עד שהודפסו בליוורנו. כתב גם את ״בנין הבית״ על צורת בית המקדש השלישי.</t>
         </is>
       </c>
-      <c r="J651" t="inlineStr">
+      <c r="J651" s="3" t="inlineStr">
         <is>
           <t>עריכה שהופכת כתבי אב לפירוש מקיף: ״מצודת דוד״ מבארת את ענייני הפסוקים ופשטם, ו״מצודת ציון״ מפרשת מילים וביטויים בתנ״ך, והוא שכלל והוסיף הוספות משלו. הפירוש המוגמר זכה לאהדה רבה מפני שהוא ברור ומובן לכל, ובמהרה נעשה אבן יסוד של פרשנות התנ״ך.</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr">
+      <c r="K651" s="3" t="inlineStr">
         <is>
           <t>רבי דוד אלטשולר</t>
         </is>
       </c>
-      <c r="L651" t="inlineStr"/>
+      <c r="L651" s="3" t="inlineStr"/>
     </row>
     <row r="652">
-      <c r="A652" t="inlineStr">
+      <c r="A652" s="3" t="inlineStr">
         <is>
           <t>651</t>
         </is>
       </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C652" t="inlineStr">
+      <c r="B652" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C652" s="3" t="inlineStr">
         <is>
           <t>רבי שלמה עדני (בעל מלאכת שלמה)</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr">
+      <c r="D652" s="3" t="inlineStr">
         <is>
           <t>כ־1567–1630</t>
         </is>
       </c>
-      <c r="E652" t="inlineStr">
+      <c r="E652" s="3" t="inlineStr">
         <is>
           <t>חברון; ירושלים; צנעא</t>
         </is>
       </c>
-      <c r="F652" t="inlineStr">
+      <c r="F652" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G652" t="inlineStr">
+      <c r="G652" s="3" t="inlineStr">
         <is>
           <t>פרשנות משנה</t>
         </is>
       </c>
-      <c r="H652" t="inlineStr">
+      <c r="H652" s="3" t="inlineStr">
         <is>
           <t>מלאכת שלמה, פירוש המשנה, נוסח המשנה, רבי חיים ויטאל, רבי בצלאל אשכנזי, בנין שלמה לחכמת בצלאל, דברי אמת, יהדות תימן</t>
         </is>
       </c>
-      <c r="I652" t="inlineStr">
+      <c r="I652" s="3" t="inlineStr">
         <is>
           <t>מגדולי מפרשי המשנה, יליד צנעא שבתימן, שעלה עם משפחתו לארץ ישראל והתיישב בצפת ואחר כך בירושלים, ובירושלים למד לפני רבי חיים ויטאל ורבי בצלאל אשכנזי. עבר לחברון וכתב בה במשך שלושים שנה את ״מלאכת שלמה״, פירוש על ששת סדרי משנה. חיבר גם את ״בנין שלמה לחכמת בצלאל״ ואת ״דברי אמת״, הגהות למקרא.</t>
         </is>
       </c>
-      <c r="J652" t="inlineStr">
+      <c r="J652" s="3" t="inlineStr">
         <is>
           <t>פירוש למשנה שמברר את נוסח המשנה וניקודה, ומתוך בקיאות בשני התלמודים, במפרשים ובפוסקים הוא דן בדבריהם עד לפסיקת ההלכה. בפירושו ניכרת חיבתו לרמב״ם, שאותו הוא מכנה ״גדול הפוסקים״.</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr">
+      <c r="K652" s="3" t="inlineStr">
         <is>
           <t>רבי בצלאל אשכנזי, רבי חיים ויטאל</t>
         </is>
       </c>
-      <c r="L652" t="inlineStr"/>
+      <c r="L652" s="3" t="inlineStr"/>
     </row>
     <row r="653">
-      <c r="A653" t="inlineStr">
+      <c r="A653" s="3" t="inlineStr">
         <is>
           <t>652</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C653" t="inlineStr">
+      <c r="B653" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C653" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב יהושע פלק (בעל פני יהושע)</t>
         </is>
       </c>
-      <c r="D653" t="inlineStr">
+      <c r="D653" s="3" t="inlineStr">
         <is>
           <t>1680–1756</t>
         </is>
       </c>
-      <c r="E653" t="inlineStr">
+      <c r="E653" s="3" t="inlineStr">
         <is>
           <t>לבוב; ברלין; מץ; פרנקפורט; גרמניה; גליציה</t>
         </is>
       </c>
-      <c r="F653" t="inlineStr">
+      <c r="F653" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G653" t="inlineStr">
+      <c r="G653" s="3" t="inlineStr">
         <is>
           <t>פרשנות התלמוד</t>
         </is>
       </c>
-      <c r="H653" t="inlineStr">
+      <c r="H653" s="3" t="inlineStr">
         <is>
           <t>פני יהושע, מגיני שלמה, תוספות, רש״י, עיון ופלפול, לבוב, ברלין, מץ, פרנקפורט, מחלוקת עמדין־אייבשיץ</t>
         </is>
       </c>
-      <c r="I653" t="inlineStr">
+      <c r="I653" s="3" t="inlineStr">
         <is>
           <t>נולד בקרקוב ב־1680, כיהן כרבן של לבוב, ברלין, מץ ופרנקפורט על המיין, ונפטר ב־1756 באופנבך. כתב את סדרת ספרי ״פני יהושע״ על התלמוד הבבלי, שבהם הוא מבאר את סוגיות הש״ס על פי התוספות ורש״י בדרך העיון, החקירה, הסברה והפלפול. לפי הקדמתו התחיל לכתוב את הספר בנדר, אחרי שניצל מפיצוץ מחסן חומר נפץ.</t>
         </is>
       </c>
-      <c r="J653" t="inlineStr">
+      <c r="J653" s="3" t="inlineStr">
         <is>
           <t>הגנה על רש״י דרך עיון: ״פני יהושע״ ממשיך את דרכו של ״מגיני שלמה״ ומיישב את קושיות בעלי התוספות על פירוש רש״י, ויורד לפרטי הפרטים של כל סוגיה. אף ששיטת הלימוד שהתקבלה בדורות האחרונים רחוקה מדרכו, הספר זוכה לפופולריות רבה בישיבות.</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
-      <c r="L653" t="inlineStr"/>
+      <c r="K653" s="3" t="inlineStr"/>
+      <c r="L653" s="3" t="inlineStr"/>
     </row>
     <row r="654">
-      <c r="A654" t="inlineStr">
+      <c r="A654" s="3" t="inlineStr">
         <is>
           <t>653</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C654" t="inlineStr">
+      <c r="B654" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C654" s="3" t="inlineStr">
         <is>
           <t>רבי יהונתן אייבשיץ</t>
         </is>
       </c>
-      <c r="D654" t="inlineStr">
+      <c r="D654" s="3" t="inlineStr">
         <is>
           <t>כ־1690–1764</t>
         </is>
       </c>
-      <c r="E654" t="inlineStr">
+      <c r="E654" s="3" t="inlineStr">
         <is>
           <t>פראג; מץ; אלטונה; המבורג</t>
         </is>
       </c>
-      <c r="F654" t="inlineStr">
+      <c r="F654" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G654" t="inlineStr">
+      <c r="G654" s="3" t="inlineStr">
         <is>
           <t>הלכה, קבלה ודרשנות</t>
         </is>
       </c>
-      <c r="H654" t="inlineStr">
+      <c r="H654" s="3" t="inlineStr">
         <is>
           <t>כרתי ופלתי, אורים ותומים, יערות דבש, מחלוקת עמדין־אייבשיץ, קמעות, שבתאות, לוחות עדות, פלפול, פראג, מץ</t>
         </is>
       </c>
-      <c r="I654" t="inlineStr">
+      <c r="I654" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבה ודרשן בפראג, ולימים רבה של מץ ורבן של קהילות אלטונה, המבורג ואנדסבק, ומגדולי פוסקי ההלכה ביהדות אשכנז בזמנו. חיבר את ״כרתי ופלתי״ על יורה דעה, את ״אורים ותומים״ על חושן משפט ואת ספר הדרשות ״יערות דבש״. עיסוקו בקבלה ובקמעות עורר נגדו פולמוס, שפתח רבי יעקב עמדין שמצא רמזים שבתאיים בכתביו; רוב רבני דורו תמכו בו והפולמוס דעך.</t>
         </is>
       </c>
-      <c r="J654" t="inlineStr">
+      <c r="J654" s="3" t="inlineStr">
         <is>
           <t>פלפול מחוכם שמלווה גם את ההלכה וגם את המוסר: חיבור של רעיונות שונים זה מזה מאפשר לו לפתור קושיות ולהתמודד עם סתירות. כפוסק הוא מחמיר, ודבקותו בשולחן ערוך גדולה, והוא מציע להתעלם מדעות שאינן מוזכרות בו.</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr">
+      <c r="K654" s="3" t="inlineStr">
         <is>
           <t>רבי אליה שפירא (בעל אליה רבה), רבי יעקב ריישר</t>
         </is>
       </c>
-      <c r="L654" t="inlineStr"/>
+      <c r="L654" s="3" t="inlineStr"/>
     </row>
     <row r="655">
-      <c r="A655" t="inlineStr">
+      <c r="A655" s="3" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C655" t="inlineStr">
+      <c r="B655" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C655" s="3" t="inlineStr">
         <is>
           <t>רבי מנחם די לונזאנו</t>
         </is>
       </c>
-      <c r="D655" t="inlineStr">
+      <c r="D655" s="3" t="inlineStr">
         <is>
           <t>כ־1550–1626</t>
         </is>
       </c>
-      <c r="E655" t="inlineStr">
+      <c r="E655" s="3" t="inlineStr">
         <is>
           <t>ירושלים; קושטא; איטליה</t>
         </is>
       </c>
-      <c r="F655" t="inlineStr">
+      <c r="F655" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G655" t="inlineStr">
+      <c r="G655" s="3" t="inlineStr">
         <is>
           <t>נוסח המקרא, מילונאות, קבלה ושירה</t>
         </is>
       </c>
-      <c r="H655" t="inlineStr">
+      <c r="H655" s="3" t="inlineStr">
         <is>
           <t>שתי ידות, אור תורה, מעריך, עבודת המקדש, דרך חיים, נוסח המקרא, מסורה, מדרש אגור, הרמד״ל</t>
         </is>
       </c>
-      <c r="I655" t="inlineStr">
+      <c r="I655" s="3" t="inlineStr">
         <is>
           <t>רב, מקובל, משורר, חוקר המסורה ומהדיר ספרי מדרש, ומן העולים הקדמונים לארץ ישראל. נולד, לפי אגרת המלצה, בפיסארו שבאיטליה, עלה לירושלים אחרי 1575 ונפטר בה לפני 1626. חיבר את ״שתי ידות״ (ונציה, 1618), ספר הכולל עשרה חיבורים: חמישה משלו, ובהם ״אור תורה״ לבירור נוסח המקרא לפי המסורה ו״מעריך״, תשלום לספר הערוך, וחמישה חיבורים קדומים של חז״ל שהדיר.</t>
         </is>
       </c>
-      <c r="J655" t="inlineStr">
+      <c r="J655" s="3" t="inlineStr">
         <is>
           <t>הכרעה בנוסח המקרא לפי כתבי היד והמסורה: ״אור תורה״ נשען על יותר מעשרה כתבי יד של המקרא ועל ספרי מגיהי המקרא שקדמוהו, ויחד עם דברי הרמ״ה (רבי מאיר הלוי אבולעפיה) ובעל ״מנחת שי״ נעשה לקובע נוסח המקרא המקובל. בנדודיו נחשף לכתבי יד עתיקים של מדרשי חז״ל והשתדל להוציאם לאור.</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr">
+      <c r="K655" s="3" t="inlineStr">
         <is>
           <t>רבי נתן מרומי, רבי שמואל די מדינה (המהרשד״ם)</t>
         </is>
       </c>
-      <c r="L655" t="inlineStr"/>
+      <c r="L655" s="3" t="inlineStr"/>
     </row>
     <row r="656">
-      <c r="A656" t="inlineStr">
+      <c r="A656" s="3" t="inlineStr">
         <is>
           <t>655</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C656" t="inlineStr">
+      <c r="B656" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C656" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב חגיז (בעל הלכות קטנות)</t>
         </is>
       </c>
-      <c r="D656" t="inlineStr">
+      <c r="D656" s="3" t="inlineStr">
         <is>
           <t>1620–1674</t>
         </is>
       </c>
-      <c r="E656" t="inlineStr">
+      <c r="E656" s="3" t="inlineStr">
         <is>
           <t>ירושלים; ליוורנו; קושטא; פאס</t>
         </is>
       </c>
-      <c r="F656" t="inlineStr">
+      <c r="F656" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G656" t="inlineStr">
+      <c r="G656" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, פרשנות משנה וראשות ישיבה</t>
         </is>
       </c>
-      <c r="H656" t="inlineStr">
+      <c r="H656" s="3" t="inlineStr">
         <is>
           <t>הלכות קטנות, עץ חיים, ישיבת בית יעקב, פתיל תכלת, תחילת חכמה, שבתי צבי, שבתאות, ליוורנו, פאס</t>
         </is>
       </c>
-      <c r="I656" t="inlineStr">
+      <c r="I656" s="3" t="inlineStr">
         <is>
           <t>נולד בפאס שבמרוקו ב־1620, עבר בצעירותו לאיטליה והדפיס שם חיבורים, ובשנת 1658 עלה לירושלים והקים בה את בית המדרש ״בית יעקב״. חיבר את שו״ת ״הלכות קטנות״, את ״עץ חיים״ על המשנה ואת ״פתיל תכלת״ על אזהרות אבן גבירול. בראש רבני ירושלים נקט קו תקיף נגד שבתי צבי, ורבני העיר בראשותו פרסמו נגדו חרם; הוא נפטר בקושטא ב־1674.</t>
         </is>
       </c>
-      <c r="J656" t="inlineStr">
+      <c r="J656" s="3" t="inlineStr">
         <is>
           <t>הכשרת דיינים ורבנים דרך התנסות: בישיבת ״בית יעקב״ קבע סדרי לימוד חדשים, ובהם מקום לתלמידים צעירים ולתלמידי חכמים; התלמידים למדו בחמישה ״שולחנות״, ואחר כך התמחו בפסיקה ובדיינות לצד עשרה חכמים, עד מינוי לדיינים בקהילות שבחוץ לארץ. גם את תשובותיו ב״הלכות קטנות״ כתב, לפי החיד״א, בדרך קצרה כדי לחדד את התלמידים.</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr">
+      <c r="K656" s="3" t="inlineStr">
         <is>
           <t>רבי משה חגיז, רבי משה גלאנטי (המג״ן)</t>
         </is>
       </c>
-      <c r="L656" t="inlineStr"/>
+      <c r="L656" s="3" t="inlineStr"/>
     </row>
     <row r="657">
-      <c r="A657" t="inlineStr">
+      <c r="A657" s="3" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C657" t="inlineStr">
+      <c r="B657" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C657" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם הלוי (בעל גינת ורדים)</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr">
+      <c r="D657" s="3" t="inlineStr">
         <is>
           <t>כ־1650–1712</t>
         </is>
       </c>
-      <c r="E657" t="inlineStr">
+      <c r="E657" s="3" t="inlineStr">
         <is>
           <t>קהיר; רוזטה; מצרים</t>
         </is>
       </c>
-      <c r="F657" t="inlineStr">
+      <c r="F657" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G657" t="inlineStr">
+      <c r="G657" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת</t>
         </is>
       </c>
-      <c r="H657" t="inlineStr">
+      <c r="H657" s="3" t="inlineStr">
         <is>
           <t>גינת ורדים, גן המלך, דרכי נועם, רבני מצרים, רוזטה, קהיר, באר היטב</t>
         </is>
       </c>
-      <c r="I657" t="inlineStr">
+      <c r="I657" s="3" t="inlineStr">
         <is>
           <t>מרבני מצרים במאה ה־17, נולד בה בסביבות 1650 ונפטר ב־1712. שימש בדיינות ואחר כך נבחר לראש רבני מצרים בקהיר, ומילא את מקום אביו, רבי מרדכי הלוי בעל ״דרכי נועם״, כראש הישיבה ואב בית הדין ברוזטה. חיבר את שו״ת ״גינת ורדים״, בסדר ארבעה טורים, שנתפרסמו אחרי מותו והשפיעו רבות בכל המזרח וגם על חכמים אשכנזים.</t>
         </is>
       </c>
-      <c r="J657" t="inlineStr">
+      <c r="J657" s="3" t="inlineStr">
         <is>
           <t>שו״ת מסודר לפי ארבעה טורים, הכולל גם תשובות של חכמי התקופה ומכתבים עם חברו ובר פלוגתא רבי יעקב פראג׳י. השפעת הספר הייתה רבה בכל המזרח וגם על חכמים אשכנזים, ובעל ״באר היטב״ מביאו פעמים רבות.</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
-      <c r="L657" t="inlineStr"/>
+      <c r="K657" s="3" t="inlineStr"/>
+      <c r="L657" s="3" t="inlineStr"/>
     </row>
     <row r="658">
-      <c r="A658" t="inlineStr">
+      <c r="A658" s="3" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C658" t="inlineStr">
+      <c r="B658" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C658" s="3" t="inlineStr">
         <is>
           <t>רבי יאיר חיים בכרך (בעל חוות יאיר)</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr">
+      <c r="D658" s="3" t="inlineStr">
         <is>
           <t>1638–1702</t>
         </is>
       </c>
-      <c r="E658" t="inlineStr">
+      <c r="E658" s="3" t="inlineStr">
         <is>
           <t>וורמייזא; מגנצא; קובלנץ; פרנקפורט</t>
         </is>
       </c>
-      <c r="F658" t="inlineStr">
+      <c r="F658" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G658" t="inlineStr">
+      <c r="G658" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת</t>
         </is>
       </c>
-      <c r="H658" t="inlineStr">
+      <c r="H658" s="3" t="inlineStr">
         <is>
           <t>חוות יאיר, מקור חיים, חוט השני, המהר״ל, וורמייזא, מגן אברהם, הט״ז, אחרי רבים להטות, פסיקה אשכנזית</t>
         </is>
       </c>
-      <c r="I658" t="inlineStr">
+      <c r="I658" s="3" t="inlineStr">
         <is>
           <t>נולד בלייפניק שבמוראביה ב־1638, כיהן כרב בקובלנץ ובמגנצא ובסוף ימיו בוורמייזא, ונפטר ב־1702. מגדולי האחרונים באשכנז, ונודע בספר השו״ת ״חוות יאיר״, שיצא לאור ב־1699 ונחשב לאחד מספרי ההלכה החשובים ביותר באשכנז. חיבר כארבעים ספרים בהלכה, ובהם ״מקור חיים״ על שולחן ערוך אורח חיים; ספרו ״חוט השני״ מכיל בעיקר תשובות של אביו וסבו.</t>
         </is>
       </c>
-      <c r="J658" t="inlineStr">
+      <c r="J658" s="3" t="inlineStr">
         <is>
           <t>פסיקה עצמאית שמחויבת לאמת: הוא חולק על הרמב״ם וקובע שייתכנו שכחה ומחלוקת גם בהלכה למשה מסיני, ושהכרעת חכמי הדור קובעת הלכה גם נגד המסורת המקורית. הוא מתנגד בחריפות לפלפול מוגזם, ובמקום לעסוק בתורת הנסתר, שהעריך את חשיבותה, מעדיף ״לעמוד על עקרי הדת ומשפטי המצוות״.</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr">
+      <c r="K658" s="3" t="inlineStr">
         <is>
           <t>המהר״ל מפראג, רבי דוד הלוי סגל (הט״ז), רבי אברהם אבלי גומבינר (המגן אברהם)</t>
         </is>
       </c>
-      <c r="L658" t="inlineStr"/>
+      <c r="L658" s="3" t="inlineStr"/>
     </row>
     <row r="659">
-      <c r="A659" t="inlineStr">
+      <c r="A659" s="3" t="inlineStr">
         <is>
           <t>658</t>
         </is>
       </c>
-      <c r="B659" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C659" t="inlineStr">
+      <c r="B659" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C659" s="3" t="inlineStr">
         <is>
           <t>רבי אליהו הכהן האתמרי (בעל שבט מוסר)</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr">
+      <c r="D659" s="3" t="inlineStr">
         <is>
           <t>כ־1659–1729</t>
         </is>
       </c>
-      <c r="E659" t="inlineStr">
+      <c r="E659" s="3" t="inlineStr">
         <is>
           <t>איזמיר</t>
         </is>
       </c>
-      <c r="F659" t="inlineStr">
+      <c r="F659" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G659" t="inlineStr">
+      <c r="G659" s="3" t="inlineStr">
         <is>
           <t>מוסר, דרשנות וקבלה</t>
         </is>
       </c>
-      <c r="H659" t="inlineStr">
+      <c r="H659" s="3" t="inlineStr">
         <is>
           <t>שבט מוסר, מדרש תלפיות, ילקוט האתמרי, איזמיר, סגפנות, צדקה, אפוטרופוסים לעניים, אגדת אליהו, ספרות המוסר</t>
         </is>
       </c>
-      <c r="I659" t="inlineStr">
+      <c r="I659" s="3" t="inlineStr">
         <is>
           <t>דיין, דרשן ומקובל מחכמי איזמיר, שנולד בעיר וישב בה כל חייו. ספרו המוסרי ״שבט מוסר״ יצא לאור לראשונה בקושטא בשנת ה׳תע״ב, נדפס מאז בעשרות מהדורות ותורגם ליידיש, ללדינו ולערבית יהודית. חיבר עשרות ספרים, בעיקר ספרי מוסר, מדרש ופרשנות המקרא, ובהם ״מדרש תלפיות״.</t>
         </is>
       </c>
-      <c r="J659" t="inlineStr">
+      <c r="J659" s="3" t="inlineStr">
         <is>
           <t>המוסר אינו עניין של הפרט בלבד: בדרשותיו הטיף לסגפנות ולהתרחקות מתענוגות העולם הזה, וראה בעוני ובאי־השוויון החברתי בעיה דתית ומוסרית שהקהילה כולה צריכה לתקן. את עשירי הקהילה ראה כ״אפוטרופוסים״ על כספי העניים וקרא להם לפזר את כספם לצדקה.</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
-      <c r="L659" t="inlineStr"/>
+      <c r="K659" s="3" t="inlineStr"/>
+      <c r="L659" s="3" t="inlineStr"/>
     </row>
     <row r="660">
-      <c r="A660" t="inlineStr">
+      <c r="A660" s="3" t="inlineStr">
         <is>
           <t>659</t>
         </is>
       </c>
-      <c r="B660" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C660" t="inlineStr">
+      <c r="B660" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C660" s="3" t="inlineStr">
         <is>
           <t>רבי עזריה פיגו (בעל גידולי תרומה)</t>
         </is>
       </c>
-      <c r="D660" t="inlineStr">
+      <c r="D660" s="3" t="inlineStr">
         <is>
           <t>1579–1647</t>
         </is>
       </c>
-      <c r="E660" t="inlineStr">
+      <c r="E660" s="3" t="inlineStr">
         <is>
           <t>ונציה; פיזה</t>
         </is>
       </c>
-      <c r="F660" t="inlineStr">
+      <c r="F660" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G660" t="inlineStr">
+      <c r="G660" s="3" t="inlineStr">
         <is>
           <t>הלכה, דרשנות</t>
         </is>
       </c>
-      <c r="H660" t="inlineStr">
+      <c r="H660" s="3" t="inlineStr">
         <is>
           <t>גידולי תרומה, בינה לעתים, ספר התרומות, רבי שמואל הסרדי, פיזה, ונציה, דרשנות, סופר סת״ם, הש״ך, יהדות איטליה</t>
         </is>
       </c>
-      <c r="I660" t="inlineStr">
+      <c r="I660" s="3" t="inlineStr">
         <is>
           <t>רב, פוסק ודרשן יליד ונציה, מחכמי איטליה במאה ה־17, שלמד תורה בעירו ורכש גם השכלה כללית באוניברסיטה. שימש כרב קהילת פיזה כעשרים שנה, ואחר כך שב לוונציה והיה בה דרשן בבתי הכנסת. את פירושו ״גידולי תרומה״ לספר התרומות של רבי שמואל הסרדי כתב כמעט ללא ספרים, ודרשותיו נדפסו בספרו ״בינה לעתים״, שיצא לאור אחרי מותו.</t>
         </is>
       </c>
-      <c r="J660" t="inlineStr">
+      <c r="J660" s="3" t="inlineStr">
         <is>
           <t>הדרשה צריכה להישאר קרובה לפשט ולעולם המעשה: לדברי מי שהוציא את דרשותיו לאור, הוא נמנע מעיונים מופשטים ומרעיונות פילוסופיים שאין להם אחיזה בעולם המעשה, שהיו דרכם של דרשני איטליה בימיו, ומבקש את פשט הדברים. ספרו נדפס עשרות פעמים וזכה לפופולריות רבה בקרב הדרשנים והמון העם. בהלכה ברר את דברי ספר התרומות ואת מקורותיו והשווה אותם לדברי פוסקים אחרים.</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr">
+      <c r="K660" s="3" t="inlineStr">
         <is>
           <t>רבנו שמואל הסרדי, רבי שבתאי הכהן (הש״ך)</t>
         </is>
       </c>
-      <c r="L660" t="inlineStr"/>
+      <c r="L660" s="3" t="inlineStr"/>
     </row>
     <row r="661">
-      <c r="A661" t="inlineStr">
+      <c r="A661" s="3" t="inlineStr">
         <is>
           <t>660</t>
         </is>
       </c>
-      <c r="B661" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C661" t="inlineStr">
+      <c r="B661" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C661" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב ריישר (בעל שבות יעקב)</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr">
+      <c r="D661" s="3" t="inlineStr">
         <is>
           <t>כ־1661–1733</t>
         </is>
       </c>
-      <c r="E661" t="inlineStr">
+      <c r="E661" s="3" t="inlineStr">
         <is>
           <t>פראג; וורמייזא; מץ</t>
         </is>
       </c>
-      <c r="F661" t="inlineStr">
+      <c r="F661" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G661" t="inlineStr">
+      <c r="G661" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, אגדה</t>
         </is>
       </c>
-      <c r="H661" t="inlineStr">
+      <c r="H661" s="3" t="inlineStr">
         <is>
           <t>שבות יעקב, חק יעקב, מנחת יעקב, עיון יעקב, תורת השלמים, עין יעקב, פראג, מץ, וורמייזא, הש״ך</t>
         </is>
       </c>
-      <c r="I661" t="inlineStr">
+      <c r="I661" s="3" t="inlineStr">
         <is>
           <t>מרבני אשכנז, פוסק ומחבר ספרי הלכה ואגדה. נולד בפראג, שימש בה כדיין ובהמשך כראש בית הדין הגדול, ואחר כך כיהן כרב וכראש ישיבה בוורמייזא ובמץ, ושם נפטר. מחיבוריו שו״ת ״שבות יעקב״, ״חק יעקב״ על הלכות פסח, ״מנחת יעקב״ ו״עיון יעקב״, פירוש לאגדות שבספר עין יעקב.</t>
         </is>
       </c>
-      <c r="J661" t="inlineStr">
+      <c r="J661" s="3" t="inlineStr">
         <is>
           <t>הלכה ואגדה יחד: הוא חיבר שו״ת וחידושים על שולחן ערוך, וחיבור על כללי הספיקות של הש״ך, וגם פירוש לאגדות התלמוד שבספר עין יעקב. הוא נהג לעמוד עם גיסיו, רבי אליה שפירא ורבי דוד אופנהיים, במשא ומתן הלכתי.</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr">
+      <c r="K661" s="3" t="inlineStr">
         <is>
           <t>רבי אליה שפירא (בעל אליה רבה), רבי שבתאי הכהן (הש״ך)</t>
         </is>
       </c>
-      <c r="L661" t="inlineStr"/>
+      <c r="L661" s="3" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/0mmLEt5P6cWWmeGViach5r</t>
+        </is>
+      </c>
     </row>
     <row r="662">
-      <c r="A662" t="inlineStr">
+      <c r="A662" s="3" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="B662" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C662" t="inlineStr">
+      <c r="B662" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C662" s="3" t="inlineStr">
         <is>
           <t>רבי שמשון חיים נחמני (בעל זרע שמשון)</t>
         </is>
       </c>
-      <c r="D662" t="inlineStr">
+      <c r="D662" s="3" t="inlineStr">
         <is>
           <t>1706–1779</t>
         </is>
       </c>
-      <c r="E662" t="inlineStr">
+      <c r="E662" s="3" t="inlineStr">
         <is>
           <t>מודינה; רג׳ו אמיליה; צפון איטליה</t>
         </is>
       </c>
-      <c r="F662" t="inlineStr">
+      <c r="F662" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G662" t="inlineStr">
+      <c r="G662" s="3" t="inlineStr">
         <is>
           <t>קבלה, הלכה, דרשנות ושירה</t>
         </is>
       </c>
-      <c r="H662" t="inlineStr">
+      <c r="H662" s="3" t="inlineStr">
         <is>
           <t>זרע שמשון, תולדות שמשון, קרבן קטורת, מודינה, רג׳ו אמיליה, רבי אביעד שר שלום באזילה, קבלה מעשית, גניזת כתבים, דרשנות</t>
         </is>
       </c>
-      <c r="I662" t="inlineStr">
+      <c r="I662" s="3" t="inlineStr">
         <is>
           <t>רב, מקובל, דרשן ומשורר יהודי איטלקי, יליד מודינה, שכיהן כרב בכמה קהילות בצפון איטליה ונחשב לאחד מגדולי רבני המדינה. למד תורה במודינה ובמנטובה וקבלה ברג׳ו אמיליה, ובשנת 1739 החל לכהן שם כרב ושם נפטר. מספריו נדפסו ״זרע שמשון״ על התורה והמגילות ו״תולדות שמשון״ על מסכת אבות, וציווה לגנוז עמו את ספריו, בעיקר בקבלה.</t>
         </is>
       </c>
-      <c r="J662" t="inlineStr">
+      <c r="J662" s="3" t="inlineStr">
         <is>
           <t>נגלה ונסתר יחד: הוא נחשב לבקי בכל חלקי התורה, נגלה ונסתר, בדרשותיו על התורה ביאר גם מאמרים תמוהים, ובהלכה נקט גישה מחמירה וראה בנטייה להקל ״כוח הטומאה״. שאיפתו, כפי שהצהיר בצוואתו, הייתה לזכות את הרבים, להעמיד תלמידים ולחדש חידושי תורה אמיתיים.</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr">
+      <c r="K662" s="3" t="inlineStr">
         <is>
           <t>רבי אביעד שר שלום באזילה</t>
         </is>
       </c>
-      <c r="L662" t="inlineStr"/>
+      <c r="L662" s="3" t="inlineStr"/>
     </row>
     <row r="663">
-      <c r="A663" t="inlineStr">
+      <c r="A663" s="3" t="inlineStr">
         <is>
           <t>662</t>
         </is>
       </c>
-      <c r="B663" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr">
+      <c r="B663" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C663" s="3" t="inlineStr">
         <is>
           <t>רבי יצחק דמן עכו (בעל מאירת עיניים)</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr">
+      <c r="D663" s="3" t="inlineStr">
         <is>
           <t>כ־1250–1340</t>
         </is>
       </c>
-      <c r="E663" t="inlineStr">
+      <c r="E663" s="3" t="inlineStr">
         <is>
           <t>עכו; ספרד</t>
         </is>
       </c>
-      <c r="F663" t="inlineStr">
+      <c r="F663" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G663" t="inlineStr">
+      <c r="G663" s="3" t="inlineStr">
         <is>
           <t>קבלה, פרשנות</t>
         </is>
       </c>
-      <c r="H663" t="inlineStr">
+      <c r="H663" s="3" t="inlineStr">
         <is>
           <t>מאירת עיניים, אוצר החיים, הרמב״ן, ספר הזוהר, רבי משה די ליאון, כיבוש עכו, חכמת הצירוף, פירוש לספר יצירה, ראשית חכמה</t>
         </is>
       </c>
-      <c r="I663" t="inlineStr">
+      <c r="I663" s="3" t="inlineStr">
         <is>
           <t>מקובל יליד עכו, שנחשב לאחד מגדולי חכמי העיר בדורו. בכיבוש עכו בידי הממלוכים ב־1291 נפל בשבי, ואחר כך נסע לספרד כדי להתחקות אחר מקורו של ספר הזוהר, ושם נפטר. בספרו ״מאירת עיניים״ ביאר את הסודות שבפירוש הרמב״ן לתורה, והחיד״א מכנה אותו תלמידו ואיש סודו של הרמב״ן, אך הדבר מסופק.</t>
         </is>
       </c>
-      <c r="J663" t="inlineStr">
+      <c r="J663" s="3" t="inlineStr">
         <is>
           <t>חקירת מקורותיו של ספר הזוהר: הוא נסע לספרד כדי להתחקות אחר מקורו של ספר הזוהר, ובמאירת עיניים ביאר את הסודות שבפירוש הרמב״ן לתורה והאריך בגנות הפילוסופיה. בספרו ״אוצר החיים״, יומן מיסטי של חוויות אקסטטיות, פירש את תורת השמיטות הקבלית.</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr">
+      <c r="K663" s="3" t="inlineStr">
         <is>
           <t>הרמב״ן (רבי משה בן נחמן), רבי אליהו די וידאש</t>
         </is>
       </c>
-      <c r="L663" t="inlineStr"/>
+      <c r="L663" s="3" t="inlineStr"/>
     </row>
     <row r="664">
-      <c r="A664" t="inlineStr">
+      <c r="A664" s="3" t="inlineStr">
         <is>
           <t>663</t>
         </is>
       </c>
-      <c r="B664" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C664" t="inlineStr">
+      <c r="B664" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C664" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל אבוהב (בעל דבר שמואל)</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr">
+      <c r="D664" s="3" t="inlineStr">
         <is>
           <t>1610–1694</t>
         </is>
       </c>
-      <c r="E664" t="inlineStr">
+      <c r="E664" s="3" t="inlineStr">
         <is>
           <t>ונציה; ורונה</t>
         </is>
       </c>
-      <c r="F664" t="inlineStr">
+      <c r="F664" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G664" t="inlineStr">
+      <c r="G664" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, מנהיגות קהילתית</t>
         </is>
       </c>
-      <c r="H664" t="inlineStr">
+      <c r="H664" s="3" t="inlineStr">
         <is>
           <t>דבר שמואל, ספר הזכרונות, ורונה, ונציה, רבי דוד פרנקו, שבתי צבי, סתם יינם, רבי משה זכות, יהדות איטליה</t>
         </is>
       </c>
-      <c r="I664" t="inlineStr">
+      <c r="I664" s="3" t="inlineStr">
         <is>
           <t>רב ופוסק הלכה בוונציה ומגדולי חכמי איטליה, יליד המבורג, שנשלח בגיל שלוש עשרה ללמוד בוונציה אצל הרב דוד פרנקו. ייסד בוורונה ישיבה שנודעה בערי איטליה, ומשנת 1650 שימש רב ואב״ד של ונציה עד סוף ימיו, והיה מראשי הלוחמים באיטליה במשיחיותו של שבתי צבי. נודע בספר תשובותיו ״דבר שמואל״ ובספר ״הזכרונות״.</t>
         </is>
       </c>
-      <c r="J664" t="inlineStr">
+      <c r="J664" s="3" t="inlineStr">
         <is>
           <t>הוא ביקש להשיב את העם אל קיום ההלכה: ב״ספר הזכרונות״, שנדפס בעילום שם, הוכיח על איסורים שרגילים לזלזל בהם, כמו ״סתם יינם״ ושעטנז, בימים שבהם יהדות איטליה הייתה פרוצה ליחסים קרובים עם תושביה הגויים. בתשובותיו לא חתם בשמו מתוך ענווה אלא צירף את שמות חכמי הישיבה.</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr">
+      <c r="K664" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב חגיז, רבי משה זכות (הרמ״ז)</t>
         </is>
       </c>
-      <c r="L664" t="inlineStr"/>
+      <c r="L664" s="3" t="inlineStr"/>
     </row>
     <row r="665">
-      <c r="A665" t="inlineStr">
+      <c r="A665" s="3" t="inlineStr">
         <is>
           <t>664</t>
         </is>
       </c>
-      <c r="B665" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr">
+      <c r="B665" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C665" s="3" t="inlineStr">
         <is>
           <t>רבי יונה לנדסופר (בעל מעיל צדקה)</t>
         </is>
       </c>
-      <c r="D665" t="inlineStr">
+      <c r="D665" s="3" t="inlineStr">
         <is>
           <t>1678–1712</t>
         </is>
       </c>
-      <c r="E665" t="inlineStr">
+      <c r="E665" s="3" t="inlineStr">
         <is>
           <t>פראג</t>
         </is>
       </c>
-      <c r="F665" t="inlineStr">
+      <c r="F665" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G665" t="inlineStr">
+      <c r="G665" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, הלכות סת״ם</t>
         </is>
       </c>
-      <c r="H665" t="inlineStr">
+      <c r="H665" s="3" t="inlineStr">
         <is>
           <t>מעיל צדקה, בני יונה, כנפי יונה, מאורי אור, רבי אברהם ברודא, שיעור הגריס, סופר סת״ם, הנדסה, המהר״ל מפראג</t>
         </is>
       </c>
-      <c r="I665" t="inlineStr">
+      <c r="I665" s="3" t="inlineStr">
         <is>
           <t>רב ופוסק, מגדולי רבני בוהמיה, יליד פראג, שנפטר בגיל צעיר ובכל זאת עשה רושם גדול בעולם ההלכה עוד בחייו. היה סופר סת״ם במקצועו ורכש לעצמו ידע רחב במדעים. שלושה מספריו הרבים נדפסו לאחר מותו: שו״ת ״מעיל צדקה״, שעל שמו כונה, ״בני יונה״ על הלכות ספר תורה ו״כנפי יונה״ על יורה דעה.</t>
         </is>
       </c>
-      <c r="J665" t="inlineStr">
+      <c r="J665" s="3" t="inlineStr">
         <is>
           <t>הלכה שנשענת על ידע מדעי: ב״מעיל צדקה״ קבע את שיעור ה״גריס״ בדיני כתמים; לספר מצורף שרטוט בגודל אמיתי שמודדים לפיו, ובסופו קונטרס בהנדסה, מלוקט מדברי אוקלידס, שכתב בתשובה לשאלה שנשאל מחכמי ההנדסה בדורו. ב״בני יונה״, שמעמדו כספר יסוד בהלכה, פסק שאין נמנעים מלקרוא בחומשים שנדפסו בידי גויים.</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr">
+      <c r="K665" s="3" t="inlineStr">
         <is>
           <t>המהר״ל מפראג</t>
         </is>
       </c>
-      <c r="L665" t="inlineStr"/>
+      <c r="L665" s="3" t="inlineStr"/>
     </row>
     <row r="666">
-      <c r="A666" t="inlineStr">
+      <c r="A666" s="3" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="B666" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr">
+      <c r="B666" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C666" s="3" t="inlineStr">
         <is>
           <t>רבי נתנאל וייל (בעל קרבן נתנאל)</t>
         </is>
       </c>
-      <c r="D666" t="inlineStr">
+      <c r="D666" s="3" t="inlineStr">
         <is>
           <t>1687–1769</t>
         </is>
       </c>
-      <c r="E666" t="inlineStr">
+      <c r="E666" s="3" t="inlineStr">
         <is>
           <t>פראג; קרלסרוהה</t>
         </is>
       </c>
-      <c r="F666" t="inlineStr">
+      <c r="F666" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G666" t="inlineStr">
+      <c r="G666" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, פירוש לפסקי הרא״ש, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H666" t="inlineStr">
+      <c r="H666" s="3" t="inlineStr">
         <is>
           <t>קרבן נתנאל, פסקי הרא״ש, נתיב חיים, תורת נתנאל, מגן אברהם, רבי אברהם ברודא, קרלסרוהה, פראג, מהר״י וייל, גירוש יהודי בוהמיה</t>
         </is>
       </c>
-      <c r="I666" t="inlineStr">
+      <c r="I666" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבה בפראג ורב קרלסרוהה, יליד שטילינגן שבגרמניה, שלמד בישיבתו של רבי אברהם ברודא. לאחר גירוש יהודי בוהמיה ב־1744 עבר לגרמניה, ובשנת 1750 נתמנה לרבה של קרלסרוהה, ושם סיים את ״קרבן נתנאל״ על פסקי הרא״ש, שנדפס ב־1755. חיבר גם את ״נתיב חיים״ על שולחן ערוך אורח חיים ואת ״תורת נתנאל״, שו״ת ודרשות.</t>
         </is>
       </c>
-      <c r="J666" t="inlineStr">
+      <c r="J666" s="3" t="inlineStr">
         <is>
           <t>ביאור לפסקי הרא״ש שמשלים את החסר: סדרי מועד ונשים נותרו בלי ביאור, והוא חיבר עליהם את ״קרבן נתנאל״, שבו הוא מפרש את דברי הרא״ש, מברר את גרסאותיו ומביא מקורות לדבריו. הפירוש נדפס בצמוד לפסקי הרא״ש בש״ס וילנא.</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr">
+      <c r="K666" s="3" t="inlineStr">
         <is>
           <t>מהר״י וייל</t>
         </is>
       </c>
-      <c r="L666" t="inlineStr"/>
+      <c r="L666" s="3" t="inlineStr"/>
     </row>
     <row r="667">
-      <c r="A667" t="inlineStr">
+      <c r="A667" s="3" t="inlineStr">
         <is>
           <t>666</t>
         </is>
       </c>
-      <c r="B667" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
+      <c r="B667" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C667" s="3" t="inlineStr">
         <is>
           <t>רבי חייא רופא (בעל מעשה חייא)</t>
         </is>
       </c>
-      <c r="D667" t="inlineStr">
+      <c r="D667" s="3" t="inlineStr">
         <is>
           <t>כ־1550–1617</t>
         </is>
       </c>
-      <c r="E667" t="inlineStr">
+      <c r="E667" s="3" t="inlineStr">
         <is>
           <t>צפת; טבריה; ירושלים</t>
         </is>
       </c>
-      <c r="F667" t="inlineStr">
+      <c r="F667" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr">
+      <c r="G667" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, קבלה, ראשות ישיבה</t>
         </is>
       </c>
-      <c r="H667" t="inlineStr">
+      <c r="H667" s="3" t="inlineStr">
         <is>
           <t>מעשה חייא, צפת, טבריה, רבי שלמה סאגיש, רבי חיים ויטאל, האר״י, סמיכה בצפת, תיקון ליל שבועות, חכמי בית הוועד</t>
         </is>
       </c>
-      <c r="I667" t="inlineStr">
+      <c r="I667" s="3" t="inlineStr">
         <is>
           <t>פוסק ומקובל, מרבני צפת וירושלים, יליד צפת. למד בישיבתו של רבי שלמה סאגיש וקבלה אצל רבי חיים ויטאל, וקיבל גם מהאר״י, ובגיל עשרים ושלוש כיהן כדיין בבית דינו של רבי משה גלאנטי הראשון. הקים ישיבה בטבריה, כיהן כאב בית דין בירושלים וכראש ישיבה בצפת, ותשובותיו וחידושיו על הש״ס נדפסו בספר ״מעשה חייא״.</t>
         </is>
       </c>
-      <c r="J667" t="inlineStr">
+      <c r="J667" s="3" t="inlineStr">
         <is>
           <t>קבלה ופסיקה יחד: את הקבלה למד מרבי חיים ויטאל וקיבל גם מהאר״י, לימד אותה לתלמידיו, ובתיקון ליל שבועות של הרמ״ז מובאת כוונה שהגיעה אל הרמ״ז ממנו דרך רבי בנימין הלוי. בצפת היה מראשי הרבנים ומעשרים ״חכמי בית הוועד״, ורבי משה גלאנטי הראשון כתב בתשובותיו שהנהגת בית המדרש בעיר תהיה על פיו ועל פי חכמים נוספים.</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr">
+      <c r="K667" s="3" t="inlineStr">
         <is>
           <t>רבי חיים ויטאל, האר״י הקדוש, רבי משה זכות (הרמ״ז)</t>
         </is>
       </c>
-      <c r="L667" t="inlineStr"/>
+      <c r="L667" s="3" t="inlineStr"/>
     </row>
     <row r="668">
-      <c r="A668" t="inlineStr">
+      <c r="A668" s="3" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="B668" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C668" t="inlineStr">
+      <c r="B668" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C668" s="3" t="inlineStr">
         <is>
           <t>רב פלטוי גאון</t>
         </is>
       </c>
-      <c r="D668" t="inlineStr">
+      <c r="D668" s="3" t="inlineStr">
         <is>
           <t>842–858 (ראש ישיבת פומבדיתא)</t>
         </is>
       </c>
-      <c r="E668" t="inlineStr">
+      <c r="E668" s="3" t="inlineStr">
         <is>
           <t>פומבדיתא</t>
         </is>
       </c>
-      <c r="F668" t="inlineStr">
+      <c r="F668" s="3" t="inlineStr">
         <is>
           <t>גאונים</t>
         </is>
       </c>
-      <c r="G668" t="inlineStr">
+      <c r="G668" s="3" t="inlineStr">
         <is>
           <t>הלכה ותשובות הגאונים, הנהגת ישיבה</t>
         </is>
       </c>
-      <c r="H668" t="inlineStr">
+      <c r="H668" s="3" t="inlineStr">
         <is>
           <t>ישיבת פומבדיתא, תשובות הגאונים, רב צמח בן פלטוי, רב שרירא גאון, רב האי גאון, תקנות, ערכאות של גויים, נוסח החרם, יהדות ספרד</t>
         </is>
       </c>
-      <c r="I668" t="inlineStr">
+      <c r="I668" s="3" t="inlineStr">
         <is>
           <t>רב פלטוי בר אביי היה גאון ישיבת פומבדיתא בשנים 842–858, ואחד הגאונים הפעילים ביותר שהקימה הישיבה. הוא התמנה בגיל צעיר יחסית ובלי מחלוקות, אף שלא בא ממשפחה מיוחסת, והשיב יותר תשובות הלכתיות מכל גאוני פומבדיתא שקדמו לו. בנו רב צמח בן פלטוי היה אף הוא גאון, ומצאצאיו רב שרירא גאון ובנו רב האי גאון.</t>
         </is>
       </c>
-      <c r="J668" t="inlineStr">
+      <c r="J668" s="3" t="inlineStr">
         <is>
           <t>גאון שחיבר את הישיבה אל הגולה: הוא יצר וביסס קשרים עם התפוצות במערב ובמיוחד עם ספרד, ולדברי אחד החוקרים הגביר את הפצת התלמוד והוראתו יותר מכל גאוני פומבדיתא שקדמו לו, ותיקן תקנות חשובות במשפט, ובהן היתר לפנות לערכאות של גויים כשהנתבע מסרב לידון בבית הדין היהודי.</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr">
+      <c r="K668" s="3" t="inlineStr">
         <is>
           <t>רב שרירא גאון, רב האי גאון</t>
         </is>
       </c>
-      <c r="L668" t="inlineStr"/>
+      <c r="L668" s="3" t="inlineStr"/>
     </row>
     <row r="669">
-      <c r="A669" t="inlineStr">
+      <c r="A669" s="3" t="inlineStr">
         <is>
           <t>668</t>
         </is>
       </c>
-      <c r="B669" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C669" t="inlineStr">
+      <c r="B669" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C669" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב הלוי ממרויש (בעל שו״ת מן השמים)</t>
         </is>
       </c>
-      <c r="D669" t="inlineStr">
+      <c r="D669" s="3" t="inlineStr">
         <is>
           <t>המאה ה־13 (נפטר 1233)</t>
         </is>
       </c>
-      <c r="E669" t="inlineStr">
+      <c r="E669" s="3" t="inlineStr">
         <is>
           <t>פרובנס</t>
         </is>
       </c>
-      <c r="F669" t="inlineStr">
+      <c r="F669" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G669" t="inlineStr">
+      <c r="G669" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, קבלה</t>
         </is>
       </c>
-      <c r="H669" t="inlineStr">
+      <c r="H669" s="3" t="inlineStr">
         <is>
           <t>שו״ת מן השמים, שאילת חלום, מרויש, פרובנס, התבודדות, הרדב״ז, רבי יעקב החסיד, הכרעה בין הפוסקים</t>
         </is>
       </c>
-      <c r="I669" t="inlineStr">
+      <c r="I669" s="3" t="inlineStr">
         <is>
           <t>רב ומקובל מחכמי יהדות פרובנס בתקופת הראשונים, בנו של רבי לוי, שנפטר בשנת 1233. התגורר במרויש, שימש כפוסק, כונה בעבר ״החסיד״ או ״הקדוש״, ולדברי הרדב״ז, שהיו בידיו קצת מתשובותיו, היה ״חכם גדול מקובל״. נודע בחיבורו ״שו״ת מן השמים״, שבו שאל את שאלותיו ההלכתיות מן השמים.</t>
         </is>
       </c>
-      <c r="J669" t="inlineStr">
+      <c r="J669" s="3" t="inlineStr">
         <is>
           <t>ההכרעה ההלכתית נשענת גם על שאלה מן השמים: כשהלכה הייתה מסופקת לו, שאל, לפי הרדב״ז, בהתבודדות, בתפילה ובהזכרת שמות, והיו משיבים לו. שאלותיו נשאלו בדרך של שאלת חלום, כשאלות לבית דין של מעלה, כדי להכריע בין הפוסקים.</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
-      <c r="L669" t="inlineStr"/>
+      <c r="K669" s="3" t="inlineStr"/>
+      <c r="L669" s="3" t="inlineStr"/>
     </row>
     <row r="670">
-      <c r="A670" t="inlineStr">
+      <c r="A670" s="3" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="B670" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C670" t="inlineStr">
+      <c r="B670" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C670" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם סבע (בעל צרור המור)</t>
         </is>
       </c>
-      <c r="D670" t="inlineStr">
+      <c r="D670" s="3" t="inlineStr">
         <is>
           <t>1440–1508</t>
         </is>
       </c>
-      <c r="E670" t="inlineStr">
+      <c r="E670" s="3" t="inlineStr">
         <is>
           <t>קסטיליה; פורטוגל; פאס; אדריאנופול</t>
         </is>
       </c>
-      <c r="F670" t="inlineStr">
+      <c r="F670" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G670" t="inlineStr">
+      <c r="G670" s="3" t="inlineStr">
         <is>
           <t>פרשנות התורה, קבלה והגות</t>
         </is>
       </c>
-      <c r="H670" t="inlineStr">
+      <c r="H670" s="3" t="inlineStr">
         <is>
           <t>צרור המור, אשכול הכופר, צרור החיים, תפארת בנים, גירוש ספרד, שמד פורטוגל, רבי יצחק די ליאון, פאס, אדריאנופול, פשט</t>
         </is>
       </c>
-      <c r="I670" t="inlineStr">
+      <c r="I670" s="3" t="inlineStr">
         <is>
           <t>רב, מקובל ופרשן מדור גירוש ספרד, יליד קסטיליה ותלמידו של רבי יצחק די ליאון. בגזירות השמד בפורטוגל ב־1497 נחטפו שני ילדיו והוטבלו לנצרות, והוא עצמו נאסר ועונה ונמלט לפאס שבמרוקו. את ספריו קבר בפורטוגל וכתב מחדש מזיכרונו, ובהם ״צרור המור״ על התורה ו״אשכול הכופר״ על רות ואסתר; הוא נפטר בדרכו לאיטליה בשנת 1508.</t>
         </is>
       </c>
-      <c r="J670" t="inlineStr">
+      <c r="J670" s="3" t="inlineStr">
         <is>
           <t>פירושו לתורה ״צרור המור״ מצרף פשט, דרוש וקבלה בביאור אחד. הוא גם עדות אישית לגירוש ספרד ולשמד פורטוגל: בפרשת ויצא מגולל סבע את תלאותיו בקונטרס ״תפארת בנים״.</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr">
+      <c r="K670" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף קארו</t>
         </is>
       </c>
-      <c r="L670" t="inlineStr"/>
+      <c r="L670" s="3" t="inlineStr"/>
     </row>
     <row r="671">
-      <c r="A671" t="inlineStr">
+      <c r="A671" s="3" t="inlineStr">
         <is>
           <t>670</t>
         </is>
       </c>
-      <c r="B671" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C671" t="inlineStr">
+      <c r="B671" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C671" s="3" t="inlineStr">
         <is>
           <t>רבי אליעזר אשכנזי (בעל מעשי ה׳)</t>
         </is>
       </c>
-      <c r="D671" t="inlineStr">
+      <c r="D671" s="3" t="inlineStr">
         <is>
           <t>כ־1513–1585</t>
         </is>
       </c>
-      <c r="E671" t="inlineStr">
+      <c r="E671" s="3" t="inlineStr">
         <is>
           <t>קהיר; ונציה; פוזנא; קרקוב</t>
         </is>
       </c>
-      <c r="F671" t="inlineStr">
+      <c r="F671" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G671" t="inlineStr">
+      <c r="G671" s="3" t="inlineStr">
         <is>
           <t>פרשנות המקרא, פילוסופיה והלכה</t>
         </is>
       </c>
-      <c r="H671" t="inlineStr">
+      <c r="H671" s="3" t="inlineStr">
         <is>
           <t>מעשי ה׳, יוסף לקח, פירוש ההגדה של פסח, פשוטו של מקרא, סליחות ופזמונים, רבי יוסף טאיטצאק, קפריסין, קרימונה, פוזנא, קרקוב</t>
         </is>
       </c>
-      <c r="I671" t="inlineStr">
+      <c r="I671" s="3" t="inlineStr">
         <is>
           <t>רב, פרשן מקרא, פייטן ופילוסוף, ככל הנראה יליד ונציה, שלמד בסלוניקי אצל רבי יוסף טאיטצאק. שימש דיין בקהיר, חי בקפריסין ובאיטליה, ולבסוף היה רב העיר ורב המדינה בפוזנא ועבר לקרקוב, שבה נפטר ב־1585. ספרו העיקרי ״מעשי ה׳״ הוא פירוש לחמשה חומשי תורה ובתוכו פירוש להגדה של פסח, והוא חיבר גם את ״יוסף לקח״ על מגילת אסתר.</t>
         </is>
       </c>
-      <c r="J671" t="inlineStr">
+      <c r="J671" s="3" t="inlineStr">
         <is>
           <t>כפרשן דבק בפשוטו של מקרא, אך אינו נרתע מלחלוק על רש״י, האבן עזרא, הרמב״ם והרמב״ן ולהציע פירושים עצמאיים. בהקדמתו כתב שהוא מקבל את הטוב ודוחה את הרע בלי להתחשב בשם האומר.</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr">
+      <c r="K671" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף טאיטצאק</t>
         </is>
       </c>
-      <c r="L671" t="inlineStr"/>
+      <c r="L671" s="3" t="inlineStr"/>
     </row>
     <row r="672">
-      <c r="A672" t="inlineStr">
+      <c r="A672" s="3" t="inlineStr">
         <is>
           <t>671</t>
         </is>
       </c>
-      <c r="B672" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C672" t="inlineStr">
+      <c r="B672" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C672" s="3" t="inlineStr">
         <is>
           <t>רבי משה גלאנטי (המג״ן)</t>
         </is>
       </c>
-      <c r="D672" t="inlineStr">
+      <c r="D672" s="3" t="inlineStr">
         <is>
           <t>כ־1620–1689</t>
         </is>
       </c>
-      <c r="E672" t="inlineStr">
+      <c r="E672" s="3" t="inlineStr">
         <is>
           <t>ירושלים; צפת</t>
         </is>
       </c>
-      <c r="F672" t="inlineStr">
+      <c r="F672" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G672" t="inlineStr">
+      <c r="G672" s="3" t="inlineStr">
         <is>
           <t>הלכה, מנהיגות ופרשנות</t>
         </is>
       </c>
-      <c r="H672" t="inlineStr">
+      <c r="H672" s="3" t="inlineStr">
         <is>
           <t>אלף המגן, זבח השלמים, קרבן חגיגה, פרפראות לחכמה, הראשון לציון, שד״ר, כספי החלוקה, ישיבת בית יעקב, רבי משה גלאנטי הראשון, רבי משה חגיז</t>
         </is>
       </c>
-      <c r="I672" t="inlineStr">
+      <c r="I672" s="3" t="inlineStr">
         <is>
           <t>הראשון לציון הראשון וראש רבני ירושלים במאה ה־17, שכונה לעיתים ״המג״ן״, יליד צפת ונכד רבי משה גלאנטי הראשון. למד בצפת אצל רבי ברוך ברזילי ורבי גבריאל איספיראנסה, ובגיל 34 עבר לירושלים, שם עמד בראש ישיבת בית יעקב ונשלח כשד״ר לחוץ לארץ. חיבר את ״אלף המגן״, אוסף שו״ת ובו אלף תשובות, ואת ״זבח השלמים״ על התורה, ונפטר בירושלים ב־1689.</t>
         </is>
       </c>
-      <c r="J672" t="inlineStr">
+      <c r="J672" s="3" t="inlineStr">
         <is>
           <t>הסכים להתמנות לרבה של ירושלים רק בתואר שאינו שררתי, ״ראשון לציון״ ולא ״רב״, כי ראה את עצמו שווה בין שווים בגדלותו בתורה. הוא תיקן לחלק את כספי החלוקה לעשרים וארבעה חלקים: שנים־עשר לירושלים, שמונה לצפת וארבעה לחברון.</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr">
+      <c r="K672" s="3" t="inlineStr">
         <is>
           <t>רבי משה חגיז, רבנו חזקיה די סילוה, הרב אברהם יצחקי</t>
         </is>
       </c>
-      <c r="L672" t="inlineStr"/>
+      <c r="L672" s="3" t="inlineStr"/>
     </row>
     <row r="673">
-      <c r="A673" t="inlineStr">
+      <c r="A673" s="3" t="inlineStr">
         <is>
           <t>672</t>
         </is>
       </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr">
+      <c r="B673" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C673" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם גלאנטי (בעל קול בוכים)</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr">
+      <c r="D673" s="3" t="inlineStr">
         <is>
           <t>תחילת המאה ה־16 – 1560</t>
         </is>
       </c>
-      <c r="E673" t="inlineStr">
+      <c r="E673" s="3" t="inlineStr">
         <is>
           <t>צפת; רומא</t>
         </is>
       </c>
-      <c r="F673" t="inlineStr">
+      <c r="F673" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G673" t="inlineStr">
+      <c r="G673" s="3" t="inlineStr">
         <is>
           <t>קבלה ופרשנות</t>
         </is>
       </c>
-      <c r="H673" t="inlineStr">
+      <c r="H673" s="3" t="inlineStr">
         <is>
           <t>קינת סתרים, קול בוכים, ירח יקר, זכות אבות, הרמ״ק, הזוהר, מגילת איכה, זהרי חמה, אור יקר, צפת</t>
         </is>
       </c>
-      <c r="I673" t="inlineStr">
+      <c r="I673" s="3" t="inlineStr">
         <is>
           <t>מקובל, יליד רומא בתחילת המאה ה־16, שעלה לצפת והיה מתלמידי הרמ״ק. כמו אביו מרדכי ואחיו המבוגר ממנו, רבי משה גלאנטי הראשון, חי חיי סגפנות וקדושה. חיבר את ״קינת סתרים״ (״קול בוכים״), פירוש קבלי למגילת איכה שהודפס בוונציה ב־1589 בעריכת בנו שמואל, את ״ירח יקר״ על הזוהר ואת ״זכות אבות״ על מסכת אבות, ונפטר ב־1560.</t>
         </is>
       </c>
-      <c r="J673" t="inlineStr">
+      <c r="J673" s="3" t="inlineStr">
         <is>
           <t>פירושו לזוהר, ״ירח יקר״, נקרא כך על שם ״אור יקר״ של רבו הרמ״ק, כמאמר ״פני משה כפני חמה״, ורבי אברהם אזולאי קיצר אותו ב״זהרי חמה״. את מגילת איכה פירש ״על דרך האמת״, כלומר בקבלה, ב״קינת סתרים״ שהודפס כמה פעמים.</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr">
+      <c r="K673" s="3" t="inlineStr">
         <is>
           <t>רבי משה קורדובירו (הרמ״ק), רבי אברהם אזולאי</t>
         </is>
       </c>
-      <c r="L673" t="inlineStr"/>
+      <c r="L673" s="3" t="inlineStr"/>
     </row>
     <row r="674">
-      <c r="A674" t="inlineStr">
+      <c r="A674" s="3" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="B674" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C674" t="inlineStr">
+      <c r="B674" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C674" s="3" t="inlineStr">
         <is>
           <t>רבי יעקב קשטרו (מהריק״ש)</t>
         </is>
       </c>
-      <c r="D674" t="inlineStr">
+      <c r="D674" s="3" t="inlineStr">
         <is>
           <t>כ־1525–1612</t>
         </is>
       </c>
-      <c r="E674" t="inlineStr">
+      <c r="E674" s="3" t="inlineStr">
         <is>
           <t>קהיר; אלכסנדריה; ירושלים</t>
         </is>
       </c>
-      <c r="F674" t="inlineStr">
+      <c r="F674" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G674" t="inlineStr">
+      <c r="G674" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת</t>
         </is>
       </c>
-      <c r="H674" t="inlineStr">
+      <c r="H674" s="3" t="inlineStr">
         <is>
           <t>ערך לחם, אהלי יעקב, תולדות יעקב, קול יעקב, מרא דאתרא, הרדב״ז, המהרלב״ח, שולחן ערוך, קהיר, יהדות מצרים</t>
         </is>
       </c>
-      <c r="I674" t="inlineStr">
+      <c r="I674" s="3" t="inlineStr">
         <is>
           <t>מרבניה הנודעים של יהדות מצרים, יליד מצרים בסביבות 1525, ששימש כרבו של קהל המוסתערבים בקהיר. למד בירושלים אצל הרלב״ח, אך רבו המובהק היה הרדב״ז, ובמצרים ראו בו גדול הדור, ״מרא דאתרא״. נתפרסם בעיקר בספרו ״ערך לחם״, הגהות על השולחן ערוך, וחיבר גם את שו״ת ״אהלי יעקב״; ככל הנראה נפטר בקהיר ב־1610 או ב־1612.</t>
         </is>
       </c>
-      <c r="J674" t="inlineStr">
+      <c r="J674" s="3" t="inlineStr">
         <is>
           <t>ב״ערך לחם״ הגיה את השולחן ערוך, והגהותיו תואמות פעמים רבות את הגהות הרמ״א. הספרדים בכל ארץ מצרים פסקו כמותו גם במקום שחלק על מרן הבית יוסף.</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr">
+      <c r="K674" s="3" t="inlineStr">
         <is>
           <t>הרדב״ז, רבי לוי בן חביב (המהרלב״ח)</t>
         </is>
       </c>
-      <c r="L674" t="inlineStr"/>
+      <c r="L674" s="3" t="inlineStr"/>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr">
+      <c r="A675" s="3" t="inlineStr">
         <is>
           <t>674</t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C675" t="inlineStr">
+      <c r="B675" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C675" s="3" t="inlineStr">
         <is>
           <t>רבי חיים כפוסי (בעל הנס)</t>
         </is>
       </c>
-      <c r="D675" t="inlineStr">
+      <c r="D675" s="3" t="inlineStr">
         <is>
           <t>כ־1540–1631</t>
         </is>
       </c>
-      <c r="E675" t="inlineStr">
+      <c r="E675" s="3" t="inlineStr">
         <is>
           <t>קהיר; אלכסנדריה; אלג׳יר</t>
         </is>
       </c>
-      <c r="F675" t="inlineStr">
+      <c r="F675" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G675" t="inlineStr">
+      <c r="G675" s="3" t="inlineStr">
         <is>
           <t>הלכה ושו״ת, פרשנות התורה</t>
         </is>
       </c>
-      <c r="H675" t="inlineStr">
+      <c r="H675" s="3" t="inlineStr">
         <is>
           <t>ספרי חיים, באור החיים, בעל הנס, מכילתא דרשב״י, קהיר, אלכסנדריה, דמיאט, אלג׳יר, יהדות מצרים, המהריק״ש</t>
         </is>
       </c>
-      <c r="I675" t="inlineStr">
+      <c r="I675" s="3" t="inlineStr">
         <is>
           <t>פוסק הלכה ופרשן, מגדולי חכמי מצרים במאות ה־16 וה־17, יליד אלג׳יר למשפחה שמוצאה מספרד. חייו היו מלאי סבל ונדודים בין קהיר, אלכסנדריה ודמיאט, ולפי אגדה נפקחו עיניו בנס אחרי שלקה בעיוורון, ומאז כונה ״בעל הנס״. תשובותיו נשארו בכתב יד מאות שנים; חיבר גם את ״באור החיים״ על התורה ואת ״ספרי חיים״ על המכילתא, ונפטר ב־1631.</t>
         </is>
       </c>
-      <c r="J675" t="inlineStr">
+      <c r="J675" s="3" t="inlineStr">
         <is>
           <t>תשובותיו משקפות את חיי היהודים במצרים ובאימפריה העות׳מאנית במשך יותר מ־60 שנה, ובהן מחלוקות הלכתיות עם רבה של מצרים, המהריק״ש. בביאורו לתורה, ״באור החיים״, הוא מפרש בדרך פשט ורמז.</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
-      <c r="L675" t="inlineStr"/>
+      <c r="K675" s="3" t="inlineStr"/>
+      <c r="L675" s="3" t="inlineStr"/>
     </row>
     <row r="676">
-      <c r="A676" t="inlineStr">
+      <c r="A676" s="3" t="inlineStr">
         <is>
           <t>675</t>
         </is>
       </c>
-      <c r="B676" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C676" t="inlineStr">
+      <c r="B676" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C676" s="3" t="inlineStr">
         <is>
           <t>רבי שמואל ויטאל (בן רבי חיים)</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr">
+      <c r="D676" s="3" t="inlineStr">
         <is>
           <t>1598–1677</t>
         </is>
       </c>
-      <c r="E676" t="inlineStr">
+      <c r="E676" s="3" t="inlineStr">
         <is>
           <t>דמשק; מצרים</t>
         </is>
       </c>
-      <c r="F676" t="inlineStr">
+      <c r="F676" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G676" t="inlineStr">
+      <c r="G676" s="3" t="inlineStr">
         <is>
           <t>קבלה והלכה</t>
         </is>
       </c>
-      <c r="H676" t="inlineStr">
+      <c r="H676" s="3" t="inlineStr">
         <is>
           <t>שער הגלגולים, כתבי האר״י, שמונה שערים, באר מים חיים, מקור חיים, תוצאות חיים, חמדת ישראל, דמשק, קבלת האר״י, רבי חיים ויטאל</t>
         </is>
       </c>
-      <c r="I676" t="inlineStr">
+      <c r="I676" s="3" t="inlineStr">
         <is>
           <t>מרבני ומקובלי דמשק ובנו של רבי חיים ויטאל: נולד בדמשק, שימש בה רב ודיין והקים ישיבה גדולה שלמדו בה גם קבלה. היה מגדולי תלמידי אביו, העתיק וסידר את כתבי אביו ואת כתבי האר״י, ובהם ״שער הגלגולים״, ובהמשך חייו עבר למצרים והקים שם ישיבה. כתב תשובות בהלכה ובקבלה ודרשות לראש חודש, ונפטר במצרים ב־1677.</t>
         </is>
       </c>
-      <c r="J676" t="inlineStr">
+      <c r="J676" s="3" t="inlineStr">
         <is>
           <t>כמעתיק ומסדר של כתבי אביו ושל כתבי האר״י שימר את תורת האר״י, וספריו נחשבו, כפי שכתב החיד״א, למדויקים והמוסמכים ביותר לכתבי קבלת האר״י. את תשובותיו בהלכה ובקבלה כתב לשואלים ממצרים, מארץ ישראל ומרחבי סוריה.</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr">
+      <c r="K676" s="3" t="inlineStr">
         <is>
           <t>רבי חיים ויטאל</t>
         </is>
       </c>
-      <c r="L676" t="inlineStr"/>
+      <c r="L676" s="3" t="inlineStr"/>
     </row>
     <row r="677">
-      <c r="A677" t="inlineStr">
+      <c r="A677" s="3" t="inlineStr">
         <is>
           <t>676</t>
         </is>
       </c>
-      <c r="B677" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C677" t="inlineStr">
+      <c r="B677" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C677" s="3" t="inlineStr">
         <is>
           <t>רבי אהרן שמואל קאיידנובר (המהרש״ק)</t>
         </is>
       </c>
-      <c r="D677" t="inlineStr">
+      <c r="D677" s="3" t="inlineStr">
         <is>
           <t>1614–1676</t>
         </is>
       </c>
-      <c r="E677" t="inlineStr">
+      <c r="E677" s="3" t="inlineStr">
         <is>
           <t>קרקוב; בריסק; פרנקפורט</t>
         </is>
       </c>
-      <c r="F677" t="inlineStr">
+      <c r="F677" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G677" t="inlineStr">
+      <c r="G677" s="3" t="inlineStr">
         <is>
           <t>הלכה ופרשנות התלמוד</t>
         </is>
       </c>
-      <c r="H677" t="inlineStr">
+      <c r="H677" s="3" t="inlineStr">
         <is>
           <t>ברכת הזבח, תפארת שמואל, אמונת שמואל, ברכת שמואל, סדר קדשים, גזירות ת״ח ת״ט, פסקי הרא״ש, המהרש״א, בריסק, קרקוב</t>
         </is>
       </c>
-      <c r="I677" t="inlineStr">
+      <c r="I677" s="3" t="inlineStr">
         <is>
           <t>רב אשכנזי מראשוני האחרונים, שנולד ככל הנראה בקוידנוב שבבלארוס, למד אצל רבי יעקב מלובלין ואחר כך אצל בנו והיה דיין בבית דינו של רבי משה לימא. בגזירות ת״ח ת״ט נרצחו שתי בנותיו ואבדו רוב כתביו, ולאחר מכן כיהן ברבנות בערים רבות, בהן בריסק, פרנקפורט וקרקוב. חיבר את ״ברכת הזבח״ על סדר קדשים ואת ״תפארת שמואל״ על פסקי הרא״ש ואת שו״ת ״אמונת שמואל״, ונפטר ב־1676.</t>
         </is>
       </c>
-      <c r="J677" t="inlineStr">
+      <c r="J677" s="3" t="inlineStr">
         <is>
           <t>כתב ״בדרך קצרה וכשרה״, כלשון החיד״א. הגהותיו על הרא״ש והשגותיו על המהרש״א נדפסו בתוך הש״ס בכל מהדורותיו עד ש״ס וילנה, והמגן אברהם קורא לו ״גאון״. הוא התנגד לפסוק לפי השולחן ערוך ונושאי כליו ותמך בפסיקה לפי ארבעה טורים עם הבית יוסף.</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr">
+      <c r="K677" s="3" t="inlineStr">
         <is>
           <t>רבי אברהם אבלי גומבינר (המגן אברהם)</t>
         </is>
       </c>
-      <c r="L677" t="inlineStr"/>
+      <c r="L677" s="3" t="inlineStr"/>
     </row>
     <row r="678">
-      <c r="A678" t="inlineStr">
+      <c r="A678" s="3" t="inlineStr">
         <is>
           <t>677</t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C678" t="inlineStr">
+      <c r="B678" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C678" s="3" t="inlineStr">
         <is>
           <t>רבי יהודה בן עטר (בעל מנחת יהודה)</t>
         </is>
       </c>
-      <c r="D678" t="inlineStr">
+      <c r="D678" s="3" t="inlineStr">
         <is>
           <t>1655–1733</t>
         </is>
       </c>
-      <c r="E678" t="inlineStr">
+      <c r="E678" s="3" t="inlineStr">
         <is>
           <t>פאס; מקנס</t>
         </is>
       </c>
-      <c r="F678" t="inlineStr">
+      <c r="F678" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G678" t="inlineStr">
+      <c r="G678" s="3" t="inlineStr">
         <is>
           <t>הלכה, דרשנות ופרשנות המקרא</t>
         </is>
       </c>
-      <c r="H678" t="inlineStr">
+      <c r="H678" s="3" t="inlineStr">
         <is>
           <t>מנחת יהודה, שיר מכתם, דרשנות, תקנות הקהילה, צורף, פאס, מקנס, יהדות מרוקו</t>
         </is>
       </c>
-      <c r="I678" t="inlineStr">
+      <c r="I678" s="3" t="inlineStr">
         <is>
           <t>אב בית דין ודיין בפאס ובמקנס שבמרוקו, פרשן מקרא ומרבניה הגדולים של המדינה, יליד פאס. התפרנס כצורף מיגיע כפיו ולא רצה שכר מקופת הציבור, למד מרבי וידאל הצרפתי השלישי ומרבי מנחם סירירו, ובשנת 1698 מונה לדיין בפאס. חיבר את ״מנחת יהודה״, דרשות על התורה, ואת ״שיר מכתם״ על הלכות שחיטה, ונפטר ב־1733.</t>
         </is>
       </c>
-      <c r="J678" t="inlineStr">
+      <c r="J678" s="3" t="inlineStr">
         <is>
           <t>ראה שתלמידיו, על גדלותם בתורה, אינם יודעים לדרוש, ולימד אותם נאום ודרוש: ״מנחת יהודה״ מקורו בדרשות שבת במנחה, שאחריהן דרש תלמיד אחר. כל חייו התפרנס מיגיע כפיו, ותיקן לקהילתו תקנות במיסים, במסחר ובהלוואות מגויים.</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
-      <c r="L678" t="inlineStr"/>
+      <c r="K678" s="3" t="inlineStr"/>
+      <c r="L678" s="3" t="inlineStr"/>
     </row>
     <row r="679">
-      <c r="A679" t="inlineStr">
+      <c r="A679" s="3" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="B679" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C679" t="inlineStr">
+      <c r="B679" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C679" s="3" t="inlineStr">
         <is>
           <t>רבי מנחם ציוני (בעל ספר ציוני)</t>
         </is>
       </c>
-      <c r="D679" t="inlineStr">
+      <c r="D679" s="3" t="inlineStr">
         <is>
           <t>כ־1340–1410</t>
         </is>
       </c>
-      <c r="E679" t="inlineStr">
+      <c r="E679" s="3" t="inlineStr">
         <is>
           <t>שפיירא; קלן; ירושלים; ונציה; גרמניה</t>
         </is>
       </c>
-      <c r="F679" t="inlineStr">
+      <c r="F679" s="3" t="inlineStr">
         <is>
           <t>ראשונים</t>
         </is>
       </c>
-      <c r="G679" t="inlineStr">
+      <c r="G679" s="3" t="inlineStr">
         <is>
           <t>קבלה, פיוט ופרשנות התורה</t>
         </is>
       </c>
-      <c r="H679" t="inlineStr">
+      <c r="H679" s="3" t="inlineStr">
         <is>
           <t>ציוני, צפוני ציוני, ספר הבהיר, הזוהר, הרמב״ן, קינות, ציון מעון חשקי, רבי יצחק מבילשטיין, שפיירא, קרימונה</t>
         </is>
       </c>
-      <c r="I679" t="inlineStr">
+      <c r="I679" s="3" t="inlineStr">
         <is>
           <t>מקובל ופייטן מחכמי אשכנז, יליד שפיירא, שנסע בצעירותו לירושלים ולמד בישיבתו של רבי יצחק מבילשטיין. הוא האדם הראשון הידוע שבחר לכנות עצמו ״ציוני״, על שם לימודיו בירושלים. חיבר את הספר ״ציוני״ על התורה, שנדפס בקרימונה ב־1559, ואת ״צפוני ציוני״, וכתב עשרות שירים.</t>
         </is>
       </c>
-      <c r="J679" t="inlineStr">
+      <c r="J679" s="3" t="inlineStr">
         <is>
           <t>ספרו ״ציוני״ מצרף את הזוהר וספר הבהיר עם דברי הראשונים, כסעדיה גאון, הרמב״ם, אבן עזרא והרמב״ן, לפירוש התורה ״על דרך האמת״, ובראשי פרקיו ובסופיהם חרוזים ובפתיחתו ובסיומו שירים. החיד״א שיבח אותו ב״שם הגדולים״, וגדולי האחרונים כהשל״ה והמגן אברהם הביאו דברים בשמו.</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr">
+      <c r="K679" s="3" t="inlineStr">
         <is>
           <t>רבי יוסף שלמה דלמדיגו – יש״ר מקנדיה, רבי ישעיה הלוי הורוויץ (השל״ה הקדוש), רבי אברהם אבלי גומבינר (המגן אברהם)</t>
         </is>
       </c>
-      <c r="L679" t="inlineStr"/>
+      <c r="L679" s="3" t="inlineStr"/>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr">
+      <c r="A680" s="3" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="B680" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C680" t="inlineStr">
+      <c r="B680" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C680" s="3" t="inlineStr">
         <is>
           <t>רבי אליהו בחור (בעל מסורת המסורת)</t>
         </is>
       </c>
-      <c r="D680" t="inlineStr">
+      <c r="D680" s="3" t="inlineStr">
         <is>
           <t>1469–1549</t>
         </is>
       </c>
-      <c r="E680" t="inlineStr">
+      <c r="E680" s="3" t="inlineStr">
         <is>
           <t>גרמניה; ונציה; פדובה; רומא</t>
         </is>
       </c>
-      <c r="F680" t="inlineStr">
+      <c r="F680" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G680" t="inlineStr">
+      <c r="G680" s="3" t="inlineStr">
         <is>
           <t>דקדוק עברי, מסורה ומילונאות</t>
         </is>
       </c>
-      <c r="H680" t="inlineStr">
+      <c r="H680" s="3" t="inlineStr">
         <is>
           <t>הבחור, התשבי, מסורת המסורת, טוב טעם, המתורגמן, סבסטיאן מינסטר, פאולוס פאגיוס, אג׳ידיו דה ויטרבו, ספרות יידיש, מלומדים נוצרים</t>
         </is>
       </c>
-      <c r="I680" t="inlineStr">
+      <c r="I680" s="3" t="inlineStr">
         <is>
           <t>בלשן עברי וחוקר המסורה בתקופת הרנסאנס, יליד נוישטאדט שבבוואריה, שעבר בצעירותו לאיטליה והתגורר בוונציה, בפדובה וברומא. לימד עברית למלומדים נוצרים, עבד כמגיה בבית דפוס בוונציה ופיקח על בית דפוס באיזנא וחיבר ספרי דקדוק ומילונים, ובהם ״הבחור״ ו״התשבי״, וכן את ״מסורת המסורת״ ו״טוב טעם״. מת בוונציה ב־1549.</t>
         </is>
       </c>
-      <c r="J680" t="inlineStr">
+      <c r="J680" s="3" t="inlineStr">
         <is>
           <t>בספרו ״מסורת המסורת״ טען שסימני הניקוד והטעמים חודשו בידי בעלי המסורה ואינם מזמן התלמוד, דעה שהחיד״א מביא ומסתייג ממנה. בספריו ובהוראתו הנחיל את הדקדוק העברי למלומדים נוצרים, שתרגמו את חיבוריו ללטינית.</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
-      <c r="L680" t="inlineStr"/>
+      <c r="K680" s="3" t="inlineStr"/>
+      <c r="L680" s="3" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>רב אחאי משבחא (בעל השאילתות)</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>680–752 לערך</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>פומבדיתא; ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>גאונים</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>הלכה, דרשנות</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>ספר השאילתות, ספרות הגאונים, ישיבת פומבדיתא, ראש הגולה, רב נטרונאי בר רב אמונה, עלייה לארץ ישראל, דרשות על פרשות השבוע, העמק שאלה</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>רב אחאי משבחא היה מחכמי פומבדיתא שבבבל, ונודע בעקבות ספרו ״השאילתות״, הספר הראשון הידוע לנו אחרי תקופת התלמוד. בעקבות מינויו של רב נטרונאי בר רב אמונה, שהיה כפוף לרב אחאי, לגאון על ידי ראש הגולה שלמה בר חסדאי, עלה רב אחאי לארץ ישראל. אף שהתואר ״גאון״ מצורף לשמו, הוא לא עמד בפועל בראש אחת משתי הישיבות הגדולות בבבל. לפי ספריא, החיבור נחשב ליצירה חשובה ביותר ובעלת סמכות רבה עבור הפוסקים שבאו אחריו.</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>ספר השאילתות הוא אוסף של דרשות מסוג השאילתא על סדר פרשות השבוע, הכתוב בארמית. כל שאילתא בנויה מארבעה חלקים: פתיחה במצווה מסוימת, שאלה הלכתית הקשורה אליה, דברי אגדה ותשובה לשאלה ההלכתית; אך דברי האגדה כמעט אינם מצויים בנוסחים שבידינו. לפי ויקיפדיה, מעטות הפסיקות בספר שאינן מצויות בתלמוד, אך בתוך ההרצאה מובלעים חידושים רבים בפרשנות התלמוד ובפסיקת ההלכה.</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/5ojAh8QooySuLiNI8GpY6u</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>רבי יצחק אייזיק מקומרנא</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>1806–1874</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>קומרנא; פינצ׳וב; זידיטשוב</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>חסידות, קבלה, פרשנות התורה והלכה</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>היכל הברכה, זוהר חי, שלחן הטהור, מגילת סתרים, אוצר החיים, חסידות קומרנא, קבלת האר״י, הבעל שם טוב, רבי צבי הירש מזידיטשוב, רבי אברהם יהושע השיל מאפטא</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>רבי יצחק אייזיק יהודה יחיאל ספרין (1806–1874) היה האדמו״ר השני בשושלת חסידות קומרנא ומחבר תורני פורה. הוא היה בנו של רבי אלכסנדר סנדר, מייסד השושלת, ולאחר שהתייתם מאביו בגיל 12 גדל אצל דודו, אחי אביו, רבי צבי הירש מזידיטשוב. לאחר חתונתו עבר לפינצ׳וב, שבה כיהן חמיו, רבי אברהם מרדכי, כרב, ובהמשך עבר לקומרנא, עירו של אביו, וחי בה עד סוף ימיו. את תורתו קיבל מרבי אברהם יהושע השיל מאפטא ומדודו, ולמד גם אצל רבי נפתלי צבי מרופשיץ, רבי משה צבי מסאווראן ורבי אשר ישעיה רובין מרופשיץ.</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>את עיקר מפעל חייו ראה בחיבור ספרים רבים, ובהם שילב את קבלת האר״י ואת תורת הבעש״ט. בין ספריו: ״היכל הברכה״, פירוש על חמישה חומשי תורה בדגש על פירוש המסורה; ״זוהר חי״, פירוש על ספר הזוהר על פי קבלת האר״י והבעש״ט; ו״שלחן הטהור״, על סדר ההלכות שבשולחן ערוך אורח חיים. הוא החשיב את הבעש״ט מורו ורבו אף שנולד אחרי פטירתו, וכתב יומן אישי שבו רשם חזיונות שנגלו לו; היומן נשמר בסוד עד אמצע המאה ה־20, ובשנות החמישים יצא לאור מכתבי יד בשם ״מגילת סתרים״.</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>הבעל שם טוב, האר״י הקדוש</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/2Hwqxeswo6x7sutb2IM9cr</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>רבי נתן נטע שפירא (בעל מגלה עמוקות)</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>כ־1585–1633</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>קרקוב; הורדנה</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>קבלה, דרשנות ופלפול</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>מגלה עמוקות, אעברה נא, פרשת ואתחנן, רנ״ב אופנים, קבלת האר״י, פלפול, הש״ך, אגרא דכלה, חידושי אנשי שם, תיקון חצות</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>מרבני פולין ומחשובי המקובלים בתקופתו, הנקרא על שם ספרו ״מגלה עמוקות״. נולד בהורדנה, בסביבות שנת 1608 עבר לקז׳ימייז׳ שליד קרקוב, ובשנת 1617 נתמנה לראש ישיבה ודרשן בקהילת קרקוב. לפי עדות בנו בהקדמת ספרו חיבר חמישה עשר ספרים בנגלה ובנסתר, ומהם שבעה על התורה; בספרו ״מגלה עמוקות״ על פרשת ואתחנן הוא מציע רנ״ב (252) אופנים לבאר את תפילת משה ״אעברה נא״. בין תלמידיו היה רבי שבתאי הכהן (הש״ך).</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>בישיבה לימד את תלמידיו את הנגלה בדרך הפלפול, ואילו בדרשותיו ברבים מדי שבת הסתמך גם על תורת הנסתר, ועל ידו התרבו העוסקים בקבלה. על צירופי מילים ומספרם בנה בניינים של מחשבה וגילה סודות קבליים הרמוזים בסתרי אותיות התורה. הוא מילא תפקיד חשוב בהפצת תורת האר״י בפולין.</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>רבי שבתאי הכהן (הש"ך), רבי יהונתן אייבשיץ, האר״י הקדוש</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/1W9jLv41tnXGcgNYDIEbrL</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>רחל אמנו</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>תקופת האבות</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>בית לחם; פדן ארם (חרן); ארץ כנען</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>תקופת המקרא</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>אמהות ישראל, תפילה ובקשת רחמים</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>יעקב אבינו, לאה אמנו, לבן, יוסף, בנימין, שבטי ישראל, קבר רחל, בית לחם, תפילה, נשים</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>אחת מארבע האמהות של עם ישראל: בתו הצעירה של לבן, אחותה של לאה ואשתו האהובה של יעקב. היא הייתה עקרה; אלוהים זכר אותה ופתח את רחמה, והיא ילדה את יוסף. בדרך לאפרת ילדה את בנימין ומתה בלידתו; היא קבורה ״בדרך אפרתה הוא בית לחם״. חז״ל סיפרו שמסרה ללאה את הסימנים שמסר לה יעקב, שלא תיכלם אחותה, ורש״י מפרש בין השאר את ״ויזכר אלהים את־רחל״: ״זכר לה שמסרה סימניה לאחותה״.</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>בנבואת ירמיהו היא האם הבוכה על בניה: ״רחל מבכה על־בניה מאנה להנחם על־בניה כי איננו״, ובפסוק הבא נאמר ״מנעי קולך מבכי ועיניך מדמעה כי יש שכר לפעלתך״. לפי רש״י, יעקב קבר אותה בדרך ״על פי הדבור״, כדי שתהא ״לעזרה לבניה״ כשיגלה אותם נבוזראדן: ״יוצאת רחל על קברה ובוכה ומבקשת עליהם רחמים״. ובברכת העם והזקנים בשער, בספר רות, נזכרת רחל לצד לאה: ״כרחל וכלאה אשר בנו שתיהם את־בית ישראל״.</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>יעקב אבינו, לאה אמנו, רבקה אמנו</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/1EKJiVlFPRzq9U3HlgXXGq</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>רב עמרם גאון</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>כ־810–כ־875</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>סורא; בבל</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>גאונים</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>ליטורגיה ונוסח התפילה, הלכה ותשובות הגאונים</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>סדר רב עמרם גאון, ישיבת סורא, רב נטרונאי גאון, תשובות הגאונים, נוסח התפילה, מאה ברכות, שערי צדק, קהילת ברצלונה, יהדות ספרד</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>רב עמרם בר ששנא, הידוע כרב עמרם גאון, עמד בראש ישיבת סורא שבבבל במחצית השנייה של המאה התשיעית. הוא היה תלמידו של רב נטרונאי גאון, וירש את ראשות הישיבה רק לאחר מותו. ערך את ״סדר רב עמרם גאון״, סידור שהיה ראשון מסוגו, כתשובה לבקשת קהילה בספרד, ככל הנראה קהילת ברצלונה, שביקשה את סדר התפילות והברכות לכל השנה. הוא חיבר תשובות הלכתיות רבות, ורבות מהן נדפסו בשאלוניקי בקובץ ״שערי צדק״.</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>סדר רב עמרם גאון מכיל לא רק את נוסחי התפילות עצמן אלא גם הלכות ומנהגים הקשורים בהן, ומקורם של קטעי ההלכה בתלמוד ובפסקי גאונים. הוא ערוך בסדר קבוע של ימי חול, שבתות ומועדים, סדר המהווה מודל למבנה של מרבית הסידורים עד ימינו, והוא השפיע השפעה רבה על נוסח התפילה בקהילות רבות בישראל. הנוסח שבידינו כנראה אינו זה שיצא מתחת ידו: כתבי היד שונים זה מזה במידה ניכרת, וההשערה המקובלת במחקר היא שאחרי ששלח את הסידור לספרד המשיכו לערוך אותו ולהוסיף עליו.</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>הרמב"ם, רבי יצחק אלפסי (הרי"ף), רב סעדיה גאון, רבי דוד אבודרהם, יעקב בן אשר, רבי יוסף קארו</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/2ULZn2cKuetkTGLFWYrUx8</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>רב יהודאי גאון</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>757–761 (ראש ישיבת סורא)</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>סורא; פומבדיתא</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>גאונים</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>הלכה, קודיפיקציה, הנהגת ישיבה</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>הלכות פסוקות, הלכות ראו, הלכות גדולות, ישיבת סורא, ישיבת פומבדיתא, רב דודאי גאון, פירקוי בן באבוי, מנהג שמד, תלמוד בבלי, תשובות הגאונים</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>ראש ישיבת סורא בשנים 757–761 ואחד מחשובי הגאונים, שהיה סגי נהור (עיוור). היה מחכמי ישיבת פומבדיתא, ולפי אגרת רב שרירא גאון העביר אותו ראש הגולה שלמה בן חסדאי לסורא מפני שלא נמצא בה מופלג בחכמה כמותו. הגאון הראשון שהחל בחיבור קובצי הלכה לאחר חתימת התלמוד הבבלי; על פי חלק מן החוקרים כתב את הספר ״הלכות פסוקות״.</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>ספר ״הלכות פסוקות״, המיוחס לו, הוא הניסיון הקודיפיקטיבי הראשון לאחר חתימת התלמוד הבבלי: הוא עוקב במידה רבה אחר הסדר התלמודי, אך במקום השקלא וטריא התלמודית מציע ניסוח תמציתי של שורה תחתונה ופסוקה. הוא לחם בחריפות למען השלטת התלמוד הבבלי כסמכות הלכתית יחידה בעם ישראל, ונתקל בהתנגדות קשה של בני ארץ ישראל, שהסתמכו על פסיקת התלמוד הירושלמי ומנהגיהם הקדומים. הוא קבע כי רבים ממנהגיהם הם ״מנהגי שמד״, שהתקבלו בזמנים קשים בהם לא הועברה המסורת בשלמותה.</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>https://open.spotify.com/episode/187HitcBGTOzR3Lgzja106</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -39919,7 +39919,7 @@
       </c>
       <c r="D661" s="3" t="inlineStr">
         <is>
-          <t>כ־1661–1733</t>
+          <t>כ־1655–1733</t>
         </is>
       </c>
       <c r="E661" s="3" t="inlineStr">

--- a/data/חכמי_ישראל.xlsx
+++ b/data/חכמי_ישראל.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L686"/>
+  <dimension ref="A1:L699"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="3" min="1" max="1"/>
@@ -41050,366 +41050,1110 @@
       <c r="L680" s="3" t="inlineStr"/>
     </row>
     <row r="681">
-      <c r="A681" t="inlineStr">
+      <c r="A681" s="3" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="B681" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C681" t="inlineStr">
+      <c r="B681" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C681" s="3" t="inlineStr">
         <is>
           <t>רב אחאי משבחא (בעל השאילתות)</t>
         </is>
       </c>
-      <c r="D681" t="inlineStr">
+      <c r="D681" s="3" t="inlineStr">
         <is>
           <t>680–752 לערך</t>
         </is>
       </c>
-      <c r="E681" t="inlineStr">
+      <c r="E681" s="3" t="inlineStr">
         <is>
           <t>פומבדיתא; ארץ ישראל</t>
         </is>
       </c>
-      <c r="F681" t="inlineStr">
+      <c r="F681" s="3" t="inlineStr">
         <is>
           <t>גאונים</t>
         </is>
       </c>
-      <c r="G681" t="inlineStr">
+      <c r="G681" s="3" t="inlineStr">
         <is>
           <t>הלכה, דרשנות</t>
         </is>
       </c>
-      <c r="H681" t="inlineStr">
+      <c r="H681" s="3" t="inlineStr">
         <is>
           <t>ספר השאילתות, ספרות הגאונים, ישיבת פומבדיתא, ראש הגולה, רב נטרונאי בר רב אמונה, עלייה לארץ ישראל, דרשות על פרשות השבוע, העמק שאלה</t>
         </is>
       </c>
-      <c r="I681" t="inlineStr">
+      <c r="I681" s="3" t="inlineStr">
         <is>
           <t>רב אחאי משבחא היה מחכמי פומבדיתא שבבבל, ונודע בעקבות ספרו ״השאילתות״, הספר הראשון הידוע לנו אחרי תקופת התלמוד. בעקבות מינויו של רב נטרונאי בר רב אמונה, שהיה כפוף לרב אחאי, לגאון על ידי ראש הגולה שלמה בר חסדאי, עלה רב אחאי לארץ ישראל. אף שהתואר ״גאון״ מצורף לשמו, הוא לא עמד בפועל בראש אחת משתי הישיבות הגדולות בבבל. לפי ספריא, החיבור נחשב ליצירה חשובה ביותר ובעלת סמכות רבה עבור הפוסקים שבאו אחריו.</t>
         </is>
       </c>
-      <c r="J681" t="inlineStr">
+      <c r="J681" s="3" t="inlineStr">
         <is>
           <t>ספר השאילתות הוא אוסף של דרשות מסוג השאילתא על סדר פרשות השבוע, הכתוב בארמית. כל שאילתא בנויה מארבעה חלקים: פתיחה במצווה מסוימת, שאלה הלכתית הקשורה אליה, דברי אגדה ותשובה לשאלה ההלכתית; אך דברי האגדה כמעט אינם מצויים בנוסחים שבידינו. לפי ויקיפדיה, מעטות הפסיקות בספר שאינן מצויות בתלמוד, אך בתוך ההרצאה מובלעים חידושים רבים בפרשנות התלמוד ובפסיקת ההלכה.</t>
         </is>
       </c>
-      <c r="L681" t="inlineStr">
+      <c r="L681" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/5ojAh8QooySuLiNI8GpY6u</t>
         </is>
       </c>
     </row>
     <row r="682">
-      <c r="A682" t="inlineStr">
+      <c r="A682" s="3" t="inlineStr">
         <is>
           <t>681</t>
         </is>
       </c>
-      <c r="B682" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C682" t="inlineStr">
+      <c r="B682" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C682" s="3" t="inlineStr">
         <is>
           <t>רבי יצחק אייזיק מקומרנא</t>
         </is>
       </c>
-      <c r="D682" t="inlineStr">
+      <c r="D682" s="3" t="inlineStr">
         <is>
           <t>1806–1874</t>
         </is>
       </c>
-      <c r="E682" t="inlineStr">
+      <c r="E682" s="3" t="inlineStr">
         <is>
           <t>קומרנא; פינצ׳וב; זידיטשוב</t>
         </is>
       </c>
-      <c r="F682" t="inlineStr">
+      <c r="F682" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G682" t="inlineStr">
+      <c r="G682" s="3" t="inlineStr">
         <is>
           <t>חסידות, קבלה, פרשנות התורה והלכה</t>
         </is>
       </c>
-      <c r="H682" t="inlineStr">
+      <c r="H682" s="3" t="inlineStr">
         <is>
           <t>היכל הברכה, זוהר חי, שלחן הטהור, מגילת סתרים, אוצר החיים, חסידות קומרנא, קבלת האר״י, הבעל שם טוב, רבי צבי הירש מזידיטשוב, רבי אברהם יהושע השיל מאפטא</t>
         </is>
       </c>
-      <c r="I682" t="inlineStr">
+      <c r="I682" s="3" t="inlineStr">
         <is>
           <t>רבי יצחק אייזיק יהודה יחיאל ספרין (1806–1874) היה האדמו״ר השני בשושלת חסידות קומרנא ומחבר תורני פורה. הוא היה בנו של רבי אלכסנדר סנדר, מייסד השושלת, ולאחר שהתייתם מאביו בגיל 12 גדל אצל דודו, אחי אביו, רבי צבי הירש מזידיטשוב. לאחר חתונתו עבר לפינצ׳וב, שבה כיהן חמיו, רבי אברהם מרדכי, כרב, ובהמשך עבר לקומרנא, עירו של אביו, וחי בה עד סוף ימיו. את תורתו קיבל מרבי אברהם יהושע השיל מאפטא ומדודו, ולמד גם אצל רבי נפתלי צבי מרופשיץ, רבי משה צבי מסאווראן ורבי אשר ישעיה רובין מרופשיץ.</t>
         </is>
       </c>
-      <c r="J682" t="inlineStr">
+      <c r="J682" s="3" t="inlineStr">
         <is>
           <t>את עיקר מפעל חייו ראה בחיבור ספרים רבים, ובהם שילב את קבלת האר״י ואת תורת הבעש״ט. בין ספריו: ״היכל הברכה״, פירוש על חמישה חומשי תורה בדגש על פירוש המסורה; ״זוהר חי״, פירוש על ספר הזוהר על פי קבלת האר״י והבעש״ט; ו״שלחן הטהור״, על סדר ההלכות שבשולחן ערוך אורח חיים. הוא החשיב את הבעש״ט מורו ורבו אף שנולד אחרי פטירתו, וכתב יומן אישי שבו רשם חזיונות שנגלו לו; היומן נשמר בסוד עד אמצע המאה ה־20, ובשנות החמישים יצא לאור מכתבי יד בשם ״מגילת סתרים״.</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr">
+      <c r="K682" s="3" t="inlineStr">
         <is>
           <t>הבעל שם טוב, האר״י הקדוש</t>
         </is>
       </c>
-      <c r="L682" t="inlineStr">
+      <c r="L682" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/2Hwqxeswo6x7sutb2IM9cr</t>
         </is>
       </c>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr">
+      <c r="A683" s="3" t="inlineStr">
         <is>
           <t>682</t>
         </is>
       </c>
-      <c r="B683" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C683" t="inlineStr">
+      <c r="B683" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C683" s="3" t="inlineStr">
         <is>
           <t>רבי נתן נטע שפירא (בעל מגלה עמוקות)</t>
         </is>
       </c>
-      <c r="D683" t="inlineStr">
+      <c r="D683" s="3" t="inlineStr">
         <is>
           <t>כ־1585–1633</t>
         </is>
       </c>
-      <c r="E683" t="inlineStr">
+      <c r="E683" s="3" t="inlineStr">
         <is>
           <t>קרקוב; הורדנה</t>
         </is>
       </c>
-      <c r="F683" t="inlineStr">
+      <c r="F683" s="3" t="inlineStr">
         <is>
           <t>אחרונים</t>
         </is>
       </c>
-      <c r="G683" t="inlineStr">
+      <c r="G683" s="3" t="inlineStr">
         <is>
           <t>קבלה, דרשנות ופלפול</t>
         </is>
       </c>
-      <c r="H683" t="inlineStr">
+      <c r="H683" s="3" t="inlineStr">
         <is>
           <t>מגלה עמוקות, אעברה נא, פרשת ואתחנן, רנ״ב אופנים, קבלת האר״י, פלפול, הש״ך, אגרא דכלה, חידושי אנשי שם, תיקון חצות</t>
         </is>
       </c>
-      <c r="I683" t="inlineStr">
+      <c r="I683" s="3" t="inlineStr">
         <is>
           <t>מרבני פולין ומחשובי המקובלים בתקופתו, הנקרא על שם ספרו ״מגלה עמוקות״. נולד בהורדנה, בסביבות שנת 1608 עבר לקז׳ימייז׳ שליד קרקוב, ובשנת 1617 נתמנה לראש ישיבה ודרשן בקהילת קרקוב. לפי עדות בנו בהקדמת ספרו חיבר חמישה עשר ספרים בנגלה ובנסתר, ומהם שבעה על התורה; בספרו ״מגלה עמוקות״ על פרשת ואתחנן הוא מציע רנ״ב (252) אופנים לבאר את תפילת משה ״אעברה נא״. בין תלמידיו היה רבי שבתאי הכהן (הש״ך).</t>
         </is>
       </c>
-      <c r="J683" t="inlineStr">
+      <c r="J683" s="3" t="inlineStr">
         <is>
           <t>בישיבה לימד את תלמידיו את הנגלה בדרך הפלפול, ואילו בדרשותיו ברבים מדי שבת הסתמך גם על תורת הנסתר, ועל ידו התרבו העוסקים בקבלה. על צירופי מילים ומספרם בנה בניינים של מחשבה וגילה סודות קבליים הרמוזים בסתרי אותיות התורה. הוא מילא תפקיד חשוב בהפצת תורת האר״י בפולין.</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr">
+      <c r="K683" s="3" t="inlineStr">
         <is>
           <t>רבי שבתאי הכהן (הש"ך), רבי יהונתן אייבשיץ, האר״י הקדוש</t>
         </is>
       </c>
-      <c r="L683" t="inlineStr">
+      <c r="L683" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/1W9jLv41tnXGcgNYDIEbrL</t>
         </is>
       </c>
     </row>
     <row r="684">
-      <c r="A684" t="inlineStr">
+      <c r="A684" s="3" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="B684" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C684" t="inlineStr">
+      <c r="B684" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C684" s="3" t="inlineStr">
         <is>
           <t>רחל אמנו</t>
         </is>
       </c>
-      <c r="D684" t="inlineStr">
+      <c r="D684" s="3" t="inlineStr">
         <is>
           <t>תקופת האבות</t>
         </is>
       </c>
-      <c r="E684" t="inlineStr">
+      <c r="E684" s="3" t="inlineStr">
         <is>
           <t>בית לחם; פדן ארם (חרן); ארץ כנען</t>
         </is>
       </c>
-      <c r="F684" t="inlineStr">
+      <c r="F684" s="3" t="inlineStr">
         <is>
           <t>תקופת המקרא</t>
         </is>
       </c>
-      <c r="G684" t="inlineStr">
+      <c r="G684" s="3" t="inlineStr">
         <is>
           <t>אמהות ישראל, תפילה ובקשת רחמים</t>
         </is>
       </c>
-      <c r="H684" t="inlineStr">
+      <c r="H684" s="3" t="inlineStr">
         <is>
           <t>יעקב אבינו, לאה אמנו, לבן, יוסף, בנימין, שבטי ישראל, קבר רחל, בית לחם, תפילה, נשים</t>
         </is>
       </c>
-      <c r="I684" t="inlineStr">
+      <c r="I684" s="3" t="inlineStr">
         <is>
           <t>אחת מארבע האמהות של עם ישראל: בתו הצעירה של לבן, אחותה של לאה ואשתו האהובה של יעקב. היא הייתה עקרה; אלוהים זכר אותה ופתח את רחמה, והיא ילדה את יוסף. בדרך לאפרת ילדה את בנימין ומתה בלידתו; היא קבורה ״בדרך אפרתה הוא בית לחם״. חז״ל סיפרו שמסרה ללאה את הסימנים שמסר לה יעקב, שלא תיכלם אחותה, ורש״י מפרש בין השאר את ״ויזכר אלהים את־רחל״: ״זכר לה שמסרה סימניה לאחותה״.</t>
         </is>
       </c>
-      <c r="J684" t="inlineStr">
+      <c r="J684" s="3" t="inlineStr">
         <is>
           <t>בנבואת ירמיהו היא האם הבוכה על בניה: ״רחל מבכה על־בניה מאנה להנחם על־בניה כי איננו״, ובפסוק הבא נאמר ״מנעי קולך מבכי ועיניך מדמעה כי יש שכר לפעלתך״. לפי רש״י, יעקב קבר אותה בדרך ״על פי הדבור״, כדי שתהא ״לעזרה לבניה״ כשיגלה אותם נבוזראדן: ״יוצאת רחל על קברה ובוכה ומבקשת עליהם רחמים״. ובברכת העם והזקנים בשער, בספר רות, נזכרת רחל לצד לאה: ״כרחל וכלאה אשר בנו שתיהם את־בית ישראל״.</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr">
+      <c r="K684" s="3" t="inlineStr">
         <is>
           <t>יעקב אבינו, לאה אמנו, רבקה אמנו</t>
         </is>
       </c>
-      <c r="L684" t="inlineStr">
+      <c r="L684" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/1EKJiVlFPRzq9U3HlgXXGq</t>
         </is>
       </c>
     </row>
     <row r="685">
-      <c r="A685" t="inlineStr">
+      <c r="A685" s="3" t="inlineStr">
         <is>
           <t>684</t>
         </is>
       </c>
-      <c r="B685" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C685" t="inlineStr">
+      <c r="B685" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C685" s="3" t="inlineStr">
         <is>
           <t>רב עמרם גאון</t>
         </is>
       </c>
-      <c r="D685" t="inlineStr">
+      <c r="D685" s="3" t="inlineStr">
         <is>
           <t>כ־810–כ־875</t>
         </is>
       </c>
-      <c r="E685" t="inlineStr">
+      <c r="E685" s="3" t="inlineStr">
         <is>
           <t>סורא; בבל</t>
         </is>
       </c>
-      <c r="F685" t="inlineStr">
+      <c r="F685" s="3" t="inlineStr">
         <is>
           <t>גאונים</t>
         </is>
       </c>
-      <c r="G685" t="inlineStr">
+      <c r="G685" s="3" t="inlineStr">
         <is>
           <t>ליטורגיה ונוסח התפילה, הלכה ותשובות הגאונים</t>
         </is>
       </c>
-      <c r="H685" t="inlineStr">
+      <c r="H685" s="3" t="inlineStr">
         <is>
           <t>סדר רב עמרם גאון, ישיבת סורא, רב נטרונאי גאון, תשובות הגאונים, נוסח התפילה, מאה ברכות, שערי צדק, קהילת ברצלונה, יהדות ספרד</t>
         </is>
       </c>
-      <c r="I685" t="inlineStr">
+      <c r="I685" s="3" t="inlineStr">
         <is>
           <t>רב עמרם בר ששנא, הידוע כרב עמרם גאון, עמד בראש ישיבת סורא שבבבל במחצית השנייה של המאה התשיעית. הוא היה תלמידו של רב נטרונאי גאון, וירש את ראשות הישיבה רק לאחר מותו. ערך את ״סדר רב עמרם גאון״, סידור שהיה ראשון מסוגו, כתשובה לבקשת קהילה בספרד, ככל הנראה קהילת ברצלונה, שביקשה את סדר התפילות והברכות לכל השנה. הוא חיבר תשובות הלכתיות רבות, ורבות מהן נדפסו בשאלוניקי בקובץ ״שערי צדק״.</t>
         </is>
       </c>
-      <c r="J685" t="inlineStr">
+      <c r="J685" s="3" t="inlineStr">
         <is>
           <t>סדר רב עמרם גאון מכיל לא רק את נוסחי התפילות עצמן אלא גם הלכות ומנהגים הקשורים בהן, ומקורם של קטעי ההלכה בתלמוד ובפסקי גאונים. הוא ערוך בסדר קבוע של ימי חול, שבתות ומועדים, סדר המהווה מודל למבנה של מרבית הסידורים עד ימינו, והוא השפיע השפעה רבה על נוסח התפילה בקהילות רבות בישראל. הנוסח שבידינו כנראה אינו זה שיצא מתחת ידו: כתבי היד שונים זה מזה במידה ניכרת, וההשערה המקובלת במחקר היא שאחרי ששלח את הסידור לספרד המשיכו לערוך אותו ולהוסיף עליו.</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr">
+      <c r="K685" s="3" t="inlineStr">
         <is>
           <t>הרמב"ם, רבי יצחק אלפסי (הרי"ף), רב סעדיה גאון, רבי דוד אבודרהם, יעקב בן אשר, רבי יוסף קארו</t>
         </is>
       </c>
-      <c r="L685" t="inlineStr">
+      <c r="L685" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/2ULZn2cKuetkTGLFWYrUx8</t>
         </is>
       </c>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr">
+      <c r="A686" s="3" t="inlineStr">
         <is>
           <t>685</t>
         </is>
       </c>
-      <c r="B686" t="inlineStr">
-        <is>
-          <t>דמות</t>
-        </is>
-      </c>
-      <c r="C686" t="inlineStr">
+      <c r="B686" s="3" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C686" s="3" t="inlineStr">
         <is>
           <t>רב יהודאי גאון</t>
         </is>
       </c>
-      <c r="D686" t="inlineStr">
+      <c r="D686" s="3" t="inlineStr">
         <is>
           <t>757–761 (ראש ישיבת סורא)</t>
         </is>
       </c>
-      <c r="E686" t="inlineStr">
+      <c r="E686" s="3" t="inlineStr">
         <is>
           <t>סורא; פומבדיתא</t>
         </is>
       </c>
-      <c r="F686" t="inlineStr">
+      <c r="F686" s="3" t="inlineStr">
         <is>
           <t>גאונים</t>
         </is>
       </c>
-      <c r="G686" t="inlineStr">
+      <c r="G686" s="3" t="inlineStr">
         <is>
           <t>הלכה, קודיפיקציה, הנהגת ישיבה</t>
         </is>
       </c>
-      <c r="H686" t="inlineStr">
+      <c r="H686" s="3" t="inlineStr">
         <is>
           <t>הלכות פסוקות, הלכות ראו, הלכות גדולות, ישיבת סורא, ישיבת פומבדיתא, רב דודאי גאון, פירקוי בן באבוי, מנהג שמד, תלמוד בבלי, תשובות הגאונים</t>
         </is>
       </c>
-      <c r="I686" t="inlineStr">
+      <c r="I686" s="3" t="inlineStr">
         <is>
           <t>ראש ישיבת סורא בשנים 757–761 ואחד מחשובי הגאונים, שהיה סגי נהור (עיוור). היה מחכמי ישיבת פומבדיתא, ולפי אגרת רב שרירא גאון העביר אותו ראש הגולה שלמה בן חסדאי לסורא מפני שלא נמצא בה מופלג בחכמה כמותו. הגאון הראשון שהחל בחיבור קובצי הלכה לאחר חתימת התלמוד הבבלי; על פי חלק מן החוקרים כתב את הספר ״הלכות פסוקות״.</t>
         </is>
       </c>
-      <c r="J686" t="inlineStr">
+      <c r="J686" s="3" t="inlineStr">
         <is>
           <t>ספר ״הלכות פסוקות״, המיוחס לו, הוא הניסיון הקודיפיקטיבי הראשון לאחר חתימת התלמוד הבבלי: הוא עוקב במידה רבה אחר הסדר התלמודי, אך במקום השקלא וטריא התלמודית מציע ניסוח תמציתי של שורה תחתונה ופסוקה. הוא לחם בחריפות למען השלטת התלמוד הבבלי כסמכות הלכתית יחידה בעם ישראל, ונתקל בהתנגדות קשה של בני ארץ ישראל, שהסתמכו על פסיקת התלמוד הירושלמי ומנהגיהם הקדומים. הוא קבע כי רבים ממנהגיהם הם ״מנהגי שמד״, שהתקבלו בזמנים קשים בהם לא הועברה המסורת בשלמותה.</t>
         </is>
       </c>
-      <c r="L686" t="inlineStr">
+      <c r="L686" s="3" t="inlineStr">
         <is>
           <t>https://open.spotify.com/episode/187HitcBGTOzR3Lgzja106</t>
         </is>
       </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>רבי שמשון בן אברהם משאנץ (הר״ש)</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>כ־1150–כ־1230</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>סנס; עכו; ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>בעלי התוספות</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>תלמוד, תוספות ופירוש המשנה</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>תוספות שאנץ, פירוש הר״ש למשנה, עליית בעלי התוספות, ישיבת שאנץ, רבנו תם, ר״י הזקן, סדר זרעים, סדר טהרות, התלמוד הירושלמי</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>רבי שמשון בן אברהם משאנץ (הר״ש) היה מחשובי בעלי התוספות בצרפת; את מקום מושבו קבע בעיר סנס (שאנץ) שבחבל בורגון. הוא נחשב ליורשו הרוחני ולתלמידו המובהק של ר״י הזקן, ובצעירותו הספיק לשמוע דברי תורה מפי רבנו תם. הוא חיבר את תוספות שאנץ ופירוש למשנה לסדר זרעים ולסדר טהרות. באחרית ימיו עלה לארץ ישראל יחד עם קבוצה של 300 רבנים, בעלייה שכונתה לימים ״עליית בעלי התוספות״.</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>לפי ספריא, רבות מהתוספות שבדפוס הש״ס נלקחו מתוספות שאנץ שלו או מבוססות עליהן. בפירושו למשנה הרבה לצטט מן התוספתא ולפרש אותה, ובפירושו לזרעים גם מן התלמוד הירושלמי. לדברי המהרש״ל, בקיאותו בירושלמי הייתה מיוחדת, ״יותר מכל אשר שמענו״.</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>רבנו תם (ר׳ יעקב בן מאיר), ר״י הזקן מדמפייר, רבי יצחק מקורביל (הסמ"ק), הריצב״א, רבי אליעזר מטוך</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>רבי שמואל אבן תיבון</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>כ־1150–כ־1230</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>לוניל; מרסיי</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>פילוסופיה, תרגום, פרשנות המקרא, רפואה</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>מורה נבוכים, פירוש המילים הזרות, מאמר יקוו המים, פירוש קהלת, תרגום כתבי הרמב״ם, הפולמוס המיימוני, פרובנס, משפחת אבן תיבון</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>רבי שמואל בן יהודה אבן תיבון (כ־1150–כ־1230) היה פילוסוף, רופא ומתרגם יהודי בדרום צרפת, בנו של המתרגם יהודה בן שאול אבן תיבון. את ״מורה נבוכים״ של הרמב״ם תרגם מערבית לעברית, ולפי ויקיפדיה העברית עשה זאת עוד בחיי הרמב״ם, שעודד אותו לכך. לפי ויקיפדיה האנגלית התייעץ עם הרמב״ם כמה פעמים במכתבים על קטעים קשים, ולפי המאמר התרגום הושלם בשנת 1204. חיבר גם את ״פירוש המילים הזרות״ (1213), הלקסיקון הפילוסופי העברי הראשון, ואת ״מאמר יקוו המים״ על חכמת הטבע ופילוסופיה.</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>לפי המאמר, בתרגומו ל״מורה נבוכים״ ובלקסיקון ״פירוש המילים הזרות״ העניק אבן תיבון לעם היהודי את הכלים המושגיים והלשוניים לכתוב פילוסופיה בעברית, והוא שטבע את השם העברי ״מורה נבוכים״. לפי המאמר הוא היה גם הוגה מקורי: ב״מאמר יקוו המים״ עסק בחכמת הטבע ובפילוסופיה, בפירושו לקהלת בתורת הנפש ותורת השכל, ולפי ויקיפדיה העברית היה במובנים רבים גם הפרשן הראשון של ״מורה נבוכים״. לפי המאמר, תרגומו ופרשנותו הרדיקלית לכתבי הרמב״ם שימשו גורם ישיר להתלקחות הפולמוס המיימוני בשנות השלושים של המאה ה־13.</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>הרמב"ם</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>רבי שמואל יפה אשכנזי</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>1525–1595</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>בורסה; קושטא; אדריאנופול</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>פרשנות המדרש ואגדות הירושלמי, דרשנות ורבנות</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>יפה תואר, יפה מראה, יפה קול, יפה ענף, יפה עיניים, מדרש רבה, התלמוד הירושלמי, הקהילה האשכנזית בקושטא, דרשנות, ביקורת הטקסט</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>רבי שמואל יפה אשכנזי (1525–1595) היה מחכמי ישראל באימפריה העות׳מאנית במאה ה־16 ומחבר פירוש ״יפה תואר״ על מדרש רבה. הוא נולד בבורסה, ועל פי עדותו נסע לקושטא כדי ״ללמוד תורה ולישא אשה״ ושהה תקופה מסוימת באדריאנופול. לפי ויקיפדיה העברית היה תלמידם של רבי יצחק בן לב ורבי שלמה אלקבץ, ומ־1564 כיהן כרב הקהילה האשכנזית בקושטא והרבה לדרוש בבתי הכנסת בעיר. פירושיו למדרש רבה על החומשים נקראים ״יפה תואר״, ועל המגילות ״יפה קול״ ו״יפה ענף״, ופירושו לאגדות התלמוד הירושלמי, ״יפה מראה״, הוא החיבור היחיד שהודפס בחייו.</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>לפי המחקר באתר, הוא החדיר ללימוד המדרש והאגדה את דרכי העיון התלמודיות, ובשיטתו תופסים ביקורת הטקסט ובירור גרסאות מקום מרכזי. לפי המחקר באתר, שמות ספריו נגזרו כולם בלשון נופל על לשון סביב המילה ״יפה״, כנגד שם משפחתו. לפי ויקיפדיה העברית, בשל גודל החיבור והרצון להדפיסו עם פירושים נוספים נעשו קיצורים לביאורו, והפירוש המצוי כיום במדרש רבה בהוצאת וילנא נלקט על ידי מרדכי פלונגיאן.</t>
+        </is>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>רבי שלמה הלוי אלקבץ, רבי חיים בנבנשתי (בעל כנסת הגדולה)</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>רבי צבי הירש אשכנזי (החכם צבי)</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>1658–1718</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>אלטונה (גרמניה); אמסטרדם (הולנד); לבוב (גליציה); בודפשט (הונגריה); סלוניקי; סרייבו; לונדון</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>פסיקה, שו״ת והנהגה רבנית</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>שו״ת חכם צבי, מאבק בשבתאות, נחמיה חייא חיון, תרנגולת בלא לב, גולם למניין, הגהות על הט״ז, שיטת הלימוד הספרדית, אמסטרדם, אלטונה, היעב״ץ</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>רבי צבי הירש אשכנזי, המכונה החכם צבי על שם ספרו, היה רב ופוסק ומחשובי הרבנים בסוף המאה ה־17 ובתחילת המאה ה־18; הוא נולד בטרביטש שבמוראביה בשנת 1658 ונפטר בלבוב בשנת 1718. למד אצל אביו ואצל סבו הרב אפרים הכהן, ובסלוניקי למד במשך שנתיים אצל הרב אליהו קובו והכיר גם את שיטת הלימוד הספרדית. כיהן כרב קהילת סרייבו, לימים כרב קהילות אה״ו (אלטונה, המבורג ואנדסבק), אחר כך כרב הקהילה האשכנזית באמסטרדם, ולבסוף כרב לבוב. בשנת 1712 הדפיס באמסטרדם את ספרו שו״ת ״חכם צבי״.</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>לפי ספריא, התנגד לדרך הפלפול, ושאלותיו ותשובותיו נחשבות בעלות חשיבות גדולה בזכות בהירותן ומיקודן. בלימודו העיוני שילב את שיטת הלימוד הספרדית עם שיטת הלימוד האשכנזית. לפי המחקר המלא על החכם צבי באתר, בפולמוס על תרנגולת שלא נמצא לבה פסק שהיא כשרה, בנימוק ששום בעל חיים בעל מערכת דם אינו יכול לחיות אפילו רגע אחד ללא לב.</t>
+        </is>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>הרב יעקב עמדין (יעב"ץ)</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>רבנו נסים בן יעקב מקירואן</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>כ־990–1062</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>קירואן; מהדיה</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>תקופת הגאונים המאוחרת/ראשית הראשונים</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>פירוש התלמוד, הלכה ואגדה</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>ספר מפתח מנעולי התלמוד, חיבור יפה מהישועה, מגילת סתרים, ישיבת קירואן, רב האי גאון, שמואל הנגיד, רבנו חננאל, התלמוד הירושלמי</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>רבנו נסים בן יעקב אבן שהין, הידוע כרב ניסים גאון, נולד בקירואן בסביבות שנת 990 ועמד בראש ישיבת קירואן; התואר ״גאון״ ניתן לו כתואר כבוד. הכשרתו התורנית התעצבה בראש ובראשונה בבית מדרשו של אביו, רבי יעקב בן נסים, ואחר כך למד אצל רבי חושיאל בן אלחנן; לאחר פטירת רבי חושיאל מילא את מקומו בראשות הישיבה, בשיתוף פעולה הדוק עם חברו רבנו חננאל בן חושיאל. הוא עמד בקשר מכתבים עם רב האי גאון ועם רבי שמואל הנגיד, ובשנת 1049 נישאה בתו היחידה ליוסף, בנו של שמואל הנגיד. לאחר שעזב את קירואן נפטר בעיר מהדיה בסביבות שנת 1062.</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>חיבורו המפורסם ביותר בתחום לימוד התלמוד, ״ספר מפתח מנעולי התלמוד״, נועד לפענח סוגיות בתלמוד הבבלי המובאות בקיצור או ברמיזה, בהפניית הלומד למקבילות מפורטות במקומות אחרים בספרות התלמודית, והוא מסתמך במיוחד על התלמוד הירושלמי. ב״חיבור יפה מהישועה״, שנכתב בערבית-יהודית, כתב ספר נחמה לחותנו דונש, המבוסס על אגדות חז״ל, מקורות גאוניים וסיפורי עם. הוא נחשב לאחד מגשרי המעבר המרכזיים מתקופת הגאונים לתקופת הראשונים.</t>
+        </is>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>רב האי גאון, רבנו חננאל בן חושיאל, שמואל הנגיד, רבי יצחק אלפסי (הרי"ף), הרמב"ם, רבי נתן מרומי, רבנו אברהם בר נתן הירחי (בעל ספר המנהיג), רבי יצחק בן אבא מרי (בעל העיטור)</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>רבי מאיר בן יעקב שיף (מהר״ם שיף)</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>כ־1605–1641</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>פרנקפורט; פולדא; פראג</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>פרשנות התלמוד וחידושי הלכות</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>חידושי הלכות מהר״ם שיף, דרושים נחמדים, דרוש הדרן, ישיבת פולדא, פרנקפורט דמיין, שריפת פרנקפורט, ביאור רבי מרדכי מארדוש, דפוס האלמנה והאחים ראם, קהילת פראג</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>רבי מאיר בן יעקב הכהן שיף (מהר״ם שיף) נולד בפרנקפורט דמיין לרבי יעקב הכהן שיף ולגוטל, ונפטר בשנת 1641. בשנת 1622 התמנה לרב ולראש ישיבה בפולדא, ומאות תלמידים למדו בישיבתו. לפני מותו נתמנה לרבה של פראג, אך נפטר בפתאומיות בגיל צעיר. חיבורו הידוע ביותר, ״חידושי הלכות מהר״ם שיף״, מודפס בסוף חלק ממסכתות התלמוד הבבלי; רוב כתביו נשרפו או אבדו.</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>חידושיו הם תמצית משיעוריו על התלמוד לתלמידי הישיבה, ושרידיהם נדפסו על חלק מ־11 מסכתות בתלמוד הבבלי. לפי ויקיפדיה העברית הוא מרבה להעמיד את שיטת רש״י ולהסביר מדוע רש״י לא סבר כתוספות ומדוע תוספות לא סבר כרש״י, ומתמקד פחות בהצלבת מקורות ויותר בהבנה מקומית מעמיקה. בעקבות סגנונו הקשה, דבריו הקצרים ושיטת הלימוד המסובכת יצא עליו ביאור מאת הרב מרדכי מארדוש מפוריצק, שנדפס יחד עם החידושים בכל ההוצאות.</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>692</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>רבי מאיר אייזנשטט (בעל פנים מאירות)</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>כ־1670–1744</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>פוזנא; שידלובצא; וורמייזא; פרוסניץ; אייזנשטט</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, חידושי ש״ס, דרשנות ופרשנות המקרא</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>פנים מאירות, מהר״ם א״ש, שבע קהילות, ישיבת אייזנשטט, אור הגנוז, כתנות אור, מאורי אש, תקנת איסור משחקי קלפים, ישיבת ורמיזא</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>רבי מאיר אייזנשטט (מהר״ם א״ש) נולד בפוזנא שבפולין בסביבות שנת ה׳ת״ל (1670), והיה נכד אחותו של רבי שבתאי הכהן (הש״ך). בשנת ה׳תע״ז (1717) התמנה לרבה של קהילת אייזנשטט ו״שבע קהילות״, והקים שם ישיבה גדולה שתלמידיה באו מקרוב ומרחוק. בפרוסניץ שבמוראביה גידל את רבי יהונתן אייבשיץ אחרי שהתייתם מהוריו, והיה לו לאב ולמורה. נפטר בכ״ז בסיוון ה׳תק״ד (1744) ונקבר בבית העלמין הישן באייזנשטט.</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>חיבורו המרכזי הוא שו״ת ״פנים מאירות״, המורכב לפי המחקר באתר מארבעה חלקים, ושני האחרונים בהם הוקדשו לחידושים על סוגיות הגמרא. חיבר גם את ״כתנות אור״, פירוש לתורה ולחמש המגילות, שיצא עם פירושי נכדו רבי אלעזר קאליר בשם ״מאורי אש״, ואת ״אור הגנוז״, חידושים על מסכת כתובות ועל הלכות יין נסך. בקהילת אייזנשטט תיקן תקנה האוסרת על משחקי קלפים, מלבד בחנוכה, בפורים ובבית היולדת.</t>
+        </is>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>רבי שבתאי הכהן (הש"ך), רבי אברהם אבלי גומבינר (המגן אברהם), רבי דוד אופנהיים, רבי יהונתן אייבשיץ</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>693</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>רבי ידידיה שלמה רפאל נורצי</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>כ־1560–לאחר 1626</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>מנטובה; איטליה</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>נוסח המקרא, מסורה ודקדוק</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>מנחת שי, גודר פרץ, נוסח המקרא, מסורה, מאמר המאריך, מנטובה, יהדות איטליה, מנחם די לונזאנו, מסורת סייג לתורה</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>רבי ידידיה שלמה רפאל בן אברהם נורצי היה רב, פרשן ומדקדק ממנטובה שבאיטליה, והתפרסם בחיבורו ״מנחת שי״ על מסורת המקרא ונוסחו. הוא למד אצל רבי משה קאציס (לפי המחקר באתר, רבו המובהק), ובשנת 1585 הוסמך לרבנות. לקראת תחילת המאה ה־17 נבחר לכהן כרב בקהילת מנטובה. את חיבורו על נוסח המקרא סיים ב־1626 וקרא לו ״גודר פרץ״, והחיבור נדפס לראשונה במנטובה בשנים 1742–1744 בשם ״מנחת שי״.</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>לפי המחקר באתר, בשיטתו הכרעה בכתיב, בניקוד ובטעמים נעשית לפי בעלי המסורה, ובמחלוקת בין מדקדק לבעל מסורה הוא פוסק כבעל המסורה. לפי אותו מחקר, קבע כלל שלא לשנות את נוסח ספרי התורה והמקרא על פי דרשות התלמוד והמדרש. לפי המחקר, ״מנחת שי״ התקבל בכל תפוצות ישראל כסמכות העליונה והסופית בקביעת נוסח המקרא.</t>
+        </is>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>רבי מנחם די לונזאנו, רבי מאיר הלוי אבולעפיה</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr"/>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>רבי דוד אופנהיים</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>1664–1736</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>וורמייזא; ניקלשבורג; פראג</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>הלכה ושו״ת, אספנות ספרים</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>נשאל דוד, ספריית אופנהיים, אספנות ספרים, כתבי יד, יהדות החצר, הספרייה הבודליאנית, נשיא ישראל, ניקלשבורג, פראג, וורמייזא</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>רבי דוד אופנהיים (1664–1736) נולד בוורמס והיה פוסק ומרא דאתרא של הקהילות היהודיות בניקלשבורג ובפראג. הוא למד אצל רבי גרשון אשכנזי במץ ואצל רבי יצחק בנימין וולף מלנדסברג, ולפי ויקיפדיה העברית בגיל 25 מונה לרבה של ניקלשבורג. ספרייתו, שהכילה אלפי ספרים ומאות כתבי יד עבריים, נרכשה ב־1829 על ידי הספרייה הבודליאנית באוקספורד, ושם היא נמצאת עד היום. הוא חיבר כעשרים ספרים בהלכה ובאגדה, ומהם הדפיס בחייו את שו״ת ״נשאל דוד״.</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>לפי המחקר המלא באתר, עושרו וקשריו עם חצר הקיסר שימשו אותו לביצור עולם התורה, לחיזוק הקהילות ולהגנה על היישוב היהודי בארץ ישראל. לפי אותו מחקר, ספרייתו הייתה כלי להנהגה, למחקר ולפסיקה הלכתית ולא רק אוסף של אספן עשיר.</t>
+        </is>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>רבי יעקב ריישר (בעל שבות יעקב), רבי יאיר חיים בכרך (בעל חוות יאיר), רבי מאיר אייזנשטט (בעל פנים מאירות)</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr"/>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>רבנו אברהם בר נתן הירחי (בעל ספר המנהיג)</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>כ־1155–1215</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>לוניל; טולדו</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>ראשונים</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>הלכה ומנהג</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>ספר המנהיג, מנהיג עולם, מנהגי ישראל, הירחי, ראב״ן הירחי, לוניל, פרובנס, טולדו, כלה רבתי</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>רבנו אברהם בר נתן הירחי (כ־1155–1215) היה מחכמי פרובנס ומחבר ״ספר המנהיג״, ושמו ״הירחי״ נגזר משם העיר לוניל. לפי המחקר באתר, למד בלוניל מפי חכמי העיר ובפוסיקייר אצל הראב״ד, ובדמפייר שבצפון צרפת בישיבתו של רבי יצחק בן שמואל (ר״י הזקן). לפי המחקר, עבר בקהילות צרפת ואשכנז וביקר באנגליה ובספרד, ובטולידו שבקשטיליה מונה לחבר בית הדין הגדול לצד הרמ״ה. את ״ספר המנהיג״, שנקרא במקורו ״מנהיג עולם״ ועוסק במנהגי בית הכנסת, התפילה, השבת והמועדים, החל לכתוב בטולידו בשנת 1204.</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>לפי המחקר באתר, תזת היסוד שלו היא שלכל מנהג רווח בקהילות ישראל יש יסוד ושורש במקורות התלמוד, המדרש או תשובות הגאונים, ולכן אין לבטלו מתוך אבחנה שטחית. לפי אותו מחקר, כשנתקל במנהג עממי שנראה מנוגד להלכה הפסוקה, לא מיהר לבטלו אלא תירץ אותו בחשיפת מקור תלמודי, בניתוח גרסאות אחרות או בדרש. לפי המחקר, הציג בספרו תיעוד השוואתי של מנהגי הקהילות השונות שבהן סייר.</t>
+        </is>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>ר״י הזקן מדמפייר, הראב"ד מפושקייר, רבי יצחק בן אבא מרי (בעל העיטור), רבי מאיר הלוי אבולעפיה, רבנו יהודה בן ברזילי הברצלוני, רבי דוד אבודרהם, יעקב בן אשר, רבי יוסף קארו, רבנו נסים בן יעקב מקירואן</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>רבי אברהם זכות</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>1452–כ־1515</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>סלמנקה; ליסבון; טוניס; ירושלים</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>ימי הביניים המאוחרים</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>אסטרונומיה והיסטוריוגרפיה</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>ספר יוחסין, החיבור הגדול, האלמנך הנצחי, אסטרולאב המתכת הימי, טבלאות נטיית השמש, גירוש ספרד, עידן התגליות, ואסקו דה גאמה, כריסטופר קולומבוס, יהדות ספרד</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>רבי אברהם בן שמואל זכות (1452–1515 בקירוב), אסטרונום והיסטוריון יהודי, נולד בעיר סלמנקה שבממלכת קסטיליה. רבו המובהק היה רבי יצחק אבוהב (״גאון קסטיליה האחרון״ בלשון המחקר), ובנוסף ללימודי הקודש למד אסטרונומיה באוניברסיטת סלמנקה. לאחר גירוש ספרד ב־1492 מינה אותו מלך פורטוגל, ז׳ואאו השני, לאסטרונום והיסטוריוגרף מלכותי; בגזירות ההמרה בשלהי 1496 סירב להמיר את דתו, ברח לטוניס וחיבר שם את ״ספר יוחסין״. על פי מקורות שונים, כך כותב המחקר, נפטר בירושלים או בדמשק בסביבות 1515.</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>לפי המחקר הושתתה משנתו על תפיסה הרואה במדע חוליה משלימה להבנת התורה וההלכה, ועל עיסוקו באסטרונומיה העיד כי כוונתו הייתה ״להבין דברי חז״ל וההלכות שכתבו בזה״. ״החיבור הגדול״ הושלם ב־1478 וכלל 65 טבלאות של מיקומי השמש, הירח וחמישה כוכבי לכת; תלמידו יוסף ויסינו תרגם אותו ללטינית, ותרגומו הודפס בלייריה שבפורטוגל ב־1496. לפי ויקיפדיה האנגלית, ה״אלמנך״ שלו סיפק את טבלת נטיית השמש המדויקת הראשונה, ויחד עם אסטרולאב המתכת הימי אפשר לנווטים לבצע מדידות מדויקות בכל מקום; לפי אותו מקור השתמש בהם ואסקו דה גאמה ב־1497 במסעו הראשון להודו.</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>רבי אהרן ברכיה ממודינה (בעל מעבר יבוק)</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>כ־1549–1639</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>מודינה; איטליה</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>אחרונים</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>קבלה, ליטורגיה והלכה</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>מעבר יבוק, אשמורת הבוקר, מעירי השחר, חברה קדישא, אבלות וטהרה, קבלת הרמ״ק, קבלת האר״י, הרמ״ע מפאנו, רבי ישראל סרוג, כנף רננים</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>רבי אהרן ברכיה בן משה ממודינה היה רב ומקובל בן יהדות איטליה, יליד העיר מודנה. הוא למד אצל רבי הלל החסיד ממודנה ואצל רבי מנחם עזריה מפאנו, ונסמך להוראה אצל רבי יום טוב צהלון. ספרו הראשון, ״אשמורת הבוקר״ (1624), נכתב עבור חבורת ״מעירי השחר״ במודנה; ספרו ״מעבר יבוק״, שבו נודע בעיקר, נדפס במנטובה ב־1626. הוא נפטר במודינה בכ״ו בתמוז, בשנת 1639.</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>לפי המחקר באתר, ספרו ״מעבר יבוק״ הגדיר מחדש את יחסה של החברה היהודית לחולי, לגסיסה, למוות ולאבלות, והיה לספר היסוד של חברות הקדישא; לפי ויקיפדיה האנגלית נכתב לבקשת חברת הקדישא של מנטובה. לפי המחקר באתר, ניכרת בהגותו סינתזה בין קבלת הרמ״ק לקבלת האר״י.</t>
+        </is>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>הרמ״ע מפאנו, רבי ישראל סרוג, רבי משה קורדובירו (הרמ״ק), האר״י הקדוש, רבי יצחק עראמה (בעל העקידה), הבן איש חי (רבי יוסף חיים מבגדד)</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>דמות</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>רב (אבא אריכא)</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>כ־175–247</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>סורא; בבל; ארץ ישראל</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>אמוראים</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>הלכה, ליטורגיה ואגדה, ייסוד ישיבת סורא</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>ישיבת סורא, אמוראי בבל, רב ושמואל, הלכה כרב באיסורי, רב תנא הוא ופליג, ירחי כלה, תקיעתא דבי רב, עלינו לשבח, רבי יהודה הנשיא</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>אבא בר אייבו, הידוע בשם רב ובכינוי ״אבא אריכא״, היה מראשוני אמוראי בבל ומייסד ישיבת סורא. נולד בעיר כפרית בבבל, ובצעירותו עלה עם דודו רבי חייא לארץ ישראל ונכנס לבית מדרשו של רבי יהודה הנשיא. בשנת 219 בקירוב חזר לבבל והקים את ישיבת סורא, שפעלה, לפי המחקר באתר, כמעט שמונה מאות שנה. לפי המחקר באתר, בין תלמידיו הבולטים היו רב הונא ורב חסדא.</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>לפי המחקר באתר, פועלו סימן את העברת מרכז הכובד הרוחני וההלכתי מארץ ישראל לבבל והציב תשתית להתפתחות התלמוד הבבלי. הכלל התלמודי ״רב תנא הוא ופליג״ נותן לו סמכות לחלוק על תנאים, ובמחלוקותיו עם שמואל נקבע הכלל ״הלכה כרב באיסורי וכשמואל בממוני״. לפי המחקר באתר, הוא נחשב למעצב המרכזי של תפילת מוסף של ראש השנה (״תקיעתא דבי רב״) וייסד את מוסד ״ירחי כלה״ בחודשים אלול ואדר.</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>רבי יהודה הנשיא, רב הונא, רב חסדא, רב יהודה בר יחזקאל, רבי חייא הגדול, שמואל (האמורא)</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
